--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PRABHA</t>
+          <t>Prabha Energy Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -602,19 +602,15 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>N K Industries Ltd leads gainers in 'B' group - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
-        </is>
-      </c>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -627,7 +623,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>Subex Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -656,22 +652,26 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
+          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
+          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Subex seeks shareholder nod for new ESOP scheme, trust loan - scanx.trade</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>Aarnav Fashions Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -711,16 +711,8 @@
       <c r="L4" s="2" t="n">
         <v>13.26</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -728,7 +720,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -741,7 +733,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>Yasho Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -768,28 +760,16 @@
       <c r="L5" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -797,60 +777,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER.NS</t>
+          <t>ICIL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>Indo Count Industries Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1782.5</v>
+        <v>388.7000122070312</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2000</v>
+        <v>462</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1782.5</v>
+        <v>387.0499877929688</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1983.599975585938</v>
+        <v>437.7000122070312</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1781.400024414062</v>
+        <v>388.7000122070312</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1983.599975585938</v>
+        <v>437.7000122070312</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>190615</v>
+        <v>25217469</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>11.35</v>
+        <v>12.61</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+          <t>Indo Count Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+          <t>Indo Count Industries Q1 Results: Audio of investor call uploaded - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Indo Count Industries Q1 Results: Audio of investor call uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Indo Count Industries appoints Pankaj Saxena as President-Retail - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Indo Count reports record Q1FY27 revenue of ₹1,224 crore - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -858,51 +846,51 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB.NS</t>
+          <t>SIGACHI.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>Sigachi Industries Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>317.9500122070312</v>
+        <v>25.90999984741211</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>351.2999877929688</v>
+        <v>30.09000015258789</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>316.8999938964844</v>
+        <v>25.90999984741211</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>313.0199890136719</v>
+        <v>26.35000038146973</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5070304</v>
+        <v>10330178</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10.81</v>
+        <v>12.37</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+          <t>Sigachi Industries Q1 Results: Net profit turns positive to ₹814 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+          <t>Sigachi Industries Q1 Results: Net profit turns positive to ₹814 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
+          <t>Sigachi Industries Q1 Results: Net profit rebounds to ₹8.14 crore - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
@@ -911,7 +899,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -919,64 +907,56 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>REGAAL.NS</t>
+          <t>MACPOWER.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>REGAAL</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>90.27999877929688</v>
+        <v>1782.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>101.5</v>
+        <v>2000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>88.65000152587891</v>
+        <v>1782.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>99.52999877929688</v>
+        <v>1983.599975585938</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>90.45999908447266</v>
+        <v>1781.400024414062</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>99.52999877929688</v>
+        <v>1983.599975585938</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2972532</v>
+        <v>190615</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10.03</v>
+        <v>11.35</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+          <t>The National Stock Exchange has sought clarification on unusual price fluctuations in several stocks. - Traders Union</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
-        </is>
-      </c>
+          <t>The National Stock Exchange has sought clarification on unusual price fluctuations in several stocks. - Traders Union</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -984,68 +964,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PARAS.NS</t>
+          <t>JINDRILL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>Jindal Drilling &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1385</v>
+        <v>587.0999755859375</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>673.5499877929688</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1384.699951171875</v>
+        <v>587.0999755859375</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>651.1500244140625</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1388.5</v>
+        <v>586.2000122070312</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>651.1500244140625</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>5405026</v>
+        <v>17885600</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10</v>
+        <v>11.08</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+          <t>Jindal Drilling Q1 Results: New ONGC Rig Contract, Order Book At ₹1,310 Crore - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
+          <t>Jindal Drilling Q1 Results: New ONGC Rig Contract, Order Book At ₹1,310 Crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1053,56 +1021,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS.NS</t>
+          <t>INDSWFTLAB.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>Ind-Swift Laboratories Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1170</v>
+        <v>317.9500122070312</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1305.75</v>
+        <v>351.2999877929688</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1165</v>
+        <v>316.8999938964844</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1305.75</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1187.050048828125</v>
+        <v>313.0199890136719</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1305.75</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>9337471</v>
+        <v>5070304</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10</v>
+        <v>10.81</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>Ind-Swift Labs releases Q1FY27 earnings call audio recording - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>Ind-Swift Laboratories: जम्मू प्लांटमध्ये ₹45 कोटींची गुंतवणूक, जागतिक बाजारात प्रवेशाची तयारी! - Whalesbook</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+          <t>Ind-Swift Laboratories: పెట్టుబడుల సమీకరణలో బ్రేక్.. ₹58.99 కోట్ల షార్ట్‌ఫాల్.. ఆందోళనలో ఇన్వెస్టర్లు? - Whalesbook</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+          <t>Ind-Swift Laboratories: जम्मू प्लांटमध्ये ₹45 कोटींची गुंतवणूक, जागतिक बाजारात प्रवेशाची तयारी! - Whalesbook</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1110,7 +1078,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1118,56 +1086,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>BI.NS</t>
+          <t>ABINFRA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>A B INFRABUILD LIMITED</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>94</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>523283</v>
+        <v>25170195</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.99</v>
+        <v>10.65</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+          <t>A B Infrabuild Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>AB Infrabuild Q1FY27 net profit up 4.4% to ₹534.3M on revenue growth - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1175,68 +1151,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE.NS</t>
+          <t>REGAAL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>REGAAL RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>426.8999938964844</v>
+        <v>90.27999877929688</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>465.1000061035156</v>
+        <v>101.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>419.7999877929688</v>
+        <v>88.65000152587891</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>425.25</v>
+        <v>90.45999908447266</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3647695</v>
+        <v>2972532</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>10.03</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today: Price Rise Review - Univest</t>
+          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today: Fall and Valuation - Univest</t>
+          <t>Regaal Resources Q1 Results: Earnings Call Scheduled for August 17 - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
+          <t>Regaal Resources షేర్లలో జోరు: Q1 లాభం **47%** దూసుకుపోయింది! - Whalesbook</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1244,56 +1220,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SUNDARAM.NS</t>
+          <t>PARAS.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>SUNDARAM</t>
+          <t>Paras Defence and Space Technologies Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.159999966621399</v>
+        <v>1385</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.240000009536743</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1.149999976158142</v>
+        <v>1384.699951171875</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.129999995231628</v>
+        <v>1388.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1399675</v>
+        <v>5405026</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.85</v>
+        <v>10</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
+          <t>Paras Defence files FY26 BRSR report detailing ESG metrics - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Paras Defence Stock Hits 52-Week High at ₹1,527.65 - Whalesbook</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Paras Defence PAT up 45% to ₹89.46 crore in FY26; proposes ₹600 cr RPT limits - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Paras Defence to host analyst meet at Manufacturing Forum 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Paras Defence hosts analyst meet at Motilal Oswal conference - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1301,56 +1289,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TPHQ.NS</t>
+          <t>DHOOTTRANS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6100000143051147</v>
+        <v>1170</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>1305.75</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.5400000214576721</v>
+        <v>1165</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>1305.75</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.5799999833106995</v>
+        <v>1187.050048828125</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>1305.75</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>33421631</v>
+        <v>9337471</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1358,68 +1354,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>INDOMIM.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>INDO-MIM LIMITED</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>910</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>40.90000152587891</v>
+        <v>952.75</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>905</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>952.75</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>37.0099983215332</v>
+        <v>866.1500244140625</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>952.75</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3327170</v>
+        <v>10245867</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+          <t>INDO-MIM Q1 Consolidated Net Profit Rises to 2.4B Rupees, Revenue at 12.2B Rupees - Sahi</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+          <t>INDO-MIM Q1 Consolidated Net Profit Rises to 2.4B Rupees, Revenue at 12.2B Rupees - Sahi</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - Univest</t>
+          <t>Indo-MIM Q1 EBITDA up 23% to ₹4,000 million; net profit surges 32% - scanx.trade</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - Insider Gaming</t>
+          <t>Newly-listed Indo-MIM surges to upper circuit, Trading 96% above issue price - Zee Business</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1427,56 +1423,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA.NS</t>
+          <t>BI.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>Bilcare Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>517.7000122070312</v>
+        <v>94</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>565</v>
+        <v>101.379997253418</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>509</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>562.0499877929688</v>
+        <v>101.379997253418</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>518.75</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>562.0499877929688</v>
+        <v>101.379997253418</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>704938</v>
+        <v>523283</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8.35</v>
+        <v>9.99</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+          <t>Bilcare Limited Announces Winding Up of Bilcare INC, A Wholly Owned Subsidiary of the Company - marketscreener.com</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+          <t>Bilcare Q1FY26 Results: Net profit falls 16% YoY to ₹13.00 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>eMudhra Ltd. Share Price Today - eMudhra Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Bilcare Q1FY26 Results: Net profit falls 16% YoY to ₹13.00 crore - scanx.trade</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
+          <t>7 Stocks That Have Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -1484,7 +1480,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1492,68 +1488,48 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>NITINSPIN.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>Nitin Spinners Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>870</v>
+        <v>556.75</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>947.9000244140625</v>
+        <v>610</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>860.0499877929688</v>
+        <v>554.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>929.2000122070312</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>857.9500122070312</v>
+        <v>553.75</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>929.2000122070312</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>5438303</v>
+        <v>3703976</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - Univest</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - Univest</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Indian Export Stocks Retail Investors May Watch As US Scrutiny Of Transshipment Grows - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Jyoti CNC Wins MeitY Nod for ₹1,020 Crore Expansion at Rajkot Plant - TipRanks</t>
-        </is>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1561,60 +1537,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA.NS</t>
+          <t>ABCOTS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>A B COTSPIN INDIA LIMITED</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2755.800048828125</v>
+        <v>202.4799957275391</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2989</v>
+        <v>225</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2755.800048828125</v>
+        <v>201.8800048828125</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2959</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2741.39990234375</v>
+        <v>199.6600036621094</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2959</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4187661</v>
+        <v>152577</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.94</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>A B Cotspin India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>AB Cotspin India Q1 Results: Unaudited financials approved by board - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Tube Investments of India Receives Crisil ESG and Core ESG Ratings for FY 2026 - TipRanks</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>AB Cotspin India Q1 Results: Unaudited financials approved by board - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>A B Cotspin India Limited Announces Appointment of Nidhi Sharma as Company Secretary and Compliance Officer, Effective August 12, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>AB Cotspin Q1FY27 revenue up 53% to ₹101.98 crore; PAT rises 21% - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1622,46 +1606,46 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SOLARA.NS</t>
+          <t>ASIANENE.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SOLARA</t>
+          <t>Asian Energy Services Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>509.1000061035156</v>
+        <v>426.8999938964844</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>559.7999877929688</v>
+        <v>465.1000061035156</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>509.1000061035156</v>
+        <v>419.7999877929688</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>549.0499877929688</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>509.1000061035156</v>
+        <v>425.25</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>549.0499877929688</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>672938</v>
+        <v>3647695</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.85</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd is Rated Sell - MarketsMojo</t>
+          <t>Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd is Rated Sell - MarketsMojo</t>
+          <t>Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
@@ -1671,7 +1655,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1679,68 +1663,48 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MCLOUD.NS</t>
+          <t>SUNDARAM.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MCLOUD</t>
+          <t>Sundaram Multi Pap Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>26.97999954223633</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>29.10000038146973</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>26.84000015258789</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>28.85000038146973</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.77000045776367</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>28.85000038146973</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>9814518</v>
+        <v>1399675</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL Order; Shares Rise 4.74% - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL AI Surveillance Contract - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud Publishes Q1 FY27 Unaudited Results via Newspaper and Web - TipRanks</t>
-        </is>
-      </c>
+        <v>8.85</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1748,43 +1712,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>JGCHEM.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>JGCHEM</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>605</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>652.4000244140625</v>
+        <v>40.90000152587891</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>602.1500244140625</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>645.8499755859375</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>600.7999877929688</v>
+        <v>37.0099983215332</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>645.8499755859375</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>871395</v>
+        <v>3327170</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited Announces Change in Designation of Dr. Ellen Jane Feehan as Chief Executive Officer - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited Announces Change in Designation of Dr. Ellen Jane Feehan as Chief Executive Officer - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Q1 Consolidated Net Profit Rises to ₹12.1 Crore; Revenue Reaches ₹45.6 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures: संचालक मंडळात मोठे बदल! दोन दिग्गजांनी दिले राजीनामे - Whalesbook</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1803,14 +1787,14 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -1909,7 +1893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1922,7 +1906,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>HARDWYN</t>
+          <t>Hardwyn India Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -1951,34 +1935,26 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Hardwyn India Reports Q1 Net Profit of ₹2.8 Crore on ₹34.6 Crore Revenue - Sahi</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - Univest</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
           <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Hardwyn India Ltd is Rated Sell - MarketsMojo</t>
-        </is>
-      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1991,7 +1967,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>KRISHIVAL FOODS LIMITED</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -2030,20 +2006,24 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
+          <t>Krishival Foods utilizes ₹799.15 lakh of rights issue funds in Q4FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
+          <t>Krishival Foods Q1 Results: Net profit rises 27% YoY to ₹560.29 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
           <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2056,7 +2036,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NELCO</t>
+          <t>Nelco Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -2085,34 +2065,34 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Nelco Share Price Falls over 12%: Why the $20 Million Elveo Investment Has Investors Worried - India Infoline</t>
+          <t>Nelco completes $20 million CCD investment in Lunar Holdco for satellite D2D - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Tata's Nelco shares tumble 12% on Tuesday after ₹1,120 peak - NewsBytes</t>
+          <t>Nelco Shares Rise 5.5% on $20 Million Investment in US Firm Elveo - Whalesbook</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-18 — cnbctv:f2ab86df1094b:0 - TradingView</t>
+          <t>Nelco partners with Elveo for D2D satellite connectivity in South Asia - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Nelco invests $20 mn in US-based Elveo for satellite connectivity; shares fall 12% - Upstox</t>
+          <t>Nelco Shares Rise 5.5% on $20 Million Investment in US Firm Elveo - Whalesbook</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Tata Group stock: Nelco zooms 108% from March low; hits 52-week high - Business Standard</t>
+          <t>Nelco Share Price: அமெரிக்க நிறுவனத்தில் முதலீடு; **5.55%** ஏற்றத்துடன் வர்த்தகம்! - Whalesbook</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2120,48 +2100,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL.NS</t>
+          <t>AHLUCONT.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL</t>
+          <t>Ahluwalia Contracts (India) Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.5</v>
+        <v>776</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>14.94999980926514</v>
+        <v>782.4000244140625</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.90999984741211</v>
+        <v>702.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>13.9399995803833</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15.14000034332275</v>
+        <v>793.8499755859375</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.9399995803833</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>7220</v>
+        <v>545834</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+        <v>-10.85</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts Q1FY27 net profit falls 78% to ₹114 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts Q1FY27 net profit falls 78% to ₹114 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Ahluwalia Contracts posts Q1 FY27 miss as margins shrink - Investing.com</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts sets Sept 22 record date for final dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts Q1 Results: Net profit down 78% YoY to ₹114 lakh - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2169,64 +2169,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT.NS</t>
+          <t>PRAXIS.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT</t>
+          <t>Praxis Home Retail Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>293</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>297.1499938964844</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>276</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>301.1000061035156</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>360673</v>
+        <v>554400</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-7.41</v>
+        <v>-8.01</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+          <t>Praxis Home Retail revises promoter reclassification disclosure - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
+          <t>Praxis Home Retail revises promoter reclassification disclosure - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2234,40 +2226,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>SHYAMTEL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>Shyam Telecom Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>263</v>
+        <v>14.5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>266.3900146484375</v>
+        <v>14.94999980926514</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>240.5</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>244.25</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>262.8500061035156</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>244.25</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>54440</v>
+        <v>7220</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-7.08</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+        <v>-7.93</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Shyam Telecom Q1FY27 loss narrows to ₹199 lakh amid going concern doubts - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Shyam Telecom Q1FY27 loss narrows to ₹199 lakh amid going concern doubts - scanx.trade</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2283,60 +2283,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TARSONS.NS</t>
+          <t>THOMASCOTT.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>TARSONS</t>
+          <t>Thomas Scott (India) Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>365</v>
+        <v>297.1499938964844</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>336.6499938964844</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>361.5</v>
+        <v>301.1000061035156</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>336.6499938964844</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1199280</v>
+        <v>360673</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-6.87</v>
+        <v>-7.41</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+          <t>Thomas Scott India releases Q1 FY27 earnings call audio recording - scanx.trade</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2344,56 +2348,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER.NS</t>
+          <t>DCMSIL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER</t>
+          <t>DCM Shriram International Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>296</v>
+        <v>75.48999786376953</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>270</v>
+        <v>67.16000366210938</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>277.7000122070312</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>297.7000122070312</v>
+        <v>74.26000213623047</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>277.7000122070312</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>10586</v>
+        <v>208024</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-6.72</v>
+        <v>-7.16</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+          <t>DCM Shriram Fine Chemicals promoter acquires 3.52% stake via gift - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
+          <t>DCM Shriram Fine Chemicals promoter acquires 3.52% stake via gift - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>DCM Shriram Fine Chemicals posts Q1FY27 profit of ₹2.4 crore; appoints Rudra Shriram as MD - scanx.trade</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2401,37 +2409,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>JUBLCPL.NS</t>
+          <t>KANPRPLA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>JUBLCPL</t>
+          <t>Kanpur Plastipack Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2362.39990234375</v>
+        <v>263</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2397.89990234375</v>
+        <v>266.3900146484375</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2142</v>
+        <v>240.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2199.10009765625</v>
+        <v>244.25</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2342.39990234375</v>
+        <v>262.8500061035156</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2199.10009765625</v>
+        <v>244.25</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>16482</v>
+        <v>54440</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-6.12</v>
+        <v>-7.08</v>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -2442,7 +2450,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2450,40 +2458,48 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NDLVENTURE.NS</t>
+          <t>TARSONS.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>Tarsons Products Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>122.1500015258789</v>
+        <v>365</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>122.7399978637695</v>
+        <v>365</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>113.9499969482422</v>
+        <v>332</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>116.1699981689453</v>
+        <v>336.6499938964844</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>123.5599975585938</v>
+        <v>361.5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>116.1699981689453</v>
+        <v>336.6499938964844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>57175</v>
+        <v>1199280</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+        <v>-6.87</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -2491,7 +2507,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2499,68 +2515,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>APEX.NS</t>
+          <t>S&amp;SPOWER.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>APEX</t>
+          <t>S&amp;S Power Switchgear Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>424</v>
+        <v>296</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>427.7999877929688</v>
+        <v>296</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>395.3999938964844</v>
+        <v>270</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>398.5</v>
+        <v>277.7000122070312</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>422.5499877929688</v>
+        <v>297.7000122070312</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>398.5</v>
+        <v>277.7000122070312</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>944026</v>
+        <v>10586</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5.69</v>
+        <v>-6.72</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+          <t>S&amp;S Power revenue up 18% in Q1FY27; EBITDA falls 46% on delays - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - Univest</t>
-        </is>
-      </c>
+          <t>S&amp;S Power revenue up 18% in Q1FY27; EBITDA falls 46% on delays - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2568,37 +2572,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NEXTMEDIA.NS</t>
+          <t>LPDC.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>NEXTMEDIA</t>
+          <t>Landmark Property Development Company Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3.980000019073486</v>
+        <v>7.860000133514404</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3.980000019073486</v>
+        <v>7.860000133514404</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3.700000047683716</v>
+        <v>7.25</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3.710000038146973</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3.910000085830688</v>
+        <v>7.869999885559082</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.710000038146973</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>38951</v>
+        <v>96741</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5.12</v>
+        <v>-6.23</v>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
@@ -2609,7 +2613,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2617,46 +2621,46 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>KHAICHEM.NS</t>
+          <t>JUBLCPL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>KHAICHEM</t>
+          <t>Jubilant Agri and Consumer Products Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60.34000015258789</v>
+        <v>2362.39990234375</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>63.29999923706055</v>
+        <v>2397.89990234375</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>56.11000061035156</v>
+        <v>2142</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.72000122070312</v>
+        <v>2199.10009765625</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>59.75</v>
+        <v>2342.39990234375</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56.72000122070312</v>
+        <v>2199.10009765625</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1445339</v>
+        <v>16482</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.07</v>
+        <v>-6.12</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - Univest</t>
+          <t>Jubilant Agri &amp; Consumer Q1 Results: Net profit rises 7.5% YoY - scanx.trade</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - Univest</t>
+          <t>Jubilant Agri &amp; Consumer Q1 Results: Net profit rises 7.5% YoY - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -2666,7 +2670,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2674,48 +2678,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>NATIONSTD.NS</t>
+          <t>SIGIND.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>NATIONSTD</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>134</v>
+        <v>70.84999847412109</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>148.1000061035156</v>
+        <v>71.5</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>134</v>
+        <v>65.31999969482422</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>134</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>141.0500030517578</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>134</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>335324</v>
+        <v>95414</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+        <v>-6.04</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Signet Industries promoter Mukesh Sangla buys 13,904 shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Signet Industries promoter Mukesh Sangla buys 13,904 shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Signet Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Signet Industries Q1 Results: Net profit rises 10.7% QoQ to ₹8.05 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Signet Industries షేర్ ధర: ఇన్వెస్టర్లకు పండగే! తొలిసారిగా భారీ లాభాలు.. 1066% జంప్ - Whalesbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2723,37 +2747,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RAMCOSYS.NS</t>
+          <t>NDLVENTURE.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>NDL Ventures Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>593.0999755859375</v>
+        <v>122.1500015258789</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>598</v>
+        <v>122.7399978637695</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>564.5</v>
+        <v>113.9499969482422</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>564.5</v>
+        <v>116.1699981689453</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>594.2000122070312</v>
+        <v>123.5599975585938</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>564.5</v>
+        <v>116.1699981689453</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>245328</v>
+        <v>57175</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5</v>
+        <v>-5.98</v>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
@@ -2764,7 +2788,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2772,37 +2796,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>MOIL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>MOIL Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>271.2000122070312</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>271.7999877929688</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>255.6000061035156</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>257.25</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>73.23000335693359</v>
+        <v>272.7999877929688</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>257.25</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>20955</v>
+        <v>2810988</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5</v>
+        <v>-5.7</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -2813,7 +2837,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2821,48 +2845,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS.NS</t>
+          <t>APEX.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>Apex Frozen Foods Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>13.44999980926514</v>
+        <v>424</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>13.5600004196167</v>
+        <v>427.7999877929688</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12.88000011444092</v>
+        <v>395.3999938964844</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>12.92000007629395</v>
+        <v>398.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>13.59000015258789</v>
+        <v>422.5499877929688</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12.92000007629395</v>
+        <v>398.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>400753</v>
+        <v>944026</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.93</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+        <v>-5.69</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Volume Gainers, August 14, 2026, 4:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods reports burgeoning profits with YoY surge in Q1 FY27 - Business Upturn</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>7 Stocks That Have Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods Hits 20% Upper Circuit on 138% Profit Jump - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods reports burgeoning profits with YoY surge in Q1 FY27 - Business Upturn</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2870,60 +2914,56 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGOLD.NS</t>
+          <t>AGL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGOLD</t>
+          <t>ALLCARGO GLOBAL LIMITED</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>269</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>269.9700012207031</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>251.2100067138672</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>253.8500061035156</v>
+        <v>13.25</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>266.8399963378906</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>253.8500061035156</v>
+        <v>13.25</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2594125</v>
+        <v>3444947</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.87</v>
+        <v>-5.42</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Ltd. Share Price Today Up 8.24% - Univest</t>
+          <t>Allcargo Global makes Q1FY27 earnings call audio recording available - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Ltd. Share Price Today Up 8.24% - Univest</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Shanti Gold International Ltd. Share Price Today Up 8.83% - Univest</t>
-        </is>
-      </c>
+          <t>Allcargo Global makes Q1FY27 earnings call audio recording available - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2931,48 +2971,60 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.369999885559082</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.369999885559082</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2.369999885559082</v>
+        <v>31.42000007629395</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.369999885559082</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.490000009536743</v>
+        <v>35.84999847412109</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.369999885559082</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>668561</v>
+        <v>20786651</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.82</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+        <v>-5.36</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech board approves ₹16 crore rights issue for equity shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech board approves ₹16 crore rights issue for equity shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Q1FY27 net profit rises 52% to ₹1 crore as margins expand - scanx.trade</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2980,48 +3032,40 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>NDGL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>Naga Dhunseri Group Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.14000034332275</v>
+        <v>2875</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>14.27999973297119</v>
+        <v>2875</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>13.38000011444092</v>
+        <v>2669</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>13.42000007629395</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.07999992370605</v>
+        <v>2878.699951171875</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13.42000007629395</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4474052</v>
+        <v>558</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - Univest</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - Univest</t>
-        </is>
-      </c>
+        <v>-5.24</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Prabha Energy Limited</t>
+          <t>PRABHA</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -587,12 +587,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>PRABHA ENERGY Share Price Gain: Technicals and Valuation - Univest</t>
+          <t>PRABHA ENERGY Share Price Gain: Technicals and Valuation - univest.in</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -602,15 +602,19 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>N K Industries Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -623,7 +627,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Subex Limited</t>
+          <t>SUBEXLTD</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -652,26 +656,22 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - univest.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Subex seeks shareholder nod for new ESOP scheme, trust loan - scanx.trade</t>
-        </is>
-      </c>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Limited</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -711,8 +711,16 @@
       <c r="L4" s="2" t="n">
         <v>13.26</v>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - univest.in</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -720,7 +728,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -733,7 +741,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Limited</t>
+          <t>YASHO</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -760,16 +768,28 @@
       <c r="L5" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -777,68 +797,60 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ICIL.NS</t>
+          <t>INDSWFTLAB.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Indo Count Industries Limited</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>388.7000122070312</v>
+        <v>317.9500122070312</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>462</v>
+        <v>351.2999877929688</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>387.0499877929688</v>
+        <v>316.8999938964844</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>437.7000122070312</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>388.7000122070312</v>
+        <v>313.0199890136719</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>437.7000122070312</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>25217469</v>
+        <v>5070304</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>12.61</v>
+        <v>10.81</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Indo Count Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Indo Count Industries Q1 Results: Audio of investor call uploaded - scanx.trade</t>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Indo Count Industries Q1 Results: Audio of investor call uploaded - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Indo Count Industries appoints Pankaj Saxena as President-Retail - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Indo Count reports record Q1FY27 revenue of ₹1,224 crore - scanx.trade</t>
-        </is>
-      </c>
+          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -846,60 +858,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SIGACHI.NS</t>
+          <t>ABINFRA.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Limited</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>25.90999984741211</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>30.09000015258789</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.90999984741211</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>29.61000061035156</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.35000038146973</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29.61000061035156</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>10330178</v>
+        <v>25170195</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Sigachi Industries Q1 Results: Net profit turns positive to ₹814 lakh - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Sigachi Industries Q1 Results: Net profit turns positive to ₹814 lakh - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Sigachi Industries Q1 Results: Net profit rebounds to ₹8.14 crore - scanx.trade</t>
-        </is>
-      </c>
+        <v>10.65</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -907,56 +907,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER.NS</t>
+          <t>PARAS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Limited</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1782.5</v>
+        <v>1385</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2000</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1782.5</v>
+        <v>1384.699951171875</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1983.599975585938</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1781.400024414062</v>
+        <v>1388.5</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1983.599975585938</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>190615</v>
+        <v>5405026</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>11.35</v>
+        <v>10</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>The National Stock Exchange has sought clarification on unusual price fluctuations in several stocks. - Traders Union</t>
+          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>The National Stock Exchange has sought clarification on unusual price fluctuations in several stocks. - Traders Union</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Paras Defence Share Price at Fresh 52-Week High - univest.in</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -964,56 +976,64 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>JINDRILL.NS</t>
+          <t>DHOOTTRANS.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Jindal Drilling &amp; Industries Limited</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>587.0999755859375</v>
+        <v>1170</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>673.5499877929688</v>
+        <v>1305.75</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>587.0999755859375</v>
+        <v>1165</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>651.1500244140625</v>
+        <v>1305.75</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>586.2000122070312</v>
+        <v>1187.050048828125</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>651.1500244140625</v>
+        <v>1305.75</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>17885600</v>
+        <v>9337471</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>11.08</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Jindal Drilling Q1 Results: New ONGC Rig Contract, Order Book At ₹1,310 Crore - scanx.trade</t>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - univest.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Jindal Drilling Q1 Results: New ONGC Rig Contract, Order Book At ₹1,310 Crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1021,64 +1041,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB.NS</t>
+          <t>BI.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Limited</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>317.9500122070312</v>
+        <v>94</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>351.2999877929688</v>
+        <v>101.379997253418</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>316.8999938964844</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>101.379997253418</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>313.0199890136719</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>101.379997253418</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5070304</v>
+        <v>523283</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10.81</v>
+        <v>9.99</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Labs releases Q1FY27 earnings call audio recording - scanx.trade</t>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories: जम्मू प्लांटमध्ये ₹45 कोटींची गुंतवणूक, जागतिक बाजारात प्रवेशाची तयारी! - Whalesbook</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Ind-Swift Laboratories: పెట్టుబడుల సమీకరణలో బ్రేక్.. ₹58.99 కోట్ల షార్ట్‌ఫాల్.. ఆందోళనలో ఇన్వెస్టర్లు? - Whalesbook</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Ind-Swift Laboratories: जम्मू प्लांटमध्ये ₹45 कोटींची गुंतवणूक, जागतिक बाजारात प्रवेशाची तयारी! - Whalesbook</t>
-        </is>
-      </c>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1086,64 +1098,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA.NS</t>
+          <t>NITINSPIN.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>A B INFRABUILD LIMITED</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11.32999992370605</v>
+        <v>556.75</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12.98999977111816</v>
+        <v>610</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>10.97999954223633</v>
+        <v>554.5</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.35999965667725</v>
+        <v>553.75</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>25170195</v>
+        <v>3703976</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10.65</v>
+        <v>9.6</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>AB Infrabuild Q1FY27 net profit up 4.4% to ₹534.3M on revenue growth - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
-        </is>
-      </c>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1151,68 +1155,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>REGAAL.NS</t>
+          <t>ASIANENE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>90.27999877929688</v>
+        <v>426.8999938964844</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>101.5</v>
+        <v>465.1000061035156</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>88.65000152587891</v>
+        <v>419.7999877929688</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>99.52999877929688</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>90.45999908447266</v>
+        <v>425.25</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>99.52999877929688</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2972532</v>
+        <v>3647695</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.03</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+          <t>Asian Energy Services Share Price Today and Valuation View - univest.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+          <t>Asian Energy Services Share Price Today and Valuation View - univest.in</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
+          <t>Asian Energy Services Share Price Today: Price Rise Review - univest.in</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Regaal Resources Q1 Results: Earnings Call Scheduled for August 17 - scanx.trade</t>
+          <t>Asian Energy Services Share Price Today: Fall and Valuation - univest.in</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Regaal Resources షేర్లలో జోరు: Q1 లాభం **47%** దూసుకుపోయింది! - Whalesbook</t>
+          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1220,68 +1224,56 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PARAS.NS</t>
+          <t>SUNDARAM.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence and Space Technologies Limited</t>
+          <t>SUNDARAM</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1385</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1384.699951171875</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1388.5</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5405026</v>
+        <v>1399675</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10</v>
+        <v>8.85</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence files FY26 BRSR report detailing ESG metrics - scanx.trade</t>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - univest.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence Stock Hits 52-Week High at ₹1,527.65 - Whalesbook</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence PAT up 45% to ₹89.46 crore in FY26; proposes ₹600 cr RPT limits - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence to host analyst meet at Manufacturing Forum 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence hosts analyst meet at Motilal Oswal conference - scanx.trade</t>
-        </is>
-      </c>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1289,64 +1281,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1170</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1305.75</v>
+        <v>40.90000152587891</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1165</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1305.75</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1187.050048828125</v>
+        <v>37.0099983215332</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1305.75</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>9337471</v>
+        <v>3327170</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>10</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - univest.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - univest.in</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - Insider Gaming</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1354,68 +1350,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM.NS</t>
+          <t>TPHQ.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM LIMITED</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>910</v>
+        <v>0.6100000143051147</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>952.75</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>905</v>
+        <v>0.5400000214576721</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>952.75</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>866.1500244140625</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>952.75</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>10245867</v>
+        <v>33421631</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Q1 Consolidated Net Profit Rises to 2.4B Rupees, Revenue at 12.2B Rupees - Sahi</t>
+          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Q1 Consolidated Net Profit Rises to 2.4B Rupees, Revenue at 12.2B Rupees - Sahi</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Indo-MIM Q1 EBITDA up 23% to ₹4,000 million; net profit surges 32% - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Newly-listed Indo-MIM surges to upper circuit, Trading 96% above issue price - Zee Business</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
-        </is>
-      </c>
+          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1423,64 +1407,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BI.NS</t>
+          <t>KERNEX.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Bilcare Limited</t>
+          <t>KERNEX</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>94</v>
+        <v>1820</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>1920</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>1756.099975585938</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>1901.800048828125</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>1751.699951171875</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>1901.800048828125</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>523283</v>
+        <v>1425146</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.99</v>
+        <v>8.57</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Bilcare Limited Announces Winding Up of Bilcare INC, A Wholly Owned Subsidiary of the Company - marketscreener.com</t>
+          <t>Kernex Microsystems Q1FY27 net profit rises 13.7x to ₹10,984.57 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bilcare Q1FY26 Results: Net profit falls 16% YoY to ₹13.00 crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Bilcare Q1FY26 Results: Net profit falls 16% YoY to ₹13.00 crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7 Stocks That Have Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
-        </is>
-      </c>
+          <t>Kernex Microsystems Q1FY27 net profit rises 13.7x to ₹10,984.57 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1488,48 +1464,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>NITINSPIN.NS</t>
+          <t>EMUDHRA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Nitin Spinners Limited</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>556.75</v>
+        <v>517.7000122070312</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>554.5</v>
+        <v>509</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>606.9000244140625</v>
+        <v>562.0499877929688</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>553.75</v>
+        <v>518.75</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>606.9000244140625</v>
+        <v>562.0499877929688</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3703976</v>
+        <v>704938</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+        <v>8.35</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>eMudhra Ltd. Share Price Today - eMudhra Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1537,68 +1529,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ABCOTS.NS</t>
+          <t>JYOTICNC.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>A B COTSPIN INDIA LIMITED</t>
+          <t>JYOTICNC</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>202.4799957275391</v>
+        <v>870</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>225</v>
+        <v>947.9000244140625</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>201.8800048828125</v>
+        <v>860.0499877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>217.3999938964844</v>
+        <v>929.2000122070312</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>199.6600036621094</v>
+        <v>857.9500122070312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>217.3999938964844</v>
+        <v>929.2000122070312</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>152577</v>
+        <v>5438303</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>A B Cotspin India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - univest.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Q1 Results: Unaudited financials approved by board - scanx.trade</t>
+          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - univest.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Q1 Results: Unaudited financials approved by board - scanx.trade</t>
+          <t>Indian Export Stocks Retail Investors May Watch As US Scrutiny Of Transshipment Grows - simplywall.st</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>A B Cotspin India Limited Announces Appointment of Nidhi Sharma as Company Secretary and Compliance Officer, Effective August 12, 2026 - marketscreener.com</t>
+          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin Q1FY27 revenue up 53% to ₹101.98 crore; PAT rises 21% - scanx.trade</t>
+          <t>Jyoti CNC Wins MeitY Nod for ₹1,020 Crore Expansion at Rajkot Plant - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1606,56 +1598,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE.NS</t>
+          <t>MCLOUD.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Limited</t>
+          <t>MCLOUD</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>426.8999938964844</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>465.1000061035156</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>419.7999877929688</v>
+        <v>26.84000015258789</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>28.85000038146973</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>425.25</v>
+        <v>26.77000045776367</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>28.85000038146973</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3647695</v>
+        <v>9814518</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>7.77</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn</t>
+          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL Order; Shares Rise 4.74% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL AI Surveillance Contract - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud Publishes Q1 FY27 Unaudited Results via Newspaper and Web - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1663,48 +1667,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SUNDARAM.NS</t>
+          <t>MMP.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Multi Pap Limited</t>
+          <t>MMP</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.159999966621399</v>
+        <v>353.8500061035156</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.240000009536743</v>
+        <v>383</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.149999976158142</v>
+        <v>345</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>377.0499877929688</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1.129999995231628</v>
+        <v>350</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>377.0499877929688</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1399675</v>
+        <v>191009</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+        <v>7.73</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>MMP Industries Standalone June 2026 Net Sales at Rs 232.11 crore, up 26.66% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>MMP Industries Standalone June 2026 Net Sales at Rs 232.11 crore, up 26.66% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>MMP Industries Share Price: 52-Week High, Valuation View - univest.in</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>MMP Industries Share Price Target 2027 to 2030: Analyst Outlook - univest.in</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>What's Going On With Precious Metals And Mining Trust Stock Sunday? - Wealth Awesome</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1712,63 +1736,43 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>KPEL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Limited</t>
+          <t>KPEL</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>243.6999969482422</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>40.90000152587891</v>
+        <v>264.9500122070312</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>240</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>262.2999877929688</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>37.0099983215332</v>
+        <v>243.75</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>262.2999877929688</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3327170</v>
+        <v>859114</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>PVP Ventures Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>PVP Ventures Limited Announces Change in Designation of Dr. Ellen Jane Feehan as Chief Executive Officer - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>PVP Ventures Limited Announces Change in Designation of Dr. Ellen Jane Feehan as Chief Executive Officer - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>PVP Ventures Q1 Consolidated Net Profit Rises to ₹12.1 Crore; Revenue Reaches ₹45.6 Crore - Sahi</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>PVP Ventures: संचालक मंडळात मोठे बदल! दोन दिग्गजांनी दिले राजीनामे - Whalesbook</t>
-        </is>
-      </c>
+        <v>7.61</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1787,7 +1791,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1893,7 +1897,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1906,7 +1910,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn India Limited</t>
+          <t>HARDWYN</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -1935,26 +1939,30 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn India Reports Q1 Net Profit of ₹2.8 Crore on ₹34.6 Crore Revenue - Sahi</t>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - univest.in</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
           <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1967,7 +1975,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL FOODS LIMITED</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -2006,24 +2014,20 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Krishival Foods utilizes ₹799.15 lakh of rights issue funds in Q4FY26 - scanx.trade</t>
+          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Krishival Foods Q1 Results: Net profit rises 27% YoY to ₹560.29 lakh - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
           <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
         </is>
       </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2031,68 +2035,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NELCO.NS</t>
+          <t>PRAXIS.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Nelco Limited</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1092.300048828125</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1098</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>938.5999755859375</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>948.7999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1081.5</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>948.7999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2128333</v>
+        <v>554400</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-12.27</v>
+        <v>-8.01</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Nelco completes $20 million CCD investment in Lunar Holdco for satellite D2D - scanx.trade</t>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - univest.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Nelco Shares Rise 5.5% on $20 Million Investment in US Firm Elveo - Whalesbook</t>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - univest.in</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Nelco partners with Elveo for D2D satellite connectivity in South Asia - scanx.trade</t>
+          <t>Praxis Precision Medicines stock hits 52-week high at 388.27 USD - Investing.com India</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Nelco Shares Rise 5.5% on $20 Million Investment in US Firm Elveo - Whalesbook</t>
+          <t>9,840 Shares in Praxis Precision Medicines, Inc. $PRAX Purchased by Handelsbanken Fonder AB - MarketBeat</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Nelco Share Price: அமெரிக்க நிறுவனத்தில் முதலீடு; **5.55%** ஏற்றத்துடன் வர்த்தகம்! - Whalesbook</t>
+          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - stocktitan.net</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2100,68 +2104,48 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT.NS</t>
+          <t>SHYAMTEL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ahluwalia Contracts (India) Limited</t>
+          <t>SHYAMTEL</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>776</v>
+        <v>14.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>782.4000244140625</v>
+        <v>14.94999980926514</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>702.5</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>707.7000122070312</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>793.8499755859375</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>707.7000122070312</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>545834</v>
+        <v>7220</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-10.85</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Ahluwalia Contracts Q1FY27 net profit falls 78% to ₹114 crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Ahluwalia Contracts Q1FY27 net profit falls 78% to ₹114 crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Earnings call transcript: Ahluwalia Contracts posts Q1 FY27 miss as margins shrink - Investing.com</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Ahluwalia Contracts sets Sept 22 record date for final dividend - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Ahluwalia Contracts Q1 Results: Net profit down 78% YoY to ₹114 lakh - scanx.trade</t>
-        </is>
-      </c>
+        <v>-7.93</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2169,56 +2153,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PRAXIS.NS</t>
+          <t>THOMASCOTT.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Praxis Home Retail Limited</t>
+          <t>THOMASCOTT</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.039999961853027</v>
+        <v>293</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6.039999961853027</v>
+        <v>297.1499938964844</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.349999904632568</v>
+        <v>276</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5.400000095367432</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5.869999885559082</v>
+        <v>301.1000061035156</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.400000095367432</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>554400</v>
+        <v>360673</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-8.01</v>
+        <v>-7.41</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Praxis Home Retail revises promoter reclassification disclosure - scanx.trade</t>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Praxis Home Retail revises promoter reclassification disclosure - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2226,56 +2218,60 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL.NS</t>
+          <t>DCMSIL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Shyam Telecom Limited</t>
+          <t>DCMSIL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.5</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>14.94999980926514</v>
+        <v>75.48999786376953</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>13.90999984741211</v>
+        <v>67.16000366210938</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>13.9399995803833</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.14000034332275</v>
+        <v>74.26000213623047</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.9399995803833</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>7220</v>
+        <v>208024</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-7.93</v>
+        <v>-7.16</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Shyam Telecom Q1FY27 loss narrows to ₹199 lakh amid going concern doubts - scanx.trade</t>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Shyam Telecom Q1FY27 loss narrows to ₹199 lakh amid going concern doubts - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - univest.in</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - univest.in</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2283,64 +2279,48 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT.NS</t>
+          <t>KANPRPLA.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Limited</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>297.1499938964844</v>
+        <v>266.3900146484375</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>276</v>
+        <v>240.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>244.25</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>301.1000061035156</v>
+        <v>262.8500061035156</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>244.25</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>360673</v>
+        <v>54440</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.41</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott India releases Q1 FY27 earnings call audio recording - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
+        <v>-7.08</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2348,51 +2328,51 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL.NS</t>
+          <t>TARSONS.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram International Limited</t>
+          <t>TARSONS</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>74</v>
+        <v>365</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>75.48999786376953</v>
+        <v>365</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>67.16000366210938</v>
+        <v>332</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.94000244140625</v>
+        <v>336.6499938964844</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>74.26000213623047</v>
+        <v>361.5</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>68.94000244140625</v>
+        <v>336.6499938964844</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>208024</v>
+        <v>1199280</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-7.16</v>
+        <v>-6.87</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Fine Chemicals promoter acquires 3.52% stake via gift - scanx.trade</t>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - univest.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Fine Chemicals promoter acquires 3.52% stake via gift - scanx.trade</t>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - univest.in</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Fine Chemicals posts Q1FY27 profit of ₹2.4 crore; appoints Rudra Shriram as MD - scanx.trade</t>
+          <t>Tarsons Products Share Price Rise: Technicals, Valuation - univest.in</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -2401,7 +2381,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2409,37 +2389,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>JUBLCPL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Limited</t>
+          <t>JUBLCPL</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>263</v>
+        <v>2362.39990234375</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>266.3900146484375</v>
+        <v>2397.89990234375</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>240.5</v>
+        <v>2142</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>244.25</v>
+        <v>2199.10009765625</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>262.8500061035156</v>
+        <v>2342.39990234375</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>244.25</v>
+        <v>2199.10009765625</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>54440</v>
+        <v>16482</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-7.08</v>
+        <v>-6.12</v>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -2450,7 +2430,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2458,48 +2438,40 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TARSONS.NS</t>
+          <t>NDLVENTURE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Limited</t>
+          <t>NDLVENTURE</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>365</v>
+        <v>122.1500015258789</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>365</v>
+        <v>122.7399978637695</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>332</v>
+        <v>113.9499969482422</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>336.6499938964844</v>
+        <v>116.1699981689453</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>361.5</v>
+        <v>123.5599975585938</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>336.6499938964844</v>
+        <v>116.1699981689453</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1199280</v>
+        <v>57175</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-6.87</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
-        </is>
-      </c>
+        <v>-5.98</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -2507,7 +2479,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2515,48 +2487,40 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER.NS</t>
+          <t>MOIL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Limited</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>296</v>
+        <v>271.2000122070312</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>296</v>
+        <v>271.7999877929688</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>270</v>
+        <v>255.6000061035156</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>277.7000122070312</v>
+        <v>257.25</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>297.7000122070312</v>
+        <v>272.7999877929688</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>277.7000122070312</v>
+        <v>257.25</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>10586</v>
+        <v>2810988</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.72</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>S&amp;S Power revenue up 18% in Q1FY27; EBITDA falls 46% on delays - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>S&amp;S Power revenue up 18% in Q1FY27; EBITDA falls 46% on delays - scanx.trade</t>
-        </is>
-      </c>
+        <v>-5.7</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -2564,7 +2528,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2572,48 +2536,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>LPDC.NS</t>
+          <t>AGL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Landmark Property Development Company Limited</t>
+          <t>AGL</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7.860000133514404</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7.860000133514404</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>7.25</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>7.380000114440918</v>
+        <v>13.25</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7.869999885559082</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.380000114440918</v>
+        <v>13.25</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>96741</v>
+        <v>3444947</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.23</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+        <v>-5.42</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Why is AGL Energy stock surging today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Agilon Health Inc (AGL) Stock Up 9.0% but GF Value Says Overvalued -- GF Score: 71/100 - GuruFocus</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2621,56 +2605,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>JUBLCPL.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Jubilant Agri and Consumer Products Limited</t>
+          <t>ATALREAL</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2362.39990234375</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2397.89990234375</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2142</v>
+        <v>31.42000007629395</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2199.10009765625</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2342.39990234375</v>
+        <v>35.84999847412109</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2199.10009765625</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>16482</v>
+        <v>20786651</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-6.12</v>
+        <v>-5.36</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Jubilant Agri &amp; Consumer Q1 Results: Net profit rises 7.5% YoY - scanx.trade</t>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Jubilant Agri &amp; Consumer Q1 Results: Net profit rises 7.5% YoY - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Share Price Near ATH With Fundamental View - univest.in</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2678,68 +2666,48 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SIGIND.NS</t>
+          <t>NDGL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>NDGL</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>70.84999847412109</v>
+        <v>2875</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>71.5</v>
+        <v>2875</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>65.31999969482422</v>
+        <v>2669</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>66.84999847412109</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>71.15000152587891</v>
+        <v>2878.699951171875</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>66.84999847412109</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>95414</v>
+        <v>558</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-6.04</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Signet Industries promoter Mukesh Sangla buys 13,904 shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Signet Industries promoter Mukesh Sangla buys 13,904 shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Signet Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Signet Industries Q1 Results: Net profit rises 10.7% QoQ to ₹8.05 crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Signet Industries షేర్ ధర: ఇన్వెస్టర్లకు పండగే! తొలిసారిగా భారీ లాభాలు.. 1066% జంప్ - Whalesbook</t>
-        </is>
-      </c>
+        <v>-5.24</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2747,40 +2715,48 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NDLVENTURE.NS</t>
+          <t>KHAICHEM.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>NDL Ventures Limited</t>
+          <t>KHAICHEM</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>122.1500015258789</v>
+        <v>60.34000015258789</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>122.7399978637695</v>
+        <v>63.29999923706055</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>113.9499969482422</v>
+        <v>56.11000061035156</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>116.1699981689453</v>
+        <v>56.72000122070312</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>123.5599975585938</v>
+        <v>59.75</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>116.1699981689453</v>
+        <v>56.72000122070312</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>57175</v>
+        <v>1445339</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+        <v>-5.07</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - univest.in</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - univest.in</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -2788,7 +2764,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2796,37 +2772,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MOIL.NS</t>
+          <t>NATIONSTD.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MOIL Limited</t>
+          <t>NATIONSTD</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>271.2000122070312</v>
+        <v>134</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>271.7999877929688</v>
+        <v>148.1000061035156</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>255.6000061035156</v>
+        <v>134</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>257.25</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>272.7999877929688</v>
+        <v>141.0500030517578</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>257.25</v>
+        <v>134</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2810988</v>
+        <v>335324</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.7</v>
+        <v>-5</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -2837,7 +2813,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2845,68 +2821,48 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>APEX.NS</t>
+          <t>RAMCOSYS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Apex Frozen Foods Limited</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>424</v>
+        <v>593.0999755859375</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>427.7999877929688</v>
+        <v>598</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>395.3999938964844</v>
+        <v>564.5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>398.5</v>
+        <v>564.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>422.5499877929688</v>
+        <v>594.2000122070312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>398.5</v>
+        <v>564.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>944026</v>
+        <v>245328</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.69</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Volume Gainers, August 14, 2026, 4:00 PM IST - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods reports burgeoning profits with YoY surge in Q1 FY27 - Business Upturn</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>7 Stocks That Have Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods Hits 20% Upper Circuit on 138% Profit Jump - Whalesbook</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods reports burgeoning profits with YoY surge in Q1 FY27 - Business Upturn</t>
-        </is>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2914,48 +2870,40 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AGL.NS</t>
+          <t>OSWALSEEDS.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO GLOBAL LIMITED</t>
+          <t>OSWALSEEDS</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14</v>
+        <v>13.44999980926514</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>13.5600004196167</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13.02999973297119</v>
+        <v>12.88000011444092</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>13.25</v>
+        <v>12.92000007629395</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13.25</v>
+        <v>12.92000007629395</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3444947</v>
+        <v>400753</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.42</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Allcargo Global makes Q1FY27 earnings call audio recording available - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Allcargo Global makes Q1FY27 earnings call audio recording available - scanx.trade</t>
-        </is>
-      </c>
+        <v>-4.93</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -2963,7 +2911,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2971,60 +2919,48 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>LORDSCHLO.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Limited</t>
+          <t>LORDSCHLO</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36.09999847412109</v>
+        <v>140.0299987792969</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>36.33000183105469</v>
+        <v>142.4499969482422</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>31.42000007629395</v>
+        <v>133</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>133.4199981689453</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>35.84999847412109</v>
+        <v>139.9799957275391</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>133.4199981689453</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>20786651</v>
+        <v>29362</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.36</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech board approves ₹16 crore rights issue for equity shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech board approves ₹16 crore rights issue for equity shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech Q1FY27 net profit rises 52% to ₹1 crore as margins expand - scanx.trade</t>
-        </is>
-      </c>
+        <v>-4.69</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:44:15</t>
+          <t>2026-08-18 20:18:32</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3032,40 +2968,48 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>NDGL.NS</t>
+          <t>SUMEETINDS.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Naga Dhunseri Group Limited</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2875</v>
+        <v>14.14000034332275</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2875</v>
+        <v>14.27999973297119</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2669</v>
+        <v>13.38000011444092</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2727.89990234375</v>
+        <v>13.42000007629395</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2878.699951171875</v>
+        <v>14.07999992370605</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2727.89990234375</v>
+        <v>13.42000007629395</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>558</v>
+        <v>4474052</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.24</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+        <v>-4.69</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -587,34 +587,34 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>PRABHA ENERGY Share Price Gain: Technicals and Valuation - univest.in</t>
+          <t>PRABHA ENERGY Share Price Gain: Technicals and Valuation - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
+          <t>Volume Gainers, August 18, 2026, 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
           <t>Prabha Energy seeks ₹150 crore QIP approval at upcoming AGM - scanx.trade</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>N K Industries Ltd leads gainers in 'B' group - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -656,12 +656,12 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - univest.in</t>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - univest.in</t>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -713,12 +713,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - univest.in</t>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - univest.in</t>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
@@ -728,7 +728,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - indianexpress.com</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -797,60 +797,48 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB.NS</t>
+          <t>ICIL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>317.9500122070312</v>
+        <v>388.7000122070312</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>351.2999877929688</v>
+        <v>462</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>316.8999938964844</v>
+        <v>387.0499877929688</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>437.7000122070312</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>313.0199890136719</v>
+        <v>388.7000122070312</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>437.7000122070312</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5070304</v>
+        <v>25217469</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
-        </is>
-      </c>
+        <v>12.61</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -858,40 +846,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA.NS</t>
+          <t>SIGACHI.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>SIGACHI</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11.32999992370605</v>
+        <v>25.90999984741211</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>12.98999977111816</v>
+        <v>30.09000015258789</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10.97999954223633</v>
+        <v>25.90999984741211</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11.35999965667725</v>
+        <v>26.35000038146973</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>25170195</v>
+        <v>10330178</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+        <v>12.37</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -899,7 +895,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -907,68 +903,60 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PARAS.NS</t>
+          <t>MACPOWER.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1385</v>
+        <v>1782.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>2000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1384.699951171875</v>
+        <v>1782.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>1983.599975585938</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1388.5</v>
+        <v>1781.400024414062</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>1983.599975585938</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>5405026</v>
+        <v>190615</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10</v>
+        <v>11.35</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence Share Price at Fresh 52-Week High - univest.in</t>
-        </is>
-      </c>
+          <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -976,64 +964,48 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS.NS</t>
+          <t>JINDRILL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1170</v>
+        <v>587.0999755859375</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1305.75</v>
+        <v>673.5499877929688</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1165</v>
+        <v>587.0999755859375</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1305.75</v>
+        <v>651.1500244140625</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1187.050048828125</v>
+        <v>586.2000122070312</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1305.75</v>
+        <v>651.1500244140625</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>9337471</v>
+        <v>17885600</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - univest.in</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - univest.in</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
-        </is>
-      </c>
+        <v>11.08</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1041,56 +1013,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>BI.NS</t>
+          <t>INDSWFTLAB.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>94</v>
+        <v>317.9500122070312</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>351.2999877929688</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>316.8999938964844</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>313.0199890136719</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>523283</v>
+        <v>5070304</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.99</v>
+        <v>10.81</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1098,48 +1074,40 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NITINSPIN.NS</t>
+          <t>ABINFRA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>556.75</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>610</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>554.5</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>606.9000244140625</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>553.75</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>606.9000244140625</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>3703976</v>
+        <v>25170195</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
-        </is>
-      </c>
+        <v>10.65</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -1147,7 +1115,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1155,68 +1123,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE.NS</t>
+          <t>REGAAL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>REGAAL</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>426.8999938964844</v>
+        <v>90.27999877929688</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>465.1000061035156</v>
+        <v>101.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>419.7999877929688</v>
+        <v>88.65000152587891</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>425.25</v>
+        <v>90.45999908447266</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3647695</v>
+        <v>2972532</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>10.03</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - univest.in</t>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - univest.in</t>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today: Price Rise Review - univest.in</t>
+          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today: Fall and Valuation - univest.in</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
-        </is>
-      </c>
+          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1224,56 +1188,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SUNDARAM.NS</t>
+          <t>DHOOTTRANS.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>SUNDARAM</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.159999966621399</v>
+        <v>1170</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.240000009536743</v>
+        <v>1305.75</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1.149999976158142</v>
+        <v>1165</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>1305.75</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.129999995231628</v>
+        <v>1187.050048828125</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>1305.75</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1399675</v>
+        <v>9337471</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.85</v>
+        <v>10</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - univest.in</t>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - univest.in</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1281,68 +1253,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>PARAS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>1385</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>40.90000152587891</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>1384.699951171875</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.0099983215332</v>
+        <v>1388.5</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3327170</v>
+        <v>5405026</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - univest.in</t>
+          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - univest.in</t>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - Insider Gaming</t>
+          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+          <t>Paras Defence Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1350,56 +1322,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>TPHQ.NS</t>
+          <t>INDOMIM.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>INDOMIM</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.6100000143051147</v>
+        <v>910</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>952.75</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.5400000214576721</v>
+        <v>905</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>952.75</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.5799999833106995</v>
+        <v>866.1500244140625</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>952.75</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>33421631</v>
+        <v>10245867</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Stocks to watch, August 18: GMR Airports, Oberoi Realty, Paytm, Nelco, INDO-MIM, Netweb Technologies - Dailyhunt</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>INDOMIM Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>INDO-MIM Board Clears Q1 FY27 Results, New Secretarial Auditor and ESOP Ratification - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>INDO-MIM Clears Q1 FY27 Results, Appoints New Secretarial Auditor and Ratifies ESOP - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1407,46 +1391,46 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KERNEX.NS</t>
+          <t>BI.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>KERNEX</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1820</v>
+        <v>94</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1920</v>
+        <v>101.379997253418</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1756.099975585938</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1901.800048828125</v>
+        <v>101.379997253418</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1751.699951171875</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1901.800048828125</v>
+        <v>101.379997253418</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1425146</v>
+        <v>523283</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8.57</v>
+        <v>9.99</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Kernex Microsystems Q1FY27 net profit rises 13.7x to ₹10,984.57 lakh - scanx.trade</t>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Kernex Microsystems Q1FY27 net profit rises 13.7x to ₹10,984.57 lakh - scanx.trade</t>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
@@ -1456,7 +1440,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1464,64 +1448,56 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA.NS</t>
+          <t>NITINSPIN.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>517.7000122070312</v>
+        <v>556.75</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>565</v>
+        <v>610</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>509</v>
+        <v>554.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>562.0499877929688</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>518.75</v>
+        <v>553.75</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>562.0499877929688</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>704938</v>
+        <v>3703976</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8.35</v>
+        <v>9.6</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>eMudhra Ltd. Share Price Today - eMudhra Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
-        </is>
-      </c>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1529,68 +1505,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>ASIANENE.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>870</v>
+        <v>426.8999938964844</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>947.9000244140625</v>
+        <v>465.1000061035156</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>860.0499877929688</v>
+        <v>419.7999877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>929.2000122070312</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>857.9500122070312</v>
+        <v>425.25</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>929.2000122070312</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5438303</v>
+        <v>3647695</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - univest.in</t>
+          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - univest.in</t>
+          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Indian Export Stocks Retail Investors May Watch As US Scrutiny Of Transshipment Grows - simplywall.st</t>
+          <t>Asian Energy Services Share Price Today: Price Rise Review - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>Asian Energy Services Share Price Today: Fall and Valuation - Univest</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Wins MeitY Nod for ₹1,020 Crore Expansion at Rajkot Plant - TipRanks</t>
+          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1598,68 +1574,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>MCLOUD.NS</t>
+          <t>ABCOTS.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MCLOUD</t>
+          <t>ABCOTS</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>26.97999954223633</v>
+        <v>202.4799957275391</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>29.10000038146973</v>
+        <v>225</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>26.84000015258789</v>
+        <v>201.8800048828125</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>28.85000038146973</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.77000045776367</v>
+        <v>199.6600036621094</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28.85000038146973</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>9814518</v>
+        <v>152577</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.77</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL Order; Shares Rise 4.74% - HDFC Sky</t>
+          <t>ABCOTS Share Price Today - AB Cotspin on NSE/BSE - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL AI Surveillance Contract - TipRanks</t>
+          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - Univest</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Magellanic Cloud Publishes Q1 FY27 Unaudited Results via Newspaper and Web - TipRanks</t>
+          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1667,68 +1643,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MMP.NS</t>
+          <t>SUNDARAM.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>SUNDARAM</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>353.8500061035156</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>383</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>345</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>377.0499877929688</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>350</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>377.0499877929688</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>191009</v>
+        <v>1399675</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.73</v>
+        <v>8.85</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>MMP Industries Standalone June 2026 Net Sales at Rs 232.11 crore, up 26.66% Y-o-Y - Moneycontrol.com</t>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MMP Industries Standalone June 2026 Net Sales at Rs 232.11 crore, up 26.66% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>MMP Industries Share Price: 52-Week High, Valuation View - univest.in</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>MMP Industries Share Price Target 2027 to 2030: Analyst Outlook - univest.in</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>What's Going On With Precious Metals And Mining Trust Stock Sunday? - Wealth Awesome</t>
-        </is>
-      </c>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1736,40 +1700,48 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>KPEL.NS</t>
+          <t>TPHQ.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>KPEL</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>243.6999969482422</v>
+        <v>0.6100000143051147</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>264.9500122070312</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>240</v>
+        <v>0.5400000214576721</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>262.2999877929688</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>243.75</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>262.2999877929688</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>859114</v>
+        <v>33421631</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -1897,7 +1869,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1949,7 +1921,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - univest.in</t>
+          <t>Hardwyn Q1 FY27 Results: Revenue Rs 35 Cr, PAT Rs 3 Cr - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1962,7 +1934,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2027,7 +1999,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2035,68 +2007,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PRAXIS.NS</t>
+          <t>NELCO.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>NELCO</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.039999961853027</v>
+        <v>1092.300048828125</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6.039999961853027</v>
+        <v>1098</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5.349999904632568</v>
+        <v>938.5999755859375</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5.400000095367432</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5.869999885559082</v>
+        <v>1081.5</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.400000095367432</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>554400</v>
+        <v>2128333</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-8.01</v>
+        <v>-12.27</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - univest.in</t>
+          <t>Nelco Share Price Falls over 12%: Why the $20 Million Elveo Investment Has Investors Worried - India Infoline</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - univest.in</t>
+          <t>Tata's Nelco shares tumble 12% on Tuesday after ₹1,120 peak - NewsBytes</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines stock hits 52-week high at 388.27 USD - Investing.com India</t>
+          <t>News by CNBC TV18 on TradingView, 2026-08-18 — cnbctv:f2ab86df1094b:0 - TradingView</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,840 Shares in Praxis Precision Medicines, Inc. $PRAX Purchased by Handelsbanken Fonder AB - MarketBeat</t>
+          <t>Nelco invests $20 mn in US-based Elveo for satellite connectivity; shares fall 12% - Upstox</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - stocktitan.net</t>
+          <t>Tata Group stock: Nelco zooms 108% from March low; hits 52-week high - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2104,40 +2076,48 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL.NS</t>
+          <t>AHLUCONT.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.5</v>
+        <v>776</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>14.94999980926514</v>
+        <v>782.4000244140625</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.90999984741211</v>
+        <v>702.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>13.9399995803833</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15.14000034332275</v>
+        <v>793.8499755859375</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.9399995803833</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>7220</v>
+        <v>545834</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+        <v>-10.85</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -2145,7 +2125,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2153,64 +2133,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT.NS</t>
+          <t>PRAXIS.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT</t>
+          <t>PRAXIS</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>293</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>297.1499938964844</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>276</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>301.1000061035156</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>360673</v>
+        <v>554400</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-7.41</v>
+        <v>-8.01</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+          <t>Praxis Precision Medicines stock hits 52-week high at 388.27 USD - Investing.com India</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>9,840 Shares in Praxis Precision Medicines, Inc. $PRAX Purchased by Handelsbanken Fonder AB - MarketBeat</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - Stock Titan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2218,60 +2202,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL.NS</t>
+          <t>SHYAMTEL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>SHYAMTEL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>74</v>
+        <v>14.5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>75.48999786376953</v>
+        <v>14.94999980926514</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>67.16000366210938</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>68.94000244140625</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>74.26000213623047</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>68.94000244140625</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>208024</v>
+        <v>7220</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-7.16</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>DCM Shriram International Ltd. Share Price Today After Fall - univest.in</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>DCM Shriram International Ltd. Share Price Today After Fall - univest.in</t>
-        </is>
-      </c>
+        <v>-7.93</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2279,48 +2251,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>THOMASCOTT.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>THOMASCOTT</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>266.3900146484375</v>
+        <v>297.1499938964844</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>240.5</v>
+        <v>276</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>244.25</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>262.8500061035156</v>
+        <v>301.1000061035156</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>244.25</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>54440</v>
+        <v>360673</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.08</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+        <v>-7.41</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2328,51 +2316,51 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TARSONS.NS</t>
+          <t>DCMSIL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>TARSONS</t>
+          <t>DCMSIL</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>365</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>365</v>
+        <v>75.48999786376953</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>332</v>
+        <v>67.16000366210938</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>336.6499938964844</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>361.5</v>
+        <v>74.26000213623047</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>336.6499938964844</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1199280</v>
+        <v>208024</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-6.87</v>
+        <v>-7.16</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - univest.in</t>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - univest.in</t>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Share Price Rise: Technicals, Valuation - univest.in</t>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -2381,7 +2369,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2389,37 +2377,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>JUBLCPL.NS</t>
+          <t>KANPRPLA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>JUBLCPL</t>
+          <t>KANPRPLA</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2362.39990234375</v>
+        <v>263</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2397.89990234375</v>
+        <v>266.3900146484375</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2142</v>
+        <v>240.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2199.10009765625</v>
+        <v>244.25</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2342.39990234375</v>
+        <v>262.8500061035156</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2199.10009765625</v>
+        <v>244.25</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>16482</v>
+        <v>54440</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-6.12</v>
+        <v>-7.08</v>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -2430,7 +2418,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2438,48 +2426,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NDLVENTURE.NS</t>
+          <t>TARSONS.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>TARSONS</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>122.1500015258789</v>
+        <v>365</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>122.7399978637695</v>
+        <v>365</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>113.9499969482422</v>
+        <v>332</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>116.1699981689453</v>
+        <v>336.6499938964844</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>123.5599975585938</v>
+        <v>361.5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>116.1699981689453</v>
+        <v>336.6499938964844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>57175</v>
+        <v>1199280</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
+        <v>-6.87</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2487,40 +2487,48 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MOIL.NS</t>
+          <t>S&amp;SPOWER.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>S&amp;SPOWER</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>271.2000122070312</v>
+        <v>296</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>271.7999877929688</v>
+        <v>296</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>255.6000061035156</v>
+        <v>270</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>257.25</v>
+        <v>277.7000122070312</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>272.7999877929688</v>
+        <v>297.7000122070312</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>257.25</v>
+        <v>277.7000122070312</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2810988</v>
+        <v>10586</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+        <v>-6.72</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -2528,7 +2536,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2536,68 +2544,56 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AGL.NS</t>
+          <t>LPDC.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AGL</t>
+          <t>LPDC</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>14</v>
+        <v>7.860000133514404</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>7.860000133514404</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>13.02999973297119</v>
+        <v>7.25</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>13.25</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>7.869999885559082</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13.25</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3444947</v>
+        <v>96741</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5.42</v>
+        <v>-6.23</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+          <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Why is AGL Energy stock surging today? - Investing.com</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Agilon Health Inc (AGL) Stock Up 9.0% but GF Value Says Overvalued -- GF Score: 71/100 - GuruFocus</t>
-        </is>
-      </c>
+          <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2605,60 +2601,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>JUBLCPL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL</t>
+          <t>JUBLCPL</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>36.09999847412109</v>
+        <v>2362.39990234375</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>36.33000183105469</v>
+        <v>2397.89990234375</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>31.42000007629395</v>
+        <v>2142</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>2199.10009765625</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35.84999847412109</v>
+        <v>2342.39990234375</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>2199.10009765625</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>20786651</v>
+        <v>16482</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.36</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech Share Price Near ATH With Fundamental View - univest.in</t>
-        </is>
-      </c>
+        <v>-6.12</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2666,40 +2650,48 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>NDGL.NS</t>
+          <t>SIGIND.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>NDGL</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2875</v>
+        <v>70.84999847412109</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2875</v>
+        <v>71.5</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2669</v>
+        <v>65.31999969482422</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>2727.89990234375</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2878.699951171875</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2727.89990234375</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>558</v>
+        <v>95414</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5.24</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+        <v>-6.04</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -2707,7 +2699,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2715,48 +2707,40 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KHAICHEM.NS</t>
+          <t>NDLVENTURE.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>KHAICHEM</t>
+          <t>NDLVENTURE</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>60.34000015258789</v>
+        <v>122.1500015258789</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>63.29999923706055</v>
+        <v>122.7399978637695</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>56.11000061035156</v>
+        <v>113.9499969482422</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.72000122070312</v>
+        <v>116.1699981689453</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>59.75</v>
+        <v>123.5599975585938</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>56.72000122070312</v>
+        <v>116.1699981689453</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1445339</v>
+        <v>57175</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - univest.in</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - univest.in</t>
-        </is>
-      </c>
+        <v>-5.98</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -2764,7 +2748,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2772,37 +2756,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>NATIONSTD.NS</t>
+          <t>MOIL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>NATIONSTD</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>134</v>
+        <v>271.2000122070312</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>148.1000061035156</v>
+        <v>271.7999877929688</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>134</v>
+        <v>255.6000061035156</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>134</v>
+        <v>257.25</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>141.0500030517578</v>
+        <v>272.7999877929688</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>134</v>
+        <v>257.25</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>335324</v>
+        <v>2810988</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5</v>
+        <v>-5.7</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -2813,7 +2797,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2821,48 +2805,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RAMCOSYS.NS</t>
+          <t>APEX.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>APEX</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>593.0999755859375</v>
+        <v>424</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>598</v>
+        <v>427.7999877929688</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>564.5</v>
+        <v>395.3999938964844</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>564.5</v>
+        <v>398.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>594.2000122070312</v>
+        <v>422.5499877929688</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>564.5</v>
+        <v>398.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>245328</v>
+        <v>944026</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+        <v>-5.69</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - cnbctv18.com</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2870,48 +2874,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS.NS</t>
+          <t>AGL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>AGL</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13.44999980926514</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>13.5600004196167</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>12.88000011444092</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>12.92000007629395</v>
+        <v>13.25</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13.59000015258789</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12.92000007629395</v>
+        <v>13.25</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>400753</v>
+        <v>3444947</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.93</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+        <v>-5.42</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Why is AGL Energy stock surging today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Agilon Health Inc (AGL) Stock Up 9.0% but GF Value Says Overvalued -- GF Score: 71/100 - GuruFocus</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2919,48 +2943,60 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>LORDSCHLO.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>LORDSCHLO</t>
+          <t>ATALREAL</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>140.0299987792969</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>142.4499969482422</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>133</v>
+        <v>31.42000007629395</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>133.4199981689453</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>139.9799957275391</v>
+        <v>35.84999847412109</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>133.4199981689453</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>29362</v>
+        <v>20786651</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+        <v>-5.36</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Share Price Near ATH With Fundamental View - Univest</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 20:18:32</t>
+          <t>2026-08-18 21:01:48</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2968,48 +3004,40 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>NDGL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>NDGL</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.14000034332275</v>
+        <v>2875</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>14.27999973297119</v>
+        <v>2875</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>13.38000011444092</v>
+        <v>2669</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>13.42000007629395</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.07999992370605</v>
+        <v>2878.699951171875</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13.42000007629395</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4474052</v>
+        <v>558</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
-        </is>
-      </c>
+        <v>-5.24</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -671,7 +671,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -728,7 +728,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - indianexpress.com</t>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -838,7 +838,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -895,7 +895,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -956,7 +956,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1005,7 +1005,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1066,7 +1066,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1115,7 +1115,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1172,15 +1172,19 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
+          <t>Regaal Resources Q1 Results: Earnings Call Scheduled for August 17 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1188,64 +1192,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS.NS</t>
+          <t>PARAS.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1170</v>
+        <v>1385</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1305.75</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1165</v>
+        <v>1384.699951171875</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1305.75</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1187.050048828125</v>
+        <v>1388.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1305.75</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>9337471</v>
+        <v>5405026</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>10</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Paras Defence Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1253,68 +1261,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PARAS.NS</t>
+          <t>DHOOTTRANS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1385</v>
+        <v>1170</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>1305.75</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1384.699951171875</v>
+        <v>1165</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>1305.75</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1388.5</v>
+        <v>1187.050048828125</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>1305.75</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5405026</v>
+        <v>9337471</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>10</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
+          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1376,14 +1380,14 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Clears Q1 FY27 Results, Appoints New Secretarial Auditor and Ratifies ESOP - TipRanks</t>
+          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1440,7 +1444,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1497,7 +1501,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1505,68 +1509,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE.NS</t>
+          <t>ABCOTS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>ABCOTS</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>426.8999938964844</v>
+        <v>202.4799957275391</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>465.1000061035156</v>
+        <v>225</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>419.7999877929688</v>
+        <v>201.8800048828125</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>425.25</v>
+        <v>199.6600036621094</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3647695</v>
+        <v>152577</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>8.890000000000001</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today: Price Rise Review - Univest</t>
+          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today: Fall and Valuation - Univest</t>
+          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
+          <t>A B Cotspin India clears Q1 FY27 results, appoints new compliance chief - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1574,68 +1578,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ABCOTS.NS</t>
+          <t>ASIANENE.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ABCOTS</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>202.4799957275391</v>
+        <v>426.8999938964844</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>225</v>
+        <v>465.1000061035156</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>201.8800048828125</v>
+        <v>419.7999877929688</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>217.3999938964844</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>199.6600036621094</v>
+        <v>425.25</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>217.3999938964844</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>152577</v>
+        <v>3647695</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>8.890000000000001</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
+          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
+          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ABCOTS Share Price Today - AB Cotspin on NSE/BSE - scanx.trade</t>
+          <t>Asian Energy Services Share Price Today: Price Rise Review - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - Univest</t>
+          <t>Asian Energy Services Share Price Today: Fall and Valuation - Univest</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
+          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1692,7 +1696,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1700,51 +1704,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TPHQ.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.6100000143051147</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>40.90000152587891</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.5400000214576721</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.5799999833106995</v>
+        <v>37.0099983215332</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>33421631</v>
+        <v>3327170</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - Univest</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - insider-gaming.com</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1869,7 +1885,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1921,7 +1937,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn Q1 FY27 Results: Revenue Rs 35 Cr, PAT Rs 3 Cr - Univest</t>
+          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1929,12 +1945,16 @@
           <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd is Rated Sell - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1991,15 +2011,19 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
+          <t>Krishival Foods utilizes ₹799.15 lakh of rights issue funds in Q4FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
           <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2068,7 +2092,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2125,7 +2149,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2187,14 +2211,14 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - Stock Titan</t>
+          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - stocktitan.net</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2243,7 +2267,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2308,7 +2332,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2369,7 +2393,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2418,7 +2442,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2470,16 +2494,20 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2536,7 +2564,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2593,7 +2621,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2642,7 +2670,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2699,7 +2727,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2748,7 +2776,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2797,7 +2825,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2854,7 +2882,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - cnbctv18.com</t>
+          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2866,7 +2894,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2918,7 +2946,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
+          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - businesstoday.in</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2935,7 +2963,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2996,7 +3024,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 21:01:48</t>
+          <t>2026-08-18 15:46:38</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -438,8 +438,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,56 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PRABHA.NS</t>
+          <t>SIGACHI.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PRABHA</t>
+          <t>SIGACHI</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>164.3099975585938</v>
+        <v>25.90999984741211</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>196.0500030517578</v>
+        <v>30.09000015258789</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>163</v>
+        <v>25.90999984741211</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>192.1999969482422</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>163.3800048828125</v>
+        <v>26.35000038146973</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>192.1999969482422</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5357086</v>
+        <v>10361044</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>17.64</v>
+        <v>12.37</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>PRABHA ENERGY Share Price Gain: Technicals and Valuation - Univest</t>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Volume Gainers, August 18, 2026, 3:00 PM IST - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Prabha Energy seeks ₹150 crore QIP approval at upcoming AGM - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>N K Industries Ltd leads gainers in 'B' group - Business Standard</t>
-        </is>
-      </c>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,48 +610,40 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SUBEXLTD.NS</t>
+          <t>JINDRILL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14.10999965667725</v>
+        <v>587.0999755859375</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>16.93000030517578</v>
+        <v>673.5499877929688</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.07999992370605</v>
+        <v>587.0999755859375</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>16.48999977111816</v>
+        <v>651.1500244140625</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14.10999965667725</v>
+        <v>586.2000122070312</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16.48999977111816</v>
+        <v>651.1500244140625</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>44567365</v>
+        <v>17885822</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
-        </is>
-      </c>
+        <v>11.08</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -671,7 +651,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -679,48 +659,40 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AARNAV.NS</t>
+          <t>ABINFRA.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>ABINFRA</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>31.35000038146973</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>36.04000091552734</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30.70000076293945</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>35.36999893188477</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>31.22999954223633</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>35.36999893188477</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>220800</v>
+        <v>25170295</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>13.26</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
+        <v>10.65</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -728,7 +700,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -736,60 +708,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>YASHO.NS</t>
+          <t>REGAAL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>REGAAL</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4400</v>
+        <v>90.27999877929688</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4994</v>
+        <v>101.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4399.89990234375</v>
+        <v>88.65000152587891</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>4915.7998046875</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4362.2998046875</v>
+        <v>90.45999908447266</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4915.7998046875</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>240190</v>
+        <v>2975990</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>12.69</v>
+        <v>10.03</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - univest.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - univest.in</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -797,48 +773,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ICIL.NS</t>
+          <t>INDOMIM.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>INDOMIM</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>388.7000122070312</v>
+        <v>910</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>462</v>
+        <v>952.75</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>387.0499877929688</v>
+        <v>905</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>437.7000122070312</v>
+        <v>952.75</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>388.7000122070312</v>
+        <v>866.1500244140625</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>437.7000122070312</v>
+        <v>952.75</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>25217469</v>
+        <v>10246021</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>INDOMIM Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Stocks to watch, August 18: GMR Airports, Oberoi Realty, Paytm, Nelco, INDO-MIM, Netweb Technologies - Upstox</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -846,46 +842,46 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SIGACHI.NS</t>
+          <t>BI.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>SIGACHI</t>
+          <t>BI</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>25.90999984741211</v>
+        <v>94</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>30.09000015258789</v>
+        <v>101.379997253418</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.90999984741211</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>29.61000061035156</v>
+        <v>101.379997253418</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.35000038146973</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29.61000061035156</v>
+        <v>101.379997253418</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>10330178</v>
+        <v>523283</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>12.37</v>
+        <v>9.99</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
@@ -895,7 +891,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -903,60 +899,56 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER.NS</t>
+          <t>NITINSPIN.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>NITINSPIN</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1782.5</v>
+        <v>556.75</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2000</v>
+        <v>610</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1782.5</v>
+        <v>554.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1983.599975585938</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1781.400024414062</v>
+        <v>553.75</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1983.599975585938</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>190615</v>
+        <v>3703991</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>11.35</v>
+        <v>9.6</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
-        </is>
-      </c>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -964,48 +956,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>JINDRILL.NS</t>
+          <t>ABCOTS.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>ABCOTS</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>587.0999755859375</v>
+        <v>202.4799957275391</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>673.5499877929688</v>
+        <v>225</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>587.0999755859375</v>
+        <v>201.8800048828125</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>651.1500244140625</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>586.2000122070312</v>
+        <v>199.6600036621094</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>651.1500244140625</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>17885600</v>
+        <v>152579</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - univest.in</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - univest.in</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>ABCOTS Share Price Today - AB Cotspin on NSE/BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1013,60 +1025,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>317.9500122070312</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>351.2999877929688</v>
+        <v>40.90000152587891</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>316.8999938964844</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>313.0199890136719</v>
+        <v>37.0099983215332</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5070304</v>
+        <v>3330020</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10.81</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - univest.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - univest.in</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - univest.in</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - Insider Gaming</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1074,48 +1094,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA.NS</t>
+          <t>EMUDHRA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11.32999992370605</v>
+        <v>517.7000122070312</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12.98999977111816</v>
+        <v>565</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>10.97999954223633</v>
+        <v>509</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>562.0499877929688</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.35999965667725</v>
+        <v>518.75</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>562.0499877929688</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>25170195</v>
+        <v>705436</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+        <v>8.35</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>eMudhra Ltd. Share Price Today - eMudhra Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>eMudhra shares surge as police close 3i Infotech's fraud complaint - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1123,68 +1163,60 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>REGAAL.NS</t>
+          <t>JYOTICNC.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>REGAAL</t>
+          <t>JYOTICNC</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>90.27999877929688</v>
+        <v>870</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>101.5</v>
+        <v>947.9000244140625</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>88.65000152587891</v>
+        <v>860.0499877929688</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>99.52999877929688</v>
+        <v>929.2000122070312</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>90.45999908447266</v>
+        <v>857.9500122070312</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>99.52999877929688</v>
+        <v>929.2000122070312</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2972532</v>
+        <v>5438972</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.03</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+          <t>Indian Export Stocks Retail Investors May Watch As US Scrutiny Of Transshipment Grows - simplywall.st</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Regaal Resources Q1 Results: Earnings Call Scheduled for August 17 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
-        </is>
-      </c>
+          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1192,68 +1224,56 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PARAS.NS</t>
+          <t>TIINDIA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1385</v>
+        <v>2755.800048828125</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>2989</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1384.699951171875</v>
+        <v>2755.800048828125</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>2959</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1388.5</v>
+        <v>2741.39990234375</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1527.300048828125</v>
+        <v>2959</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5405026</v>
+        <v>4188005</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10</v>
+        <v>7.94</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Paras Defence Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
+          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1261,64 +1281,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS.NS</t>
+          <t>KPEL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>KPEL</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1170</v>
+        <v>243.6999969482422</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1305.75</v>
+        <v>264.9500122070312</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1165</v>
+        <v>240</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1305.75</v>
+        <v>262.2999877929688</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1187.050048828125</v>
+        <v>243.75</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1305.75</v>
+        <v>262.2999877929688</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>9337471</v>
+        <v>859476</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
-        </is>
-      </c>
+        <v>7.61</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1326,68 +1330,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM.NS</t>
+          <t>MMFL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM</t>
+          <t>MMFL</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>910</v>
+        <v>639.7000122070312</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>952.75</v>
+        <v>687.9500122070312</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>905</v>
+        <v>632.7999877929688</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>952.75</v>
+        <v>680.2000122070312</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>866.1500244140625</v>
+        <v>632.2999877929688</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>952.75</v>
+        <v>680.2000122070312</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>10245867</v>
+        <v>935497</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10</v>
+        <v>7.58</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - univest.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Stocks to watch, August 18: GMR Airports, Oberoi Realty, Paytm, Nelco, INDO-MIM, Netweb Technologies - Dailyhunt</t>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - univest.in</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM Historical Data - Equitypandit</t>
+          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Board Clears Q1 FY27 Results, New Secretarial Auditor and ESOP Ratification - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
-        </is>
-      </c>
+          <t>MM Forgings Clarifies ₹56.25 Crore Exceptional Gain from Oragadam Land Sale - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1395,48 +1395,40 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BI.NS</t>
+          <t>PFOCUS.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>94</v>
+        <v>266.0499877929688</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>289</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>264</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>286.25</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>266.3999938964844</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>286.25</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>523283</v>
+        <v>2789751</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
-        </is>
-      </c>
+        <v>7.45</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -1444,7 +1436,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1452,48 +1444,40 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>NITINSPIN.NS</t>
+          <t>MSTCLTD.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>556.75</v>
+        <v>658.1500244140625</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>610</v>
+        <v>709</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>554.5</v>
+        <v>655</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>606.9000244140625</v>
+        <v>701.5499877929688</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>553.75</v>
+        <v>653.2000122070312</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>606.9000244140625</v>
+        <v>701.5499877929688</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3703976</v>
+        <v>1266456</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
-        </is>
-      </c>
+        <v>7.4</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -1501,7 +1485,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1509,68 +1493,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ABCOTS.NS</t>
+          <t>RITCO.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ABCOTS</t>
+          <t>RITCO</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>202.4799957275391</v>
+        <v>288.0499877929688</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>225</v>
+        <v>318.3999938964844</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>201.8800048828125</v>
+        <v>288.0499877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>217.3999938964844</v>
+        <v>313</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>199.6600036621094</v>
+        <v>292.5</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>217.3999938964844</v>
+        <v>313</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>152577</v>
+        <v>381642</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
+          <t>Ritco Logistics Ltd. (RITCO) Share Price Today: Price Action Analysis - univest.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
+          <t>Ritco Logistics Ltd. (RITCO) Share Price Today: Price Action Analysis - univest.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - Univest</t>
+          <t>Ritco Logistics Q1 Results: Unaudited financials published - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
+          <t>Ritco Logistics consolidated net profit declines 43.36% in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>A B Cotspin India clears Q1 FY27 results, appoints new compliance chief - TipRanks</t>
+          <t>Ritco Logistics Q1 Results FY27: PAT Rs 3 Cr, Revenue Rs 365 cror - univest.in</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1578,68 +1562,56 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE.NS</t>
+          <t>SGMART.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>426.8999938964844</v>
+        <v>750.6500244140625</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>465.1000061035156</v>
+        <v>809</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>419.7999877929688</v>
+        <v>744</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>804.9500122070312</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>425.25</v>
+        <v>752.2999877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>463.0499877929688</v>
+        <v>804.9500122070312</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3647695</v>
+        <v>907346</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>7</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+          <t>SG Mart Share Price at Fresh 52-Week High: Full Analysis - univest.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Asian Energy Services Share Price Today: Price Rise Review - Univest</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Asian Energy Services Share Price Today: Fall and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
-        </is>
-      </c>
+          <t>SG Mart Share Price at Fresh 52-Week High: Full Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1647,56 +1619,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SUNDARAM.NS</t>
+          <t>RBA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>SUNDARAM</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.159999966621399</v>
+        <v>99.80000305175781</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.240000009536743</v>
+        <v>108.4100036621094</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.149999976158142</v>
+        <v>99.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>106.3399963378906</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1.129999995231628</v>
+        <v>99.58999633789062</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>106.3399963378906</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1399675</v>
+        <v>17134006</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>8.85</v>
+        <v>6.78</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
+          <t>RBA stock hits 52-week low at 83.55 USD By Investing.com - Investing.com India</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>The Goldman Sachs Group, Inc. $GS Shares Sold by RBA Wealth Management LLC - marketbeat.com</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Why RB Global (RBA) Stock Is Down Today - Quiver Quantitative</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>The Goldman Sachs Group, Inc. $GS Shares Sold by RBA Wealth Management LLC - marketbeat.com</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Lenexis pledges 14.84% RBA stake to fund INR 3,873 crore acquisition debt - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1704,61 +1688,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>AVALON.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>2059.39990234375</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>40.90000152587891</v>
+        <v>2258</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>2055.89990234375</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>2197.300048828125</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>37.0099983215332</v>
+        <v>2059.39990234375</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>2197.300048828125</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3327170</v>
+        <v>1136151</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+          <t>Avalon Technologies Share Price Today Near One-Year High - univest.in</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+          <t>98,730 Shares in The TJX Companies, Inc. $TJX Acquired by Avalon Trust Co - marketbeat.com</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - Univest</t>
+          <t>Avalon Technologies Ltd. Share Price at Fresh 52-Week High - univest.in</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - insider-gaming.com</t>
+          <t>Avalon Trust Co Buys Shares of 35,466 Thermo Fisher Scientific Inc. $TMO - marketbeat.com</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+          <t>Avalon Trust Co Purchases Shares of 8,734 The Travelers Companies, Inc. $TRV - marketbeat.com</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1869,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1893,68 +1877,64 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HARDWYN.NS</t>
+          <t>KRISHIVAL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>HARDWYN</t>
+          <t>KRISHIVAL</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.94999980926514</v>
+        <v>403</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11.10999965667725</v>
+        <v>403</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>8.800000190734863</v>
+        <v>350.6000061035156</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.420000076293945</v>
+        <v>355.75</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10.94999980926514</v>
+        <v>408.2999877929688</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.420000076293945</v>
+        <v>355.75</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>9633380</v>
+        <v>170859</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-13.97</v>
+        <v>-12.87</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Krishival Foods lists converted equity shares on NSE and BSE - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - Univest</t>
+          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Hardwyn India Ltd is Rated Sell - MarketsMojo</t>
-        </is>
-      </c>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1962,68 +1942,56 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL.NS</t>
+          <t>AHLUCONT.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>403</v>
+        <v>776</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>403</v>
+        <v>782.4000244140625</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>350.6000061035156</v>
+        <v>702.5</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>355.75</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>408.2999877929688</v>
+        <v>793.8499755859375</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>355.75</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>170799</v>
+        <v>545925</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-12.87</v>
+        <v>-10.85</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Krishival Foods lists converted equity shares on NSE and BSE - scanx.trade</t>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Krishival Foods utilizes ₹799.15 lakh of rights issue funds in Q4FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
-        </is>
-      </c>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2031,68 +1999,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NELCO.NS</t>
+          <t>THOMASCOTT.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NELCO</t>
+          <t>THOMASCOTT</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1092.300048828125</v>
+        <v>293</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1098</v>
+        <v>297.1499938964844</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>938.5999755859375</v>
+        <v>276</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>948.7999877929688</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1081.5</v>
+        <v>301.1000061035156</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>948.7999877929688</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2128333</v>
+        <v>360674</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-12.27</v>
+        <v>-7.41</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Nelco Share Price Falls over 12%: Why the $20 Million Elveo Investment Has Investors Worried - India Infoline</t>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Tata's Nelco shares tumble 12% on Tuesday after ₹1,120 peak - NewsBytes</t>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-18 — cnbctv:f2ab86df1094b:0 - TradingView</t>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Nelco invests $20 mn in US-based Elveo for satellite connectivity; shares fall 12% - Upstox</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Tata Group stock: Nelco zooms 108% from March low; hits 52-week high - Business Standard</t>
-        </is>
-      </c>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2100,48 +2064,40 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT.NS</t>
+          <t>MOIL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>776</v>
+        <v>271.2000122070312</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>782.4000244140625</v>
+        <v>271.7999877929688</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>702.5</v>
+        <v>255.6000061035156</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>707.7000122070312</v>
+        <v>257.25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>793.8499755859375</v>
+        <v>272.7999877929688</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>707.7000122070312</v>
+        <v>257.25</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>545834</v>
+        <v>2820394</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-10.85</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
-        </is>
-      </c>
+        <v>-5.7</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -2149,7 +2105,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2157,68 +2113,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PRAXIS.NS</t>
+          <t>APEX.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PRAXIS</t>
+          <t>APEX</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.039999961853027</v>
+        <v>424</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6.039999961853027</v>
+        <v>427.7999877929688</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.349999904632568</v>
+        <v>395.3999938964844</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5.400000095367432</v>
+        <v>398.5</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5.869999885559082</v>
+        <v>422.5499877929688</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.400000095367432</v>
+        <v>398.5</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>554400</v>
+        <v>944431</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-8.01</v>
+        <v>-5.69</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
+          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines stock hits 52-week high at 388.27 USD - Investing.com India</t>
+          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,840 Shares in Praxis Precision Medicines, Inc. $PRAX Purchased by Handelsbanken Fonder AB - MarketBeat</t>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - stocktitan.net</t>
+          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - univest.in</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2226,48 +2182,60 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL</t>
+          <t>ATALREAL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.5</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>14.94999980926514</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>13.90999984741211</v>
+        <v>31.42000007629395</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>13.9399995803833</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.14000034332275</v>
+        <v>35.84999847412109</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.9399995803833</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>7220</v>
+        <v>20814653</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
+        <v>-5.36</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Share Price Near ATH With Fundamental View - univest.in</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2275,64 +2243,60 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT.NS</t>
+          <t>MASTEK.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>293</v>
+        <v>1811</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>297.1499938964844</v>
+        <v>1811</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>276</v>
+        <v>1702</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>1717.5</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>301.1000061035156</v>
+        <v>1811.800048828125</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>1717.5</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>360673</v>
+        <v>103567</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.41</v>
+        <v>-5.2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+          <t>Mastek Ltd. Share Price Today: Price Fall and Fundamentals - univest.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+          <t>Mastek Ltd. Share Price Today: Price Fall and Fundamentals - univest.in</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
+          <t>Mastek fixes Aug 31 record date for ₹16 per share final dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2340,60 +2304,48 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL.NS</t>
+          <t>INDOTHAI.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>74</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>75.48999786376953</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>67.16000366210938</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.94000244140625</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>74.26000213623047</v>
+        <v>73.23000335693359</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>68.94000244140625</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>208024</v>
+        <v>20979</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-7.16</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
-        </is>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2401,37 +2353,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>RAMCOSYS.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>RAMCOSYS</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>263</v>
+        <v>593.0999755859375</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>266.3900146484375</v>
+        <v>598</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>240.5</v>
+        <v>564.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>244.25</v>
+        <v>564.5</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>262.8500061035156</v>
+        <v>594.2000122070312</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>244.25</v>
+        <v>564.5</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>54440</v>
+        <v>245543</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-7.08</v>
+        <v>-5</v>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -2442,7 +2394,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2450,64 +2402,48 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TARSONS.NS</t>
+          <t>ABANSENT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>TARSONS</t>
+          <t>ABANSENT</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>365</v>
+        <v>32.79000091552734</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>365</v>
+        <v>32.79000091552734</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>332</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>336.6499938964844</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>361.5</v>
+        <v>31.88999938964844</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>336.6499938964844</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1199280</v>
+        <v>28145</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-6.87</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
+        <v>-4.99</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2515,46 +2451,46 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER.NS</t>
+          <t>SUMEETINDS.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>296</v>
+        <v>14.14000034332275</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>296</v>
+        <v>14.27999973297119</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>270</v>
+        <v>13.38000011444092</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>277.7000122070312</v>
+        <v>13.42000007629395</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>297.7000122070312</v>
+        <v>14.07999992370605</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>277.7000122070312</v>
+        <v>13.42000007629395</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>10586</v>
+        <v>4474212</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.72</v>
+        <v>-4.69</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
@@ -2564,7 +2500,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2572,56 +2508,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>LPDC.NS</t>
+          <t>ARVIND.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>LPDC</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7.860000133514404</v>
+        <v>554.4500122070312</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7.860000133514404</v>
+        <v>555.2000122070312</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>7.25</v>
+        <v>522.5999755859375</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>7.380000114440918</v>
+        <v>526.5</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7.869999885559082</v>
+        <v>552.2999877929688</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.380000114440918</v>
+        <v>526.5</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>96741</v>
+        <v>928757</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.23</v>
+        <v>-4.67</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
+          <t>Arvind SmartSpaces submits FY26 business responsibility report - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Arvind SmartSpaces submits FY26 business responsibility report - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Arvind posts strong Q1 2026 growth, shares slip - Investing.com</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Arvind sees no immediate acquisitions, focuses on Dalco GFT integration - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Rubrik CTO Arvind Nithrakashyap Sells $3.0 Million Stock - fool.com</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2629,40 +2577,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>JUBLCPL.NS</t>
+          <t>SHRIKRISH.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>JUBLCPL</t>
+          <t>SHRIKRISH</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2362.39990234375</v>
+        <v>38.54999923706055</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2397.89990234375</v>
+        <v>38.97000122070312</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2142</v>
+        <v>38</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2199.10009765625</v>
+        <v>38.45999908447266</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2342.39990234375</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2199.10009765625</v>
+        <v>38.45999908447266</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>16482</v>
+        <v>709</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-6.12</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+        <v>-4.57</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Shri Krishna Devcon Ltd. Share Price Fall and Stock Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Shri Krishna Devcon Ltd. Share Price Fall and Stock Analysis - univest.in</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -2670,7 +2626,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2678,48 +2634,40 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SIGIND.NS</t>
+          <t>ASIANTILES.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>70.84999847412109</v>
+        <v>47.97000122070312</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>71.5</v>
+        <v>47.97000122070312</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>65.31999969482422</v>
+        <v>45.5</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>66.84999847412109</v>
+        <v>45.81000137329102</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>71.15000152587891</v>
+        <v>47.97000122070312</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>66.84999847412109</v>
+        <v>45.81000137329102</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>95414</v>
+        <v>9346225</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-6.04</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
-        </is>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -2727,7 +2675,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2735,48 +2683,60 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NDLVENTURE.NS</t>
+          <t>SBICARD.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>122.1500015258789</v>
+        <v>642</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>122.7399978637695</v>
+        <v>643.1500244140625</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>113.9499969482422</v>
+        <v>613.9000244140625</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>116.1699981689453</v>
+        <v>615</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>123.5599975585938</v>
+        <v>641.75</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>116.1699981689453</v>
+        <v>615</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>57175</v>
+        <v>2769735</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
+        <v>-4.17</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>SBICARD Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>SBI Cards And Payment Services Ltd. (SBICARD) Share Price Falls 3.35%: Price Action, Sector and Peer Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>SBI Cards And Payment Services Ltd. (SBICARD) Share Price Falls 3.35%: Price Action, Sector and Peer Analysis - univest.in</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2784,40 +2744,48 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MOIL.NS</t>
+          <t>INOXWIND.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>271.2000122070312</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>271.7999877929688</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>255.6000061035156</v>
+        <v>74.69000244140625</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>257.25</v>
+        <v>74.94999694824219</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>272.7999877929688</v>
+        <v>78.12999725341797</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>257.25</v>
+        <v>74.94999694824219</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2810988</v>
+        <v>18198825</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+        <v>-4.07</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Inox Wind Limited (NSE:INOXWIND) Analysts Just Slashed This Year's Estimates - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Inox Wind Limited (NSE:INOXWIND) Analysts Just Slashed This Year's Estimates - simplywall.st</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -2825,7 +2793,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2833,68 +2801,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>APEX.NS</t>
+          <t>HMAAGRO.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>APEX</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>424</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>427.7999877929688</v>
+        <v>24</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>395.3999938964844</v>
+        <v>21.93000030517578</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>398.5</v>
+        <v>22.02000045776367</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>422.5499877929688</v>
+        <v>22.95000076293945</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>398.5</v>
+        <v>22.02000045776367</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>944026</v>
+        <v>9306605</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.69</v>
+        <v>-4.05</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+          <t>HMA Agro Industries Ltd. Share Price Rise: Price Analysis - univest.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+          <t>HMA Agro Industries Ltd. Share Price Rise: Price Analysis - univest.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
+          <t>HMA Agro Publishes Investor Presentation for June 2026 Quarter - TipRanks</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - Univest</t>
-        </is>
-      </c>
+          <t>HMA Agro Industries Releases Q1 FY2026 Investor Presentation - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2902,68 +2866,48 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AGL.NS</t>
+          <t>MANCREDIT.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>AGL</t>
+          <t>MANCREDIT</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14</v>
+        <v>242.5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>243.6999969482422</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13.02999973297119</v>
+        <v>225</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>13.25</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>236.7299957275391</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13.25</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3444947</v>
+        <v>169721</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.42</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - businesstoday.in</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Why is AGL Energy stock surging today? - Investing.com</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Agilon Health Inc (AGL) Stock Up 9.0% but GF Value Says Overvalued -- GF Score: 71/100 - GuruFocus</t>
-        </is>
-      </c>
+        <v>-4.02</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2971,60 +2915,48 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>AAREYDRUGS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36.09999847412109</v>
+        <v>83.01000213623047</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>36.33000183105469</v>
+        <v>85.45999908447266</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>31.42000007629395</v>
+        <v>81.30999755859375</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>82.16000366210938</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>35.84999847412109</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>82.16000366210938</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>20786651</v>
+        <v>668238</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.36</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech Share Price Near ATH With Fundamental View - Univest</t>
-        </is>
-      </c>
+        <v>-4</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:38</t>
+          <t>2026-08-19 08:56:49</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3032,40 +2964,48 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>NDGL.NS</t>
+          <t>KSHITIJPOL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>NDGL</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2875</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2875</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2669</v>
+        <v>2.880000114440918</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2727.89990234375</v>
+        <v>2.910000085830688</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2878.699951171875</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2727.89990234375</v>
+        <v>2.910000085830688</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>558</v>
+        <v>2109693</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.24</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+        <v>-3.96</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Kshitij Polyline launches Rs 29.3 crore rights issue to bolster equity base - TipRanks</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Kshitij Polyline launches Rs 29.3 crore rights issue to bolster equity base - TipRanks</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -438,15 +438,15 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,46 +553,46 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SIGACHI.NS</t>
+          <t>MYSORPETRO.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SIGACHI</t>
+          <t>MYSORPETRO</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25.90999984741211</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.09000015258789</v>
+        <v>137.9100036621094</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.90999984741211</v>
+        <v>116</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>29.61000061035156</v>
+        <v>137.9100036621094</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26.35000038146973</v>
+        <v>114.9300003051758</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>29.61000061035156</v>
+        <v>137.9100036621094</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>10361044</v>
+        <v>68040</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>12.37</v>
+        <v>19.99</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -610,37 +610,37 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>JINDRILL.NS</t>
+          <t>TECILCHEM.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>TECILCHEM</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>587.0999755859375</v>
+        <v>8.75</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>673.5499877929688</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>587.0999755859375</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>651.1500244140625</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>586.2000122070312</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>651.1500244140625</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>17885822</v>
+        <v>80792</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>11.08</v>
+        <v>19.91</v>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
@@ -651,7 +651,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -659,40 +659,48 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA.NS</t>
+          <t>EXCELINDUS.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11.32999992370605</v>
+        <v>991.0499877929688</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>12.98999977111816</v>
+        <v>1148.550048828125</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10.97999954223633</v>
+        <v>990.9000244140625</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>1133.25</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11.35999965667725</v>
+        <v>985.2000122070312</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>1133.25</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>25170295</v>
+        <v>1055759</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+        <v>15.03</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Excel Industries Ltd. Share Price Update: Price Action View - univest.in</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Excel Industries Ltd. Share Price Update: Price Action View - univest.in</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -700,7 +708,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -708,64 +716,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>REGAAL.NS</t>
+          <t>KAMANWALA.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>REGAAL</t>
+          <t>KAMANWALA</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>90.27999877929688</v>
+        <v>19.3799991607666</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>101.5</v>
+        <v>19.51000022888184</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>88.65000152587891</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>99.52999877929688</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>90.45999908447266</v>
+        <v>16.26000022888184</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>99.52999877929688</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2975990</v>
+        <v>474236</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>10.03</v>
+        <v>14.58</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - univest.in</t>
+          <t>Volume Gainers on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - univest.in</t>
+          <t>Volume Gainers on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
+          <t>Most Active Equities on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Lalithaa Jewellery Mart IPO Day 3 Subscription Status: Issue Booked 6.84x so Far - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -773,68 +785,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM.NS</t>
+          <t>KOHINOOR.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>910</v>
+        <v>27.8799991607666</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>952.75</v>
+        <v>32.72999954223633</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>905</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>952.75</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>866.1500244140625</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>952.75</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>10246021</v>
+        <v>1432482</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>10</v>
+        <v>14.04</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+          <t>Kohinoor Foods Ltd Locks at Upper Circuit With 20% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>INDOMIM Historical Data - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Stocks to watch, August 18: GMR Airports, Oberoi Realty, Paytm, Nelco, INDO-MIM, Netweb Technologies - Upstox</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
-        </is>
-      </c>
+          <t>Kohinoor Foods Ltd Locks at Upper Circuit With 20% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -842,56 +842,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BI.NS</t>
+          <t>ZAGGLE.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>94</v>
+        <v>187.3999938964844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>194.6999969482422</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>180</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>186.0399932861328</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>92.16999816894531</v>
+        <v>165.8800048828125</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>101.379997253418</v>
+        <v>186.0399932861328</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>523283</v>
+        <v>39145837</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>9.99</v>
+        <v>12.15</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+          <t>Zaggle rebounds 26% from Tuesday's low on heavy volumes; here's why - Business Standard</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Vijay Kedia's Kedia Securities acquires stake in AI-led SaaS fintech Zaggle Prepaid, stock surges more than 17% on NSE - TradingView</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>YC Holdings sells Rs 1,435 crore Groww stake; Vijay Kedia firm buys 1.48% in Zaggle Prepaid - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Vijay Kedia buys Rs 33 crore stake in Zaggle Prepaid Ocean Services via bulk deal, stock skyrockets 17% - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Ocean Services Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -899,46 +911,46 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>NITINSPIN.NS</t>
+          <t>SONAMLTD.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>SONAMLTD</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>556.75</v>
+        <v>62.29999923706055</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>610</v>
+        <v>68.98999786376953</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>554.5</v>
+        <v>60.7400016784668</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>606.9000244140625</v>
+        <v>67.19000244140625</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>553.75</v>
+        <v>60.31000137329102</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>606.9000244140625</v>
+        <v>67.19000244140625</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3703991</v>
+        <v>964817</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>9.6</v>
+        <v>11.41</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
+          <t>Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
+          <t>Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
@@ -948,7 +960,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -956,68 +968,48 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ABCOTS.NS</t>
+          <t>LAXMICOT.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ABCOTS</t>
+          <t>LAXMICOT</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>202.4799957275391</v>
+        <v>13.75</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>225</v>
+        <v>16.14999961853027</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>201.8800048828125</v>
+        <v>13.5</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>217.3999938964844</v>
+        <v>14.89000034332275</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>199.6600036621094</v>
+        <v>13.46000003814697</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>217.3999938964844</v>
+        <v>14.89000034332275</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>152579</v>
+        <v>357640</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - univest.in</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - univest.in</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>ABCOTS Share Price Today - AB Cotspin on NSE/BSE - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - univest.in</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
-        </is>
-      </c>
+        <v>10.62</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1025,68 +1017,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>NILKAMAL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>NILKAMAL</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>1848.699951171875</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>40.90000152587891</v>
+        <v>2105</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>1832.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>2033.800048828125</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>37.0099983215332</v>
+        <v>1846.699951171875</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>2033.800048828125</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3330020</v>
+        <v>1423712</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>10.13</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - univest.in</t>
+          <t>Nilkamal Ltd Upgraded to Buy on Improved Technicals and Valuation - MarketsMojo</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+          <t>Nilkamal Ltd Surges 8.0% to Day's High of Rs 1970 — Outperforms Sector by 7.27 Percentage Points - MarketsMojo</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - univest.in</t>
+          <t>Nilkamal Ltd Technical Momentum Shifts Signal Bullish Outlook Amid Market Volatility - MarketsMojo</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - univest.in</t>
+          <t>Nilkamal Ltd Upgraded to Buy by MarketsMOJO on Strong Financial and Technical Grounds - MarketsMojo</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - Insider Gaming</t>
+          <t>Nilkamal Ltd Surges 8.0% to Day's High of Rs 1970 — Outperforms Sector by 7.27 Percentage Points - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1094,68 +1086,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA.NS</t>
+          <t>MANBRO.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>MANBRO</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>517.7000122070312</v>
+        <v>53</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>565</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>509</v>
+        <v>52.79999923706055</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>562.0499877929688</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>518.75</v>
+        <v>53.09999847412109</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>562.0499877929688</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>705436</v>
+        <v>132482</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8.35</v>
+        <v>10</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+          <t>Total common shares outstanding of KD Green Industries Limited – NSE:MANBRO - TradingView</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+          <t>Total common shares outstanding of KD Green Industries Limited – NSE:MANBRO - TradingView</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>eMudhra Ltd. Share Price Today - eMudhra Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>eMudhra shares surge as police close 3i Infotech's fraud complaint - Whalesbook</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
-        </is>
-      </c>
+          <t>Manbro Ind Q1 Results FY27: Revenue Rs 34 crore, Net Profit Rs 3 Crore - univest.in</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1163,60 +1147,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>MILKYMIST.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>870</v>
+        <v>190</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>947.9000244140625</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>860.0499877929688</v>
+        <v>190</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>929.2000122070312</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>857.9500122070312</v>
+        <v>181.5</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>929.2000122070312</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>5438972</v>
+        <v>27974362</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Indian Export Stocks Retail Investors May Watch As US Scrutiny Of Transshipment Grows - simplywall.st</t>
+          <t>Milky Mist shares make decent market debut at 18% premium; should you buy, sell or hold? - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>Milky Mist Dairy Food Limited: Target Price Consensus and Analysts Recommendations | MILKYMIST | INE00IT01020 - marketscreener.com</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Milky Mist IPO Listing: Shares Debut at ₹165, Gain 18%; Stock Rises 29.64% From Issue Price - India Infoline</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Milky Mist share price up 30% after IPO listing: Should investors hold or book profits? - India Today</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Milky Mist Share Price Hits 10% Upper Circuit After Strong Listing. Should Investors Buy, Sell Or Hold? - NDTV Profit</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1224,56 +1216,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA.NS</t>
+          <t>SIEL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>SIEL</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2755.800048828125</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2989</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2755.800048828125</v>
+        <v>39.38999938964844</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2959</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2741.39990234375</v>
+        <v>38.56999969482422</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2959</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4188005</v>
+        <v>13463</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>7.94</v>
+        <v>9.98</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1281,40 +1277,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>KPEL.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>KPEL</t>
+          <t>BAJAJHIND</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>243.6999969482422</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>264.9500122070312</v>
+        <v>21.28000068664551</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>240</v>
+        <v>18.54000091552734</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>262.2999877929688</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>243.75</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>262.2999877929688</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>859476</v>
+        <v>176267431</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+        <v>9.57</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1322,7 +1326,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1330,64 +1334,48 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>MMFL.NS</t>
+          <t>TPHQ.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MMFL</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>639.7000122070312</v>
+        <v>0.6499999761581421</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>687.9500122070312</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>632.7999877929688</v>
+        <v>0.6100000143051147</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>680.2000122070312</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>632.2999877929688</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>680.2000122070312</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>935497</v>
+        <v>23477345</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - univest.in</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - univest.in</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>MM Forgings Clarifies ₹56.25 Crore Exceptional Gain from Oragadam Land Sale - TipRanks</t>
-        </is>
-      </c>
+        <v>9.52</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1395,40 +1383,48 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS.NS</t>
+          <t>RPEL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>266.0499877929688</v>
+        <v>1500</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>289</v>
+        <v>1665</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>264</v>
+        <v>1500</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>286.25</v>
+        <v>1637.400024414062</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>266.3999938964844</v>
+        <v>1495.199951171875</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>286.25</v>
+        <v>1637.400024414062</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2789751</v>
+        <v>375042</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+        <v>9.51</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - univest.in</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - univest.in</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -1436,7 +1432,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1444,40 +1440,48 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD.NS</t>
+          <t>HEALTHX.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>HEALTHX</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>658.1500244140625</v>
+        <v>288</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>709</v>
+        <v>327.8999938964844</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>655</v>
+        <v>286.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>701.5499877929688</v>
+        <v>313.7000122070312</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>653.2000122070312</v>
+        <v>288.5</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>701.5499877929688</v>
+        <v>313.7000122070312</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1266456</v>
+        <v>8983</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+        <v>8.73</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Sastasundar Ventures Ltd. Share Price Rise: Key Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Sastasundar Ventures Ltd. Share Price Rise: Key Analysis - univest.in</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -1485,7 +1489,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1493,68 +1497,56 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RITCO.NS</t>
+          <t>AVROIND.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>RITCO</t>
+          <t>AVROIND</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>288.0499877929688</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>318.3999938964844</v>
+        <v>9.829999923706055</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>288.0499877929688</v>
+        <v>8.420000076293945</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>313</v>
+        <v>9.539999961853027</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>292.5</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>313</v>
+        <v>9.539999961853027</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>381642</v>
+        <v>1242003</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.01</v>
+        <v>8.41</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Ritco Logistics Ltd. (RITCO) Share Price Today: Price Action Analysis - univest.in</t>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - univest.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Ritco Logistics Ltd. (RITCO) Share Price Today: Price Action Analysis - univest.in</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Ritco Logistics Q1 Results: Unaudited financials published - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Ritco Logistics consolidated net profit declines 43.36% in the June 2026 quarter - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Ritco Logistics Q1 Results FY27: PAT Rs 3 Cr, Revenue Rs 365 cror - univest.in</t>
-        </is>
-      </c>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - univest.in</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1562,46 +1554,46 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SGMART.NS</t>
+          <t>DCMSIL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>DCMSIL</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>750.6500244140625</v>
+        <v>70</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>809</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>744</v>
+        <v>68.01999664306641</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>804.9500122070312</v>
+        <v>74.58000183105469</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>752.2999877929688</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>804.9500122070312</v>
+        <v>74.58000183105469</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>907346</v>
+        <v>144562</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7</v>
+        <v>8.18</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SG Mart Share Price at Fresh 52-Week High: Full Analysis - univest.in</t>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>SG Mart Share Price at Fresh 52-Week High: Full Analysis - univest.in</t>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
@@ -1611,7 +1603,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1619,68 +1611,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RBA.NS</t>
+          <t>DWARKESH.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>99.80000305175781</v>
+        <v>44.86000061035156</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>108.4100036621094</v>
+        <v>50.04999923706055</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>99.5</v>
+        <v>44.56000137329102</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>106.3399963378906</v>
+        <v>48.27999877929688</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>99.58999633789062</v>
+        <v>44.63999938964844</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>106.3399963378906</v>
+        <v>48.27999877929688</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>17134006</v>
+        <v>9610957</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6.78</v>
+        <v>8.15</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>RBA stock hits 52-week low at 83.55 USD By Investing.com - Investing.com India</t>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc. $GS Shares Sold by RBA Wealth Management LLC - marketbeat.com</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Why RB Global (RBA) Stock Is Down Today - Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>The Goldman Sachs Group, Inc. $GS Shares Sold by RBA Wealth Management LLC - marketbeat.com</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Lenexis pledges 14.84% RBA stake to fund INR 3,873 crore acquisition debt - scanx.trade</t>
-        </is>
-      </c>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1688,63 +1668,43 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>AVALON.NS</t>
+          <t>BLUSPRING.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>BLUSPRING</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2059.39990234375</v>
+        <v>111.25</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2258</v>
+        <v>120.7600021362305</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2055.89990234375</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2197.300048828125</v>
+        <v>119.8600006103516</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2059.39990234375</v>
+        <v>111.2099990844727</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2197.300048828125</v>
+        <v>119.8600006103516</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1136151</v>
+        <v>872655</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Avalon Technologies Share Price Today Near One-Year High - univest.in</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>98,730 Shares in The TJX Companies, Inc. $TJX Acquired by Avalon Trust Co - marketbeat.com</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Avalon Technologies Ltd. Share Price at Fresh 52-Week High - univest.in</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Avalon Trust Co Buys Shares of 35,466 Thermo Fisher Scientific Inc. $TMO - marketbeat.com</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Avalon Trust Co Purchases Shares of 8,734 The Travelers Companies, Inc. $TRV - marketbeat.com</t>
-        </is>
-      </c>
+        <v>7.78</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1869,7 +1829,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1877,64 +1837,48 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL.NS</t>
+          <t>KJMCFIN.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>KJMCFIN</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>403</v>
+        <v>61.9900016784668</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>403</v>
+        <v>61.9900016784668</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>350.6000061035156</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>355.75</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>408.2999877929688</v>
+        <v>61.9900016784668</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>355.75</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>170859</v>
+        <v>322</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-12.87</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Krishival Foods lists converted equity shares on NSE and BSE - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
-        </is>
-      </c>
+        <v>-10.71</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1942,56 +1886,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT.NS</t>
+          <t>YASHO.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>YASHO</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>776</v>
+        <v>4910</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>782.4000244140625</v>
+        <v>4911.2001953125</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>702.5</v>
+        <v>4411.60009765625</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>707.7000122070312</v>
+        <v>4470.7998046875</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>793.8499755859375</v>
+        <v>4915.7998046875</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>707.7000122070312</v>
+        <v>4470.7998046875</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>545925</v>
+        <v>167699</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-10.85</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>183.68% Stock Return, 372.3% Profit Growth: What's Driving Yasho Industries Ltd's Multibagger Rerating? - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1999,56 +1955,56 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT.NS</t>
+          <t>AAKASH.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT</t>
+          <t>AAKASH</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>293</v>
+        <v>9.130000114440918</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>297.1499938964844</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>276</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>8.449999809265137</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>301.1000061035156</v>
+        <v>9.130000114440918</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>8.449999809265137</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>360674</v>
+        <v>719753</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.41</v>
+        <v>-7.45</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+          <t>Aakash Explorat Standalone June 2026 Net Sales at Rs 27.89 crore, up 16.93% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+          <t>Aakash Explorat Standalone June 2026 Net Sales at Rs 27.89 crore, up 16.93% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+          <t>If you have a genius like Jasprit Bumrah, and if his body needs some rest, why would you play him? Aakash Chopra on star pacer's workload - CricTracker</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+          <t>Aakash Exploration Promoters Reshuffle Holdings via Exempt Share Transfer - TipRanks</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -2056,7 +2012,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2064,40 +2020,48 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MOIL.NS</t>
+          <t>INDSWFTLAB.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>271.2000122070312</v>
+        <v>347.4700012207031</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>271.7999877929688</v>
+        <v>348</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>255.6000061035156</v>
+        <v>320.0499877929688</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>257.25</v>
+        <v>322.0599975585938</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>272.7999877929688</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>257.25</v>
+        <v>322.0599975585938</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2820394</v>
+        <v>1534549</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+        <v>-7.15</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -2105,7 +2069,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2113,68 +2077,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>APEX.NS</t>
+          <t>CGVAK.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>APEX</t>
+          <t>CGVAK</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>424</v>
+        <v>151.2400054931641</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>427.7999877929688</v>
+        <v>151.2400054931641</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>395.3999938964844</v>
+        <v>136.6199951171875</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>398.5</v>
+        <v>140.7299957275391</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>422.5499877929688</v>
+        <v>151.2400054931641</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>398.5</v>
+        <v>140.7299957275391</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>944431</v>
+        <v>508</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-5.69</v>
+        <v>-6.95</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
+          <t>Average basic shares outstanding of CG-VAK Software &amp; Exports Ltd. – NSE:CGVAK - TradingView</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - univest.in</t>
-        </is>
-      </c>
+          <t>Average basic shares outstanding of CG-VAK Software &amp; Exports Ltd. – NSE:CGVAK - TradingView</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2182,60 +2134,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>ANTELOPUS.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>36.09999847412109</v>
+        <v>863</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>36.33000183105469</v>
+        <v>863</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>31.42000007629395</v>
+        <v>793.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>798.3499755859375</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>35.84999847412109</v>
+        <v>856.5499877929688</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>798.3499755859375</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>20814653</v>
+        <v>209718</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5.36</v>
+        <v>-6.79</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
+          <t>Antelopus Selan Energy Ltd Surges 7.14% to Day's High of Rs 857.5 — Outperforms Sector by 6.12 Percentage Points - MarketsMojo</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Atal Realtech Share Price Near ATH With Fundamental View - univest.in</t>
-        </is>
-      </c>
+          <t>Antelopus Selan Energy Ltd Surges 7.14% to Day's High of Rs 857.5 — Outperforms Sector by 6.12 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2243,60 +2191,56 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MASTEK.NS</t>
+          <t>MEDICAPQ.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>MEDICAPQ</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1811</v>
+        <v>26.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1811</v>
+        <v>27.45000076293945</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1702</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1717.5</v>
+        <v>23.55999946594238</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1811.800048828125</v>
+        <v>25.04999923706055</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1717.5</v>
+        <v>23.55999946594238</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>103567</v>
+        <v>2778</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.2</v>
+        <v>-5.95</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Mastek Ltd. Share Price Today: Price Fall and Fundamentals - univest.in</t>
+          <t>Medi-Caps Ltd. Financial Statements – NSE:MEDICAPQ - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Mastek Ltd. Share Price Today: Price Fall and Fundamentals - univest.in</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Mastek fixes Aug 31 record date for ₹16 per share final dividend - scanx.trade</t>
-        </is>
-      </c>
+          <t>Medi-Caps Ltd. Financial Statements – NSE:MEDICAPQ - TradingView</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2304,37 +2248,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>BHARATSE.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>240.9100036621094</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>240.9100036621094</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>224.9900054931641</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>227.1900024414062</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>73.23000335693359</v>
+        <v>240.9100036621094</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>227.1900024414062</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>20979</v>
+        <v>440887</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5</v>
+        <v>-5.7</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
@@ -2345,7 +2289,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2353,37 +2297,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>RAMCOSYS.NS</t>
+          <t>MALUPAPER.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>MALUPAPER</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>593.0999755859375</v>
+        <v>32.20000076293945</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>598</v>
+        <v>32.20000076293945</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>564.5</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>564.5</v>
+        <v>30.81999969482422</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>594.2000122070312</v>
+        <v>32.58000183105469</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>564.5</v>
+        <v>30.81999969482422</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>245543</v>
+        <v>61691</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5</v>
+        <v>-5.4</v>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -2394,7 +2338,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2402,40 +2346,48 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ABANSENT.NS</t>
+          <t>UEL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ABANSENT</t>
+          <t>UEL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>32.79000091552734</v>
+        <v>200.8000030517578</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>32.79000091552734</v>
+        <v>200.8000030517578</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30.29999923706055</v>
+        <v>200.8000030517578</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>30.29999923706055</v>
+        <v>200.8000030517578</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.88999938964844</v>
+        <v>211.3600006103516</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>30.29999923706055</v>
+        <v>200.8000030517578</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>28145</v>
+        <v>4624</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.99</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -2443,7 +2395,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2451,48 +2403,40 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>INDOTHAI.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>INDOTHAI</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14.14000034332275</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>14.27999973297119</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>13.38000011444092</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>13.42000007629395</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>14.07999992370605</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13.42000007629395</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>4474212</v>
+        <v>42916</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
-        </is>
-      </c>
+        <v>-4.99</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -2500,7 +2444,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2508,68 +2452,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ARVIND.NS</t>
+          <t>ONIXSOLAR.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>ONIXSOLAR</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>554.4500122070312</v>
+        <v>338.8500061035156</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>555.2000122070312</v>
+        <v>338.8500061035156</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>522.5999755859375</v>
+        <v>338.8500061035156</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>526.5</v>
+        <v>338.8500061035156</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>552.2999877929688</v>
+        <v>356.6499938964844</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>526.5</v>
+        <v>338.8500061035156</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>928757</v>
+        <v>5926</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.67</v>
+        <v>-4.99</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Arvind SmartSpaces submits FY26 business responsibility report - scanx.trade</t>
+          <t>Total common shares outstanding of Onix Solar Energy Ltd. – NSE:ONIXSOLAR - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Arvind SmartSpaces submits FY26 business responsibility report - scanx.trade</t>
+          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Arvind posts strong Q1 2026 growth, shares slip - Investing.com</t>
+          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Arvind sees no immediate acquisitions, focuses on Dalco GFT integration - CNBC TV18</t>
+          <t>Onix Solar Energy shares permitted to trade on NSE from August 17 - scanx.trade</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Rubrik CTO Arvind Nithrakashyap Sells $3.0 Million Stock - fool.com</t>
+          <t>Onix Solar Energy Ltd - Equitypandit</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2577,46 +2521,46 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SHRIKRISH.NS</t>
+          <t>SUMEETINDS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SHRIKRISH</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>38.54999923706055</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>38.97000122070312</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>38</v>
+        <v>12.75</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>38.45999908447266</v>
+        <v>12.75</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>13.42000007629395</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>38.45999908447266</v>
+        <v>12.75</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>709</v>
+        <v>3255667</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.57</v>
+        <v>-4.99</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Shri Krishna Devcon Ltd. Share Price Fall and Stock Analysis - univest.in</t>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Shri Krishna Devcon Ltd. Share Price Fall and Stock Analysis - univest.in</t>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -2626,7 +2570,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2634,40 +2578,48 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ASIANTILES.NS</t>
+          <t>KEEPLEARN.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>KEEPLEARN</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>47.97000122070312</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>47.97000122070312</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>45.5</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45.81000137329102</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>47.97000122070312</v>
+        <v>2.009999990463257</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>45.81000137329102</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>9346225</v>
+        <v>50562</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+        <v>-4.98</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -2675,7 +2627,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2683,60 +2635,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SBICARD.NS</t>
+          <t>RBA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>642</v>
+        <v>104.5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>643.1500244140625</v>
+        <v>104.5999984741211</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>613.9000244140625</v>
+        <v>99.5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>615</v>
+        <v>101.0599975585938</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>641.75</v>
+        <v>106.3399963378906</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>615</v>
+        <v>101.0599975585938</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2769735</v>
+        <v>12913965</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.17</v>
+        <v>-4.97</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>SBICARD Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+          <t>RBA stock hits 52-week low at 83.55 USD By Investing.com - Investing.com India</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>SBI Cards And Payment Services Ltd. (SBICARD) Share Price Falls 3.35%: Price Action, Sector and Peer Analysis - univest.in</t>
+          <t>ANZ Stock And 2 Australian Bank Shares Facing the Next RBA Rate Test - simplywall.st</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>SBI Cards And Payment Services Ltd. (SBICARD) Share Price Falls 3.35%: Price Action, Sector and Peer Analysis - univest.in</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>RB Global Inc (RBA) Stock Up 4.5% and Still Undervalued -- GF Sc - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>ANZ Stock And 2 Australian Bank Shares Facing the Next RBA Rate Test - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Why RB Global (RBA) Stock Is Down Today - Quiver Quantitative</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2744,56 +2704,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>INOXWIND.NS</t>
+          <t>POWERICA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>POWERICA</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>78</v>
+        <v>562.7999877929688</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>78.19000244140625</v>
+        <v>562.7999877929688</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>74.69000244140625</v>
+        <v>530.2999877929688</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>74.94999694824219</v>
+        <v>532.8499755859375</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>78.12999725341797</v>
+        <v>560.6500244140625</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>74.94999694824219</v>
+        <v>532.8499755859375</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>18198825</v>
+        <v>218225</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.07</v>
+        <v>-4.96</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Inox Wind Limited (NSE:INOXWIND) Analysts Just Slashed This Year's Estimates - simplywall.st</t>
+          <t>Powerica Ltd. Share Price Today - Powerica Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Inox Wind Limited (NSE:INOXWIND) Analysts Just Slashed This Year's Estimates - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t>Powerica schedules virtual analyst meet on August 21 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>POWERICA Share Price Today - Powerica Ltd. Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Powerica schedules virtual analyst meet on August 21 - scanx.trade</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2801,64 +2769,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>HMAAGRO.NS</t>
+          <t>CESC.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>22.89999961853027</v>
+        <v>162</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>24</v>
+        <v>162.2599945068359</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>21.93000030517578</v>
+        <v>158.5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>22.02000045776367</v>
+        <v>159.6600036621094</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.95000076293945</v>
+        <v>167.9799957275391</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22.02000045776367</v>
+        <v>159.6600036621094</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>9306605</v>
+        <v>2881453</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.05</v>
+        <v>-4.95</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>HMA Agro Industries Ltd. Share Price Rise: Price Analysis - univest.in</t>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - businesstoday.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>HMA Agro Industries Ltd. Share Price Rise: Price Analysis - univest.in</t>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - businesstoday.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>HMA Agro Publishes Investor Presentation for June 2026 Quarter - TipRanks</t>
+          <t>CESC Limited Earnings Missed Analyst Estimates: Here's What Analysts Are Forecasting Now - simplywall.st</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>HMA Agro Industries Releases Q1 FY2026 Investor Presentation - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Stocks to Watch Today: PB Fintech, Juniper Green, CESC, Dr Reddys Labs, Texmaco Rail, Voltas,... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>CESC Ltd soars 1.23% - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2866,37 +2838,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>MANCREDIT.NS</t>
+          <t>ADROITINFO.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MANCREDIT</t>
+          <t>ADROITINFO</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>242.5</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>243.6999969482422</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>225</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>227.2100067138672</v>
+        <v>9.850000381469727</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>236.7299957275391</v>
+        <v>10.35999965667725</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>227.2100067138672</v>
+        <v>9.850000381469727</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>169721</v>
+        <v>19995</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.02</v>
+        <v>-4.92</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
@@ -2907,7 +2879,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2915,37 +2887,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>AAREYDRUGS.NS</t>
+          <t>WEBELSOLAR.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>83.01000213623047</v>
+        <v>86.93000030517578</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>85.45999908447266</v>
+        <v>87.12000274658203</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>81.30999755859375</v>
+        <v>82.58999633789062</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>82.16000366210938</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>85.58000183105469</v>
+        <v>86.93000030517578</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>82.16000366210938</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>668238</v>
+        <v>2433185</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4</v>
+        <v>-4.84</v>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
@@ -2956,7 +2928,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:49</t>
+          <t>2026-08-19 16:27:02</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2964,46 +2936,46 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL.NS</t>
+          <t>PLAZACABLE.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3.039999961853027</v>
+        <v>51.5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>3.089999914169312</v>
+        <v>53.02000045776367</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2.880000114440918</v>
+        <v>49.77000045776367</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2.910000085830688</v>
+        <v>49.86000061035156</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3.029999971389771</v>
+        <v>52.38000106811523</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.910000085830688</v>
+        <v>49.86000061035156</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2109693</v>
+        <v>75805</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.96</v>
+        <v>-4.81</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline launches Rs 29.3 crore rights issue to bolster equity base - TipRanks</t>
+          <t>Here's Why We Think Plaza Wires (NSE:PLAZACABLE) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline launches Rs 29.3 crore rights issue to bolster equity base - TipRanks</t>
+          <t>Here's Why We Think Plaza Wires (NSE:PLAZACABLE) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -446,7 +446,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,48 +553,40 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO.NS</t>
+          <t>EXCELINDUS.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO</t>
+          <t>EXCELINDUS</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>116</v>
+        <v>991.0499877929688</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>137.9100036621094</v>
+        <v>1148.550048828125</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>116</v>
+        <v>990.9000244140625</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>137.9100036621094</v>
+        <v>1133.25</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>114.9300003051758</v>
+        <v>985.2000122070312</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>137.9100036621094</v>
+        <v>1133.25</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>68040</v>
+        <v>1055831</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
-        </is>
-      </c>
+        <v>15.03</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -602,7 +594,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -610,40 +602,48 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM.NS</t>
+          <t>KOHINOOR.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM</t>
+          <t>KOHINOOR</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8.75</v>
+        <v>27.8799991607666</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>10.23999977111816</v>
+        <v>32.72999954223633</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8.350000381469727</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.23999977111816</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8.539999961853027</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10.23999977111816</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>80792</v>
+        <v>1434186</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+        <v>14.04</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -651,7 +651,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -659,56 +659,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EXCELINDUS.NS</t>
+          <t>ZAGGLE.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>991.0499877929688</v>
+        <v>187.3999938964844</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1148.550048828125</v>
+        <v>194.6999969482422</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>990.9000244140625</v>
+        <v>180</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1133.25</v>
+        <v>186.0399932861328</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>985.2000122070312</v>
+        <v>165.8800048828125</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1133.25</v>
+        <v>186.0399932861328</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1055759</v>
+        <v>39149680</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>15.03</v>
+        <v>12.15</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Excel Industries Ltd. Share Price Update: Price Action View - univest.in</t>
+          <t>Vijay Kedia buys Rs 33 crore stake in Zaggle Prepaid Ocean Services via bulk deal, stock skyrockets 17% - economictimes.com</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Excel Industries Ltd. Share Price Update: Price Action View - univest.in</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Vijay Kedia-backed firm buys 20 lakh Zaggle shares | Tap to know more | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>YC Holdings sells Rs 1,435 crore Groww stake; Vijay Kedia firm buys 1.48% in Zaggle Prepaid - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Zaggle rebounds 26% from Tuesday's low on heavy volumes; here's why - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Ocean Services crashes 20%, hits lower circuit after Q1 PAT declines 33% YoY - economictimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -716,68 +728,48 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KAMANWALA.NS</t>
+          <t>AHLADA.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>KAMANWALA</t>
+          <t>AHLADA</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>19.3799991607666</v>
+        <v>37.40000152587891</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>19.51000022888184</v>
+        <v>43.70999908447266</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>18</v>
+        <v>36.15999984741211</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18.6299991607666</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16.26000022888184</v>
+        <v>36.43000030517578</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18.6299991607666</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>474236</v>
+        <v>230285</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Volume Gainers on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Volume Gainers on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Most Active Equities on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Lalithaa Jewellery Mart IPO Day 3 Subscription Status: Issue Booked 6.84x so Far - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
-        </is>
-      </c>
+        <v>12.05</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -785,48 +777,40 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR.NS</t>
+          <t>SONAMLTD.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR</t>
+          <t>SONAMLTD</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>27.8799991607666</v>
+        <v>62.29999923706055</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>32.72999954223633</v>
+        <v>68.98999786376953</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>27.42000007629395</v>
+        <v>60.7400016784668</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>67.19000244140625</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.42000007629395</v>
+        <v>60.31000137329102</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>67.19000244140625</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1432482</v>
+        <v>977582</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>14.04</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Kohinoor Foods Ltd Locks at Upper Circuit With 20% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Kohinoor Foods Ltd Locks at Upper Circuit With 20% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
-        </is>
-      </c>
+        <v>11.41</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -834,7 +818,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -842,68 +826,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE.NS</t>
+          <t>GFLLIMITED.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>187.3999938964844</v>
+        <v>52</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>194.6999969482422</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>180</v>
+        <v>51.22999954223633</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>186.0399932861328</v>
+        <v>56.7599983215332</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>165.8800048828125</v>
+        <v>51.22000122070312</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>186.0399932861328</v>
+        <v>56.7599983215332</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>39145837</v>
+        <v>770053</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Zaggle rebounds 26% from Tuesday's low on heavy volumes; here's why - Business Standard</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Vijay Kedia's Kedia Securities acquires stake in AI-led SaaS fintech Zaggle Prepaid, stock surges more than 17% on NSE - TradingView</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>YC Holdings sells Rs 1,435 crore Groww stake; Vijay Kedia firm buys 1.48% in Zaggle Prepaid - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Vijay Kedia buys Rs 33 crore stake in Zaggle Prepaid Ocean Services via bulk deal, stock skyrockets 17% - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Zaggle Prepaid Ocean Services Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
-        </is>
-      </c>
+        <v>10.82</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -911,56 +875,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SONAMLTD.NS</t>
+          <t>MILKYMIST.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SONAMLTD</t>
+          <t>MILKYMIST</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>62.29999923706055</v>
+        <v>190</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>68.98999786376953</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>60.7400016784668</v>
+        <v>190</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.19000244140625</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>60.31000137329102</v>
+        <v>181.5</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>67.19000244140625</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>964817</v>
+        <v>29368751</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>11.41</v>
+        <v>10</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st</t>
+          <t>Milky Mist shares make decent market debut at 18% premium; should you buy, sell or hold? - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Milky Mist share price extends post-listing gains, hits 10% upper circuit - Business Standard</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Milky Mist IPO Listing: Shares Debut at ₹165, Gain 18%; Stock Rises 29.64% From Issue Price - India Infoline</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Milky Mist share price up 30% after IPO listing: Should investors hold or book profits? - India Today</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -968,48 +944,64 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>LAXMICOT.NS</t>
+          <t>SIEL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>LAXMICOT</t>
+          <t>SIEL</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13.75</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>16.14999961853027</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13.5</v>
+        <v>39.38999938964844</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>14.89000034332275</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13.46000003814697</v>
+        <v>38.56999969482422</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14.89000034332275</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>357640</v>
+        <v>20184</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1017,68 +1009,48 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>NILKAMAL.NS</t>
+          <t>TPHQ.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>NILKAMAL</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1848.699951171875</v>
+        <v>0.6499999761581421</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2105</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1832.5</v>
+        <v>0.6100000143051147</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2033.800048828125</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1846.699951171875</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2033.800048828125</v>
+        <v>0.6899999976158142</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1423712</v>
+        <v>23488941</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Nilkamal Ltd Upgraded to Buy on Improved Technicals and Valuation - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Nilkamal Ltd Surges 8.0% to Day's High of Rs 1970 — Outperforms Sector by 7.27 Percentage Points - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Nilkamal Ltd Technical Momentum Shifts Signal Bullish Outlook Amid Market Volatility - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Nilkamal Ltd Upgraded to Buy by MarketsMOJO on Strong Financial and Technical Grounds - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Nilkamal Ltd Surges 8.0% to Day's High of Rs 1970 — Outperforms Sector by 7.27 Percentage Points - MarketsMojo</t>
-        </is>
-      </c>
+        <v>9.52</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1086,60 +1058,48 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>MANBRO.NS</t>
+          <t>RPEL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MANBRO</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>53</v>
+        <v>1500</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>58.40999984741211</v>
+        <v>1665</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>52.79999923706055</v>
+        <v>1500</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.40999984741211</v>
+        <v>1637.400024414062</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>53.09999847412109</v>
+        <v>1495.199951171875</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>58.40999984741211</v>
+        <v>1637.400024414062</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>132482</v>
+        <v>375056</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Total common shares outstanding of KD Green Industries Limited – NSE:MANBRO - TradingView</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Total common shares outstanding of KD Green Industries Limited – NSE:MANBRO - TradingView</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Manbro Ind Q1 Results FY27: Revenue Rs 34 crore, Net Profit Rs 3 Crore - univest.in</t>
-        </is>
-      </c>
+        <v>9.51</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1147,68 +1107,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST.NS</t>
+          <t>DWARKESH.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>DWARKESH</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>190</v>
+        <v>44.86000061035156</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>50.04999923706055</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>190</v>
+        <v>44.56000137329102</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>48.27999877929688</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>181.5</v>
+        <v>44.63999938964844</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>48.27999877929688</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>27974362</v>
+        <v>9613344</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10</v>
+        <v>8.15</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist shares make decent market debut at 18% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Limited: Target Price Consensus and Analysts Recommendations | MILKYMIST | INE00IT01020 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist IPO Listing: Shares Debut at ₹165, Gain 18%; Stock Rises 29.64% From Issue Price - India Infoline</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist share price up 30% after IPO listing: Should investors hold or book profits? - India Today</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist Share Price Hits 10% Upper Circuit After Strong Listing. Should Investors Buy, Sell Or Hold? - NDTV Profit</t>
-        </is>
-      </c>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1216,60 +1164,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SIEL.NS</t>
+          <t>DHOOTTRANS.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>SIEL</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>1297.699951171875</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>1436.300048828125</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>39.38999938964844</v>
+        <v>1272</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>1404.050048828125</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38.56999969482422</v>
+        <v>1305.75</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>1404.050048828125</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>13463</v>
+        <v>16993686</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>9.98</v>
+        <v>7.53</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+          <t>Total common shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+          <t>DHOOTTRANS Share Price Today - Dhoot Transmission Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - Dhoot Transmission Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1277,48 +1229,40 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>TFCILTD.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND</t>
+          <t>TFCILTD</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>125</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>21.28000068664551</v>
+        <v>131.9900054931641</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>18.54000091552734</v>
+        <v>124.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20.3799991607666</v>
+        <v>131.4100036621094</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>123.6999969482422</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20.3799991607666</v>
+        <v>131.4100036621094</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>176267431</v>
+        <v>18203710</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
-        </is>
-      </c>
+        <v>6.23</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1326,7 +1270,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1334,37 +1278,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>TPHQ.NS</t>
+          <t>DBOL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.6499999761581421</v>
+        <v>123</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.6899999976158142</v>
+        <v>131.3999938964844</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.6100000143051147</v>
+        <v>123</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.6899999976158142</v>
+        <v>129.2599945068359</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>121.9899978637695</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6899999976158142</v>
+        <v>129.2599945068359</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>23477345</v>
+        <v>814499</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>9.52</v>
+        <v>5.96</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
@@ -1375,7 +1319,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1383,48 +1327,40 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RPEL.NS</t>
+          <t>SINGERIND.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>SINGERIND</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1500</v>
+        <v>79.80000305175781</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1665</v>
+        <v>84.98999786376953</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1500</v>
+        <v>77.41999816894531</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1637.400024414062</v>
+        <v>83.36000061035156</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1495.199951171875</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1637.400024414062</v>
+        <v>83.36000061035156</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>375042</v>
+        <v>116136</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - univest.in</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - univest.in</t>
-        </is>
-      </c>
+        <v>5.92</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -1432,7 +1368,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1440,46 +1376,46 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>HEALTHX.NS</t>
+          <t>MARSONS.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>HEALTHX</t>
+          <t>MARSONS</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>288</v>
+        <v>102.7799987792969</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>327.8999938964844</v>
+        <v>111.5999984741211</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>286.5</v>
+        <v>102.3099975585938</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>313.7000122070312</v>
+        <v>108.370002746582</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>288.5</v>
+        <v>102.3099975585938</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>313.7000122070312</v>
+        <v>108.370002746582</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>8983</v>
+        <v>4951490</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8.73</v>
+        <v>5.92</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Sastasundar Ventures Ltd. Share Price Rise: Key Analysis - univest.in</t>
+          <t>Marsons Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Sastasundar Ventures Ltd. Share Price Rise: Key Analysis - univest.in</t>
+          <t>Marsons Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
@@ -1489,7 +1425,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1497,48 +1433,40 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>AVROIND.NS</t>
+          <t>RAJSREESUG.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>AVROIND</t>
+          <t>RAJSREESUG</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8.630000114440918</v>
+        <v>35.25</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>9.829999923706055</v>
+        <v>38.43999862670898</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>8.420000076293945</v>
+        <v>34.95999908447266</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.539999961853027</v>
+        <v>36.90000152587891</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>8.800000190734863</v>
+        <v>34.95999908447266</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9.539999961853027</v>
+        <v>36.90000152587891</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1242003</v>
+        <v>308611</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - univest.in</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - univest.in</t>
-        </is>
-      </c>
+        <v>5.55</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -1546,7 +1474,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1554,56 +1482,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL.NS</t>
+          <t>JNPR.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL</t>
+          <t>JNPR</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>70</v>
+        <v>241.1000061035156</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>75.11000061035156</v>
+        <v>258.7999877929688</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>68.01999664306641</v>
+        <v>238.8099975585938</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>74.58000183105469</v>
+        <v>253.7100067138672</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>68.94000244140625</v>
+        <v>240.5899963378906</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>74.58000183105469</v>
+        <v>253.7100067138672</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>144562</v>
+        <v>3169674</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8.18</v>
+        <v>5.45</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
+          <t>JNPR Share Price Today - Juniper Green Energy Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>HPE Shares Rise, NextEra Falls, Robinhood Launches Stock Tokens | Stock Movers Xrp (mFxBq7V8sx) - Mshale</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1611,48 +1547,40 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH.NS</t>
+          <t>ARIHANTCAP.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>44.86000061035156</v>
+        <v>73.98000335693359</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>50.04999923706055</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44.56000137329102</v>
+        <v>73.08999633789062</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>48.27999877929688</v>
+        <v>77.68000030517578</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>44.63999938964844</v>
+        <v>73.76999664306641</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>48.27999877929688</v>
+        <v>77.68000030517578</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>9610957</v>
+        <v>541197</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
-        </is>
-      </c>
+        <v>5.3</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -1660,7 +1588,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1668,40 +1596,48 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING.NS</t>
+          <t>EMSLIMITED.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING</t>
+          <t>EMSLIMITED</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>111.25</v>
+        <v>388.7999877929688</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>120.7600021362305</v>
+        <v>411</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>110</v>
+        <v>382.2000122070312</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>119.8600006103516</v>
+        <v>394.9500122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>111.2099990844727</v>
+        <v>375.75</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>119.8600006103516</v>
+        <v>394.9500122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>872655</v>
+        <v>3336792</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+        <v>5.11</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>EMS shares in focus on project win worth Rs 1,908 crore in Rajasthan - TradingView</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>EMS shares in focus on project win worth Rs 1,908 crore in Rajasthan - TradingView</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -1730,7 +1666,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -1829,7 +1765,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1837,48 +1773,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KJMCFIN.NS</t>
+          <t>YASHO.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>KJMCFIN</t>
+          <t>YASHO</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>61.9900016784668</v>
+        <v>4910</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>61.9900016784668</v>
+        <v>4911.2001953125</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>55.34999847412109</v>
+        <v>4411.60009765625</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>55.34999847412109</v>
+        <v>4470.7998046875</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>61.9900016784668</v>
+        <v>4915.7998046875</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>55.34999847412109</v>
+        <v>4470.7998046875</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>322</v>
+        <v>167724</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-10.71</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd is Rated Buy - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>183.68% Stock Return, 372.3% Profit Growth: What's Driving Yasho Industries Ltd's Multibagger Rerating? - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1886,68 +1842,56 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>YASHO.NS</t>
+          <t>DEEPINDS.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4910</v>
+        <v>717.9500122070312</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4911.2001953125</v>
+        <v>720</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4411.60009765625</v>
+        <v>656.7000122070312</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4470.7998046875</v>
+        <v>667.3499755859375</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4915.7998046875</v>
+        <v>717.9500122070312</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4470.7998046875</v>
+        <v>667.3499755859375</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>167699</v>
+        <v>622935</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.050000000000001</v>
+        <v>-7.05</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+          <t>There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>183.68% Stock Return, 372.3% Profit Growth: What's Driving Yasho Industries Ltd's Multibagger Rerating? - MarketsMojo</t>
-        </is>
-      </c>
+          <t>There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1955,64 +1899,48 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AAKASH.NS</t>
+          <t>BHARATSE.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>AAKASH</t>
+          <t>BHARATSE</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.130000114440918</v>
+        <v>240.9100036621094</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>9.199999809265137</v>
+        <v>240.9100036621094</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8.060000419616699</v>
+        <v>224.9900054931641</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8.449999809265137</v>
+        <v>227.1900024414062</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9.130000114440918</v>
+        <v>240.9100036621094</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8.449999809265137</v>
+        <v>227.1900024414062</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>719753</v>
+        <v>441229</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.45</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Aakash Explorat Standalone June 2026 Net Sales at Rs 27.89 crore, up 16.93% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Aakash Explorat Standalone June 2026 Net Sales at Rs 27.89 crore, up 16.93% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>If you have a genius like Jasprit Bumrah, and if his body needs some rest, why would you play him? Aakash Chopra on star pacer's workload - CricTracker</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Aakash Exploration Promoters Reshuffle Holdings via Exempt Share Transfer - TipRanks</t>
-        </is>
-      </c>
+        <v>-5.7</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2020,46 +1948,46 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB.NS</t>
+          <t>HATSUN.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>HATSUN</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>347.4700012207031</v>
+        <v>985.3499755859375</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>348</v>
+        <v>1000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>320.0499877929688</v>
+        <v>921</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>322.0599975585938</v>
+        <v>930.2999877929688</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>346.8699951171875</v>
+        <v>985.3499755859375</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>322.0599975585938</v>
+        <v>930.2999877929688</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1534549</v>
+        <v>147018</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.15</v>
+        <v>-5.59</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+          <t>Hatsun Agro Product Ltd leads losers in 'A' group - Dailyhunt</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+          <t>Hatsun Agro Product Ltd leads losers in 'A' group - Dailyhunt</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
@@ -2069,7 +1997,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2077,56 +2005,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CGVAK.NS</t>
+          <t>SUYOG.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CGVAK</t>
+          <t>SUYOG</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>151.2400054931641</v>
+        <v>801.8499755859375</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>151.2400054931641</v>
+        <v>805.0499877929688</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>136.6199951171875</v>
+        <v>750.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>140.7299957275391</v>
+        <v>759.25</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>151.2400054931641</v>
+        <v>801.2000122070312</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>140.7299957275391</v>
+        <v>759.25</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>508</v>
+        <v>90236</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.95</v>
+        <v>-5.24</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of CG-VAK Software &amp; Exports Ltd. – NSE:CGVAK - TradingView</t>
+          <t>Suyog Tele Standalone June 2026 Net Sales at Rs 65.27 crore, up 26.45% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of CG-VAK Software &amp; Exports Ltd. – NSE:CGVAK - TradingView</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Suyog Telematics Downgraded to Sell Amid Technical and Valuation Concerns - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Suyog Gurbaxani Funicular Ropeways recommends ₹0.50 final dividend for FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Suyog Gurbaxani Funicular Ropeways Ltd. (SGFRL) Share Price Rises 8.25% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Suyog Telematics Downgraded to Sell Amid Technical and Valuation Concerns - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2134,48 +2074,40 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ANTELOPUS.NS</t>
+          <t>WEBELSOLAR.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>863</v>
+        <v>86.93000030517578</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>863</v>
+        <v>87.12000274658203</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>793.75</v>
+        <v>82.58999633789062</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>798.3499755859375</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>856.5499877929688</v>
+        <v>86.93000030517578</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>798.3499755859375</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>209718</v>
+        <v>2436130</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.79</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Antelopus Selan Energy Ltd Surges 7.14% to Day's High of Rs 857.5 — Outperforms Sector by 6.12 Percentage Points - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Antelopus Selan Energy Ltd Surges 7.14% to Day's High of Rs 857.5 — Outperforms Sector by 6.12 Percentage Points - MarketsMojo</t>
-        </is>
-      </c>
+        <v>-4.84</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -2183,7 +2115,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2191,46 +2123,46 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MEDICAPQ.NS</t>
+          <t>KUSUMGAR.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MEDICAPQ</t>
+          <t>KUSUMGAR</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>26.5</v>
+        <v>595.9500122070312</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>27.45000076293945</v>
+        <v>599</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>21</v>
+        <v>560.7000122070312</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>23.55999946594238</v>
+        <v>566.3499755859375</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25.04999923706055</v>
+        <v>595</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>23.55999946594238</v>
+        <v>566.3499755859375</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2778</v>
+        <v>451848</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.95</v>
+        <v>-4.82</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Medi-Caps Ltd. Financial Statements – NSE:MEDICAPQ - TradingView</t>
+          <t>Kusumgar seeks shareholder approval to ratify ESOP scheme post-IPO - scanx.trade</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Medi-Caps Ltd. Financial Statements – NSE:MEDICAPQ - TradingView</t>
+          <t>Kusumgar seeks shareholder approval to ratify ESOP scheme post-IPO - scanx.trade</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
@@ -2240,7 +2172,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2248,37 +2180,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BHARATSE.NS</t>
+          <t>ACUTAAS.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>240.9100036621094</v>
+        <v>3399.10009765625</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>240.9100036621094</v>
+        <v>3399.10009765625</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>224.9900054931641</v>
+        <v>3219</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>227.1900024414062</v>
+        <v>3228.89990234375</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>240.9100036621094</v>
+        <v>3391.39990234375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>227.1900024414062</v>
+        <v>3228.89990234375</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>440887</v>
+        <v>279967</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.7</v>
+        <v>-4.79</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
@@ -2289,7 +2221,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2297,48 +2229,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MALUPAPER.NS</t>
+          <t>AARTIPHARM.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>MALUPAPER</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>32.20000076293945</v>
+        <v>878</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>32.20000076293945</v>
+        <v>878.9500122070312</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30.20000076293945</v>
+        <v>826.5499877929688</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>30.81999969482422</v>
+        <v>834.1500244140625</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>32.58000183105469</v>
+        <v>874.5499877929688</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>30.81999969482422</v>
+        <v>834.1500244140625</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>61691</v>
+        <v>377267</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
+        <v>-4.62</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>AARTIPHARM Consolidated June 2026 Net Sales at Rs 535.80 crore, up 38.74% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>AARTIPHARM Consolidated June 2026 Net Sales at Rs 535.80 crore, up 38.74% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Mercantile Ventures Posts Consolidated Net Loss of Rs 0.65 Crore in June 2026 Quarter; Sales Climb 9.25% - Guidance Revision Trend - Vinanet</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2346,48 +2290,40 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>UEL.NS</t>
+          <t>DBREALTY.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>UEL</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>200.8000030517578</v>
+        <v>107.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>200.8000030517578</v>
+        <v>107.75</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>200.8000030517578</v>
+        <v>101.5</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>200.8000030517578</v>
+        <v>101.7900009155273</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>211.3600006103516</v>
+        <v>106.4800033569336</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>200.8000030517578</v>
+        <v>101.7900009155273</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4624</v>
+        <v>1242300</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
-        </is>
-      </c>
+        <v>-4.4</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -2395,7 +2331,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2403,37 +2339,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>CEMPRO.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>66.09999847412109</v>
+        <v>1324</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>66.09999847412109</v>
+        <v>1334</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>66.09999847412109</v>
+        <v>1257.800048828125</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.09999847412109</v>
+        <v>1265.699951171875</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>1324</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>66.09999847412109</v>
+        <v>1265.699951171875</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>42916</v>
+        <v>344424</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.99</v>
+        <v>-4.4</v>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
@@ -2444,7 +2380,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2452,68 +2388,48 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ONIXSOLAR.NS</t>
+          <t>INDOFARM.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ONIXSOLAR</t>
+          <t>INDOFARM</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>338.8500061035156</v>
+        <v>143.8999938964844</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>338.8500061035156</v>
+        <v>144.1699981689453</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>338.8500061035156</v>
+        <v>135.9100036621094</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>338.8500061035156</v>
+        <v>137.1600036621094</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>356.6499938964844</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>338.8500061035156</v>
+        <v>137.1600036621094</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5926</v>
+        <v>324275</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.99</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Total common shares outstanding of Onix Solar Energy Ltd. – NSE:ONIXSOLAR - TradingView</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Onix Solar Energy shares permitted to trade on NSE from August 17 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Onix Solar Energy Ltd - Equitypandit</t>
-        </is>
-      </c>
+        <v>-4.3</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2521,48 +2437,40 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>SHREERAMA.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>SHREERAMA</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13.39999961853027</v>
+        <v>46.79999923706055</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>13.39999961853027</v>
+        <v>46.79999923706055</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>12.75</v>
+        <v>44.11000061035156</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>12.75</v>
+        <v>44.36999893188477</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.42000007629395</v>
+        <v>46.34000015258789</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12.75</v>
+        <v>44.36999893188477</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3255667</v>
+        <v>113898</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.99</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
-        </is>
-      </c>
+        <v>-4.25</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -2570,7 +2478,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2578,56 +2486,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>KEEPLEARN.NS</t>
+          <t>THYROCARE.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>KEEPLEARN</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>620</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>620</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1.899999976158142</v>
+        <v>577</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.909999966621399</v>
+        <v>582.5</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2.009999990463257</v>
+        <v>608.25</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.909999966621399</v>
+        <v>582.5</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>50562</v>
+        <v>544224</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.98</v>
+        <v>-4.23</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
+          <t>API Holdings turns debt-free — frees Thyrocare shares from pledge - expresshealthcare.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>API Holdings Clears ₹1,050 Cr Debt, Unpledges Thyrocare Stake - BW Healthcare</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>API Holdings repays Rs 1050 Cr, frees Thyrocare shares from pledge - BioSpectrum India</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Why PharmEasy Keeps Selling Thyrocare Shares? - UnlistedZone</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>API Holdings Clears ₹1,050 Cr Debt, Unpledges Thyrocare Stake - BW Healthcare</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2635,68 +2555,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RBA.NS</t>
+          <t>BATAINDIA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>104.5</v>
+        <v>730</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>104.5999984741211</v>
+        <v>730</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>99.5</v>
+        <v>710.1500244140625</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>101.0599975585938</v>
+        <v>721.2999877929688</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>106.3399963378906</v>
+        <v>753.0999755859375</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>101.0599975585938</v>
+        <v>721.2999877929688</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>12913965</v>
+        <v>770121</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.97</v>
+        <v>-4.22</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>RBA stock hits 52-week low at 83.55 USD By Investing.com - Investing.com India</t>
+          <t>Here's What Analysts Are Forecasting For Bata India Limited (NSE:BATAINDIA) After Its First-Quarter Results - simplywall.st</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>ANZ Stock And 2 Australian Bank Shares Facing the Next RBA Rate Test - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>RB Global Inc (RBA) Stock Up 4.5% and Still Undervalued -- GF Sc - GuruFocus</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>ANZ Stock And 2 Australian Bank Shares Facing the Next RBA Rate Test - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Why RB Global (RBA) Stock Is Down Today - Quiver Quantitative</t>
-        </is>
-      </c>
+          <t>Here's What Analysts Are Forecasting For Bata India Limited (NSE:BATAINDIA) After Its First-Quarter Results - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2704,64 +2612,48 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>POWERICA.NS</t>
+          <t>KRISHNADEF.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>POWERICA</t>
+          <t>KRISHNADEF</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>562.7999877929688</v>
+        <v>1130</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>562.7999877929688</v>
+        <v>1143.699951171875</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>530.2999877929688</v>
+        <v>1072</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>532.8499755859375</v>
+        <v>1077.800048828125</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>560.6500244140625</v>
+        <v>1125</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>532.8499755859375</v>
+        <v>1077.800048828125</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>218225</v>
+        <v>94943</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.96</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Powerica Ltd. Share Price Today - Powerica Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Powerica schedules virtual analyst meet on August 21 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>POWERICA Share Price Today - Powerica Ltd. Stock Price Live NSE/BSE - univest.in</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Powerica schedules virtual analyst meet on August 21 - scanx.trade</t>
-        </is>
-      </c>
+        <v>-4.2</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2769,68 +2661,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CESC.NS</t>
+          <t>POWERINDIA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>162</v>
+        <v>35100</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>162.2599945068359</v>
+        <v>35100</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>158.5</v>
+        <v>33360</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>159.6600036621094</v>
+        <v>33800</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>167.9799957275391</v>
+        <v>35275</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>159.6600036621094</v>
+        <v>33800</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2881453</v>
+        <v>186593</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.95</v>
+        <v>-4.18</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - businesstoday.in</t>
+          <t>Hitachi Energy India Stock Leads A Fresh Look At Power Capex Winners - simplywall.st</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - businesstoday.in</t>
+          <t>Hitachi Energy India Stock Leads A Fresh Look At Power Capex Winners - simplywall.st</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>CESC Limited Earnings Missed Analyst Estimates: Here's What Analysts Are Forecasting Now - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Stocks to Watch Today: PB Fintech, Juniper Green, CESC, Dr Reddys Labs, Texmaco Rail, Voltas,... - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>CESC Ltd soars 1.23% - Business Standard</t>
-        </is>
-      </c>
+          <t>POWERINDIA Share Price | Hitachi Energy India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2838,48 +2722,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO.NS</t>
+          <t>FILATEX.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO</t>
+          <t>FILATEX</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10.10000038146973</v>
+        <v>86.5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>10.23999977111816</v>
+        <v>86.59999847412109</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>9.800000190734863</v>
+        <v>82.51000213623047</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.850000381469727</v>
+        <v>83.15000152587891</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10.35999965667725</v>
+        <v>86.75</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9.850000381469727</v>
+        <v>83.15000152587891</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>19995</v>
+        <v>1502803</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+        <v>-4.15</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Filatex Fashions fined ₹56,640 each by NSE and BSE for compliance lapse - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Filatex Fashions Share News Today,filatex Fashions Share Analysis,filatex Fashions Share Price/news Julio Rodríguez (hxc2EVlwyH) - Mshale</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Filatex Fashion | Filatex Fashion Share Latest News | Filatex Fashion News | Filatex Fashion Share Cigarette (pEVfqWC9K9) - Mshale</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Filatex Fashions Share News Today,filatex Fashions Share Analysis,filatex Fashions Share Price/news Julio Rodríguez (hxc2EVlwyH) - Mshale</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2887,37 +2787,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR.NS</t>
+          <t>GUJRAFFIA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>GUJRAFFIA</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>86.93000030517578</v>
+        <v>42.45000076293945</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>87.12000274658203</v>
+        <v>42.45000076293945</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>82.58999633789062</v>
+        <v>40.2599983215332</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>82.72000122070312</v>
+        <v>40.65999984741211</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>86.93000030517578</v>
+        <v>42.40999984741211</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>82.72000122070312</v>
+        <v>40.65999984741211</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2433185</v>
+        <v>2024</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.84</v>
+        <v>-4.13</v>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
@@ -2928,7 +2828,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:27:02</t>
+          <t>2026-08-20 08:55:20</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2936,48 +2836,40 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PLAZACABLE.NS</t>
+          <t>3MINDIA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>3MINDIA</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>51.5</v>
+        <v>35100</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>53.02000045776367</v>
+        <v>35100</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>49.77000045776367</v>
+        <v>33355</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>49.86000061035156</v>
+        <v>33505</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>52.38000106811523</v>
+        <v>34945</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>49.86000061035156</v>
+        <v>33505</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>75805</v>
+        <v>7449</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.81</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Here's Why We Think Plaza Wires (NSE:PLAZACABLE) Is Well Worth Watching - simplywall.st</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Here's Why We Think Plaza Wires (NSE:PLAZACABLE) Is Well Worth Watching - simplywall.st</t>
-        </is>
-      </c>
+        <v>-4.12</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gainers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Losers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gainers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,48 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EXCELINDUS.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>EXCELINDUS</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>991.0499877929688</v>
+        <v>658.25</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1148.550048828125</v>
+        <v>738.9500122070312</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>990.9000244140625</v>
+        <v>655.0499877929688</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1133.25</v>
+        <v>736.7999877929688</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>985.2000122070312</v>
+        <v>650.7999877929688</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1133.25</v>
+        <v>736.7999877929688</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1055831</v>
+        <v>12573227</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>15.03</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+        <v>13.21</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -602,56 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR</t>
+          <t>BAJAJHIND</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27.8799991607666</v>
+        <v>20.73999977111816</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>32.72999954223633</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>27.42000007629395</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>22.17000007629395</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27.42000007629395</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>22.17000007629395</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1434186</v>
+        <v>131939293</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>14.04</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>We Think That There Are Some Issues For Bajaj Hindusthan Sugar (NSE:BAJAJHIND) Beyond Its Promising Earnings - simplywall.st</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>BAJAJHIND Mar 2026 Earnings: Solid EPS of ₹1.65 on Revenue of ₹1,657 Crore - Downward Estimate Revision - Vinanet</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHIND Mar 2026 Earnings: Solid EPS of ₹1.65 on Revenue of ₹1,657 Crore - Downward Estimate Revision - Vinanet</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>There's No Escaping Bajaj Hindusthan Sugar Limited's (NSE:BAJAJHIND) Muted Revenues - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHIND Mar 2026 Earnings: EPS of ₹1.65 on Revenue of ₹1,657 Crore as Sugar &amp; Ethanol Operations Hold Steady - Long-Term Guidance - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -659,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE.NS</t>
+          <t>RAJSREESUG.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>RAJSREESUG</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>187.3999938964844</v>
+        <v>37.0099983215332</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>194.6999969482422</v>
+        <v>40.79000091552734</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>186.0399932861328</v>
+        <v>39.65000152587891</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>165.8800048828125</v>
+        <v>36.90000152587891</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>186.0399932861328</v>
+        <v>39.65000152587891</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39149680</v>
+        <v>487665</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>12.15</v>
+        <v>7.45</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Vijay Kedia buys Rs 33 crore stake in Zaggle Prepaid Ocean Services via bulk deal, stock skyrockets 17% - economictimes.com</t>
+          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Vijay Kedia-backed firm buys 20 lakh Zaggle shares | Tap to know more | Inshorts - Inshorts</t>
+          <t>Rajshree Sugars (RAJSREESUG.NS) Holds Near Support as Sugar Sector Awaits Policy Clarity - Fund Manager Survey - Vinanet</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>YC Holdings sells Rs 1,435 crore Groww stake; Vijay Kedia firm buys 1.48% in Zaggle Prepaid - Moneycontrol.com</t>
+          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Zaggle rebounds 26% from Tuesday's low on heavy volumes; here's why - Business Standard</t>
+          <t>Rajshree Sugars (RAJSREESUG.NS) Holds Near Support as Sugar Sector Awaits Policy Clarity - Fund Manager Survey - Vinanet</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Zaggle Prepaid Ocean Services crashes 20%, hits lower circuit after Q1 PAT declines 33% YoY - economictimes.com</t>
+          <t>Rajshree Sugar &amp; Chem Share Price - Upstox</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -728,48 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AHLADA.NS</t>
+          <t>DHAMPURSUG.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>AHLADA</t>
+          <t>DHAMPURSUG</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37.40000152587891</v>
+        <v>179.6999969482422</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43.70999908447266</v>
+        <v>190.75</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>36.15999984741211</v>
+        <v>178.9700012207031</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>40.81999969482422</v>
+        <v>188</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>36.43000030517578</v>
+        <v>176.1799926757812</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>40.81999969482422</v>
+        <v>188</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>230285</v>
+        <v>3569317</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+        <v>6.71</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills (DHAMPURSUG) Gains 2.33%: Support Holds amid Sugar Sector Activity - Bearish Pattern Stocks - Vinanet</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Q2 2026 Earnings: EPS of ₹10.09 on Steady Revenue of ₹19,674.4 Million - Basic EPS Analysis - Vinanet</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills (DHAMPURSUG.NS): Mild Decline as Price Hovers Near Support Zone - Fibonacci Fan - Vinanet</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Share Price - Live NSE: DHAMPURSUG Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Fined by Uttar Pradesh Excise Authority for Storage Lapses - The Globe and Mail</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -777,48 +829,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SONAMLTD.NS</t>
+          <t>ZUARIIND.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SONAMLTD</t>
+          <t>ZUARIIND</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>62.29999923706055</v>
+        <v>268.8999938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>68.98999786376953</v>
+        <v>284.8999938964844</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>60.7400016784668</v>
+        <v>261.8500061035156</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>67.19000244140625</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>60.31000137329102</v>
+        <v>262.1000061035156</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>67.19000244140625</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>977582</v>
+        <v>283179</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+        <v>6.37</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Zuari Industries Limited's (NSE:ZUARIIND) 25% Price Boost Is Out Of Tune With Revenues - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>ZUARIIND Q2 FY26 Earnings: Revenue Grows 7.68% YoY to ₹1,044.82 Crore, EPS at ₹36.25 - Next Quarter Guidance - Vinanet</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ZUARI Industries (ZUARIIND.NS) Slips Over 3% as Selling Pressure Intensifies - Narrow Range Breakout - Vinanet</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>ZUARIIND Stock Price and Chart — NSE:ZUARIIND - TradingView</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>ZUARIIND Q2 FY26 Earnings: Revenue Grows 7.68% YoY to ₹1,044.82 Crore, EPS at ₹36.25 - Next Quarter Guidance - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -826,48 +898,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GFLLIMITED.NS</t>
+          <t>ARVIND.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>52</v>
+        <v>519.9000244140625</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>58.04999923706055</v>
+        <v>541</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>51.22999954223633</v>
+        <v>519.5499877929688</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.7599983215332</v>
+        <v>534.75</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>51.22000122070312</v>
+        <v>516.5</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>56.7599983215332</v>
+        <v>534.75</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>770053</v>
+        <v>541059</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+        <v>3.53</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Arvind posts strong Q1 2026 growth, shares slip - Investing.com</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Arvind sees no immediate acquisitions, focuses on Dalco GFT integration - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Rubrik CTO Arvind Nithrakashyap Sells $3.0 Million Stock - The Motley Fool</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -875,68 +967,60 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST.NS</t>
+          <t>EIDPARRY.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST</t>
+          <t>EIDPARRY</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>190</v>
+        <v>793.7999877929688</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>814.8499755859375</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>190</v>
+        <v>787.5499877929688</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>803.4500122070312</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>181.5</v>
+        <v>787.0499877929688</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>803.4500122070312</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>29368751</v>
+        <v>1151102</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10</v>
+        <v>2.08</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist shares make decent market debut at 18% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+          <t>Raja Venkatraman recommends three stocks for 5 August - livemint.com</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist share price extends post-listing gains, hits 10% upper circuit - Business Standard</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist IPO Listing: Shares Debut at ₹165, Gain 18%; Stock Rises 29.64% From Issue Price - India Infoline</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist share price up 30% after IPO listing: Should investors hold or book profits? - India Today</t>
-        </is>
-      </c>
+          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -944,64 +1028,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SIEL.NS</t>
+          <t>DCW.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SIEL</t>
+          <t>DCW</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>43.47000122070312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>44.38000106811523</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.38999938964844</v>
+        <v>43.33000183105469</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>44.13000106811523</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>38.56999969482422</v>
+        <v>43.2599983215332</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>44.13000106811523</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>20184</v>
+        <v>383685</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>9.98</v>
+        <v>2.01</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+          <t>DCW Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>‘Call 181, receive justice quickly’: Delhi DCW Chair Lata Gupta's first message after appointment - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>DCW Limited to host Q1FY27 earnings call on August 14 - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1009,40 +1097,48 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TPHQ.NS</t>
+          <t>BOMDYEING.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>BOMDYEING</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.6499999761581421</v>
+        <v>113.2399978637695</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.6899999976158142</v>
+        <v>113.4300003051758</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.6100000143051147</v>
+        <v>112.6600036621094</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6899999976158142</v>
+        <v>113</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>111.5699996948242</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6899999976158142</v>
+        <v>113</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>23488941</v>
+        <v>144788</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1050,7 +1146,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1058,48 +1154,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RPEL.NS</t>
+          <t>SAIL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1500</v>
+        <v>174.1000061035156</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1665</v>
+        <v>176.4299926757812</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1500</v>
+        <v>173.4100036621094</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1637.400024414062</v>
+        <v>174.8999938964844</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1495.199951171875</v>
+        <v>172.75</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1637.400024414062</v>
+        <v>174.8999938964844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>375056</v>
+        <v>7842795</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+        <v>1.24</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>CrowdStrike Setup 'Constructive,' But Truist Favors Rubrik, SailPoint Ahead Of Q2 Earnings - TradingView</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Metal tanks 3% in two days on profit-taking; NALCO, SAIL top losers - business-standard.com</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Outlook: Records a Muted Move to $19.19 on the Day; Chart View: Price Remains Between $18.23 Support and $20.15 Resistance in the Latest Session - Daily Profile - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1107,56 +1223,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH.NS</t>
+          <t>INFY.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>44.86000061035156</v>
+        <v>1143</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>50.04999923706055</v>
+        <v>1144.699951171875</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>44.56000137329102</v>
+        <v>1125.699951171875</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>48.27999877929688</v>
+        <v>1130.300048828125</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>44.63999938964844</v>
+        <v>1119.800048828125</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>48.27999877929688</v>
+        <v>1130.300048828125</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>9613344</v>
+        <v>4384372</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Infosys Ltd (INFY) Stock Down 3.9% -- Now Undervalued? GF Score: 86/100 - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Infosys (NSEI:INFY) Stock Fair Value Falls After Analysts Cut Targets On Weaker Outlook - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>INFY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1164,64 +1292,56 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS.NS</t>
+          <t>ASHOKLEY.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1297.699951171875</v>
+        <v>174.6999969482422</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1436.300048828125</v>
+        <v>175.5700073242188</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1272</v>
+        <v>173.7400054931641</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1404.050048828125</v>
+        <v>174.6000061035156</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1305.75</v>
+        <v>173.1000061035156</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1404.050048828125</v>
+        <v>174.6000061035156</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>16993686</v>
+        <v>3036626</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>7.53</v>
+        <v>0.87</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+          <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - Dhoot Transmission Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>DHOOTTRANS Share Price Today - Dhoot Transmission Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
+          <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1229,40 +1349,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TFCILTD.NS</t>
+          <t>SURYAROSNI.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TFCILTD</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>125</v>
+        <v>219.8999938964844</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>131.9900054931641</v>
+        <v>222.0899963378906</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>124.5</v>
+        <v>216.8000030517578</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>131.4100036621094</v>
+        <v>220.3300018310547</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>123.6999969482422</v>
+        <v>218.7100067138672</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>131.4100036621094</v>
+        <v>220.3300018310547</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>18203710</v>
+        <v>645331</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1270,7 +1398,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1278,40 +1406,48 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DBOL.NS</t>
+          <t>CGPOWER.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>123</v>
+        <v>868.5499877929688</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>131.3999938964844</v>
+        <v>874</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>123</v>
+        <v>862.6500244140625</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>129.2599945068359</v>
+        <v>868.6500244140625</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>121.9899978637695</v>
+        <v>863.0499877929688</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>129.2599945068359</v>
+        <v>868.6500244140625</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>814499</v>
+        <v>1012503</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+        <v>0.65</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -1319,7 +1455,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1327,48 +1463,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SINGERIND.NS</t>
+          <t>FEDERALBNK.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SINGERIND</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>79.80000305175781</v>
+        <v>361.8999938964844</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>84.98999786376953</v>
+        <v>364.2000122070312</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>77.41999816894531</v>
+        <v>360.25</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>83.36000061035156</v>
+        <v>361</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>78.69999694824219</v>
+        <v>358.7999877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>83.36000061035156</v>
+        <v>361</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>116136</v>
+        <v>2183173</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+        <v>0.61</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Federal Bank (NSEI:FEDERALBNK) Stock Gets Fair Value Boost Before Board Results Review - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>The Federal Bank Ltd. (FEDERALBNK) Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1376,46 +1528,46 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MARSONS.NS</t>
+          <t>BIRLACORPN.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MARSONS</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>102.7799987792969</v>
+        <v>885</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>111.5999984741211</v>
+        <v>892</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>102.3099975585938</v>
+        <v>884.7999877929688</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>108.370002746582</v>
+        <v>889.7000122070312</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>102.3099975585938</v>
+        <v>884.9000244140625</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>108.370002746582</v>
+        <v>889.7000122070312</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4951490</v>
+        <v>9790</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5.92</v>
+        <v>0.54</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Marsons Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
+          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Marsons Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
+          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
@@ -1425,7 +1577,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1433,48 +1585,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG.NS</t>
+          <t>ABB.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>35.25</v>
+        <v>7450.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>38.43999862670898</v>
+        <v>7481.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>34.95999908447266</v>
+        <v>7393</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>36.90000152587891</v>
+        <v>7461.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>34.95999908447266</v>
+        <v>7430</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>36.90000152587891</v>
+        <v>7461.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>308611</v>
+        <v>115415</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+        <v>0.42</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>ABB stock benefits from strong Q2 orders as valuation debate grows - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>ABB Ltd: ABB share buybacks - August 6, 2026 - August 12, 2026 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Is ABB (SWX:ABBN) Fully Priced Following Its LevelTen Energy Deal? - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1482,64 +1654,56 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>JNPR.NS</t>
+          <t>HINDUNILVR.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>JNPR</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>241.1000061035156</v>
+        <v>2022.900024414062</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>258.7999877929688</v>
+        <v>2041.699951171875</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>238.8099975585938</v>
+        <v>2018.199951171875</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>253.7100067138672</v>
+        <v>2029</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>240.5899963378906</v>
+        <v>2020.699951171875</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>253.7100067138672</v>
+        <v>2029</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3169674</v>
+        <v>684111</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5.45</v>
+        <v>0.41</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>JNPR Share Price Today - Juniper Green Energy Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>HPE Shares Rise, NextEra Falls, Robinhood Launches Stock Tokens | Stock Movers Xrp (mFxBq7V8sx) - Mshale</t>
-        </is>
-      </c>
+          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1547,48 +1711,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ARIHANTCAP.NS</t>
+          <t>VOLTAS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>73.98000335693359</v>
+        <v>1234</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>79</v>
+        <v>1234</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>73.08999633789062</v>
+        <v>1215.599975585938</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>77.68000030517578</v>
+        <v>1227.699951171875</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>73.76999664306641</v>
+        <v>1223</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>77.68000030517578</v>
+        <v>1227.699951171875</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>541197</v>
+        <v>710177</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+        <v>0.38</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Voltas stock falls 4% after Q1, top midcap loser; brokerages split as margin concerns outweigh strong AC... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Voltas Share Price Declines 2.05% in Mid-Morning Trade - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Voltas shares fall 6% from intraday high post Q1; brokerages split - BusinessLine</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Voltas shares slip 4% despite strong Q1 show; analysts flag margin risk - business-standard.com</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Voltas posts strong Q1 2026 profit growth, shares rise 2.4% - Investing.com</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1596,51 +1780,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EMSLIMITED.NS</t>
+          <t>CANFINHOME.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>EMSLIMITED</t>
+          <t>CANFINHOME</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>388.7999877929688</v>
+        <v>821.4000244140625</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>411</v>
+        <v>829.7999877929688</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>382.2000122070312</v>
+        <v>817.9000244140625</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>394.9500122070312</v>
+        <v>820.4500122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>375.75</v>
+        <v>817.6500244140625</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>394.9500122070312</v>
+        <v>820.4500122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3336792</v>
+        <v>118262</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5.11</v>
+        <v>0.34</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>EMS shares in focus on project win worth Rs 1,908 crore in Rajasthan - TradingView</t>
+          <t>CANFINHOME Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>EMS shares in focus on project win worth Rs 1,908 crore in Rajasthan - TradingView</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>CANFINHOME Mar 2026 Earnings: EPS of ₹25.96 Reflects Steady Performance Amidst Housing Finance Sector Tailwinds - Estimate Uncertainty - Vinanet</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Can Fin Homes (CANFINHOME) Holds Steady at ₹886 – Key Levels in Focus - Chandelier Stop - Vinanet</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Can Fin Homes Ltd (CANFINHOME.NS) Falls 5.5% – Testing Key Support Near ₹795 - Fear Greed Extreme - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, Can Fin Homes (NSE:CANFINHOME) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1666,7 +1862,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -1765,7 +1961,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1773,68 +1969,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>YASHO.NS</t>
+          <t>GLFL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>GLFL</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4910</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4911.2001953125</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4411.60009765625</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4470.7998046875</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4915.7998046875</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4470.7998046875</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>167724</v>
+        <v>143</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-9.050000000000001</v>
+        <v>-3.09</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+          <t>Gujarat Lease Financing (GLFL) Slips 2%: Stock Tests Key Support at ₹6.05 - Long Short Pair - Vinanet</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+          <t>Gujarat Lease Financing Limited (GLFL.NS): Consolidating Near Support at ₹6.0 Amidst Stalled Momentum - Value ETF - Vinanet</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+          <t>Gujarat Lease Financing Limited (GLFL.NS): Consolidating Near Support at ₹6.0 Amidst Stalled Momentum - Value ETF - Vinanet</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd is Rated Buy - MarketsMojo</t>
+          <t>Gujarat Lease Financing Limited (GLFL.NS) Q2 2025 Earnings: Minimal EPS of ₹0.02 Reflecting Subdued Activity - Vinanet</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>183.68% Stock Return, 372.3% Profit Growth: What's Driving Yasho Industries Ltd's Multibagger Rerating? - MarketsMojo</t>
+          <t>Gujarat Lease Financing (GLFL) Slips 1.96% as Stock Tests Critical Support Zone - Passive Flow - Vinanet</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1842,56 +2038,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DEEPINDS.NS</t>
+          <t>CESC.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>717.9500122070312</v>
+        <v>159.2100067138672</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>720</v>
+        <v>160.1999969482422</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>656.7000122070312</v>
+        <v>156.5599975585938</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>667.3499755859375</v>
+        <v>157.3500061035156</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>717.9500122070312</v>
+        <v>159.6600036621094</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>667.3499755859375</v>
+        <v>157.3500061035156</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>622935</v>
+        <v>1144241</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-7.05</v>
+        <v>-1.45</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st</t>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>For CESC investors, renewable energy should yield dual benefits of stock rerating and growth - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>CESC Limited Earnings Missed Analyst Estimates: Here's What Analysts Are Forecasting Now - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>CESC Ltd soars 1.23% - business-standard.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1899,48 +2107,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BHARATSE.NS</t>
+          <t>BPL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>BPL</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>240.9100036621094</v>
+        <v>50.90000152587891</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>240.9100036621094</v>
+        <v>50.91999816894531</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>224.9900054931641</v>
+        <v>49.41999816894531</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>227.1900024414062</v>
+        <v>49.63000106811523</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>240.9100036621094</v>
+        <v>50.33000183105469</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>227.1900024414062</v>
+        <v>49.63000106811523</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>441229</v>
+        <v>23151</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+        <v>-1.39</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>This consumer electronics firm shares hit 20% upper circuit after NCLT move; what investors need to know - Upstox</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Eli Lilly to Boost Neuroscience Pipeline With AtaiBeckley Buyout - TradingView</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>BPL Share Price Forecast: 3 Year Outlook to 2030 - Univest</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>AtaiBeckley Stock Outlook Depends on Key Pipeline Catalysts in 2026 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>BPL Limited (BPL.NS) Gains 3.31% as Price Approaches Key Resistance at ₹59.98 - ETF Outflow Streak - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1948,56 +2176,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HATSUN.NS</t>
+          <t>IPCALAB.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>HATSUN</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>985.3499755859375</v>
+        <v>1922</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1000</v>
+        <v>1928.400024414062</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>921</v>
+        <v>1882.099975585938</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>930.2999877929688</v>
+        <v>1883.800048828125</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>985.3499755859375</v>
+        <v>1903.699951171875</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>930.2999877929688</v>
+        <v>1883.800048828125</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>147018</v>
+        <v>89876</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-5.59</v>
+        <v>-1.05</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Hatsun Agro Product Ltd leads losers in 'A' group - Dailyhunt</t>
+          <t>Ipca Laboratories Ltd. Share Price Fall: Price Action View - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Hatsun Agro Product Ltd leads losers in 'A' group - Dailyhunt</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd. Stock News: Share Price Up 4.76% - Univest</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares fall over 2%; strong financial performance reported - TradingView</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2005,68 +2245,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SUYOG.NS</t>
+          <t>FINCABLES.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SUYOG</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>801.8499755859375</v>
+        <v>1313.699951171875</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>805.0499877929688</v>
+        <v>1331</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>750.5</v>
+        <v>1301.449951171875</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>759.25</v>
+        <v>1301.75</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>801.2000122070312</v>
+        <v>1313.699951171875</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>759.25</v>
+        <v>1301.75</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>90236</v>
+        <v>283491</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-5.24</v>
+        <v>-0.91</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Suyog Tele Standalone June 2026 Net Sales at Rs 65.27 crore, up 26.45% Y-o-Y - Moneycontrol.com</t>
+          <t>FINCABLES Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Suyog Telematics Downgraded to Sell Amid Technical and Valuation Concerns - MarketsMojo</t>
+          <t>Finolex Cables Declines Over 3.5%, Finds Support Near ₹995.6 - Donchian Channel - Vinanet</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Suyog Gurbaxani Funicular Ropeways recommends ₹0.50 final dividend for FY26 - scanx.trade</t>
+          <t>Finolex Cables Limited (NSE:FINCABLES) Stock's Been Sliding But Fundamentals Look Decent: Will The Market Correct The Share Price In The Future? - simplywall.st</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Suyog Gurbaxani Funicular Ropeways Ltd. (SGFRL) Share Price Rises 8.25% Today - Univest</t>
+          <t>Finolex Cables (FINCABLES.NS) Declines 2.13% as Stock Approaches Key Support Zone - Advance Decline Line - Vinanet</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Suyog Telematics Downgraded to Sell Amid Technical and Valuation Concerns - MarketsMojo</t>
+          <t>Solid Earnings May Not Tell The Whole Story For Finolex Cables (NSE:FINCABLES) - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2074,48 +2314,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR.NS</t>
+          <t>GNFC.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>86.93000030517578</v>
+        <v>603</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>87.12000274658203</v>
+        <v>606.25</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>82.58999633789062</v>
+        <v>593.2999877929688</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>82.72000122070312</v>
+        <v>597.4500122070312</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>86.93000030517578</v>
+        <v>602.2999877929688</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>82.72000122070312</v>
+        <v>597.4500122070312</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2436130</v>
+        <v>242386</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-4.84</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>GNFC Share Price Today: 5.56% Gain, Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>GNFC Standalone June 2026 Net Sales at Rs 2,238.00 crore, up 39.79% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>GNFC transfers unclaimed equity shares to IEPF account - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2123,56 +2383,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KUSUMGAR.NS</t>
+          <t>ASIANPAINT.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>KUSUMGAR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>595.9500122070312</v>
+        <v>2635.10009765625</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>599</v>
+        <v>2641.800048828125</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>560.7000122070312</v>
+        <v>2607</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>566.3499755859375</v>
+        <v>2614.300048828125</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>595</v>
+        <v>2630.800048828125</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>566.3499755859375</v>
+        <v>2614.300048828125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>451848</v>
+        <v>191499</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.82</v>
+        <v>-0.63</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Kusumgar seeks shareholder approval to ratify ESOP scheme post-IPO - scanx.trade</t>
+          <t>ASIANPAINT Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Kusumgar seeks shareholder approval to ratify ESOP scheme post-IPO - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>ASIANPAINT Q2 FY2026 Earnings: Steady Revenue Growth of 5.1% Supports Stable Bottom Line - Earnings Revision Downgrade - Vinanet</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Investing in Asian Paints (NSE:ASIANPAINT) a year ago would have delivered you a 21% gain - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Asian Paints (ASIANPAINT) Sees Mild Dip; Support Level at ₹2,598 in Sight - Day Trade Opportunities - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>While institutions own 30% of Asian Paints Limited (NSE:ASIANPAINT), private companies are its largest shareholders with 40% ownership - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2180,48 +2452,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS.NS</t>
+          <t>IFCI.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3399.10009765625</v>
+        <v>82</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3399.10009765625</v>
+        <v>82.52999877929688</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3219</v>
+        <v>80.37000274658203</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3228.89990234375</v>
+        <v>81.25</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3391.39990234375</v>
+        <v>81.68000030517578</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3228.89990234375</v>
+        <v>81.25</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>279967</v>
+        <v>13197842</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.79</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+        <v>-0.53</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>IFCI Share Price Rises 3.19% Today: Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>IFCI Standalone June 2026 Net Sales at Rs 102.64 crore, down 34% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>IFCI Q1 Results: Revenue declines, profit improves sequentially to ₹60 crore - livemint.com</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2229,60 +2521,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM.NS</t>
+          <t>GFLLIMITED.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>878</v>
+        <v>57.95000076293945</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>878.9500122070312</v>
+        <v>57.95000076293945</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>826.5499877929688</v>
+        <v>55</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>834.1500244140625</v>
+        <v>56.54999923706055</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>874.5499877929688</v>
+        <v>56.7599983215332</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>834.1500244140625</v>
+        <v>56.54999923706055</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>377267</v>
+        <v>157949</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4.62</v>
+        <v>-0.37</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM Consolidated June 2026 Net Sales at Rs 535.80 crore, up 38.74% Y-o-Y - Moneycontrol.com</t>
+          <t>GFL Limited Gains Slightly as Stock Hovers Near Mid-Range Levels - Wide Range Bar - Vinanet</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM Consolidated June 2026 Net Sales at Rs 535.80 crore, up 38.74% Y-o-Y - Moneycontrol.com</t>
+          <t>GFL Limited Gains Slightly as Stock Hovers Near Mid-Range Levels - Wide Range Bar - Vinanet</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Mercantile Ventures Posts Consolidated Net Loss of Rs 0.65 Crore in June 2026 Quarter; Sales Climb 9.25% - Guidance Revision Trend - Vinanet</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>GFL Limited Sees Modest Gain as Stock Holds Key Support Levels - ETF Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>GFL Limited Stock Dips 1.19%: Support and Resistance Levels in Focus - TRIN Signal - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>GFL Limited (GFLLIMITED) Declines 1.54%; Support at ₹43.08 in Focus - Counter Trend Trade - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2290,48 +2590,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY.NS</t>
+          <t>HEG.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>107.5</v>
+        <v>710</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>107.75</v>
+        <v>718.6500244140625</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>101.5</v>
+        <v>696.0999755859375</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>101.7900009155273</v>
+        <v>705.9000244140625</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>106.4800033569336</v>
+        <v>708.0499877929688</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>101.7900009155273</v>
+        <v>705.9000244140625</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1242300</v>
+        <v>730425</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+        <v>-0.3</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>HEG gets NCLT nod for demerger; shareholders to receive 1:1 shares in HEG Graphite - CNBC TV18 - LinkedIn</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>HEG receives NCLT approval for demerger scheme; shareholders to get 1:1 shares in HEG Graphite - livemint.com</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>HEG Gets NCLT Approval For Demerger Plan In 1:1 Share Ratio - Sahi</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>HEG receives NCLT approval for demerger scheme; shareholders to get 1:1 shares in HEG Graphite - livemint.com</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-19 — cnbctv:02f6ca213094b:0 - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2339,48 +2659,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO.NS</t>
+          <t>WEIZMANIND.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>WEIZMANIND</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1324</v>
+        <v>76.45999908447266</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1334</v>
+        <v>76.47000122070312</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1257.800048828125</v>
+        <v>74.09999847412109</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1265.699951171875</v>
+        <v>75.66999816894531</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1324</v>
+        <v>75.90000152587891</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1265.699951171875</v>
+        <v>75.66999816894531</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>344424</v>
+        <v>195</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+        <v>-0.3</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Weizmann Limited (WEIZMANIND.NS) Faces Mild Selling Pressure as Price Holds Above Key Support - Volume Breadth - Vinanet</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Here's What We Like About Weizmann's (NSE:WEIZMANIND) Upcoming Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Here's What We Like About Weizmann's (NSE:WEIZMANIND) Upcoming Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Weizmann Limited Holds Near Support Amid Modest Gains – WEIZMANIND.NS Analysis - Fundamental Weighted - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Weizmann Limited (WEIZMANIND.NS): Mild Uptick Near ₹84.5 as Stock Holds Support Zone - Leading Diagonal - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2388,40 +2728,48 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>INDOFARM.NS</t>
+          <t>CUMMINSIND.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>INDOFARM</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>143.8999938964844</v>
+        <v>5250</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>144.1699981689453</v>
+        <v>5252.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>135.9100036621094</v>
+        <v>5192.5</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>137.1600036621094</v>
+        <v>5211</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>143.3300018310547</v>
+        <v>5220</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>137.1600036621094</v>
+        <v>5211</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>324275</v>
+        <v>122662</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+        <v>-0.17</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -2429,7 +2777,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2437,48 +2785,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SHREERAMA.NS</t>
+          <t>HLVLTD.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SHREERAMA</t>
+          <t>HLVLTD</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46.79999923706055</v>
+        <v>6.699999809265137</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>46.79999923706055</v>
+        <v>6.699999809265137</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>44.11000061035156</v>
+        <v>6.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>44.36999893188477</v>
+        <v>6.619999885559082</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46.34000015258789</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>44.36999893188477</v>
+        <v>6.619999885559082</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>113898</v>
+        <v>129901</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+        <v>-0.15</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>HLV Limited's (NSE:HLVLTD) Shares May Have Run Too Fast Too Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>HLV Limited: Navigating Resistance Near ₹8.05 Amid Modest Decline - Ratio Spread Trade - Vinanet</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>HLV Limited (HLVLTD.NS) Gains Modestly as Stock Holds Above Key Support Level - Extension Target - Vinanet</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>HLV (NSE:HLVLTD) Seems To Use Debt Quite Sensibly - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>HLV Limited (HLVLTD.NS) Gains 2.43% – Approaching Key Resistance at ₹8.42 - Monthly Profile - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2486,68 +2854,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE.NS</t>
+          <t>SBIN.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>620</v>
+        <v>1052.900024414062</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>620</v>
+        <v>1052.900024414062</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>577</v>
+        <v>1045.699951171875</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>582.5</v>
+        <v>1047</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>608.25</v>
+        <v>1048.599975585938</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>582.5</v>
+        <v>1047</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>544224</v>
+        <v>3080220</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.23</v>
+        <v>-0.15</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>API Holdings turns debt-free — frees Thyrocare shares from pledge - expresshealthcare.in</t>
+          <t>SBI Share Price - Live NSE: SBIN Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>API Holdings Clears ₹1,050 Cr Debt, Unpledges Thyrocare Stake - BW Healthcare</t>
+          <t>State Bank of India Stock Update: Shares Dip Amid Recruitment Woes, RBI Policy Shift - latestly.com</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>API Holdings repays Rs 1050 Cr, frees Thyrocare shares from pledge - BioSpectrum India</t>
+          <t>SBIN Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Why PharmEasy Keeps Selling Thyrocare Shares? - UnlistedZone</t>
+          <t>SBIN Share Price Today - State Bank Of India Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>API Holdings Clears ₹1,050 Cr Debt, Unpledges Thyrocare Stake - BW Healthcare</t>
+          <t>State Bank of India Stock Update: Share Price Dips on Recruitment Concerns - latestly.com</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2555,56 +2923,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA.NS</t>
+          <t>SUNPHARMA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>730</v>
+        <v>1905</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>730</v>
+        <v>1911.599975585938</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>710.1500244140625</v>
+        <v>1890.300048828125</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>721.2999877929688</v>
+        <v>1898</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>753.0999755859375</v>
+        <v>1900</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>721.2999877929688</v>
+        <v>1898</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>770121</v>
+        <v>501385</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.22</v>
+        <v>-0.11</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Here's What Analysts Are Forecasting For Bata India Limited (NSE:BATAINDIA) After Its First-Quarter Results - simplywall.st</t>
+          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Here's What Analysts Are Forecasting For Bata India Limited (NSE:BATAINDIA) After Its First-Quarter Results - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Why is Sun Pharmaceutical Industries stock falling today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Results: Sun Pharmaceutical Industries Limited Exceeded Expectations And The Consensus Has Updated Its Estimates - simplywall.st</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2612,48 +2988,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>KRISHNADEF.NS</t>
+          <t>HIMATSEIDE.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>KRISHNADEF</t>
+          <t>HIMATSEIDE</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1130</v>
+        <v>70.09999847412109</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1143.699951171875</v>
+        <v>71.69999694824219</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1072</v>
+        <v>69.05999755859375</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1077.800048828125</v>
+        <v>71.47000122070312</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1125</v>
+        <v/>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1077.800048828125</v>
+        <v>71.47000122070312</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>94943</v>
+        <v>444716</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Himatsingka Seide Limited. Actuals &amp; Estimates (NSE:HIMATSEIDE) - TradingView</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>HIMATSEIDE Q2 2026 Earnings: Revenue Declines 9.5% YoY; EPS at ₹4.93 Amid Challenging Textile Demand - Vinanet</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Himatsingka Seide Share Price Target 2026: Rs 89 Analyst Forecast - Univest</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Himatsingka Seide Falls 3% – Stock Nears Key Support at ₹73.50 Amid Weaker Textile Sentiment - RVOL Spike - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Here's What We Like About Himatsingka Seide's (NSE:HIMATSEIDE) Upcoming Dividend - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2661,60 +3057,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>POWERINDIA.NS</t>
+          <t>WILLAMAGOR.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>WILLAMAGOR</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>35100</v>
+        <v>25.10000038146973</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>35100</v>
+        <v>25.71999931335449</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>33360</v>
+        <v>24.5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>33800</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>35275</v>
+        <v/>
       </c>
       <c r="J18" s="2" t="n">
-        <v>33800</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>186593</v>
+        <v>1647</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.18</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Hitachi Energy India Stock Leads A Fresh Look At Power Capex Winners - simplywall.st</t>
+          <t>Williamson Magor (WILLAMAGOR.NS) Gains 3.58% – Support and Resistance Levels in Focus - Trade Entry Signals - Vinanet</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Hitachi Energy India Stock Leads A Fresh Look At Power Capex Winners - simplywall.st</t>
+          <t>Williamson Magor Q2 2026 Earnings: Revenue Plunges 46% YoY as Investment Holding Company Posts Net Loss - Return On Equity - Vinanet</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>POWERINDIA Share Price | Hitachi Energy India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Williamson Magor Holds Near Support; Resistance Test Ahead for WILLAMAGOR.NS - Scalping Stock Signals - Vinanet</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR Q2 2025 Earnings: Revenue Growth of 18.1% Driven by Higher Other Income, but Net Loss Deepens to ₹165.56 Per Share - Analyst Coverage Count - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR Stock Price and Chart — NSE:WILLAMAGOR - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2722,64 +3126,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>FILATEX.NS</t>
+          <t>VINDHYATEL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>FILATEX</t>
+          <t>VINDHYATEL</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>86.5</v>
+        <v>2459</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>86.59999847412109</v>
+        <v>2498</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>82.51000213623047</v>
+        <v>2421.89990234375</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>83.15000152587891</v>
+        <v>2439.199951171875</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>86.75</v>
+        <v/>
       </c>
       <c r="J19" s="2" t="n">
-        <v>83.15000152587891</v>
+        <v>2439.199951171875</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1502803</v>
+        <v>13066</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.15</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions fined ₹56,640 each by NSE and BSE for compliance lapse - scanx.trade</t>
+          <t>Vindhya Telelinks Limited's (NSE:VINDHYATEL) largest shareholders are individual investors who were rewarded as market cap surged ₹2.6b last week - simplywall.st</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions Share News Today,filatex Fashions Share Analysis,filatex Fashions Share Price/news Julio Rodríguez (hxc2EVlwyH) - Mshale</t>
+          <t>VINDHYATEL Mar 2026 Earnings: EPS of ₹16.75 on Revenue of ₹1,005.0 Crore; Stock Declines 1.5% - Estimate Dispersion - Vinanet</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashion | Filatex Fashion Share Latest News | Filatex Fashion News | Filatex Fashion Share Cigarette (pEVfqWC9K9) - Mshale</t>
+          <t>VINDHYATEL Stock Price and Chart — NSE:VINDHYATEL - TradingView</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions Share News Today,filatex Fashions Share Analysis,filatex Fashions Share Price/news Julio Rodríguez (hxc2EVlwyH) - Mshale</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Vindhya Telelinks (VINDHYATEL.NS) Retreats from Resistance, Tests Key Support Levels - MAMA Signal - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Vindhya Telelinks (VINDHYATEL.NS): Modest Decline as Stock Consolidates Near Key Support Levels - Flat Correction - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2787,48 +3195,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>GUJRAFFIA.NS</t>
+          <t>ESCORTS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GUJRAFFIA</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>42.45000076293945</v>
+        <v>3059.60009765625</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>42.45000076293945</v>
+        <v>3099</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40.2599983215332</v>
+        <v>3059</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>40.65999984741211</v>
+        <v>3087.699951171875</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>42.40999984741211</v>
+        <v/>
       </c>
       <c r="J20" s="2" t="n">
-        <v>40.65999984741211</v>
+        <v>3087.699951171875</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2024</v>
+        <v>35023</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.13</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Shares Fall 2.13% to Rs 3,067.00 Amid Bullish Sentiment - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Q1FY27: Revenue jumps 28% Y-o-Y, profit at ₹386 crore - business-standard.com</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Escorts Kubota schedules analyst meet with Valuequest on Aug 21 - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:55:20</t>
+          <t>2026-08-20 07:04:21</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2836,40 +3264,48 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3MINDIA.NS</t>
+          <t>JAYSREETEA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>JAYSREETEA</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>35100</v>
+        <v>94.52999877929688</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>35100</v>
+        <v>99.40000152587891</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>33355</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>33505</v>
+        <v>99.19999694824219</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>34945</v>
+        <v/>
       </c>
       <c r="J21" s="2" t="n">
-        <v>33505</v>
+        <v>99.19999694824219</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>7449</v>
+        <v>173240</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -436,10 +436,10 @@
   <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>BALRAMCHIN.NS</t>
+          <t>KRONOX.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>Kronox Lab Sciences Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>658.25</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>738.9500122070312</v>
+        <v>178.6999969482422</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>655.0499877929688</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>736.7999877929688</v>
+        <v>176.0500030517578</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>650.7999877929688</v>
+        <v>155.1600036621094</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>736.7999877929688</v>
+        <v>176.0500030517578</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>12573227</v>
+        <v>2949367</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>13.21</v>
+        <v>13.46</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+          <t>Rs 246 Crore Acquisition: Indo Borax &amp; Chemicals to Acquire 64.26% Stake in Kronox Lab Sciences; Share Price Rises 7% - insights.dsij.in</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+          <t>Momentum Stocks: Kronox Lab Sciences, Waterways Leisure, Genus Power rise up to % on sheer momentum - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+          <t>Indo Borax acquires 64.26% stake in Kronox Lab Sciences for ₹246.12 crore - scanx.trade</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+          <t>Kronox Lab Sciences Q1 Results: Net profit up 60% YoY to ₹25.8 crore - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND</t>
+          <t>Balrampur Chini Mills Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20.73999977111816</v>
+        <v>658.25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>22.6200008392334</v>
+        <v>739.8499755859375</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20.59000015258789</v>
+        <v>655.0499877929688</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>22.17000007629395</v>
+        <v>734</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20.3799991607666</v>
+        <v>650.7999877929688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22.17000007629395</v>
+        <v>734</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>131939293</v>
+        <v>14806969</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>12.78</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>We Think That There Are Some Issues For Bajaj Hindusthan Sugar (NSE:BAJAJHIND) Beyond Its Promising Earnings - simplywall.st</t>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND Mar 2026 Earnings: Solid EPS of ₹1.65 on Revenue of ₹1,657 Crore - Downward Estimate Revision - Vinanet</t>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND Mar 2026 Earnings: Solid EPS of ₹1.65 on Revenue of ₹1,657 Crore - Downward Estimate Revision - Vinanet</t>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>There's No Escaping Bajaj Hindusthan Sugar Limited's (NSE:BAJAJHIND) Muted Revenues - simplywall.st</t>
+          <t>Earnings call transcript: Balrampur Chini Mills Q1 2026 stock falls as outlook stays firm - Investing.com</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND Mar 2026 Earnings: EPS of ₹1.65 on Revenue of ₹1,657 Crore as Sugar &amp; Ethanol Operations Hold Steady - Long-Term Guidance - Vinanet</t>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG.NS</t>
+          <t>DWARKESH.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG</t>
+          <t>Dwarikesh Sugar Industries Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37.0099983215332</v>
+        <v>48.77000045776367</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>40.79000091552734</v>
+        <v>55.25</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>37</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>39.65000152587891</v>
+        <v>54.34000015258789</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>36.90000152587891</v>
+        <v>48.27999877929688</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39.65000152587891</v>
+        <v>54.34000015258789</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>487665</v>
+        <v>25736600</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7.45</v>
+        <v>12.55</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars (RAJSREESUG.NS) Holds Near Support as Sugar Sector Awaits Policy Clarity - Fund Manager Survey - Vinanet</t>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars (RAJSREESUG.NS) Holds Near Support as Sugar Sector Awaits Policy Clarity - Fund Manager Survey - Vinanet</t>
+          <t>Is It Worth Considering Dwarikesh Sugar Industries Limited (NSE:DWARKESH) For Its Upcoming Dividend? - simplywall.st</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugar &amp; Chem Share Price - Upstox</t>
+          <t>Dwarikesh Sugar Industries Ltd. Share Price: Major Drop - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +760,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DHAMPURSUG.NS</t>
+          <t>KOHINOOR.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>DHAMPURSUG</t>
+          <t>Kohinoor Foods Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>179.6999969482422</v>
+        <v>32.09999847412109</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>190.75</v>
+        <v>35.75</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>178.9700012207031</v>
+        <v>30.95000076293945</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>188</v>
+        <v>35.04999923706055</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>176.1799926757812</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>188</v>
+        <v>35.04999923706055</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3569317</v>
+        <v>1400201</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>6.71</v>
+        <v>12.09</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills (DHAMPURSUG) Gains 2.33%: Support Holds amid Sugar Sector Activity - Bearish Pattern Stocks - Vinanet</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Q2 2026 Earnings: EPS of ₹10.09 on Steady Revenue of ₹19,674.4 Million - Basic EPS Analysis - Vinanet</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills (DHAMPURSUG.NS): Mild Decline as Price Hovers Near Support Zone - Fibonacci Fan - Vinanet</t>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - marketsmojo.com</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Share Price - Live NSE: DHAMPURSUG Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Dhampur Sugar Mills Fined by Uttar Pradesh Excise Authority for Storage Lapses - The Globe and Mail</t>
-        </is>
-      </c>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,68 +825,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ZUARIIND.NS</t>
+          <t>KWIL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ZUARIIND</t>
+          <t>Kwality Wall's (India) Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>268.8999938964844</v>
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>284.8999938964844</v>
+        <v>42.2400016784668</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>261.8500061035156</v>
+        <v>37.75</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>42.11000061035156</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>262.1000061035156</v>
+        <v>37.70999908447266</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>278.7999877929688</v>
+        <v>42.11000061035156</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>283179</v>
+        <v>39174599</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6.37</v>
+        <v>11.67</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Zuari Industries Limited's (NSE:ZUARIIND) 25% Price Boost Is Out Of Tune With Revenues - simplywall.st</t>
+          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>ZUARIIND Q2 FY26 Earnings: Revenue Grows 7.68% YoY to ₹1,044.82 Crore, EPS at ₹36.25 - Next Quarter Guidance - Vinanet</t>
+          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ZUARI Industries (ZUARIIND.NS) Slips Over 3% as Selling Pressure Intensifies - Narrow Range Breakout - Vinanet</t>
+          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>ZUARIIND Stock Price and Chart — NSE:ZUARIIND - TradingView</t>
+          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - thehindu.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>ZUARIIND Q2 FY26 Earnings: Revenue Grows 7.68% YoY to ₹1,044.82 Crore, EPS at ₹36.25 - Next Quarter Guidance - Vinanet</t>
+          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -898,68 +894,60 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ARVIND.NS</t>
+          <t>KOTARISUG.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>Kothari Sugars And Chemicals Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>519.9000244140625</v>
+        <v>27.8799991607666</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>541</v>
+        <v>31.39999961853027</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>519.5499877929688</v>
+        <v>27.68000030517578</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>534.75</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>516.5</v>
+        <v>27.21999931335449</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>534.75</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>541059</v>
+        <v>817791</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>3.53</v>
+        <v>10.95</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Arvind posts strong Q1 2026 growth, shares slip - Investing.com</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Arvind sees no immediate acquisitions, focuses on Dalco GFT integration - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Rubrik CTO Arvind Nithrakashyap Sells $3.0 Million Stock - The Motley Fool</t>
-        </is>
-      </c>
+          <t>Are Wall Street Analysts Predicting PepsiCo Stock Will Climb or Sink? - Earnings Call Q&amp;A - Vinanet</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -967,60 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EIDPARRY.NS</t>
+          <t>SUVEN.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>EIDPARRY</t>
+          <t>Suven Life Sciences Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>793.7999877929688</v>
+        <v>335</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>814.8499755859375</v>
+        <v>367.8500061035156</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>787.5499877929688</v>
+        <v>335</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>803.4500122070312</v>
+        <v>367.3999938964844</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>787.0499877929688</v>
+        <v>332.5499877929688</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>803.4500122070312</v>
+        <v>367.3999938964844</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1151102</v>
+        <v>1501088</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2.08</v>
+        <v>10.48</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Raja Venkatraman recommends three stocks for 5 August - livemint.com</t>
+          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
+          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences seeks AGM approval for related party transaction and fund reallocation - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1028,68 +1024,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DCW.NS</t>
+          <t>MAWANASUG.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DCW</t>
+          <t>Mawana Sugars Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>43.47000122070312</v>
+        <v>130.9900054931641</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>44.38000106811523</v>
+        <v>143.1499938964844</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>43.33000183105469</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>44.13000106811523</v>
+        <v>141.7100067138672</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>43.2599983215332</v>
+        <v>128.7200012207031</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>44.13000106811523</v>
+        <v>141.7100067138672</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>383685</v>
+        <v>1294171</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2.01</v>
+        <v>10.09</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>DCW Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+          <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>‘Call 181, receive justice quickly’: Delhi DCW Chair Lata Gupta's first message after appointment - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>DCW Limited to host Q1FY27 earnings call on August 14 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1097,56 +1081,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>BOMDYEING.NS</t>
+          <t>CORDELIA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>BOMDYEING</t>
+          <t>Waterways Leisure Tourism Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>113.2399978637695</v>
+        <v>820.5499877929688</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>113.4300003051758</v>
+        <v>907.75</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>112.6600036621094</v>
+        <v>820.5499877929688</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>113</v>
+        <v>907.75</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>111.5699996948242</v>
+        <v>825.25</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>113</v>
+        <v>907.75</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>144788</v>
+        <v>686273</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.28</v>
+        <v>10</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
+          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Share Market News: Waterways Leisure Tourism's profit increases 28 percent in first quarter post listing, rev - India.com</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1154,68 +1146,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SAIL.NS</t>
+          <t>NETWORK18.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Network18 Media &amp; Investments Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>174.1000061035156</v>
+        <v>28.23999977111816</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>176.4299926757812</v>
+        <v>31.21999931335449</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>173.4100036621094</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>174.8999938964844</v>
+        <v>30.86000061035156</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>172.75</v>
+        <v>28.06999969482422</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>174.8999938964844</v>
+        <v>30.86000061035156</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>7842795</v>
+        <v>24924047</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1.24</v>
+        <v>9.94</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+          <t>Network18 Media &amp; Investments schedules 31st AGM for September 16 - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+          <t>Network18 Media &amp; Investments schedules 31st AGM for September 16 - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>CrowdStrike Setup 'Constructive,' But Truist Favors Rubrik, SailPoint Ahead Of Q2 Earnings - TradingView</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Metal tanks 3% in two days on profit-taking; NALCO, SAIL top losers - business-standard.com</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>SailPoint (SAIL) Outlook: Records a Muted Move to $19.19 on the Day; Chart View: Price Remains Between $18.23 Support and $20.15 Resistance in the Latest Session - Daily Profile - Vinanet</t>
-        </is>
-      </c>
+          <t>Network18 sets Oct 1 hearing for News18 Marathi amalgamation - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1223,68 +1207,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>INFY.NS</t>
+          <t>RANASUG.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>Rana Sugars Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1143</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1144.699951171875</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1125.699951171875</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1130.300048828125</v>
+        <v>15.02999973297119</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1119.800048828125</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1130.300048828125</v>
+        <v>15.02999973297119</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>4384372</v>
+        <v>2286027</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
+          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Infosys Ltd (INFY) Stock Down 3.9% -- Now Undervalued? GF Score: 86/100 - GuruFocus</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Infosys (NSEI:INFY) Stock Fair Value Falls After Analysts Cut Targets On Weaker Outlook - Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>INFY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
-        </is>
-      </c>
+          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1292,56 +1264,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ASHOKLEY.NS</t>
+          <t>SIGACHI.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>Sigachi Industries Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>174.6999969482422</v>
+        <v>29</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>175.5700073242188</v>
+        <v>31.81999969482422</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>173.7400054931641</v>
+        <v>29</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>174.6000061035156</v>
+        <v>31.51000022888184</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>173.1000061035156</v>
+        <v>28.8799991607666</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>174.6000061035156</v>
+        <v>31.51000022888184</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3036626</v>
+        <v>6444144</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0.87</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Sigachi Industries board to consider preferential issue on August 22 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Sigachi Ind Q1 Results FY27: PAT Rs 8 Cr, Revenue Rs 121 crore - Univest</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Sigachi Industries postpones Q1FY27 earnings call due to unavoidable circumstances - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1349,56 +1333,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>Bajaj Hindusthan Sugar Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>219.8999938964844</v>
+        <v>20.73999977111816</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>222.0899963378906</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>216.8000030517578</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>220.3300018310547</v>
+        <v>22.19000053405762</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>218.7100067138672</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>220.3300018310547</v>
+        <v>22.19000053405762</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>645331</v>
+        <v>145436948</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.74</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1406,56 +1394,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CGPOWER.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>868.5499877929688</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>874</v>
+        <v>42.70000076293945</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>862.6500244140625</v>
+        <v>39.45999908447266</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>868.6500244140625</v>
+        <v>42.54999923706055</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>863.0499877929688</v>
+        <v>39.13000106811523</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>868.6500244140625</v>
+        <v>42.54999923706055</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1012503</v>
+        <v>2238046</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.65</v>
+        <v>8.74</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Share Price Forecast: 3 Year Outlook to 2030 - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1463,64 +1463,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>FEDERALBNK.NS</t>
+          <t>RAJSREESUG.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>Rajshree Sugars &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>361.8999938964844</v>
+        <v>37.0099983215332</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>364.2000122070312</v>
+        <v>40.79000091552734</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>360.25</v>
+        <v>37</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>361</v>
+        <v>40.09999847412109</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>358.7999877929688</v>
+        <v>36.90000152587891</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>361</v>
+        <v>40.09999847412109</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2183173</v>
+        <v>509524</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.61</v>
+        <v>8.67</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Federal Bank (NSEI:FEDERALBNK) Stock Gets Fair Value Boost Before Board Results Review - Yahoo Finance</t>
+          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>The Federal Bank Ltd. (FEDERALBNK) Share Price Hits 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Rajshree Sugars &amp; Chemicals Ltd: Stock Climbs 1.67%, Testing Key Resistance at ₹35.72 - Mean Reversion Trade - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1528,56 +1532,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN.NS</t>
+          <t>KAYA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>Kaya Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>885</v>
+        <v>339.9500122070312</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>892</v>
+        <v>370</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>884.7999877929688</v>
+        <v>336.5499877929688</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>889.7000122070312</v>
+        <v>365.25</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>884.9000244140625</v>
+        <v>338.4500122070312</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>889.7000122070312</v>
+        <v>365.25</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>9790</v>
+        <v>119931</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.54</v>
+        <v>7.92</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+          <t>Scholastic director Kaya Henderson sells $130,812 in stock - Investing.com</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Kaya To Issue 1.82 Million Equity Shares At 274.10 Rupees Per Share For Aggregate Cash Consideration Of Approx 500 Million Rupees - TradingView</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Kaya Standalone June 2026 Net Sales at Rs 60.14 crore, up 13.91% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1585,68 +1601,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ABB.NS</t>
+          <t>DHAMPURSUG.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dhampur Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7450.5</v>
+        <v>179.6999969482422</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7481.5</v>
+        <v>190.75</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>7393</v>
+        <v>178.9700012207031</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7461.5</v>
+        <v>189.2100067138672</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7430</v>
+        <v>176.1799926757812</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7461.5</v>
+        <v>189.2100067138672</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>115415</v>
+        <v>3891705</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.42</v>
+        <v>7.4</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>ABB stock benefits from strong Q2 orders as valuation debate grows - Ad-hoc-news.de</t>
+          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+          <t>Dhampur Sugar to Consider Quarterly Results Tomorrow; Stock Declines 2.75% in Previous Session - TradingView</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>ABB Ltd: ABB share buybacks - August 6, 2026 - August 12, 2026 - TradingView</t>
+          <t>Dhampur Sugar Mills sets book closure dates for 91st AGM - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Is ABB (SWX:ABBN) Fully Priced Following Its LevelTen Energy Deal? - simplywall.st</t>
+          <t>Dhampur Sugar Mills settles ₹100 crore commercial paper - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1654,56 +1670,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR.NS</t>
+          <t>NIBE.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NIBE Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2022.900024414062</v>
+        <v>1435</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2041.699951171875</v>
+        <v>1542.800048828125</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2018.199951171875</v>
+        <v>1421</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2029</v>
+        <v>1513</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2020.699951171875</v>
+        <v>1411.099975585938</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2029</v>
+        <v>1513</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>684111</v>
+        <v>254734</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.41</v>
+        <v>7.22</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+          <t>NIBE Q1 FY27 Results: Revenue fell to Rs 63 Cr, Net Loss -1300% - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Di: This is what it will take for the Nibe stock to gain momentum - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Di: This is what it will take for the Nibe stock to gain momentum - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Nibe Industrier stock holds steady as leadership change adds to long term growth story - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Nibe Industrier stock holds firm after Q2 sales rose - Ad-hoc-news.de</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1711,68 +1739,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VOLTAS.NS</t>
+          <t>KIRIINDUS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>Kiri Industries Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1234</v>
+        <v>435</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1234</v>
+        <v>479.9500122070312</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1215.599975585938</v>
+        <v>434</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1227.699951171875</v>
+        <v>462</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1223</v>
+        <v>431.2999877929688</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1227.699951171875</v>
+        <v>462</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>710177</v>
+        <v>5177321</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.38</v>
+        <v>7.12</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Voltas stock falls 4% after Q1, top midcap loser; brokerages split as margin concerns outweigh strong AC... - Moneycontrol.com</t>
+          <t>Kiri Industries Limited (NSE:KIRIINDUS) Stock Rockets 34% As Investors Are Less Pessimistic Than Expected - simplywall.st</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Voltas Share Price Declines 2.05% in Mid-Morning Trade - Moneycontrol.com</t>
+          <t>KIRIINDUS.NS Q2 2026 Earnings: Robust Profitability Amidst Modest Revenue Growth - Earnings Cycle Report - Vinanet</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Voltas shares fall 6% from intraday high post Q1; brokerages split - BusinessLine</t>
+          <t>Kiri Industries (KIRIINDUS) Stock Consolidates Near Key Support Amid Modest Decline - Percent Above MA - Vinanet</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Voltas shares slip 4% despite strong Q1 show; analysts flag margin risk - business-standard.com</t>
+          <t>KIRIDYES.BO interactive stock chart | Kiri Industries Limited stock - Yahoo Finance Australia</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Voltas posts strong Q1 2026 profit growth, shares rise 2.4% - Investing.com</t>
+          <t>Shareholders Shouldn’t Be Too Comfortable With Kiri Industries' (NSE:KIRIINDUS) Strong Earnings - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1780,61 +1808,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CANFINHOME.NS</t>
+          <t>DALMIASUG.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CANFINHOME</t>
+          <t>Dalmia Bharat Sugar and Industries Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>821.4000244140625</v>
+        <v>475.8500061035156</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>829.7999877929688</v>
+        <v>517</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>817.9000244140625</v>
+        <v>469.2000122070312</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>820.4500122070312</v>
+        <v>508.5</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>817.6500244140625</v>
+        <v>475.5499877929688</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>820.4500122070312</v>
+        <v>508.5</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>118262</v>
+        <v>1379021</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.34</v>
+        <v>6.93</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>CANFINHOME Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>Dalmia Bharat Sugar and Industries Limited (NSE:DALMIASUG) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹560 - simplywall.st</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>CANFINHOME Mar 2026 Earnings: EPS of ₹25.96 Reflects Steady Performance Amidst Housing Finance Sector Tailwinds - Estimate Uncertainty - Vinanet</t>
+          <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today - 20 August 2026 - TradingView</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Can Fin Homes (CANFINHOME) Holds Steady at ₹886 – Key Levels in Focus - Chandelier Stop - Vinanet</t>
+          <t>Dalmia Bharat Sugar And Industries Ltd. (DALMIASUG) Share Price Rises 14.03% Today - Univest</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Can Fin Homes Ltd (CANFINHOME.NS) Falls 5.5% – Testing Key Support Near ₹795 - Fear Greed Extreme - Vinanet</t>
+          <t>Dalmia Bharat Sugar Share Price Technicals and Market Cap - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Can Fin Homes (NSE:CANFINHOME) Makes An Interesting Case - simplywall.st</t>
+          <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today - 20 August 2026 - TradingView</t>
         </is>
       </c>
     </row>
@@ -1852,10 +1880,10 @@
   <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1961,7 +1989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1969,68 +1997,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GLFL.NS</t>
+          <t>INDOMIM.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>GLFL</t>
+          <t>INDO-MIM Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6</v>
+        <v>965</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6</v>
+        <v>965</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5.639999866485596</v>
+        <v>907.2999877929688</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5.639999866485596</v>
+        <v>918.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5.820000171661377</v>
+        <v>967.9500122070312</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5.639999866485596</v>
+        <v>918.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>143</v>
+        <v>2577690</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-3.09</v>
+        <v>-5.11</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing (GLFL) Slips 2%: Stock Tests Key Support at ₹6.05 - Long Short Pair - Vinanet</t>
+          <t>INDO-MIM LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing Limited (GLFL.NS): Consolidating Near Support at ₹6.0 Amidst Stalled Momentum - Value ETF - Vinanet</t>
+          <t>INDO-MIM Board Clears Q1 FY27 Unaudited Results, Publishes in Newspapers - TipRanks</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing Limited (GLFL.NS): Consolidating Near Support at ₹6.0 Amidst Stalled Momentum - Value ETF - Vinanet</t>
+          <t>INDOMIM Share Price Today - INDO-MIM LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing Limited (GLFL.NS) Q2 2025 Earnings: Minimal EPS of ₹0.02 Reflecting Subdued Activity - Vinanet</t>
+          <t>IndoMIM Share Price Today - Indo-MIM Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing (GLFL) Slips 1.96% as Stock Tests Critical Support Zone - Passive Flow - Vinanet</t>
+          <t>Indo-MIM IPO: GMP jumps as issue subscribed 72.34 times - livemint.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2038,68 +2066,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CESC.NS</t>
+          <t>SIEL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>Superior Industrial Enterprises Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>159.2100067138672</v>
+        <v>44.54000091552734</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>160.1999969482422</v>
+        <v>44.54000091552734</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>156.5599975585938</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>157.3500061035156</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>159.6600036621094</v>
+        <v>42.41999816894531</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>157.3500061035156</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1144241</v>
+        <v>8873</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-1.45</v>
+        <v>-5</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>For CESC investors, renewable energy should yield dual benefits of stock rerating and growth - Moneycontrol.com</t>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>CESC Limited Earnings Missed Analyst Estimates: Here's What Analysts Are Forecasting Now - simplywall.st</t>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>CESC Ltd soars 1.23% - business-standard.com</t>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2107,68 +2135,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BPL.NS</t>
+          <t>UCAL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>BPL</t>
+          <t>UCAL LIMITED</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>50.90000152587891</v>
+        <v>147.8999938964844</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>50.91999816894531</v>
+        <v>147.8999938964844</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>49.41999816894531</v>
+        <v>138.8800048828125</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>49.63000106811523</v>
+        <v>140.0099945068359</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>50.33000183105469</v>
+        <v>146.1799926757812</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>49.63000106811523</v>
+        <v>140.0099945068359</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>23151</v>
+        <v>26454</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-1.39</v>
+        <v>-4.22</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>This consumer electronics firm shares hit 20% upper circuit after NCLT move; what investors need to know - Upstox</t>
+          <t>UCAL Ltd. Share Price Near 52-Week High Analysis - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Eli Lilly to Boost Neuroscience Pipeline With AtaiBeckley Buyout - TradingView</t>
+          <t>UCAL Ltd. Share Price Near 52-Week High Analysis - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>BPL Share Price Forecast: 3 Year Outlook to 2030 - Univest</t>
+          <t>UCAL Ltd. Share Price Today: 9.08% Rise, Valuation Check - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>AtaiBeckley Stock Outlook Depends on Key Pipeline Catalysts in 2026 - TradingView</t>
+          <t>UCAL Share Price Rises 10.34%: Technicals, Fundamentals - Univest</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>BPL Limited (BPL.NS) Gains 3.31% as Price Approaches Key Resistance at ₹59.98 - ETF Outflow Streak - Vinanet</t>
+          <t>Ucal reports consolidated net profit of Rs 5.84 crore in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2176,68 +2204,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>KUANTUM.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>Kuantum Papers Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1922</v>
+        <v>76.25</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1928.400024414062</v>
+        <v>77.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1882.099975585938</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1883.800048828125</v>
+        <v>75.37999725341797</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1903.699951171875</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1883.800048828125</v>
+        <v>75.37999725341797</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>89876</v>
+        <v>237483</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-1.05</v>
+        <v>-4.22</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Ipca Laboratories Ltd. Share Price Fall: Price Action View - Univest</t>
+          <t>Kuantum Papers Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+          <t>Mazagon Dock and 9 Other Stocks in Focus as They Turn Ex-Dividend Tomorrow - Trade Brains</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ipca Laboratories Ltd. Stock News: Share Price Up 4.76% - Univest</t>
+          <t>Kuantum Papers proposes ₹2.50 dividend, sets August 27 AGM date - scanx.trade</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Ipca Laboratories shares fall over 2%; strong financial performance reported - TradingView</t>
+          <t>Kuantum Papers declares ₹2.50 dividend for FY26, sets Aug 20 record date - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+          <t>Kuantum Papers reports 100% sustainable sourcing in FY26 BRSR filing - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2245,68 +2273,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>FINCABLES.NS</t>
+          <t>AHLADA.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>Ahlada Engineers Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1313.699951171875</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1331</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1301.449951171875</v>
+        <v>38.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1301.75</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1313.699951171875</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1301.75</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>283491</v>
+        <v>32335</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.91</v>
+        <v>-3.72</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>FINCABLES Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>Ahlada Engineers to hold 21st AGM on August 5, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables Declines Over 3.5%, Finds Support Near ₹995.6 - Donchian Channel - Vinanet</t>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - marketsmojo.com</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables Limited (NSE:FINCABLES) Stock's Been Sliding But Fundamentals Look Decent: Will The Market Correct The Share Price In The Future? - simplywall.st</t>
+          <t>RYN Q1 2026 Earnings: EPS of $0.07 Delivers 112.94% Surprise, Shares Gain 1.82% - Management Tone Analysis - Vinanet</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables (FINCABLES.NS) Declines 2.13% as Stock Approaches Key Support Zone - Advance Decline Line - Vinanet</t>
+          <t>15 Best Bank Account Bonuses of August 2026: Earn Up to $3,000 in Cash Rewards - Next Quarter Guidance - Vinanet</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Solid Earnings May Not Tell The Whole Story For Finolex Cables (NSE:FINCABLES) - simplywall.st</t>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - marketsmojo.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2314,68 +2342,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GNFC.NS</t>
+          <t>ASTERDM.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>Aster DM Quality Care Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>603</v>
+        <v>798.3499755859375</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>606.25</v>
+        <v>798.3499755859375</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>593.2999877929688</v>
+        <v>771.0499877929688</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>597.4500122070312</v>
+        <v>776.4000244140625</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>602.2999877929688</v>
+        <v>800.2000122070312</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>597.4500122070312</v>
+        <v>776.4000244140625</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>242386</v>
+        <v>3948903</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.97</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>GNFC Share Price Today: 5.56% Gain, Price Action Analysis - Univest</t>
+          <t>Aster DM Healthcare to rename as Aster DM Quality Care Limited - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+          <t>Aster DM Healthcare: Over 84M Shares Pledged as Security - InvestyWise</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>GNFC Standalone June 2026 Net Sales at Rs 2,238.00 crore, up 39.79% Y-o-Y - Moneycontrol.com</t>
+          <t>Aster DM Healthcare Ltd. Share Price Fall and Market Action - Univest</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>GNFC transfers unclaimed equity shares to IEPF account - scanx.trade</t>
+          <t>Aster DM Healthcare Ltd. (ASTERDM) Share Price Hits Fresh 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2383,68 +2411,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT.NS</t>
+          <t>FCL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2635.10009765625</v>
+        <v>45.09999847412109</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2641.800048828125</v>
+        <v>45.47999954223633</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2607</v>
+        <v>43.36999893188477</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2614.300048828125</v>
+        <v>43.65000152587891</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2630.800048828125</v>
+        <v>44.97999954223633</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2614.300048828125</v>
+        <v>43.65000152587891</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>191499</v>
+        <v>6874033</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.63</v>
+        <v>-2.96</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT Q2 FY2026 Earnings: Steady Revenue Growth of 5.1% Supports Stable Bottom Line - Earnings Revision Downgrade - Vinanet</t>
+          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Investing in Asian Paints (NSE:ASIANPAINT) a year ago would have delivered you a 21% gain - simplywall.st</t>
+          <t>Why Are Investors Watching Fineos (ASX:FCL) After Its Latest Share Price Decline? - Kalkine</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Asian Paints (ASIANPAINT) Sees Mild Dip; Support Level at ₹2,598 in Sight - Day Trade Opportunities - Vinanet</t>
+          <t>Fineos (ASX: FCL) Crosses Profitability Inflection Point In H1 FY 2026 - arichlife.com.au</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>While institutions own 30% of Asian Paints Limited (NSE:ASIANPAINT), private companies are its largest shareholders with 40% ownership - simplywall.st</t>
+          <t>Manulife Ideal Cnd Div Growth7575 FCL (0P000180PM.TO) interactive stock chart - uk.finance.yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2452,68 +2480,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>CHENNPETRO.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>Chennai Petroleum Corporation Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>82</v>
+        <v>1457</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>82.52999877929688</v>
+        <v>1466</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>80.37000274658203</v>
+        <v>1379.599975585938</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>81.25</v>
+        <v>1397.800048828125</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>81.68000030517578</v>
+        <v>1440.300048828125</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>81.25</v>
+        <v>1397.800048828125</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>13197842</v>
+        <v>1565064</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.53</v>
+        <v>-2.95</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+          <t>Chennai Petroleum Corporation Limited (NSE:CHENNPETRO) Looks Interesting, And It's About To Pay A Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>IFCI Share Price Rises 3.19% Today: Price Action Analysis - Univest</t>
+          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Rises 5.01% Today - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>IFCI Standalone June 2026 Net Sales at Rs 102.64 crore, down 34% Y-o-Y - Moneycontrol.com</t>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>IFCI Q1 Results: Revenue declines, profit improves sequentially to ₹60 crore - livemint.com</t>
+          <t>Chennai Petroleum Corporation Ltd. Stock News: Price Up 5.8% - Univest</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2521,68 +2549,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GFLLIMITED.NS</t>
+          <t>MILKYMIST.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>Milky Mist Dairy Food Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>57.95000076293945</v>
+        <v>207.8000030517578</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>57.95000076293945</v>
+        <v>211.8000030517578</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>55</v>
+        <v>191.25</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.54999923706055</v>
+        <v>194.0700073242188</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>56.7599983215332</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>56.54999923706055</v>
+        <v>194.0700073242188</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>157949</v>
+        <v>42030536</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.37</v>
+        <v>-2.79</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>GFL Limited Gains Slightly as Stock Hovers Near Mid-Range Levels - Wide Range Bar - Vinanet</t>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>GFL Limited Gains Slightly as Stock Hovers Near Mid-Range Levels - Wide Range Bar - Vinanet</t>
+          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>GFL Limited Sees Modest Gain as Stock Holds Key Support Levels - ETF Flow - Vinanet</t>
+          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>GFL Limited Stock Dips 1.19%: Support and Resistance Levels in Focus - TRIN Signal - Vinanet</t>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>GFL Limited (GFLLIMITED) Declines 1.54%; Support at ₹43.08 in Focus - Counter Trend Trade - Vinanet</t>
+          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2590,68 +2618,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HEG.NS</t>
+          <t>DREDGECORP.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>HEG</t>
+          <t>Dredging Corporation of India Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>710</v>
+        <v>1199</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>718.6500244140625</v>
+        <v>1204</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>696.0999755859375</v>
+        <v>1154.800048828125</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>705.9000244140625</v>
+        <v>1156</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>708.0499877929688</v>
+        <v>1189.199951171875</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>705.9000244140625</v>
+        <v>1156</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>730425</v>
+        <v>114984</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-0.3</v>
+        <v>-2.79</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>HEG gets NCLT nod for demerger; shareholders to receive 1:1 shares in HEG Graphite - CNBC TV18 - LinkedIn</t>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>HEG receives NCLT approval for demerger scheme; shareholders to get 1:1 shares in HEG Graphite - livemint.com</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>HEG Gets NCLT Approval For Demerger Plan In 1:1 Share Ratio - Sahi</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>HEG receives NCLT approval for demerger scheme; shareholders to get 1:1 shares in HEG Graphite - livemint.com</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-19 — cnbctv:02f6ca213094b:0 - TradingView</t>
-        </is>
-      </c>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2659,68 +2675,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>WEIZMANIND.NS</t>
+          <t>SSWL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>WEIZMANIND</t>
+          <t>Steel Strips Wheels Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>76.45999908447266</v>
+        <v>316.25</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>76.47000122070312</v>
+        <v>319.6000061035156</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>74.09999847412109</v>
+        <v>306.6000061035156</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>75.66999816894531</v>
+        <v>307.3500061035156</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>75.90000152587891</v>
+        <v>315.8500061035156</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>75.66999816894531</v>
+        <v>307.3500061035156</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>195</v>
+        <v>337310</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-0.3</v>
+        <v>-2.69</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Weizmann Limited (WEIZMANIND.NS) Faces Mild Selling Pressure as Price Holds Above Key Support - Volume Breadth - Vinanet</t>
+          <t>SSWL Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Here's What We Like About Weizmann's (NSE:WEIZMANIND) Upcoming Dividend - simplywall.st</t>
+          <t>Steel Strips Wheels (SSWL) Dips 2.45%: Testing Near-Term Support After Pullback - RSI Oversold Picks - Vinanet</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Here's What We Like About Weizmann's (NSE:WEIZMANIND) Upcoming Dividend - simplywall.st</t>
+          <t>Steel Strips Wheels (NSE:SSWL) Is Looking To Continue Growing Its Returns On Capital - simplywall.st</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Weizmann Limited Holds Near Support Amid Modest Gains – WEIZMANIND.NS Analysis - Fundamental Weighted - Vinanet</t>
+          <t>SSWL Mar 2026 Earnings: Robust Revenue and Positive Stock Momentum Amidst Operational Efficiency - EPS Surprise History - Vinanet</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Weizmann Limited (WEIZMANIND.NS): Mild Uptick Near ₹84.5 as Stock Holds Support Zone - Leading Diagonal - Vinanet</t>
+          <t>Steel Strips Wheels Limited Receives ESG Score of 68.6 from SES ESG Research - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2728,56 +2744,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CUMMINSIND.NS</t>
+          <t>YASHO.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>Yasho Industries Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5250</v>
+        <v>4500</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>5252.5</v>
+        <v>4500</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5192.5</v>
+        <v>4300</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>5211</v>
+        <v>4365</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>5220</v>
+        <v>4470.7998046875</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>5211</v>
+        <v>4365</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>122662</v>
+        <v>81327</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-0.17</v>
+        <v>-2.37</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Ind. Standalone June 2026 Net Sales at Rs 314.09 crore, up 58.73% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Q1 FY27 Results: PAT Rs 36 Cr, Revenue Rs 307 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Q1 Results: Net profit surges 547% YoY - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2785,68 +2813,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>HLVLTD.NS</t>
+          <t>VSSL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>HLVLTD</t>
+          <t>Vardhman Special Steels Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6.699999809265137</v>
+        <v>362</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6.699999809265137</v>
+        <v>362.1000061035156</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>6.5</v>
+        <v>350</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6.619999885559082</v>
+        <v>350.25</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6.630000114440918</v>
+        <v>358.6499938964844</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6.619999885559082</v>
+        <v>350.25</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>129901</v>
+        <v>59020</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-0.15</v>
+        <v>-2.34</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>HLV Limited's (NSE:HLVLTD) Shares May Have Run Too Fast Too Soon - simplywall.st</t>
+          <t>Vardhman Special Steels lays foundation for ₹1,116 crore forging unit - scanx.trade</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>HLV Limited: Navigating Resistance Near ₹8.05 Amid Modest Decline - Ratio Spread Trade - Vinanet</t>
+          <t>Vardhman Special Steels Ltd. Share Price at 52-Week High - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>HLV Limited (HLVLTD.NS) Gains Modestly as Stock Holds Above Key Support Level - Extension Target - Vinanet</t>
+          <t>Vardhman Special Steels Ltd. Share Price at 52-Week High - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>HLV (NSE:HLVLTD) Seems To Use Debt Quite Sensibly - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>HLV Limited (HLVLTD.NS) Gains 2.43% – Approaching Key Resistance at ₹8.42 - Monthly Profile - Vinanet</t>
-        </is>
-      </c>
+          <t>Vardhman Special Steels hosts investor meet in Mumbai on Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2854,68 +2878,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SBIN.NS</t>
+          <t>LCL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>Lohia Corp Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1052.900024414062</v>
+        <v>552</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1052.900024414062</v>
+        <v>576.9500122070312</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1045.699951171875</v>
+        <v>542.8499755859375</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1047</v>
+        <v>548.2999877929688</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1048.599975585938</v>
+        <v>561.2999877929688</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1047</v>
+        <v>548.2999877929688</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3080220</v>
+        <v>1288345</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-0.15</v>
+        <v>-2.32</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>SBI Share Price - Live NSE: SBIN Stock Price &amp; Chart - Upstox</t>
+          <t>LOHIA CORP LIMITED Share Price: New One-Year High Analysis - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>State Bank of India Stock Update: Shares Dip Amid Recruitment Woes, RBI Policy Shift - latestly.com</t>
+          <t>Lohia Corp Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>SBIN Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+          <t>Total common shares outstanding of Lohia Corp Limited – NSE:LCL - TradingView</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>SBIN Share Price Today - State Bank Of India Stock Price Live NSE/BSE - Univest</t>
+          <t>Lohia Corp Shares List At Over 8% Premium On NSE - fintechbiznews.com</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>State Bank of India Stock Update: Share Price Dips on Recruitment Concerns - latestly.com</t>
+          <t>Lohia Corp raises ₹492 crore from anchor investors ahead of IPO opening on Thursday - livemint.com</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2923,64 +2947,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA.NS</t>
+          <t>PFC.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>Power Finance Corporation Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1905</v>
+        <v>374.4500122070312</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1911.599975585938</v>
+        <v>375.1000061035156</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1890.300048828125</v>
+        <v>365.0499877929688</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1898</v>
+        <v>365.8500061035156</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1900</v>
+        <v>374.4500122070312</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1898</v>
+        <v>365.8500061035156</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>501385</v>
+        <v>7174654</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-0.11</v>
+        <v>-2.3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+          <t>PFC, REC Shares Fall As Morgan Stanley Downgrades Both Stocks — Check Target Price, Potential Upside - NDTV Profit</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Why is Sun Pharmaceutical Industries stock falling today? - Investing.com</t>
+          <t>'Consensus buy' PFC, 'no sell' REC get downgraded; Check rationale and new targets - CNBC TV18</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Results: Sun Pharmaceutical Industries Limited Exceeded Expectations And The Consensus Has Updated Its Estimates - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>PFC, REC shares fall up to 8% as CLSA cuts target prices on 'mixed' Q1 results - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2988,68 +3016,56 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>HIMATSEIDE.NS</t>
+          <t>SRM.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>HIMATSEIDE</t>
+          <t>SRM Contractors Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>70.09999847412109</v>
+        <v>497.3999938964844</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>71.69999694824219</v>
+        <v>498.3999938964844</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>69.05999755859375</v>
+        <v>482.6499938964844</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>71.47000122070312</v>
+        <v>482.6499938964844</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v/>
+        <v>493.75</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>71.47000122070312</v>
+        <v>482.6499938964844</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>444716</v>
+        <v>41403</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Himatsingka Seide Limited. Actuals &amp; Estimates (NSE:HIMATSEIDE) - TradingView</t>
+          <t>SRM Contractors Share Price Forecast to 2030 - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>HIMATSEIDE Q2 2026 Earnings: Revenue Declines 9.5% YoY; EPS at ₹4.93 Amid Challenging Textile Demand - Vinanet</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Himatsingka Seide Share Price Target 2026: Rs 89 Analyst Forecast - Univest</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Himatsingka Seide Falls 3% – Stock Nears Key Support at ₹73.50 Amid Weaker Textile Sentiment - RVOL Spike - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Here's What We Like About Himatsingka Seide's (NSE:HIMATSEIDE) Upcoming Dividend - simplywall.st</t>
-        </is>
-      </c>
+          <t>SRM Contractors Share Price Forecast to 2030 - Univest</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3057,68 +3073,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>WILLAMAGOR.NS</t>
+          <t>SAMMAANCAP.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>WILLAMAGOR</t>
+          <t>Sammaan Capital Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>25.10000038146973</v>
+        <v>154.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>25.71999931335449</v>
+        <v>155.3999938964844</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24.5</v>
+        <v>149.6999969482422</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>25.42000007629395</v>
+        <v>150.1999969482422</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v/>
+        <v>153.6300048828125</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25.42000007629395</v>
+        <v>150.1999969482422</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1647</v>
+        <v>5950881</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>-2.23</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Williamson Magor (WILLAMAGOR.NS) Gains 3.58% – Support and Resistance Levels in Focus - Trade Entry Signals - Vinanet</t>
+          <t>Sammaan Capital Ltd Actuals &amp; Estimates (NSE:SAMMAANCAP) - TradingView</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Williamson Magor Q2 2026 Earnings: Revenue Plunges 46% YoY as Investment Holding Company Posts Net Loss - Return On Equity - Vinanet</t>
+          <t>SAMMAANCAP Mar 2026 Earnings: Massive Loss of ₹72.97 Per Share Reported - Earnings Season Outlook - Vinanet</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Williamson Magor Holds Near Support; Resistance Test Ahead for WILLAMAGOR.NS - Scalping Stock Signals - Vinanet</t>
+          <t>Sammaan Capital Limited Open Offer Receives 41,110 Shares Tendered by April 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>WILLAMAGOR Q2 2025 Earnings: Revenue Growth of 18.1% Driven by Higher Other Income, but Net Loss Deepens to ₹165.56 Per Share - Analyst Coverage Count - Vinanet</t>
+          <t>Indiabulls Housing Finance Share Price - Upstox</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>WILLAMAGOR Stock Price and Chart — NSE:WILLAMAGOR - TradingView</t>
+          <t>Sammaan Capital Limited Gains 1.70%: Price Action and Key Levels - Factor Crowding - Vinanet</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3126,68 +3142,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VINDHYATEL.NS</t>
+          <t>NEPHROPLUS.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>VINDHYATEL</t>
+          <t>Nephrocare Health Services Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2459</v>
+        <v>698</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2498</v>
+        <v>698</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2421.89990234375</v>
+        <v>673.1500244140625</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2439.199951171875</v>
+        <v>676.5499877929688</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v/>
+        <v>691</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2439.199951171875</v>
+        <v>676.5499877929688</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>13066</v>
+        <v>132304</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>-2.09</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Vindhya Telelinks Limited's (NSE:VINDHYATEL) largest shareholders are individual investors who were rewarded as market cap surged ₹2.6b last week - simplywall.st</t>
+          <t>NEPHROPLUS Stock Price and Chart — NSE:NEPHROPLUS - TradingView</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>VINDHYATEL Mar 2026 Earnings: EPS of ₹16.75 on Revenue of ₹1,005.0 Crore; Stock Declines 1.5% - Estimate Dispersion - Vinanet</t>
+          <t>Nephrocare Health Services Limited (NEPHROPLUS.NS) Q2 2026 Earnings: Revenue Surges 32% YoY, EPS of ₹8.1 Reflects Strong Operational Execution - Performance Review - Vinanet</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>VINDHYATEL Stock Price and Chart — NSE:VINDHYATEL - TradingView</t>
+          <t>NEPHROPLUS to acquire dialysis center assets in Paranaque City, Philippines - Business Standard</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Vindhya Telelinks (VINDHYATEL.NS) Retreats from Resistance, Tests Key Support Levels - MAMA Signal - Vinanet</t>
+          <t>Nephrocare Health Services Ltd Share Price Today – Live NSE/BSE - INDmoney</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Vindhya Telelinks (VINDHYATEL.NS): Modest Decline as Stock Consolidates Near Key Support Levels - Flat Correction - Vinanet</t>
+          <t>SAM, Khaitan, CAM, Trilegal guide Nephroplus’ INR 871 cr IPO - ETLegalWorld.com</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3195,68 +3211,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ESCORTS.NS</t>
+          <t>MMFL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>MM Forgings Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3059.60009765625</v>
+        <v>660.0999755859375</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3099</v>
+        <v>669.4500122070312</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3059</v>
+        <v>635</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3087.699951171875</v>
+        <v>644.0999755859375</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v/>
+        <v>657.7999877929688</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3087.699951171875</v>
+        <v>644.0999755859375</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>35023</v>
+        <v>138252</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>-2.08</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Escorts Kubota Shares Fall 2.13% to Rs 3,067.00 Amid Bullish Sentiment - Moneycontrol.com</t>
+          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Escorts Kubota Q1FY27: Revenue jumps 28% Y-o-Y, profit at ₹386 crore - business-standard.com</t>
+          <t>M M Forgings Limited Announces Resignation of Chandrasekar S from Company Secretary and Compliance Officer, Effective August 14, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Escorts Kubota schedules analyst meet with Valuequest on Aug 21 - scanx.trade</t>
+          <t>M M Forgings postpones Q1FY26 board meeting to Aug 14 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 07:04:21</t>
+          <t>2026-08-20 13:06:47 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3264,46 +3280,46 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>JAYSREETEA.NS</t>
+          <t>TALBROAUTO.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>JAYSREETEA</t>
+          <t>Talbros Automotive Components Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>94.52999877929688</v>
+        <v>423.1000061035156</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>99.40000152587891</v>
+        <v>428.1499938964844</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>94</v>
+        <v>410.3500061035156</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>99.19999694824219</v>
+        <v>414.25</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v/>
+        <v>423.0499877929688</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>99.19999694824219</v>
+        <v>414.25</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>173240</v>
+        <v>220538</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>-2.08</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+          <t>Transcript : Talbros Automotive Components Limited, Q1 2027 Earnings Call, Aug 11, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+          <t>Transcript : Talbros Automotive Components Limited, Q1 2027 Earnings Call, Aug 11, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gainers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gainers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KRONOX.NS</t>
+          <t>MPDL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Limited</t>
+          <t>MPDL Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>155.0099945068359</v>
+        <v>34.29999923706055</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>178.6999969482422</v>
+        <v>34.31999969482422</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>155.0099945068359</v>
+        <v>23.26000022888184</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>176.0500030517578</v>
+        <v>34.31999969482422</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>155.1600036621094</v>
+        <v>28.60000038146973</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>176.0500030517578</v>
+        <v>34.31999969482422</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2949367</v>
+        <v>8795</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>13.46</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Rs 246 Crore Acquisition: Indo Borax &amp; Chemicals to Acquire 64.26% Stake in Kronox Lab Sciences; Share Price Rises 7% - insights.dsij.in</t>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Momentum Stocks: Kronox Lab Sciences, Waterways Leisure, Genus Power rise up to % on sheer momentum - Moneycontrol.com</t>
+          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax acquires 64.26% stake in Kronox Lab Sciences for ₹246.12 crore - scanx.trade</t>
+          <t>MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Q1 Results: Net profit up 60% YoY to ₹25.8 crore - scanx.trade</t>
+          <t>MPDL reports consolidated net loss of Rs 4.20 crore in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>BALRAMCHIN.NS</t>
+          <t>MYSORPETRO.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Limited</t>
+          <t>Mysore Petro Chemicals Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>658.25</v>
+        <v>160</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>739.8499755859375</v>
+        <v>165.4900054931641</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>655.0499877929688</v>
+        <v>155.3000030517578</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>734</v>
+        <v>165.4900054931641</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>650.7999877929688</v>
+        <v>137.9100036621094</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>734</v>
+        <v>165.4900054931641</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>14806969</v>
+        <v>383979</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>12.78</v>
+        <v>20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+          <t>20% Upper Circuit: 8 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Balrampur Chini Mills Q1 2026 stock falls as outlook stays firm - Investing.com</t>
+          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+          <t>20% Upper Circuit: 8 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH.NS</t>
+          <t>KRONOX.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Limited</t>
+          <t>Kronox Lab Sciences Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>48.77000045776367</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>55.25</v>
+        <v>186.1900024414062</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>48.70000076293945</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>54.34000015258789</v>
+        <v>186.1900024414062</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>48.27999877929688</v>
+        <v>155.1600036621094</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>54.34000015258789</v>
+        <v>186.1900024414062</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>25736600</v>
+        <v>5888825</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>12.55</v>
+        <v>20</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+          <t>Indo Borax &amp; Chemicals Limited executed a Share Purchase Agreement to acquire 64.26% stake in Kronox Lab Sciences Limited from Ketan Vinodchandra Ramani, Pritesh Vinodchandra Ramani and Jogindersingh Gianchand Jaswal for INR 2.5 billion. - marketscreener.com</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Is It Worth Considering Dwarikesh Sugar Industries Limited (NSE:DWARKESH) For Its Upcoming Dividend? - simplywall.st</t>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Ltd. Share Price: Major Drop - Univest</t>
+          <t>Momentum Stocks: Kronox Lab Sciences, Waterways Leisure, Genus Power rise up to % on sheer momentum - TradingView</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,64 +760,60 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR.NS</t>
+          <t>KJMCFIN.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Limited</t>
+          <t>KJMC Financial Services Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32.09999847412109</v>
+        <v>66.34999847412109</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>35.75</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30.95000076293945</v>
+        <v>61.90000152587891</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>35.04999923706055</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>35.04999923706055</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1400201</v>
+        <v>3326</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>12.09</v>
+        <v>20</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd is Rated Strong Sell - marketsmojo.com</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
-        </is>
-      </c>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -825,68 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>KWIL.NS</t>
+          <t>MINALIND.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (India) Limited</t>
+          <t>Minal Industries Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>38</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>42.2400016784668</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>37.75</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>42.11000061035156</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>37.70999908447266</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42.11000061035156</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>39174599</v>
+        <v>312753</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>11.67</v>
+        <v>19.91</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
+          <t>Total common shares outstanding of Minal Industries Limited – NSE:MINALIND - TradingView</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
+          <t>Total common shares outstanding of Minal Industries Limited – NSE:MINALIND - TradingView</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
+          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - thehindu.com</t>
+          <t>Minal Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
+          <t>Minal Industries Ltd - Equitypandit</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -894,60 +890,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>KOTARISUG.NS</t>
+          <t>CRSL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Limited</t>
+          <t>Cressanda Railway Solutions Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27.8799991607666</v>
+        <v>2.789999961853027</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>31.39999961853027</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>27.68000030517578</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>30.20000076293945</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27.21999931335449</v>
+        <v>2.579999923706055</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30.20000076293945</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>817791</v>
+        <v>8160294</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10.95</v>
+        <v>19.77</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
+          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
+          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Are Wall Street Analysts Predicting PepsiCo Stock Will Climb or Sink? - Earnings Call Q&amp;A - Vinanet</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Ltd Income Statement – NSE:CRSL - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,68 +959,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SUVEN.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Suven Life Sciences Limited</t>
+          <t>Balrampur Chini Mills Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>335</v>
+        <v>658.25</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>367.8500061035156</v>
+        <v>780.9500122070312</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>335</v>
+        <v>655.0499877929688</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>367.3999938964844</v>
+        <v>767.0999755859375</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>332.5499877929688</v>
+        <v>650.7999877929688</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>367.3999938964844</v>
+        <v>767.0999755859375</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1501088</v>
+        <v>33513023</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10.48</v>
+        <v>17.87</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView</t>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit</t>
+          <t>Earnings call transcript: Balrampur Chini Mills Q1 2026 stock falls as outlook stays firm - Investing.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Suven Life Sciences seeks AGM approval for related party transaction and fund reallocation - scanx.trade</t>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1024,56 +1028,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MAWANASUG.NS</t>
+          <t>BANARISUG.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Mawana Sugars Limited</t>
+          <t>Bannari Amman Sugars Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>130.9900054931641</v>
+        <v>3635</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>143.1499938964844</v>
+        <v>4338</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>129.3000030517578</v>
+        <v>3635</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>141.7100067138672</v>
+        <v>4240.7001953125</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>128.7200012207031</v>
+        <v>3617.39990234375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>141.7100067138672</v>
+        <v>4240.7001953125</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1294171</v>
+        <v>71288</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10.09</v>
+        <v>17.23</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
+          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1081,64 +1097,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CORDELIA.NS</t>
+          <t>SOLARA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Waterways Leisure Tourism Limited</t>
+          <t>Solara Active Pharma Sciences Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>820.5499877929688</v>
+        <v>551.9500122070312</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>907.75</v>
+        <v>654.4000244140625</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>820.5499877929688</v>
+        <v>551.9500122070312</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>907.75</v>
+        <v>640</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>825.25</v>
+        <v>550.0499877929688</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>907.75</v>
+        <v>640</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>686273</v>
+        <v>6915514</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10</v>
+        <v>16.35</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Share Market News: Waterways Leisure Tourism's profit increases 28 percent in first quarter post listing, rev - India.com</t>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Solara Active Pharma shares jump 5% as Q1 profit rises 55%; Ibuprofen business remains a drag - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>SOLARA ACTIVE P Standalone June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1146,51 +1166,51 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18.NS</t>
+          <t>SOMICONVEY.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Network18 Media &amp; Investments Limited</t>
+          <t>Somi Conveyor Beltings Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>28.23999977111816</v>
+        <v>96</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>31.21999931335449</v>
+        <v>103.9300003051758</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>28.04999923706055</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>30.86000061035156</v>
+        <v>100.0699996948242</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.06999969482422</v>
+        <v>86.61000061035156</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>30.86000061035156</v>
+        <v>100.0699996948242</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>24924047</v>
+        <v>687119</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.94</v>
+        <v>15.54</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Network18 Media &amp; Investments schedules 31st AGM for September 16 - scanx.trade</t>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Network18 Media &amp; Investments schedules 31st AGM for September 16 - scanx.trade</t>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Network18 sets Oct 1 hearing for News18 Marathi amalgamation - scanx.trade</t>
+          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1199,7 +1219,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1207,56 +1227,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>RANASUG.NS</t>
+          <t>KWIL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Limited</t>
+          <t>Kwality Wall's (India) Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13.85999965667725</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>15.17000007629395</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>13.85999965667725</v>
+        <v>37.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>15.02999973297119</v>
+        <v>43.47000122070312</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13.76000022888184</v>
+        <v>37.70999908447266</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>15.02999973297119</v>
+        <v>43.47000122070312</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2286027</v>
+        <v>101230788</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>9.23</v>
+        <v>15.27</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
+          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1264,68 +1296,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SIGACHI.NS</t>
+          <t>INDOBORAX.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Limited</t>
+          <t>Indo Borax &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29</v>
+        <v>439</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>31.81999969482422</v>
+        <v>509.8999938964844</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>29</v>
+        <v>431</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>31.51000022888184</v>
+        <v>498.1499938964844</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.8799991607666</v>
+        <v>433.8500061035156</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>31.51000022888184</v>
+        <v>498.1499938964844</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>6444144</v>
+        <v>6099190</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>9.109999999999999</v>
+        <v>14.82</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+          <t>INDOBORAX Q2 FY2026 Earnings: Robust Revenue Growth of 22.9% Drives Strong EPS of ₹15.67 - EPS Consistency Score - Vinanet</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries board to consider preferential issue on August 22 - scanx.trade</t>
+          <t>Indo Borax &amp; Chemicals Limited Receives Open Offer from Zenrock Chemicals for 83.43 Lakh Shares - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Ind Q1 Results FY27: PAT Rs 8 Cr, Revenue Rs 121 crore - Univest</t>
+          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries postpones Q1FY27 earnings call due to unavoidable circumstances - scanx.trade</t>
+          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1333,60 +1365,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>DWARKESH.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited</t>
+          <t>Dwarikesh Sugar Industries Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>20.73999977111816</v>
+        <v>48.77000045776367</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>22.6200008392334</v>
+        <v>56.45000076293945</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20.59000015258789</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>22.19000053405762</v>
+        <v>55.38000106811523</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20.3799991607666</v>
+        <v>48.27999877929688</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22.19000053405762</v>
+        <v>55.38000106811523</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>145436948</v>
+        <v>42665668</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Dwarikesh Sugar Industries Ltd. (DWARKESH) Share Price Rises 8.84% Today - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Is It Worth Considering Dwarikesh Sugar Industries Limited (NSE:DWARKESH) For Its Upcoming Dividend? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Ltd. (DWARKESH) Share Price Rises 8.84% Today - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1394,68 +1434,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Limited</t>
+          <t>Bajaj Hindusthan Sugar Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>39.97000122070312</v>
+        <v>20.73999977111816</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>42.70000076293945</v>
+        <v>23.97999954223633</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>39.45999908447266</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>42.54999923706055</v>
+        <v>23.32999992370605</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>39.13000106811523</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42.54999923706055</v>
+        <v>23.32999992370605</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2238046</v>
+        <v>256544491</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>8.74</v>
+        <v>14.47</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - marketsmojo.com</t>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>PVP Ventures Share Price Forecast: 3 Year Outlook to 2030 - Univest</t>
-        </is>
-      </c>
+          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1463,68 +1495,60 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG.NS</t>
+          <t>PACIFICI.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars &amp; Chemicals Limited</t>
+          <t>Pacific Industries Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>37.0099983215332</v>
+        <v>133.5500030517578</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>40.79000091552734</v>
+        <v>159</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>37</v>
+        <v>133.5500030517578</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>40.09999847412109</v>
+        <v>150.9799957275391</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>36.90000152587891</v>
+        <v>133.5500030517578</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>40.09999847412109</v>
+        <v>150.9799957275391</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>509524</v>
+        <v>8374</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8.67</v>
+        <v>13.05</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
+          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Rajshree Sugars &amp; Chemicals Ltd: Stock Climbs 1.67%, Testing Key Resistance at ₹35.72 - Mean Reversion Trade - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
-        </is>
-      </c>
+          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1532,68 +1556,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>KAYA.NS</t>
+          <t>CGVAK.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Kaya Limited</t>
+          <t>CG Vak Software &amp; Exports Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>339.9500122070312</v>
+        <v>159</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>370</v>
+        <v>162.5500030517578</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>336.5499877929688</v>
+        <v>152.0099945068359</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>365.25</v>
+        <v>158.5800018310547</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>338.4500122070312</v>
+        <v>140.7299957275391</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>365.25</v>
+        <v>158.5800018310547</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>119931</v>
+        <v>13494</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7.92</v>
+        <v>12.68</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Scholastic director Kaya Henderson sells $130,812 in stock - Investing.com</t>
+          <t>CGVAK Share Price Today - CG-VAK Software &amp; Exports Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Kaya To Issue 1.82 Million Equity Shares At 274.10 Rupees Per Share For Aggregate Cash Consideration Of Approx 500 Million Rupees - TradingView</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Kaya Standalone June 2026 Net Sales at Rs 60.14 crore, up 13.91% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1601,68 +1617,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DHAMPURSUG.NS</t>
+          <t>SUVEN.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Limited</t>
+          <t>Suven Life Sciences Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>179.6999969482422</v>
+        <v>335</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>190.75</v>
+        <v>377.4500122070312</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>178.9700012207031</v>
+        <v>335</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>189.2100067138672</v>
+        <v>373.6000061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>176.1799926757812</v>
+        <v>332.5499877929688</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>189.2100067138672</v>
+        <v>373.6000061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3891705</v>
+        <v>3256156</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.4</v>
+        <v>12.34</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar to Consider Quarterly Results Tomorrow; Stock Declines 2.75% in Previous Session - TradingView</t>
+          <t>Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills sets book closure dates for 91st AGM - scanx.trade</t>
+          <t>Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills settles ₹100 crore commercial paper - scanx.trade</t>
+          <t>Suven Life Sciences seeks AGM approval for related party transaction and fund reallocation - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1670,68 +1686,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>NIBE.NS</t>
+          <t>UTTAMSUGAR.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>NIBE Limited</t>
+          <t>Uttam Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1435</v>
+        <v>303.0899963378906</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1542.800048828125</v>
+        <v>344</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1421</v>
+        <v>301.8500061035156</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1513</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1411.099975585938</v>
+        <v>300.989990234375</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1513</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>254734</v>
+        <v>2292635</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.22</v>
+        <v>11.7</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>NIBE Q1 FY27 Results: Revenue fell to Rs 63 Cr, Net Loss -1300% - Univest</t>
+          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Di: This is what it will take for the Nibe stock to gain momentum - marketscreener.com</t>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Di: This is what it will take for the Nibe stock to gain momentum - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Nibe Industrier stock holds steady as leadership change adds to long term growth story - Ad-hoc-news.de</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Nibe Industrier stock holds firm after Q2 sales rose - Ad-hoc-news.de</t>
-        </is>
-      </c>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1739,68 +1747,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KIRIINDUS.NS</t>
+          <t>SWISSMLTRY.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries Limited</t>
+          <t>Swiss Military Consumer Goods Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>435</v>
+        <v>15.1899995803833</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>479.9500122070312</v>
+        <v>16.79999923706055</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>434</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>462</v>
+        <v>16.44000053405762</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>431.2999877929688</v>
+        <v>14.75</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>462</v>
+        <v>16.44000053405762</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>5177321</v>
+        <v>870159</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.12</v>
+        <v>11.46</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries Limited (NSE:KIRIINDUS) Stock Rockets 34% As Investors Are Less Pessimistic Than Expected - simplywall.st</t>
+          <t>SWISSMLTRY Share Price Today - Swiss Military Consumer Goods Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>KIRIINDUS.NS Q2 2026 Earnings: Robust Profitability Amidst Modest Revenue Growth - Earnings Cycle Report - Vinanet</t>
+          <t>Swiss Military Consumer Goods equity shares admitted on NSE - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries (KIRIINDUS) Stock Consolidates Near Key Support Amid Modest Decline - Percent Above MA - Vinanet</t>
+          <t>Swiss Military Consumer Goods Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>KIRIDYES.BO interactive stock chart | Kiri Industries Limited stock - Yahoo Finance Australia</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Shareholders Shouldn’t Be Too Comfortable With Kiri Industries' (NSE:KIRIINDUS) Strong Earnings - simplywall.st</t>
-        </is>
-      </c>
+          <t>Swiss Military Consumer Goods equity shares admitted on NSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1808,63 +1812,59 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DALMIASUG.NS</t>
+          <t>KOHINOOR.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Sugar and Industries Limited</t>
+          <t>Kohinoor Foods Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>475.8500061035156</v>
+        <v>32.09999847412109</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>517</v>
+        <v>35.75</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>469.2000122070312</v>
+        <v>30.95000076293945</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>508.5</v>
+        <v>34.81000137329102</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>475.5499877929688</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>508.5</v>
+        <v>34.81000137329102</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1379021</v>
+        <v>1739882</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6.93</v>
+        <v>11.32</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Sugar and Industries Limited (NSE:DALMIASUG) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹560 - simplywall.st</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today - 20 August 2026 - TradingView</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Sugar And Industries Ltd. (DALMIASUG) Share Price Rises 14.03% Today - Univest</t>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Dalmia Bharat Sugar Share Price Technicals and Market Cap - Univest</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today - 20 August 2026 - TradingView</t>
-        </is>
-      </c>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1989,7 +1989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1997,68 +1997,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM.NS</t>
+          <t>TECILCHEM.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Limited</t>
+          <t>TECIL Chemicals and Hydro Power Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>965</v>
+        <v>11.28999996185303</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>965</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>907.2999877929688</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>918.5</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>967.9500122070312</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>918.5</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2577690</v>
+        <v>306021</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-5.11</v>
+        <v>-10.74</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM LIMITED Share Price - Upstox</t>
+          <t>TECIL Chemicals (TECILCHEM) Declines to ₹11.6, Approaches Key Support Zone - McClellan Summation - Vinanet</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Board Clears Q1 FY27 Unaudited Results, Publishes in Newspapers - TipRanks</t>
+          <t>Dollar Steadies as US-Iran Tensions Escalate; Yen Weakens on Pension Concerns - Profit Announcement - Vinanet</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM Share Price Today - INDO-MIM LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - Vinanet</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>IndoMIM Share Price Today - Indo-MIM Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+          <t>TECIL Chemicals (TECILCHEM.NS) Declines Nearly 3.5%, Approaches Key Support at ₹9.19 - Liquidity Order Flow - Vinanet</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Indo-MIM IPO: GMP jumps as issue subscribed 72.34 times - livemint.com</t>
+          <t>TECILCHEM.NS Q2 2025 Earnings: No Revenue, Net Loss Amid Minimal Business Activity - EBITDA Margin Trends - Vinanet</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2066,68 +2066,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SIEL.NS</t>
+          <t>KAMANWALA.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises Limited</t>
+          <t>Kamanwala Housing Construction Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44.54000091552734</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>44.54000091552734</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>16.11000061035156</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>16.68000030517578</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>42.41999816894531</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>16.68000030517578</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>8873</v>
+        <v>56343</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-5</v>
+        <v>-10.47</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+          <t>Kamanwala Housing Construction Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+          <t>Japanese stocks rebound as bond yields ease - Business Standard</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+          <t>Volume Gainers on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+          <t>Horizon Industrial Parks IPO Day 3 Subscription Status: Issue Booked 0.30x So Far - HDFC Sky</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+          <t>Chinese stocks rebound as policy hopes build - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2135,68 +2135,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UCAL.NS</t>
+          <t>BTML.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>UCAL LIMITED</t>
+          <t>Bodhi Tree Multimedia Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>147.8999938964844</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>147.8999938964844</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>138.8800048828125</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>140.0099945068359</v>
+        <v>7.920000076293945</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>146.1799926757812</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>140.0099945068359</v>
+        <v>7.920000076293945</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>26454</v>
+        <v>1261909</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-4.22</v>
+        <v>-9.17</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>UCAL Ltd. Share Price Near 52-Week High Analysis - Univest</t>
+          <t>Bodhi Tree Multimedia Ltd. Stock News: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>UCAL Ltd. Share Price Near 52-Week High Analysis - Univest</t>
+          <t>DD Q1 2026 Earnings: EPS Surges Past Estimates by 10.4% as Shares Retreat 1.33% - Earnings Acceleration Picks - Vinanet</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>UCAL Ltd. Share Price Today: 9.08% Rise, Valuation Check - Univest</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>UCAL Share Price Rises 10.34%: Technicals, Fundamentals - Univest</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Ucal reports consolidated net profit of Rs 5.84 crore in the June 2026 quarter - Business Standard</t>
-        </is>
-      </c>
+          <t>DD Q1 2026 Earnings: EPS Surges Past Estimates by 10.4% as Shares Retreat 1.33% - Earnings Acceleration Picks - Vinanet</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2204,68 +2196,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KUANTUM.NS</t>
+          <t>ADDIND.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Kuantum Papers Limited</t>
+          <t>Addi Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>76.25</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>77.5</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>74.20999908447266</v>
+        <v>71.05000305175781</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>75.37999725341797</v>
+        <v>80</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>78.69999694824219</v>
+        <v>87</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>75.37999725341797</v>
+        <v>80</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>237483</v>
+        <v>612</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-4.22</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Kuantum Papers Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
+          <t>Addi Industries Limited Statistics – NSE:ADDIND - TradingView</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Mazagon Dock and 9 Other Stocks in Focus as They Turn Ex-Dividend Tomorrow - Trade Brains</t>
+          <t>Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Kuantum Papers proposes ₹2.50 dividend, sets August 27 AGM date - scanx.trade</t>
+          <t>Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Kuantum Papers declares ₹2.50 dividend for FY26, sets Aug 20 record date - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Kuantum Papers reports 100% sustainable sourcing in FY26 BRSR filing - scanx.trade</t>
-        </is>
-      </c>
+          <t>Addi Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2273,68 +2261,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AHLADA.NS</t>
+          <t>NKIND.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ahlada Engineers Limited</t>
+          <t>NK Industries Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40.81999969482422</v>
+        <v>60.9900016784668</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40.81999969482422</v>
+        <v>60.9900016784668</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>38.5</v>
+        <v>56.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>39.29999923706055</v>
+        <v>56.59999847412109</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>40.81999969482422</v>
+        <v>61.54999923706055</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39.29999923706055</v>
+        <v>56.59999847412109</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>32335</v>
+        <v>183</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-3.72</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Ahlada Engineers to hold 21st AGM on August 5, 2026 - scanx.trade</t>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Ahlada Engineers Ltd is Rated Strong Sell - marketsmojo.com</t>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>RYN Q1 2026 Earnings: EPS of $0.07 Delivers 112.94% Surprise, Shares Gain 1.82% - Management Tone Analysis - Vinanet</t>
+          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - Vinanet</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15 Best Bank Account Bonuses of August 2026: Earn Up to $3,000 in Cash Rewards - Next Quarter Guidance - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Ahlada Engineers Ltd is Rated Strong Sell - marketsmojo.com</t>
-        </is>
-      </c>
+          <t>Fennec (FENC) Technical Check: Adds 0.51% to Close at $11.89 at the Close; Current Setup: the Supplied Trading Band Runs From $11.30 to $12.48 - Throwback Trade - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2342,68 +2326,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ASTERDM.NS</t>
+          <t>GCSL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Quality Care Limited</t>
+          <t>Gretex Corporate Services Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>798.3499755859375</v>
+        <v>526.2999877929688</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>798.3499755859375</v>
+        <v>540.9500122070312</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>771.0499877929688</v>
+        <v>470</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>776.4000244140625</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>800.2000122070312</v>
+        <v>521.7000122070312</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>776.4000244140625</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3948903</v>
+        <v>615891</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-2.97</v>
+        <v>-7.6</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare to rename as Aster DM Quality Care Limited - scanx.trade</t>
+          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare: Over 84M Shares Pledged as Security - InvestyWise</t>
+          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
+          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare Ltd. Share Price Fall and Market Action - Univest</t>
+          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare Ltd. (ASTERDM) Share Price Hits Fresh 52-Week High - Univest</t>
+          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2411,68 +2395,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>FCL.NS</t>
+          <t>MILKYMIST.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Fineotex Chemical Limited</t>
+          <t>Milky Mist Dairy Food Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45.09999847412109</v>
+        <v>207.8000030517578</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45.47999954223633</v>
+        <v>211.8000030517578</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43.36999893188477</v>
+        <v>181.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>43.65000152587891</v>
+        <v>184.8899993896484</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>44.97999954223633</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43.65000152587891</v>
+        <v>184.8899993896484</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>6874033</v>
+        <v>56530266</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-2.96</v>
+        <v>-7.39</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
+          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Why Are Investors Watching Fineos (ASX:FCL) After Its Latest Share Price Decline? - Kalkine</t>
+          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Fineos (ASX: FCL) Crosses Profitability Inflection Point In H1 FY 2026 - arichlife.com.au</t>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Manulife Ideal Cnd Div Growth7575 FCL (0P000180PM.TO) interactive stock chart - uk.finance.yahoo.com</t>
+          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2480,68 +2464,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CHENNPETRO.NS</t>
+          <t>WEL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Limited</t>
+          <t>Wonder Electricals Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1457</v>
+        <v>148.3999938964844</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1466</v>
+        <v>149.7799987792969</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1379.599975585938</v>
+        <v>132</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1397.800048828125</v>
+        <v>136.0399932861328</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1440.300048828125</v>
+        <v>146.2599945068359</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1397.800048828125</v>
+        <v>136.0399932861328</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1565064</v>
+        <v>1505497</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-2.95</v>
+        <v>-6.99</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Limited (NSE:CHENNPETRO) Looks Interesting, And It's About To Pay A Dividend - simplywall.st</t>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Rises 5.01% Today - Univest</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Chennai Petroleum Corporation Ltd. Stock News: Price Up 5.8% - Univest</t>
-        </is>
-      </c>
+          <t>Enterprise value to EBIT forward of Wel-Dish. Incorporated – TSE:2901 - TradingView</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2549,68 +2525,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST.NS</t>
+          <t>SINTERCOM.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Limited</t>
+          <t>Sintercom India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>207.8000030517578</v>
+        <v>86.98999786376953</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>211.8000030517578</v>
+        <v>86.98999786376953</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>191.25</v>
+        <v>79.05999755859375</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>194.0700073242188</v>
+        <v>79.38999938964844</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>85</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>194.0700073242188</v>
+        <v>79.38999938964844</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>42030536</v>
+        <v>5959</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-2.79</v>
+        <v>-6.6</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+          <t>Sintercom India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
+          <t>Sintercom India standalone net profit rises 88.46% in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
+          <t>Sintercom India standalone net profit rises 88.46% in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
-        </is>
-      </c>
+          <t>Copper Hits Record High as "Dr. Copper" Sends Conflicting Economic Signals - Consensus Forecast Report - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2618,56 +2590,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DREDGECORP.NS</t>
+          <t>CENTEXT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation of India Limited</t>
+          <t>Century Extrusions Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1199</v>
+        <v>21.95000076293945</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1204</v>
+        <v>22.10000038146973</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1154.800048828125</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1156</v>
+        <v>20.63999938964844</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1189.199951171875</v>
+        <v>22.07999992370605</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1156</v>
+        <v>20.63999938964844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>114984</v>
+        <v>440018</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-2.79</v>
+        <v>-6.52</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+          <t>Century Extrusions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Vicor Corporation (VICR) Climbs Nearly 8% as Shares Test Key Resistance Zone - WMA Signal - Vinanet</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Century Extrusions Ltd. Share Price Today: 13.47% Increase - Univest</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Century Extrusions Limited Approves Appointment of Shri Charan Singh as A Non-Executive Independent Director - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Century Extrusions posts 10.97% sales rise in FY26, sets Aug 14 AGM date - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2675,68 +2659,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SSWL.NS</t>
+          <t>ATAM.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Steel Strips Wheels Limited</t>
+          <t>Atam Valves Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>316.25</v>
+        <v>60.95000076293945</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>319.6000061035156</v>
+        <v>60.95000076293945</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>306.6000061035156</v>
+        <v>54.59999847412109</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>307.3500061035156</v>
+        <v>55.52999877929688</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>315.8500061035156</v>
+        <v>59.36000061035156</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>307.3500061035156</v>
+        <v>55.52999877929688</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>337310</v>
+        <v>88804</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-2.69</v>
+        <v>-6.45</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SSWL Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Steel Strips Wheels (SSWL) Dips 2.45%: Testing Near-Term Support After Pullback - RSI Oversold Picks - Vinanet</t>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Steel Strips Wheels (NSE:SSWL) Is Looking To Continue Growing Its Returns On Capital - simplywall.st</t>
+          <t>VRSN Q2 2026 Earnings: EPS Misses Consensus by 1.45% as Shares Decline 1.95% - ROIC Trend Report - Vinanet</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>SSWL Mar 2026 Earnings: Robust Revenue and Positive Stock Momentum Amidst Operational Efficiency - EPS Surprise History - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Steel Strips Wheels Limited Receives ESG Score of 68.6 from SES ESG Research - scanx.trade</t>
-        </is>
-      </c>
+          <t>Shivansh Finserve: புதிய வளர்ச்சிக்கு முக்கிய முடிவு! பெரும் கையகப்படுத்துதல் திட்டம்? - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2744,68 +2724,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>YASHO.NS</t>
+          <t>BALAXI.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Limited</t>
+          <t>BALAXI PHARMACEUTICALS LIMITED</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4500</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>4500</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4300</v>
+        <v>21.5</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4365</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4470.7998046875</v>
+        <v>23.79000091552734</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4365</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>81327</v>
+        <v>139294</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-2.37</v>
+        <v>-6.26</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+          <t>Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - marketsmojo.com</t>
+          <t>Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Yasho Ind. Standalone June 2026 Net Sales at Rs 314.09 crore, up 58.73% Y-o-Y - Moneycontrol.com</t>
+          <t>Balaxi Pharma Q1 results FY27: PAT Rs 1 Cr, Revenue Rs 80 Cr - Univest</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Q1 FY27 Results: PAT Rs 36 Cr, Revenue Rs 307 Cr - Univest</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Yasho Industries Q1 Results: Net profit surges 547% YoY - scanx.trade</t>
-        </is>
-      </c>
+          <t>Balaxi Pharmaceuticals Q1 FY27: Strong Revenue Recovery Masks Deep Structural Concerns - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2813,56 +2789,56 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VSSL.NS</t>
+          <t>LAXMICOT.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Vardhman Special Steels Limited</t>
+          <t>Laxmi Cotspin Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>362</v>
+        <v>15.26000022888184</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>362.1000061035156</v>
+        <v>15.28999996185303</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>350</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>350.25</v>
+        <v>13.96000003814697</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>358.6499938964844</v>
+        <v>14.89000034332275</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>350.25</v>
+        <v>13.96000003814697</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>59020</v>
+        <v>64470</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-2.34</v>
+        <v>-6.25</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Vardhman Special Steels lays foundation for ₹1,116 crore forging unit - scanx.trade</t>
+          <t>Laxmi Cotspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Vardhman Special Steels Ltd. Share Price at 52-Week High - Univest</t>
+          <t>Laxmi Cotspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Vardhman Special Steels Ltd. Share Price at 52-Week High - Univest</t>
+          <t>GRAIL Inc. Faces Selling Pressure as Shares Dip Below $67 - Gamma Squeeze - Vinanet</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Vardhman Special Steels hosts investor meet in Mumbai on Aug 14 - scanx.trade</t>
+          <t>Coastal Financial (CCB) Advances 2.71% as Shares Approach Key Resistance at $43 - Gap and Reverse - Vinanet</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -2870,7 +2846,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2878,68 +2854,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>LCL.NS</t>
+          <t>HSCL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Lohia Corp Limited</t>
+          <t>Himadri Speciality Chemical Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>552</v>
+        <v>755</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>576.9500122070312</v>
+        <v>767.5999755859375</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>542.8499755859375</v>
+        <v>695.5</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>548.2999877929688</v>
+        <v>704.2000122070312</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>561.2999877929688</v>
+        <v>750.25</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>548.2999877929688</v>
+        <v>704.2000122070312</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1288345</v>
+        <v>12470045</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-2.32</v>
+        <v>-6.14</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>LOHIA CORP LIMITED Share Price: New One-Year High Analysis - Univest</t>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Lohia Corp Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Total common shares outstanding of Lohia Corp Limited – NSE:LCL - TradingView</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Lohia Corp Shares List At Over 8% Premium On NSE - fintechbiznews.com</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Lohia Corp raises ₹492 crore from anchor investors ahead of IPO opening on Thursday - livemint.com</t>
-        </is>
-      </c>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2947,68 +2911,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PFC.NS</t>
+          <t>DREDGECORP.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>Dredging Corporation of India Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>374.4500122070312</v>
+        <v>1199</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>375.1000061035156</v>
+        <v>1204</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>365.0499877929688</v>
+        <v>1111.5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>365.8500061035156</v>
+        <v>1118.300048828125</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>374.4500122070312</v>
+        <v>1189.199951171875</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>365.8500061035156</v>
+        <v>1118.300048828125</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>7174654</v>
+        <v>253496</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-2.3</v>
+        <v>-5.96</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>PFC, REC Shares Fall As Morgan Stanley Downgrades Both Stocks — Check Target Price, Potential Upside - NDTV Profit</t>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>'Consensus buy' PFC, 'no sell' REC get downgraded; Check rationale and new targets - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>PFC, REC shares fall up to 8% as CLSA cuts target prices on 'mixed' Q1 results - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3016,56 +2968,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SRM.NS</t>
+          <t>GLOBECIVIL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>SRM Contractors Limited</t>
+          <t>Globe Civil Projects Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>497.3999938964844</v>
+        <v>45.45999908447266</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>498.3999938964844</v>
+        <v>45.45999908447266</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>482.6499938964844</v>
+        <v>41.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>482.6499938964844</v>
+        <v>42.34000015258789</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>493.75</v>
+        <v>44.97000122070312</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>482.6499938964844</v>
+        <v>42.34000015258789</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>41403</v>
+        <v>102543</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-2.25</v>
+        <v>-5.85</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>SRM Contractors Share Price Forecast to 2030 - Univest</t>
+          <t>Globe Civil Projects Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>SRM Contractors Share Price Forecast to 2030 - Univest</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Femasys Inc. (FEMY) Q1 2026 Earnings: EPS Beat on Narrower Loss, Stock Slips - Dividend Earnings Report - Vinanet</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3073,68 +3033,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SAMMAANCAP.NS</t>
+          <t>SHREEJISPG.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sammaan Capital Limited</t>
+          <t>Shreeji Shipping Global Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>154.5</v>
+        <v>657</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>155.3999938964844</v>
+        <v>661.9500122070312</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>149.6999969482422</v>
+        <v>609.8499755859375</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>150.1999969482422</v>
+        <v>613.3499755859375</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>153.6300048828125</v>
+        <v>649.4500122070312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>150.1999969482422</v>
+        <v>613.3499755859375</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5950881</v>
+        <v>1441160</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-2.23</v>
+        <v>-5.56</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd Actuals &amp; Estimates (NSE:SAMMAANCAP) - TradingView</t>
+          <t>Shreeji Shipping Global Ltd. (SHREEJISPG) Share Price Hits 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>SAMMAANCAP Mar 2026 Earnings: Massive Loss of ₹72.97 Per Share Reported - Earnings Season Outlook - Vinanet</t>
+          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Sammaan Capital Limited Open Offer Receives 41,110 Shares Tendered by April 30, 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Indiabulls Housing Finance Share Price - Upstox</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Sammaan Capital Limited Gains 1.70%: Price Action and Key Levels - Factor Crowding - Vinanet</t>
-        </is>
-      </c>
+          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3142,68 +3094,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>NEPHROPLUS.NS</t>
+          <t>AHLADA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Nephrocare Health Services Limited</t>
+          <t>Ahlada Engineers Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>698</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>698</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>673.1500244140625</v>
+        <v>38.5</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>676.5499877929688</v>
+        <v>38.59000015258789</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>691</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>676.5499877929688</v>
+        <v>38.59000015258789</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>132304</v>
+        <v>42109</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-2.09</v>
+        <v>-5.46</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>NEPHROPLUS Stock Price and Chart — NSE:NEPHROPLUS - TradingView</t>
+          <t>Ahlada Engineers to hold 21st AGM on August 5, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Nephrocare Health Services Limited (NEPHROPLUS.NS) Q2 2026 Earnings: Revenue Surges 32% YoY, EPS of ₹8.1 Reflects Strong Operational Execution - Performance Review - Vinanet</t>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>NEPHROPLUS to acquire dialysis center assets in Paranaque City, Philippines - Business Standard</t>
+          <t>RYN Q1 2026 Earnings: EPS of $0.07 Delivers 112.94% Surprise, Shares Gain 1.82% - Management Tone Analysis - Vinanet</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Nephrocare Health Services Ltd Share Price Today – Live NSE/BSE - INDmoney</t>
+          <t>15 Best Bank Account Bonuses of August 2026: Earn Up to $3,000 in Cash Rewards - Next Quarter Guidance - Vinanet</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>SAM, Khaitan, CAM, Trilegal guide Nephroplus’ INR 871 cr IPO - ETLegalWorld.com</t>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3211,68 +3163,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MMFL.NS</t>
+          <t>DHABRIYA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MM Forgings Limited</t>
+          <t>Dhabriya Polywood Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>660.0999755859375</v>
+        <v>600</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>669.4500122070312</v>
+        <v>600</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>635</v>
+        <v>548</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>644.0999755859375</v>
+        <v>555.25</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>657.7999877929688</v>
+        <v>587</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>644.0999755859375</v>
+        <v>555.25</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>138252</v>
+        <v>59063</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-2.08</v>
+        <v>-5.41</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
+          <t>DHABRIYA Share Price Today - Dhabriya Polywood Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
+          <t>Dhabriya Polywood Ltd Income Statement – NSE:DHABRIYA - TradingView</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
+          <t>Dhabriya Polywood Ltd. Share Price and 52-Week High View - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>M M Forgings Limited Announces Resignation of Chandrasekar S from Company Secretary and Compliance Officer, Effective August 14, 2026 - marketscreener.com</t>
+          <t>Free float of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>M M Forgings postpones Q1FY26 board meeting to Aug 14 - scanx.trade</t>
+          <t>Dhabriya Polywood Ltd. Share Price News: Price Rise Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 13:06:47 IST</t>
+          <t>2026-08-20 16:10:48 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3280,51 +3232,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TALBROAUTO.NS</t>
+          <t>TIJARIA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Talbros Automotive Components Limited</t>
+          <t>Tijaria Polypipes Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>423.1000061035156</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>428.1499938964844</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>410.3500061035156</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>414.25</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>423.0499877929688</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>414.25</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>220538</v>
+        <v>209055</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-2.08</v>
+        <v>-5.39</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Transcript : Talbros Automotive Components Limited, Q1 2027 Earnings Call, Aug 11, 2026 - marketscreener.com</t>
+          <t>Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Transcript : Talbros Automotive Components Limited, Q1 2027 Earnings Call, Aug 11, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Tijaria Polypipes Q1 Results: Net loss widens 36% YoY to ₹36.11 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Vardhman Jain Tijaria raises stake in Tijaria Polypipes to 4.33% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes board to approve Q2FY27 results, accept director resignation - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes appoints new independent director, renews auditor at 20th AGM - scanx.trade</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,60 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO.NS</t>
+          <t>KJMCFIN.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Limited</t>
+          <t>KJMC Financial Services Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>160</v>
+        <v>66.34999847412109</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>165.4900054931641</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>155.3000030517578</v>
+        <v>61.90000152587891</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>165.4900054931641</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>137.9100036621094</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>165.4900054931641</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>383979</v>
+        <v>3326</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 8 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>20% Upper Circuit: 8 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
-        </is>
-      </c>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -752,7 +744,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,60 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KJMCFIN.NS</t>
+          <t>BANARISUG.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited</t>
+          <t>Bannari Amman Sugars Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>66.34999847412109</v>
+        <v>3635</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>66.41999816894531</v>
+        <v>4338</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>61.90000152587891</v>
+        <v>3635</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>66.41999816894531</v>
+        <v>4240.7001953125</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>55.34999847412109</v>
+        <v>3617.39990234375</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>66.41999816894531</v>
+        <v>4240.7001953125</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3326</v>
+        <v>71288</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>20</v>
+        <v>17.23</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,68 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MINALIND.NS</t>
+          <t>SOLARA.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries Limited</t>
+          <t>Solara Active Pharma Sciences Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.240000009536743</v>
+        <v>551.9500122070312</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.650000095367432</v>
+        <v>654.4000244140625</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.230000019073486</v>
+        <v>551.9500122070312</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.650000095367432</v>
+        <v>640</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2.210000038146973</v>
+        <v>550.0499877929688</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.650000095367432</v>
+        <v>640</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>312753</v>
+        <v>6915514</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>19.91</v>
+        <v>16.35</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of Minal Industries Limited – NSE:MINALIND - TradingView</t>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of Minal Industries Limited – NSE:MINALIND - TradingView</t>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Solara Active Pharma shares jump 5% as Q1 profit rises 55%; Ibuprofen business remains a drag - CNBC TV18</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries Ltd - Equitypandit</t>
+          <t>SOLARA ACTIVE P Standalone June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -890,68 +890,60 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CRSL.NS</t>
+          <t>SOMICONVEY.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Limited</t>
+          <t>Somi Conveyor Beltings Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.789999961853027</v>
+        <v>96</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3.089999914169312</v>
+        <v>103.9300003051758</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2.700000047683716</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3.089999914169312</v>
+        <v>100.0699996948242</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2.579999923706055</v>
+        <v>86.61000061035156</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.089999914169312</v>
+        <v>100.0699996948242</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>8160294</v>
+        <v>687119</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>19.77</v>
+        <v>15.54</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Cressanda Railway Solutions Ltd Income Statement – NSE:CRSL - TradingView</t>
-        </is>
-      </c>
+          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -959,68 +951,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>BALRAMCHIN.NS</t>
+          <t>KWIL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Limited</t>
+          <t>Kwality Wall's (India) Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>658.25</v>
+        <v>38</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>780.9500122070312</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>655.0499877929688</v>
+        <v>37.75</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>767.0999755859375</v>
+        <v>43.47000122070312</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>650.7999877929688</v>
+        <v>37.70999908447266</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>767.0999755859375</v>
+        <v>43.47000122070312</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>33513023</v>
+        <v>101230788</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>17.87</v>
+        <v>15.27</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Balrampur Chini Mills Q1 2026 stock falls as outlook stays firm - Investing.com</t>
+          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1028,68 +1020,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BANARISUG.NS</t>
+          <t>INDOBORAX.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Limited</t>
+          <t>Indo Borax &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3635</v>
+        <v>439</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4338</v>
+        <v>509.8999938964844</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3635</v>
+        <v>431</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4240.7001953125</v>
+        <v>498.1499938964844</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3617.39990234375</v>
+        <v>433.8500061035156</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4240.7001953125</v>
+        <v>498.1499938964844</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>71288</v>
+        <v>6099190</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>17.23</v>
+        <v>14.82</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
+          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+          <t>INDOBORAX Q2 FY2026 Earnings: Robust Revenue Growth of 22.9% Drives Strong EPS of ₹15.67 - EPS Consistency Score - Vinanet</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
+          <t>Indo Borax &amp; Chemicals Limited Receives Open Offer from Zenrock Chemicals for 83.43 Lakh Shares - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
+          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1097,68 +1089,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SOLARA.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Limited</t>
+          <t>Bajaj Hindusthan Sugar Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>551.9500122070312</v>
+        <v>20.73999977111816</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>654.4000244140625</v>
+        <v>23.97999954223633</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>551.9500122070312</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>640</v>
+        <v>23.32999992370605</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>550.0499877929688</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>640</v>
+        <v>23.32999992370605</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>6915514</v>
+        <v>256544491</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>16.35</v>
+        <v>14.47</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Solara Active Pharma shares jump 5% as Q1 profit rises 55%; Ibuprofen business remains a drag - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>SOLARA ACTIVE P Standalone June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1166,51 +1150,51 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SOMICONVEY.NS</t>
+          <t>PACIFICI.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Limited</t>
+          <t>Pacific Industries Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>96</v>
+        <v>133.5500030517578</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>103.9300003051758</v>
+        <v>159</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>95</v>
+        <v>133.5500030517578</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>100.0699996948242</v>
+        <v>150.9799957275391</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>86.61000061035156</v>
+        <v>133.5500030517578</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>100.0699996948242</v>
+        <v>150.9799957275391</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>687119</v>
+        <v>8374</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>15.54</v>
+        <v>13.05</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
+          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1219,7 +1203,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1227,68 +1211,60 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>KWIL.NS</t>
+          <t>CGVAK.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (India) Limited</t>
+          <t>CG Vak Software &amp; Exports Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>44.29999923706055</v>
+        <v>162.5500030517578</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>37.75</v>
+        <v>152.0099945068359</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>43.47000122070312</v>
+        <v>158.5800018310547</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>37.70999908447266</v>
+        <v>140.7299957275391</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>43.47000122070312</v>
+        <v>158.5800018310547</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>101230788</v>
+        <v>13494</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>15.27</v>
+        <v>12.68</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
+          <t>CGVAK Share Price Today - CG-VAK Software &amp; Exports Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
+          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
-        </is>
-      </c>
+          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1296,68 +1272,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX.NS</t>
+          <t>KOHINOOR.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals Limited</t>
+          <t>Kohinoor Foods Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>439</v>
+        <v>32.09999847412109</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>509.8999938964844</v>
+        <v>35.75</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>431</v>
+        <v>30.95000076293945</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>498.1499938964844</v>
+        <v>34.81000137329102</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>433.8500061035156</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>498.1499938964844</v>
+        <v>34.81000137329102</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>6099190</v>
+        <v>1739882</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>14.82</v>
+        <v>11.32</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX Q2 FY2026 Earnings: Robust Revenue Growth of 22.9% Drives Strong EPS of ₹15.67 - EPS Consistency Score - Vinanet</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals Limited Receives Open Offer from Zenrock Chemicals for 83.43 Lakh Shares - scanx.trade</t>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
-        </is>
-      </c>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1365,68 +1337,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>48.77000045776367</v>
+        <v>51.40000152587891</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>56.45000076293945</v>
+        <v>57.63999938964844</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>48.70000076293945</v>
+        <v>50.7599983215332</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.38000106811523</v>
+        <v>56.06999969482422</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>48.27999877929688</v>
+        <v>50.40999984741211</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>55.38000106811523</v>
+        <v>56.06999969482422</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>42665668</v>
+        <v>3789357</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>14.71</v>
+        <v>11.23</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+          <t>Only Three Days Left To Cash In On Ugar Sugar Works' (NSE:UGARSUGAR) Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Ltd. (DWARKESH) Share Price Rises 8.84% Today - Univest</t>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+          <t>The Ugar Sugar Works Ltd. (UGARSUGAR) Share Price Surges 8.63% Today - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Is It Worth Considering Dwarikesh Sugar Industries Limited (NSE:DWARKESH) For Its Upcoming Dividend? - simplywall.st</t>
+          <t>The Ugar Sugar Works Ltd. Share Price Today: Key Analysis - Univest</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Ltd. (DWARKESH) Share Price Rises 8.84% Today - Univest</t>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1434,60 +1406,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>KOTARISUG.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited</t>
+          <t>Kothari Sugars And Chemicals Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>20.73999977111816</v>
+        <v>27.8799991607666</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>23.97999954223633</v>
+        <v>31.39999961853027</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20.59000015258789</v>
+        <v>27.68000030517578</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>23.32999992370605</v>
+        <v>30.25</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20.3799991607666</v>
+        <v>27.21999931335449</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>23.32999992370605</v>
+        <v>30.25</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>256544491</v>
+        <v>1120625</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>14.47</v>
+        <v>11.13</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
+          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Are Wall Street Analysts Predicting PepsiCo Stock Will Climb or Sink? - Earnings Call Q&amp;A - Vinanet</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1495,51 +1471,51 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PACIFICI.NS</t>
+          <t>RANASUG.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Limited</t>
+          <t>Rana Sugars Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>133.5500030517578</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>159</v>
+        <v>15.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>133.5500030517578</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>150.9799957275391</v>
+        <v>15.21000003814697</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>133.5500030517578</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>150.9799957275391</v>
+        <v>15.21000003814697</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>8374</v>
+        <v>3630422</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>13.05</v>
+        <v>10.54</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -1548,7 +1524,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1556,51 +1532,51 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CGVAK.NS</t>
+          <t>SAKHTISUG.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CG Vak Software &amp; Exports Limited</t>
+          <t>Sakthi Sugars Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>159</v>
+        <v>19.76000022888184</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>162.5500030517578</v>
+        <v>22.05999946594238</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>152.0099945068359</v>
+        <v>19.76000022888184</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>158.5800018310547</v>
+        <v>21.77000045776367</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>140.7299957275391</v>
+        <v>19.70000076293945</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>158.5800018310547</v>
+        <v>21.77000045776367</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>13494</v>
+        <v>1960983</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>12.68</v>
+        <v>10.51</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>CGVAK Share Price Today - CG-VAK Software &amp; Exports Stock Analysis - Equitypandit</t>
+          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+          <t>Sakthi Sugars Limited Appoints R. Jeysree to Head the Internal Audit Department(In-House), Effective August 13, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr"/>
@@ -1609,7 +1585,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1617,68 +1593,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SUVEN.NS</t>
+          <t>HUBTOWN.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Suven Life Sciences Limited</t>
+          <t>Hubtown Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>335</v>
+        <v>180.4499969482422</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>377.4500122070312</v>
+        <v>205.6999969482422</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>335</v>
+        <v>180.0099945068359</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>373.6000061035156</v>
+        <v>198.8099975585938</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>332.5499877929688</v>
+        <v>180.1199951171875</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>373.6000061035156</v>
+        <v>198.8099975585938</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3256156</v>
+        <v>4728946</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>12.34</v>
+        <v>10.38</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
+          <t>Hubtown Q1 PAT slides 69% YoY to Rs 25 crore - Business Standard</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
+          <t>Hubtown Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView</t>
+          <t>Hubtown Consolidated June 2026 Net Sales at Rs 155.62 crore, down 16.96% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit</t>
+          <t>Hubtown Q1 results FY27: PAT Rs 26 Cr, Revenue Rs 155 Cr - Univest</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Suven Life Sciences seeks AGM approval for related party transaction and fund reallocation - scanx.trade</t>
+          <t>Hubtown makes Q1 FY27 earnings call audio available online - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1686,60 +1662,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Limited</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>303.0899963378906</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>344</v>
+        <v>43.70000076293945</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>301.8500061035156</v>
+        <v>39.45999908447266</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>336.2200012207031</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>300.989990234375</v>
+        <v>39.13000106811523</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>336.2200012207031</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2292635</v>
+        <v>3957967</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>11.7</v>
+        <v>10.27</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1747,64 +1731,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SWISSMLTRY.NS</t>
+          <t>VERANDA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Swiss Military Consumer Goods Limited</t>
+          <t>Veranda Learning Solutions Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15.1899995803833</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>16.79999923706055</v>
+        <v>265.8500061035156</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14</v>
+        <v>236</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>16.44000053405762</v>
+        <v>255.8999938964844</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>14.75</v>
+        <v>233.6999969482422</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16.44000053405762</v>
+        <v>255.8999938964844</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>870159</v>
+        <v>9972204</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>11.46</v>
+        <v>9.5</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>SWISSMLTRY Share Price Today - Swiss Military Consumer Goods Stock Analysis - Equitypandit</t>
+          <t>Veranda Learning Solutions Q1 Results: Earnings call audio uploaded - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Swiss Military Consumer Goods equity shares admitted on NSE - scanx.trade</t>
+          <t>Why are Crizac, Jaro, Veranda Learning and other e-learning stocks down today? Explained - Zee Business</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Swiss Military Consumer Goods Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Veranda Learning Solutions shareholders approve CMD reappointment - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Swiss Military Consumer Goods equity shares admitted on NSE - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Veranda Learning Solutions discloses JSCEL scheme compliance updates - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>NCLT approves Veranda Learning Solutions subsidiary amalgamation - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1812,59 +1800,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR.NS</t>
+          <t>RAJSREESUG.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Limited</t>
+          <t>Rajshree Sugars &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>32.09999847412109</v>
+        <v>37.0099983215332</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>35.75</v>
+        <v>40.79000091552734</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30.95000076293945</v>
+        <v>37</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>34.81000137329102</v>
+        <v>40.38000106811523</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>36.90000152587891</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34.81000137329102</v>
+        <v>40.38000106811523</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1739882</v>
+        <v>746681</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>11.32</v>
+        <v>9.43</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Rajshree Sugars &amp; Chemicals Ltd: Stock Climbs 1.67%, Testing Key Resistance at ₹35.72 - Mean Reversion Trade - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1989,7 +1981,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2058,7 +2050,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2127,7 +2119,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2135,60 +2127,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BTML.NS</t>
+          <t>GCSL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Bodhi Tree Multimedia Limited</t>
+          <t>Gretex Corporate Services Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8.789999961853027</v>
+        <v>526.2999877929688</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>8.800000190734863</v>
+        <v>540.9500122070312</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>7.849999904632568</v>
+        <v>470</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>7.920000076293945</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>8.720000267028809</v>
+        <v>521.7000122070312</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7.920000076293945</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1261909</v>
+        <v>615891</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.17</v>
+        <v>-7.6</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Bodhi Tree Multimedia Ltd. Stock News: Price Rise Analysis - Univest</t>
+          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>DD Q1 2026 Earnings: EPS Surges Past Estimates by 10.4% as Shares Retreat 1.33% - Earnings Acceleration Picks - Vinanet</t>
+          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>DD Q1 2026 Earnings: EPS Surges Past Estimates by 10.4% as Shares Retreat 1.33% - Earnings Acceleration Picks - Vinanet</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2196,64 +2196,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ADDIND.NS</t>
+          <t>MILKYMIST.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Limited</t>
+          <t>Milky Mist Dairy Food Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>87.94999694824219</v>
+        <v>207.8000030517578</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>87.94999694824219</v>
+        <v>211.8000030517578</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>71.05000305175781</v>
+        <v>181.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>80</v>
+        <v>184.8899993896484</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>87</v>
+        <v>199.6499938964844</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>80</v>
+        <v>184.8899993896484</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>612</v>
+        <v>56530266</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.39</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Limited Statistics – NSE:ADDIND - TradingView</t>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits</t>
+          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits</t>
+          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2261,64 +2265,60 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NKIND.NS</t>
+          <t>WEL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited</t>
+          <t>Wonder Electricals Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>60.9900016784668</v>
+        <v>148.3999938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>60.9900016784668</v>
+        <v>149.7799987792969</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>56.5</v>
+        <v>132</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>56.59999847412109</v>
+        <v>136.0399932861328</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>61.54999923706055</v>
+        <v>146.2599945068359</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>56.59999847412109</v>
+        <v>136.0399932861328</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>183</v>
+        <v>1505497</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-8.039999999999999</v>
+        <v>-6.99</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - Vinanet</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Fennec (FENC) Technical Check: Adds 0.51% to Close at $11.89 at the Close; Current Setup: the Supplied Trading Band Runs From $11.30 to $12.48 - Throwback Trade - Vinanet</t>
-        </is>
-      </c>
+          <t>Enterprise value to EBIT forward of Wel-Dish. Incorporated – TSE:2901 - TradingView</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2326,68 +2326,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GCSL.NS</t>
+          <t>ATAM.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Limited</t>
+          <t>Atam Valves Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>526.2999877929688</v>
+        <v>60.95000076293945</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>540.9500122070312</v>
+        <v>60.95000076293945</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>470</v>
+        <v>54.59999847412109</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>482.0499877929688</v>
+        <v>55.52999877929688</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>521.7000122070312</v>
+        <v>59.36000061035156</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>482.0499877929688</v>
+        <v>55.52999877929688</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>615891</v>
+        <v>88804</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-7.6</v>
+        <v>-6.45</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
+          <t>VRSN Q2 2026 Earnings: EPS Misses Consensus by 1.45% as Shares Decline 1.95% - ROIC Trend Report - Vinanet</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
-        </is>
-      </c>
+          <t>Shivansh Finserve: புதிய வளர்ச்சிக்கு முக்கிய முடிவு! பெரும் கையகப்படுத்துதல் திட்டம்? - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2395,68 +2391,56 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST.NS</t>
+          <t>DREDGECORP.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Limited</t>
+          <t>Dredging Corporation of India Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>207.8000030517578</v>
+        <v>1199</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>211.8000030517578</v>
+        <v>1204</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>181.5</v>
+        <v>1111.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>184.8899993896484</v>
+        <v>1118.300048828125</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>1189.199951171875</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>184.8899993896484</v>
+        <v>1118.300048828125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>56530266</v>
+        <v>253496</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.39</v>
+        <v>-5.96</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
-        </is>
-      </c>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2464,60 +2448,64 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>WEL.NS</t>
+          <t>GLOBECIVIL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Wonder Electricals Limited</t>
+          <t>Globe Civil Projects Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>148.3999938964844</v>
+        <v>45.45999908447266</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>149.7799987792969</v>
+        <v>45.45999908447266</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>132</v>
+        <v>41.5</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>136.0399932861328</v>
+        <v>42.34000015258789</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>146.2599945068359</v>
+        <v>44.97000122070312</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>136.0399932861328</v>
+        <v>42.34000015258789</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1505497</v>
+        <v>102543</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-6.99</v>
+        <v>-5.85</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+          <t>Globe Civil Projects Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value to EBIT forward of Wel-Dish. Incorporated – TSE:2901 - TradingView</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
+          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Femasys Inc. (FEMY) Q1 2026 Earnings: EPS Beat on Narrower Loss, Stock Slips - Dividend Earnings Report - Vinanet</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2525,64 +2513,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SINTERCOM.NS</t>
+          <t>DHABRIYA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sintercom India Limited</t>
+          <t>Dhabriya Polywood Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>86.98999786376953</v>
+        <v>600</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>86.98999786376953</v>
+        <v>600</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>79.05999755859375</v>
+        <v>548</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>79.38999938964844</v>
+        <v>555.25</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>79.38999938964844</v>
+        <v>555.25</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5959</v>
+        <v>59063</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-6.6</v>
+        <v>-5.41</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Sintercom India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>DHABRIYA Share Price Today - Dhabriya Polywood Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sintercom India standalone net profit rises 88.46% in the June 2026 quarter - Business Standard</t>
+          <t>Dhabriya Polywood Ltd Income Statement – NSE:DHABRIYA - TradingView</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Sintercom India standalone net profit rises 88.46% in the June 2026 quarter - Business Standard</t>
+          <t>Dhabriya Polywood Ltd. Share Price and 52-Week High View - Univest</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Copper Hits Record High as "Dr. Copper" Sends Conflicting Economic Signals - Consensus Forecast Report - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Free float of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Ltd. Share Price News: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2590,68 +2582,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CENTEXT.NS</t>
+          <t>TIJARIA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions Limited</t>
+          <t>Tijaria Polypipes Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>21.95000076293945</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>22.10000038146973</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20.39999961853027</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>20.63999938964844</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22.07999992370605</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20.63999938964844</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>440018</v>
+        <v>209055</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-6.52</v>
+        <v>-5.39</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Vicor Corporation (VICR) Climbs Nearly 8% as Shares Test Key Resistance Zone - WMA Signal - Vinanet</t>
+          <t>Tijaria Polypipes Q1 Results: Net loss widens 36% YoY to ₹36.11 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions Ltd. Share Price Today: 13.47% Increase - Univest</t>
+          <t>Vardhman Jain Tijaria raises stake in Tijaria Polypipes to 4.33% - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions Limited Approves Appointment of Shri Charan Singh as A Non-Executive Independent Director - marketscreener.com</t>
+          <t>Tijaria Polypipes board to approve Q2FY27 results, accept director resignation - scanx.trade</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions posts 10.97% sales rise in FY26, sets Aug 14 AGM date - scanx.trade</t>
+          <t>Tijaria Polypipes appoints new independent director, renews auditor at 20th AGM - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2659,64 +2651,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ATAM.NS</t>
+          <t>XTRANET.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Limited</t>
+          <t>Xtranet Technologies Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>60.95000076293945</v>
+        <v>161</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>60.95000076293945</v>
+        <v>166.5399932861328</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>54.59999847412109</v>
+        <v>155.6100006103516</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.52999877929688</v>
+        <v>160.1799926757812</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>59.36000061035156</v>
+        <v>169.1100006103516</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>55.52999877929688</v>
+        <v>160.1799926757812</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>88804</v>
+        <v>961010</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.45</v>
+        <v>-5.28</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+          <t>Aditya Infotech Share Price Up 4.27% Today; XtraNet Falls 4.35% - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>VRSN Q2 2026 Earnings: EPS Misses Consensus by 1.45% as Shares Decline 1.95% - ROIC Trend Report - Vinanet</t>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Shivansh Finserve: புதிய வளர்ச்சிக்கு முக்கிய முடிவு! பெரும் கையகப்படுத்துதல் திட்டம்? - Whalesbook</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Stocks to Watch Today: BSE, United Spirits, Hyundai Motor, XtraNet Tech, Autoline Industries, EMS, Ramco... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies adopts fair disclosure code for UPSI - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2724,64 +2720,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BALAXI.NS</t>
+          <t>KEEPLEARN.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>BALAXI PHARMACEUTICALS LIMITED</t>
+          <t>DSJ Keep Learning Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24.20000076293945</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>24.20000076293945</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>21.5</v>
+        <v>1.75</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>22.29999923706055</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>23.79000091552734</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22.29999923706055</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>139294</v>
+        <v>65231</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.26</v>
+        <v>-5.24</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com</t>
+          <t>DSJ Keep Learning Q1 Results: Net profit rises 66% YoY to ₹10 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com</t>
+          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Balaxi Pharma Q1 results FY27: PAT Rs 1 Cr, Revenue Rs 80 Cr - Univest</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Balaxi Pharmaceuticals Q1 FY27: Strong Revenue Recovery Masks Deep Structural Concerns - MarketsMojo</t>
-        </is>
-      </c>
+          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2789,64 +2781,56 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>LAXMICOT.NS</t>
+          <t>CALSOFT.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Cotspin Limited</t>
+          <t>California Software Company Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.26000022888184</v>
+        <v>29.88999938964844</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>15.28999996185303</v>
+        <v>29.88999938964844</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>13.90999984741211</v>
+        <v>27.04999923706055</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>13.96000003814697</v>
+        <v>27.04999923706055</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>14.89000034332275</v>
+        <v>28.46999931335449</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13.96000003814697</v>
+        <v>27.04999923706055</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>64470</v>
+        <v>1227668</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-6.25</v>
+        <v>-4.99</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Cotspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Cotspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>GRAIL Inc. Faces Selling Pressure as Shares Dip Below $67 - Gamma Squeeze - Vinanet</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Coastal Financial (CCB) Advances 2.71% as Shares Approach Key Resistance at $43 - Gap and Reverse - Vinanet</t>
-        </is>
-      </c>
+          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2854,56 +2838,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>HSCL.NS</t>
+          <t>INDOTHAI.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Limited</t>
+          <t>Indo Thai Securities Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>755</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>767.5999755859375</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>695.5</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>704.2000122070312</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>750.25</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>704.2000122070312</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>12470045</v>
+        <v>44689</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-6.14</v>
+        <v>-4.99</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2911,56 +2899,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DREDGECORP.NS</t>
+          <t>SVGLOBAL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation of India Limited</t>
+          <t>S V Global Mill Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1199</v>
+        <v>139.5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1204</v>
+        <v>143.4900054931641</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1111.5</v>
+        <v>120.9300003051758</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1118.300048828125</v>
+        <v>123.5299987792969</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1189.199951171875</v>
+        <v>130</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1118.300048828125</v>
+        <v>123.5299987792969</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>253496</v>
+        <v>363</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.96</v>
+        <v>-4.98</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+          <t>Total common shares outstanding of S V Global Mill Ltd. – NSE:SVGLOBAL - TradingView</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>SVGLOBAL Share Price Today - S V Global Mill Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited Announces Resignation of B. Parameswar as Key Managerial Personnel, Effective August 3, 2026 - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2968,64 +2968,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>GLOBECIVIL.NS</t>
+          <t>ABANSENT.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Globe Civil Projects Limited</t>
+          <t>Abans Enterprises Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45.45999908447266</v>
+        <v>28.79000091552734</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45.45999908447266</v>
+        <v>29.98999977111816</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>41.5</v>
+        <v>27.36000061035156</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>42.34000015258789</v>
+        <v>27.36000061035156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>44.97000122070312</v>
+        <v>28.79000091552734</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>42.34000015258789</v>
+        <v>27.36000061035156</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>102543</v>
+        <v>22519</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.85</v>
+        <v>-4.97</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Globe Civil Projects Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Abans Enterprises (ABANSENT.NS) Gains 1.63%: Support Holds Near ₹26.07 - Channel Breakout - Vinanet</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+          <t>ABANSENT.NS Mar 2026 Earnings: Modest EPS of ₹0.15 Despite Revenue Decline - Revenue Surprise History - Vinanet</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+          <t>Abans Enterprises Gains 3% as Stock Approaches Key Resistance — ABANSENT.NS - Zero Lag EMA - Vinanet</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Femasys Inc. (FEMY) Q1 2026 Earnings: EPS Beat on Narrower Loss, Stock Slips - Dividend Earnings Report - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Abans Enterprises (ABANSENT.NS) Surges 3.96% – Support and Resistance Levels in Focus - Zero Gamma Level - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Abans Enterprises Slips 5% as Stock Tests Crucial Support Levels - Earnings Sentiment - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3033,60 +3037,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SHREEJISPG.NS</t>
+          <t>KSR.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Limited</t>
+          <t>KSR Footwear Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>657</v>
+        <v>28.51000022888184</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>661.9500122070312</v>
+        <v>30</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>609.8499755859375</v>
+        <v>27</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>613.3499755859375</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>649.4500122070312</v>
+        <v>28.84000015258789</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>613.3499755859375</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1441160</v>
+        <v>77833</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.56</v>
+        <v>-4.92</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Ltd. (SHREEJISPG) Share Price Hits 52-Week High - Univest</t>
+          <t>KSR Footwear Standalone June 2026 Net Sales at Rs 52.25 crore, up 0.36% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>KSR Footwear Q1 Results: Net profit turns positive at ₹3.17 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>KSR Footwear dispatches FY26 annual report, sets August 24 AGM date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3094,68 +3106,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AHLADA.NS</t>
+          <t>ALPHAGEO.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ahlada Engineers Limited</t>
+          <t>Alphageo (India) Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>40.81999969482422</v>
+        <v>359.5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>40.81999969482422</v>
+        <v>359.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>38.5</v>
+        <v>328.1400146484375</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>38.59000015258789</v>
+        <v>328.6600036621094</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>40.81999969482422</v>
+        <v>345.4100036621094</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38.59000015258789</v>
+        <v>328.6600036621094</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>42109</v>
+        <v>34455</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.46</v>
+        <v>-4.85</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Ahlada Engineers to hold 21st AGM on August 5, 2026 - scanx.trade</t>
+          <t>Alphageo Standalone June 2026 Net Sales at Rs 54.38 crore, up 33.14% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Ahlada Engineers Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Alphageo (India) Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>RYN Q1 2026 Earnings: EPS of $0.07 Delivers 112.94% Surprise, Shares Gain 1.82% - Management Tone Analysis - Vinanet</t>
+          <t>Alphageo (India) Ltd. Share Price News and Price Action - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15 Best Bank Account Bonuses of August 2026: Earn Up to $3,000 in Cash Rewards - Next Quarter Guidance - Vinanet</t>
+          <t>Alphageo promoter Anisha Alla sells 2,100 shares on market - scanx.trade</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Ahlada Engineers Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Alphageo promoter Sashank Alla sells 1,500 equity shares on market - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3163,68 +3175,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DHABRIYA.NS</t>
+          <t>LAOPALA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dhabriya Polywood Limited</t>
+          <t>La Opala RG Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>600</v>
+        <v>182.0500030517578</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>600</v>
+        <v>182.0500030517578</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>548</v>
+        <v>176.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>555.25</v>
+        <v>178.3500061035156</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>587</v>
+        <v>187.2400054931641</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>555.25</v>
+        <v>178.3500061035156</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>59063</v>
+        <v>395733</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.41</v>
+        <v>-4.75</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>DHABRIYA Share Price Today - Dhabriya Polywood Stock Analysis - Equitypandit</t>
+          <t>Interested In La Opala RG's (NSE:LAOPALA) Upcoming ₹5.00 Dividend? You Have Two Days Left - simplywall.st</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Dhabriya Polywood Ltd Income Statement – NSE:DHABRIYA - TradingView</t>
+          <t>Mazagon Dock and 9 Other Stocks in Focus as They Turn Ex-Dividend Tomorrow - Trade Brains</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Dhabriya Polywood Ltd. Share Price and 52-Week High View - Univest</t>
+          <t>La Opala RG's (NSE:LAOPALA) Anemic Earnings Might Be Worse Than You Think - webull.com</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Free float of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView</t>
+          <t>La Opala RG Limited Releases Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Dhabriya Polywood Ltd. Share Price News: Price Rise Analysis - Univest</t>
+          <t>La Opala RG sets Aug 20 record date for ₹5 dividend - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:10:48 IST</t>
+          <t>2026-08-20 16:27:52 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3232,61 +3244,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TIJARIA.NS</t>
+          <t>TAKE.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Limited</t>
+          <t>TAKE Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6.119999885559082</v>
+        <v>23.3700008392334</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>6.289999961853027</v>
+        <v>23.3700008392334</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>5.619999885559082</v>
+        <v>21.75</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>5.789999961853027</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6.119999885559082</v>
+        <v>22.88999938964844</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5.789999961853027</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>209055</v>
+        <v>611881</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.39</v>
+        <v>-4.59</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times</t>
+          <t>GTA 6 leaks cause minor Take-Two stock jump; fo... - Pluang</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Q1 Results: Net loss widens 36% YoY to ₹36.11 lakh - scanx.trade</t>
+          <t>Take-Two Interactive stock steadies as GTA VI launch and fresh guidance shape 2026 outlook - Ad-hoc-news.de</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Vardhman Jain Tijaria raises stake in Tijaria Polypipes to 4.33% - scanx.trade</t>
+          <t>Wall Street analysts just called this healthcare stock a buy — here’s our take - CNBC</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes board to approve Q2FY27 results, accept director resignation - scanx.trade</t>
+          <t>Take-Two director Michael Sheresky sells $31,116 in shares By Investing.com - Investing.com India</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes appoints new independent director, renews auditor at 20th AGM - scanx.trade</t>
+          <t>LLY Stock: Where Compounding Could Take The Price - Trefis</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MPDL.NS</t>
+          <t>KRONOX.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MPDL Limited</t>
+          <t>Kronox Lab Sciences Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>34.29999923706055</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>34.31999969482422</v>
+        <v>186.1900024414062</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>23.26000022888184</v>
+        <v>155.0099945068359</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>34.31999969482422</v>
+        <v>186.1900024414062</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.60000038146973</v>
+        <v>155.1600036621094</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>34.31999969482422</v>
+        <v>186.1900024414062</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>8795</v>
+        <v>5889347</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+          <t>Vadodara-based Kronox Lab Sciences to change hands 2 yrs after listing - BusinessLine</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade</t>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>MPDL reports consolidated net loss of Rs 4.20 crore in the June 2026 quarter - Business Standard</t>
+          <t>Kronox Lab Sciences promoters sell 64.26% stake to Indo Borax - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,60 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KJMCFIN.NS</t>
+          <t>SOLARA.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited</t>
+          <t>Solara Active Pharma Sciences Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>66.34999847412109</v>
+        <v>551.9500122070312</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>66.41999816894531</v>
+        <v>654.4000244140625</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>61.90000152587891</v>
+        <v>551.9500122070312</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.41999816894531</v>
+        <v>640</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>55.34999847412109</v>
+        <v>550.0499877929688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>66.41999816894531</v>
+        <v>640</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3326</v>
+        <v>6915687</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>20</v>
+        <v>16.35</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>SOLARA ACTIVE P Consolidated June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences revises CIO Ajit Manocha’s joining date - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KRONOX.NS</t>
+          <t>KWIL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Limited</t>
+          <t>Kwality Wall's (India) Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>155.0099945068359</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>186.1900024414062</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>155.0099945068359</v>
+        <v>37.75</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>186.1900024414062</v>
+        <v>43.47000122070312</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>155.1600036621094</v>
+        <v>37.70999908447266</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>186.1900024414062</v>
+        <v>43.47000122070312</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>5888825</v>
+        <v>101299688</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>20</v>
+        <v>15.27</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals Limited executed a Share Purchase Agreement to acquire 64.26% stake in Kronox Lab Sciences Limited from Ketan Vinodchandra Ramani, Pritesh Vinodchandra Ramani and Jogindersingh Gianchand Jaswal for INR 2.5 billion. - marketscreener.com</t>
+          <t>Kwality Wall's (KWIL) Consolidates Near Support as Price Action Remains Range-Bound - Technical Analysis Picks - Vinanet</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Momentum Stocks: Kronox Lab Sciences, Waterways Leisure, Genus Power rise up to % on sheer momentum - TradingView</t>
+          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>BANARISUG.NS</t>
+          <t>INDOBORAX.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Limited</t>
+          <t>Indo Borax &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3635</v>
+        <v>439</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4338</v>
+        <v>509.8999938964844</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3635</v>
+        <v>431</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>4240.7001953125</v>
+        <v>498.1499938964844</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3617.39990234375</v>
+        <v>433.8500061035156</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4240.7001953125</v>
+        <v>498.1499938964844</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>71288</v>
+        <v>6099644</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>17.23</v>
+        <v>14.82</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
+          <t>Indo Borax &amp; Chemicals Limited Shareholders Approve All Board Appointments Through Postal Ballot - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+          <t>INDOBORAX Q2 2026 Earnings: Revenue Surges 22.93% YoY, EPS Stands at ₹15.67 - High Growth Earnings - Vinanet</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
+          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
+          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,68 +829,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SOLARA.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Limited</t>
+          <t>Bajaj Hindusthan Sugar Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>551.9500122070312</v>
+        <v>20.73999977111816</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>654.4000244140625</v>
+        <v>23.97999954223633</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>551.9500122070312</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>640</v>
+        <v>23.32999992370605</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>550.0499877929688</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>640</v>
+        <v>23.32999992370605</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6915514</v>
+        <v>256556792</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>16.35</v>
+        <v>14.47</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Solara Active Pharma shares jump 5% as Q1 profit rises 55%; Ibuprofen business remains a drag - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>SOLARA ACTIVE P Standalone June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -890,60 +886,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SOMICONVEY.NS</t>
+          <t>UTTAMSUGAR.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Limited</t>
+          <t>Uttam Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>96</v>
+        <v>303.0899963378906</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>103.9300003051758</v>
+        <v>344</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>95</v>
+        <v>301.8500061035156</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>100.0699996948242</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>86.61000061035156</v>
+        <v>300.989990234375</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>100.0699996948242</v>
+        <v>336.2200012207031</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>687119</v>
+        <v>2301215</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>15.54</v>
+        <v>11.7</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -951,68 +951,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KWIL.NS</t>
+          <t>KOHINOOR.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (India) Limited</t>
+          <t>Kohinoor Foods Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>38</v>
+        <v>32.09999847412109</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>44.29999923706055</v>
+        <v>35.75</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>37.75</v>
+        <v>30.95000076293945</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>43.47000122070312</v>
+        <v>34.81000137329102</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37.70999908447266</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43.47000122070312</v>
+        <v>34.81000137329102</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>101230788</v>
+        <v>1740167</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>15.27</v>
+        <v>11.32</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
+          <t>Kohinoor Textile to install 48MW battery storage amid 9MW solar expansion - Business Recorder</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1020,68 +1020,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX.NS</t>
+          <t>RANASUG.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals Limited</t>
+          <t>Rana Sugars Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>439</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>509.8999938964844</v>
+        <v>15.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>431</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>498.1499938964844</v>
+        <v>15.21000003814697</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>433.8500061035156</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>498.1499938964844</v>
+        <v>15.21000003814697</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>6099190</v>
+        <v>3647306</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>14.82</v>
+        <v>10.54</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX Q2 FY2026 Earnings: Robust Revenue Growth of 22.9% Drives Strong EPS of ₹15.67 - EPS Consistency Score - Vinanet</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Indo Borax &amp; Chemicals Limited Receives Open Offer from Zenrock Chemicals for 83.43 Lakh Shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
-        </is>
-      </c>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1089,60 +1077,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>KAYA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited</t>
+          <t>Kaya Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>20.73999977111816</v>
+        <v>339.9500122070312</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>23.97999954223633</v>
+        <v>385</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20.59000015258789</v>
+        <v>336.5499877929688</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>23.32999992370605</v>
+        <v>374.1000061035156</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.3799991607666</v>
+        <v>338.4500122070312</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23.32999992370605</v>
+        <v>374.1000061035156</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>256544491</v>
+        <v>245362</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>14.47</v>
+        <v>10.53</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Scholastic director Kaya Henderson sells $130,812 in stock - Investing.com</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Kaya To Issue 1.82 Million Equity Shares At 274.10 Rupees Per Share For Aggregate Cash Consideration Of Approx 500 Million Rupees - TradingView</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Kaya Standalone June 2026 Net Sales at Rs 60.14 crore, up 13.91% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1150,60 +1146,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>PACIFICI.NS</t>
+          <t>HUBTOWN.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Limited</t>
+          <t>Hubtown Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>133.5500030517578</v>
+        <v>180.4499969482422</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>159</v>
+        <v>205.6999969482422</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>133.5500030517578</v>
+        <v>180.0099945068359</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>150.9799957275391</v>
+        <v>198.8099975585938</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>133.5500030517578</v>
+        <v>180.1199951171875</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>150.9799957275391</v>
+        <v>198.8099975585938</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>8374</v>
+        <v>4731451</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>13.05</v>
+        <v>10.38</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
+          <t>Hubtown Ltd. Share Price Up 9.01%: Price, Valuation View - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
+          <t>Hubtown Ltd. Share Price Up 9.01%: Price, Valuation View - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Hubtown Q1 PAT slides 69% YoY to Rs 25 crore - Business Standard</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Hubtown Consolidated June 2026 Net Sales at Rs 155.62 crore, down 16.96% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Hubtown makes Q1 FY27 earnings call audio available online - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1211,51 +1215,51 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CGVAK.NS</t>
+          <t>CORDELIA.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CG Vak Software &amp; Exports Limited</t>
+          <t>Waterways Leisure Tourism Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>159</v>
+        <v>820.5499877929688</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>162.5500030517578</v>
+        <v>907.75</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>152.0099945068359</v>
+        <v>820.5499877929688</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>158.5800018310547</v>
+        <v>907.75</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>140.7299957275391</v>
+        <v>825.25</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>158.5800018310547</v>
+        <v>907.75</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>13494</v>
+        <v>700284</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>12.68</v>
+        <v>10</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>CGVAK Share Price Today - CG-VAK Software &amp; Exports Stock Analysis - Equitypandit</t>
+          <t>Cordelia Cruises Share Price Falls 7.71% to Rs 842.25 After Q1 Results - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
@@ -1264,7 +1268,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1272,64 +1276,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR.NS</t>
+          <t>VERANDA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Limited</t>
+          <t>Veranda Learning Solutions Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>32.09999847412109</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>35.75</v>
+        <v>265.8500061035156</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30.95000076293945</v>
+        <v>236</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>34.81000137329102</v>
+        <v>255.8999938964844</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>233.6999969482422</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>34.81000137329102</v>
+        <v>255.8999938964844</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1739882</v>
+        <v>9972226</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>11.32</v>
+        <v>9.5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>Veranda Learning Solutions shareholders approve CMD reappointment - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>Why are Crizac, Jaro, Veranda Learning and other e-learning stocks down today? Explained - Zee Business</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Veranda Learning Solutions Q1 Results: Earnings call audio uploaded - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Veranda Learning Solutions discloses JSCEL scheme compliance updates - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>NCLT approves Veranda Learning Solutions subsidiary amalgamation - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1337,68 +1345,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>ORIENTCER.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>ORIENT CERATECH LIMITED</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>51.40000152587891</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>57.63999938964844</v>
+        <v>47.22999954223633</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>50.7599983215332</v>
+        <v>42.52000045776367</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.06999969482422</v>
+        <v>46.72999954223633</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>50.40999984741211</v>
+        <v>43.11999893188477</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56.06999969482422</v>
+        <v>46.72999954223633</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3789357</v>
+        <v>353057</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>11.23</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Only Three Days Left To Cash In On Ugar Sugar Works' (NSE:UGARSUGAR) Dividend - simplywall.st</t>
+          <t>Do Its Financials Have Any Role To Play In Driving Orient Ceratech Limited's (NSE:ORIENTCER) Stock Up Recently? - simplywall.st</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
+          <t>ORIENTCER.NS Mar 2026 Earnings: EPS of ₹0.43 on Revenue of ₹95.24 Crore; Stock Gains 2.37% - Post-Earnings Reaction - Vinanet</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Ltd. (UGARSUGAR) Share Price Surges 8.63% Today - Univest</t>
+          <t>ORIENTCER.NS Mar 2026 Earnings: EPS of ₹0.43 on Revenue of ₹95.24 Crore; Stock Gains 2.37% - Post-Earnings Reaction - Vinanet</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Ltd. Share Price Today: Key Analysis - Univest</t>
+          <t>Ashapura International Limited Increases Shareholding in Orient Ceratech Limited to 8.35% - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
+          <t>ORIENT CERATECH Limited (ORIENTCER.NS): Modest Uptick Amid Range-Bound Trading - OBV Trend Line - Vinanet</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1406,64 +1414,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>KOTARISUG.NS</t>
+          <t>KRYSTAL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Limited</t>
+          <t>Krystal Integrated Services Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>27.8799991607666</v>
+        <v>635</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>31.39999961853027</v>
+        <v>689</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>27.68000030517578</v>
+        <v>620.7000122070312</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>30.25</v>
+        <v>681.3499755859375</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.21999931335449</v>
+        <v>629.4500122070312</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>30.25</v>
+        <v>681.3499755859375</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1120625</v>
+        <v>688365</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>11.13</v>
+        <v>8.25</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
+          <t>Krystal Integrated Services Shares Gain 4% on Rs 134 Crore Order - Equitypandit</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
+          <t>Krystal Integrated Services Ltd (KRYSTAL) Share Price Rises 8.53% Today - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
+          <t>Krystal Integrated Services Ltd (KRYSTAL) Share Price Rises 8.53% Today - Univest</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Are Wall Street Analysts Predicting PepsiCo Stock Will Climb or Sink? - Earnings Call Q&amp;A - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Small-cap stock jumps after receipt of ₹134 crore order from Maharashtra Road Transport - livemint.com</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Krystal Integrated Services makes decent debut, lists at 9.7% premium on NSE - Upstox</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1471,60 +1483,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RANASUG.NS</t>
+          <t>GENUSPOWER.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Limited</t>
+          <t>Genus Power Infrastructures Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13.85999965667725</v>
+        <v>310.8999938964844</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>15.5</v>
+        <v>340.8999938964844</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>13.85999965667725</v>
+        <v>310.8999938964844</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>15.21000003814697</v>
+        <v>334.25</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>13.76000022888184</v>
+        <v>309.2999877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15.21000003814697</v>
+        <v>334.25</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3630422</v>
+        <v>16393463</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>10.54</v>
+        <v>8.07</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+          <t>GENUSPOWER Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+          <t>Genus Power Q2 2026 Earnings: Revenue Surges 94.55% YoY, EPS at ₹21.29 - Revenue Warning Signal - Vinanet</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Genus Power Infrastructures (NSE:GENUSPOWER) Strong Profits May Be Masking Some Underlying Issues - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Genus Power Infrastructures Limited (GENUSPOWER.NS) – Moderate Decline on Profit Booking Amid Sector Headwinds - Symmetrical Triangle - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Genus Power Infrastructures Limited's (NSE:GENUSPOWER) Stock Has Been Sliding But Fundamentals Look Strong: Is The Market Wrong? - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1532,60 +1552,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SAKHTISUG.NS</t>
+          <t>JNPR.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Limited</t>
+          <t>Juniper Green Energy Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>19.76000022888184</v>
+        <v>252.8099975585938</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>22.05999946594238</v>
+        <v>275.5199890136719</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>19.76000022888184</v>
+        <v>251.7299957275391</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>21.77000045776367</v>
+        <v>273.760009765625</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19.70000076293945</v>
+        <v>253.7100067138672</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21.77000045776367</v>
+        <v>273.760009765625</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1960983</v>
+        <v>7029425</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>10.51</v>
+        <v>7.9</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
+          <t>JNPR Share Price Today - Juniper Green Energy Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
+          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Limited Appoints R. Jeysree to Head the Internal Audit Department(In-House), Effective August 13, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>JNPR Share Price Today - Juniper Green Energy Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Juniper Green Energy Ltd Share Price Today,, JNPR Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1593,68 +1621,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>HUBTOWN.NS</t>
+          <t>RENUKA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Limited</t>
+          <t>Shree Renuka Sugars Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>180.4499969482422</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>205.6999969482422</v>
+        <v>26.43000030517578</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>180.0099945068359</v>
+        <v>24.5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>198.8099975585938</v>
+        <v>26.1299991607666</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>180.1199951171875</v>
+        <v>24.23999977111816</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>198.8099975585938</v>
+        <v>26.1299991607666</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4728946</v>
+        <v>95136169</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>10.38</v>
+        <v>7.8</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Q1 PAT slides 69% YoY to Rs 25 crore - Business Standard</t>
+          <t>Shree Renuka Sugars Ltd. Share Price: 8.7% Gain Analysis - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Shree Renuka Sugars Ltd. Share Price: 8.7% Gain Analysis - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Consolidated June 2026 Net Sales at Rs 155.62 crore, down 16.96% Y-o-Y - Moneycontrol.com</t>
+          <t>Balrampur Chini, Bajaj Hind, Shree Renuka shares rise up to 13%; here's why - Business Today</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Q1 results FY27: PAT Rs 26 Cr, Revenue Rs 155 Cr - Univest</t>
+          <t>Bajaj Hind, Dwarikesh, Renuka rally up to 14%; what's driving sugar stocks? - Business Standard</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Hubtown makes Q1 FY27 earnings call audio available online - scanx.trade</t>
+          <t>Sweet Gains Continue: Shree Renuka, Dalmia Bharat Rally Up To 7% Despite Govt's Inventory Clampdown - NDTV Profit</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1662,68 +1690,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>DHAMPURSUG.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Limited</t>
+          <t>Dhampur Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>39.97000122070312</v>
+        <v>179.6999969482422</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>43.70000076293945</v>
+        <v>192.8899993896484</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>39.45999908447266</v>
+        <v>178.9700012207031</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>43.15000152587891</v>
+        <v>189.7599945068359</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>39.13000106811523</v>
+        <v>176.1799926757812</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>43.15000152587891</v>
+        <v>189.7599945068359</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3957967</v>
+        <v>6615935</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>10.27</v>
+        <v>7.71</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+          <t>Dhampur Sugar Mills sets book closure dates for 91st AGM - scanx.trade</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>Dhampur Sugar Mills settles ₹100 crore commercial paper - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1731,68 +1759,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VERANDA.NS</t>
+          <t>EPL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions Limited</t>
+          <t>EPL Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>236.8999938964844</v>
+        <v>252</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>265.8500061035156</v>
+        <v>273</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>255.8999938964844</v>
+        <v>270.1000061035156</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>233.6999969482422</v>
+        <v>250.8000030517578</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>255.8999938964844</v>
+        <v>270.1000061035156</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>9972204</v>
+        <v>6480002</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+          <t>EPL Ltd. Share Price Reaches One-Year High: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Why are Crizac, Jaro, Veranda Learning and other e-learning stocks down today? Explained - Zee Business</t>
+          <t>EPL Ltd. Share Price Reaches One-Year High: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions shareholders approve CMD reappointment - scanx.trade</t>
+          <t>EPL Standalone June 2026 Net Sales at Rs 400.30 crore, up 19.85% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions discloses JSCEL scheme compliance updates - scanx.trade</t>
+          <t>EPL Limited Q1FY27 results: Consolidated revenue up 25% to ₹13,879mn - scanx.trade</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>NCLT approves Veranda Learning Solutions subsidiary amalgamation - scanx.trade</t>
+          <t>Old Namibia uranium data guides Skeleton Coast's planned fieldwork - Stock Titan</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1800,61 +1828,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG.NS</t>
+          <t>RATNAVEER.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars &amp; Chemicals Limited</t>
+          <t>Ratnaveer Precision Engineering Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>37.0099983215332</v>
+        <v>253.2299957275391</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>40.79000091552734</v>
+        <v>270.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>37</v>
+        <v>252</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.38000106811523</v>
+        <v>269.239990234375</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>36.90000152587891</v>
+        <v>250.3999938964844</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>40.38000106811523</v>
+        <v>269.239990234375</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>746681</v>
+        <v>11344542</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9.43</v>
+        <v>7.52</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
+          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+          <t>Ratnaveer Precision Engineering appoints Seema Sanghavi as WTD - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
+          <t>Ratnaveer Precision approves rights issue of 1.25 crore shares at ₹264 each - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars &amp; Chemicals Ltd: Stock Climbs 1.67%, Testing Key Resistance at ₹35.72 - Mean Reversion Trade - Vinanet</t>
+          <t>Press Release Distribution India - Business Wire India</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+          <t>Ratnaveer Standalone June 2026 Net Sales at Rs 314.64 crore, up 18.9% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1903,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1981,7 +2009,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1989,68 +2017,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM.NS</t>
+          <t>GCSL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>TECIL Chemicals and Hydro Power Limited</t>
+          <t>Gretex Corporate Services Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11.28999996185303</v>
+        <v>526.2999877929688</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11.55000019073486</v>
+        <v>540.9500122070312</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>9</v>
+        <v>470</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.140000343322754</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10.23999977111816</v>
+        <v>521.7000122070312</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.140000343322754</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>306021</v>
+        <v>615899</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-10.74</v>
+        <v>-7.6</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>TECIL Chemicals (TECILCHEM) Declines to ₹11.6, Approaches Key Support Zone - McClellan Summation - Vinanet</t>
+          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Dollar Steadies as US-Iran Tensions Escalate; Yen Weakens on Pension Concerns - Profit Announcement - Vinanet</t>
+          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - Vinanet</t>
+          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>TECIL Chemicals (TECILCHEM.NS) Declines Nearly 3.5%, Approaches Key Support at ₹9.19 - Liquidity Order Flow - Vinanet</t>
+          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM.NS Q2 2025 Earnings: No Revenue, Net Loss Amid Minimal Business Activity - EBITDA Margin Trends - Vinanet</t>
+          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2058,68 +2086,60 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KAMANWALA.NS</t>
+          <t>HSCL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Kamanwala Housing Construction Limited</t>
+          <t>Himadri Speciality Chemical Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18.59000015258789</v>
+        <v>755</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>18.59000015258789</v>
+        <v>767.5999755859375</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>16.11000061035156</v>
+        <v>695.5</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>16.68000030517578</v>
+        <v>704.2000122070312</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18.6299991607666</v>
+        <v>750.25</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16.68000030517578</v>
+        <v>704.2000122070312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>56343</v>
+        <v>12482496</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-10.47</v>
+        <v>-6.14</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Kamanwala Housing Construction Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Japanese stocks rebound as bond yields ease - Business Standard</t>
+          <t>Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Volume Gainers on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Horizon Industrial Parks IPO Day 3 Subscription Status: Issue Booked 0.30x So Far - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Chinese stocks rebound as policy hopes build - Business Standard</t>
-        </is>
-      </c>
+          <t>Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2127,68 +2147,56 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GCSL.NS</t>
+          <t>DREDGECORP.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Limited</t>
+          <t>Dredging Corporation of India Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>526.2999877929688</v>
+        <v>1199</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>540.9500122070312</v>
+        <v>1204</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>470</v>
+        <v>1111.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>482.0499877929688</v>
+        <v>1118.300048828125</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>521.7000122070312</v>
+        <v>1189.199951171875</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>482.0499877929688</v>
+        <v>1118.300048828125</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>615891</v>
+        <v>253900</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.6</v>
+        <v>-5.96</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
-        </is>
-      </c>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2196,68 +2204,60 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST.NS</t>
+          <t>SHREEJISPG.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Limited</t>
+          <t>Shreeji Shipping Global Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>207.8000030517578</v>
+        <v>657</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>211.8000030517578</v>
+        <v>661.9500122070312</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>181.5</v>
+        <v>609.8499755859375</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>184.8899993896484</v>
+        <v>613.3499755859375</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>199.6499938964844</v>
+        <v>649.4500122070312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>184.8899993896484</v>
+        <v>613.3499755859375</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>56530266</v>
+        <v>1441163</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.39</v>
+        <v>-5.56</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+          <t>Shreeji Shipping Global Ltd. (SHREEJISPG) Share Price Hits 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
+          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
-        </is>
-      </c>
+          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2265,60 +2265,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>WEL.NS</t>
+          <t>UEL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Wonder Electricals Limited</t>
+          <t>Ujaas Energy Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>148.3999938964844</v>
+        <v>190.7599945068359</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>149.7799987792969</v>
+        <v>190.7599945068359</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>132</v>
+        <v>190.7599945068359</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>136.0399932861328</v>
+        <v>190.7599945068359</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>146.2599945068359</v>
+        <v>200.8000030517578</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>136.0399932861328</v>
+        <v>190.7599945068359</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1505497</v>
+        <v>6358</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.99</v>
+        <v>-5</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+          <t>Ujaas Energy Ltd. Share Price Shows Strong Price Action - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value to EBIT forward of Wel-Dish. Incorporated – TSE:2901 - TradingView</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Ltd. Share Price Jumps to New 52-Week Peak - Univest</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2326,64 +2334,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ATAM.NS</t>
+          <t>INDOTHAI.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Limited</t>
+          <t>Indo Thai Securities Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60.95000076293945</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>60.95000076293945</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>54.59999847412109</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.52999877929688</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>59.36000061035156</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>55.52999877929688</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>88804</v>
+        <v>45140</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.45</v>
+        <v>-4.99</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>VRSN Q2 2026 Earnings: EPS Misses Consensus by 1.45% as Shares Decline 1.95% - ROIC Trend Report - Vinanet</t>
+          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Shivansh Finserve: புதிய வளர்ச்சிக்கு முக்கிய முடிவு! பெரும் கையகப்படுத்துதல் திட்டம்? - Whalesbook</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities unsecured creditors approve broking demerger - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2391,56 +2403,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DREDGECORP.NS</t>
+          <t>KSR.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation of India Limited</t>
+          <t>KSR Footwear Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1199</v>
+        <v>28.51000022888184</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1204</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1111.5</v>
+        <v>27</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1118.300048828125</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1189.199951171875</v>
+        <v>28.84000015258789</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1118.300048828125</v>
+        <v>27.42000007629395</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>253496</v>
+        <v>77843</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.96</v>
+        <v>-4.92</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+          <t>KSR Footwear Standalone June 2026 Net Sales at Rs 52.25 crore, up 0.36% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>KSR Footwear Q1 Results: Net profit turns positive at ₹3.17 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>KSR Footwear dispatches FY26 annual report, sets August 24 AGM date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2448,64 +2472,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>GLOBECIVIL.NS</t>
+          <t>GANGAFORGE.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Globe Civil Projects Limited</t>
+          <t>Ganga Forging Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>45.45999908447266</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45.45999908447266</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>41.5</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>42.34000015258789</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>44.97000122070312</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>42.34000015258789</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>102543</v>
+        <v>968342</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.85</v>
+        <v>-4.87</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Globe Civil Projects Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Femasys Inc. (FEMY) Q1 2026 Earnings: EPS Beat on Narrower Loss, Stock Slips - Dividend Earnings Report - Vinanet</t>
-        </is>
-      </c>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2513,68 +2529,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DHABRIYA.NS</t>
+          <t>ASTERDM.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Dhabriya Polywood Limited</t>
+          <t>Aster DM Quality Care Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>600</v>
+        <v>798.3499755859375</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>600</v>
+        <v>798.3499755859375</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>548</v>
+        <v>756.0499877929688</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>555.25</v>
+        <v>765.6500244140625</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>587</v>
+        <v>800.2000122070312</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>555.25</v>
+        <v>765.6500244140625</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>59063</v>
+        <v>9884475</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.41</v>
+        <v>-4.32</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>DHABRIYA Share Price Today - Dhabriya Polywood Stock Analysis - Equitypandit</t>
+          <t>Aster DM Healthcare to rename as Aster DM Quality Care Limited - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Dhabriya Polywood Ltd Income Statement – NSE:DHABRIYA - TradingView</t>
+          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Dhabriya Polywood Ltd. Share Price and 52-Week High View - Univest</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Free float of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Dhabriya Polywood Ltd. Share Price News: Price Rise Analysis - Univest</t>
-        </is>
-      </c>
+          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2582,68 +2590,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TIJARIA.NS</t>
+          <t>KPEL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Limited</t>
+          <t>K.P. Energy Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6.119999885559082</v>
+        <v>268.2000122070312</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>6.289999961853027</v>
+        <v>271</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5.619999885559082</v>
+        <v>255.1499938964844</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5.789999961853027</v>
+        <v>256.6499938964844</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6.119999885559082</v>
+        <v>268.2000122070312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.789999961853027</v>
+        <v>256.6499938964844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>209055</v>
+        <v>442666</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.39</v>
+        <v>-4.31</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times</t>
+          <t>K.P. Energy Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Q1 Results: Net loss widens 36% YoY to ₹36.11 lakh - scanx.trade</t>
+          <t>K.P. Energy Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Vardhman Jain Tijaria raises stake in Tijaria Polypipes to 4.33% - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Tijaria Polypipes board to approve Q2FY27 results, accept director resignation - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Tijaria Polypipes appoints new independent director, renews auditor at 20th AGM - scanx.trade</t>
-        </is>
-      </c>
+          <t>K.P. Energy Q1FY27 revenue surges 137% to ₹519.46 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2651,68 +2651,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>XTRANET.NS</t>
+          <t>YASHO.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Limited</t>
+          <t>Yasho Industries Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>161</v>
+        <v>4500</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>166.5399932861328</v>
+        <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>155.6100006103516</v>
+        <v>4230</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>160.1799926757812</v>
+        <v>4284.2001953125</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>169.1100006103516</v>
+        <v>4470.7998046875</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>160.1799926757812</v>
+        <v>4284.2001953125</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>961010</v>
+        <v>123163</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5.28</v>
+        <v>-4.17</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Aditya Infotech Share Price Up 4.27% Today; XtraNet Falls 4.35% - Univest</t>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+          <t>Yasho Industries Share Price Today, Yasho Industries Stock Price Live NSE/BSE Updates - The Economic Times</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Stocks to Watch Today: BSE, United Spirits, Hyundai Motor, XtraNet Tech, Autoline Industries, EMS, Ramco... - Moneycontrol.com</t>
+          <t>Yasho Ind. Standalone June 2026 Net Sales at Rs 314.09 crore, up 58.73% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies adopts fair disclosure code for UPSI - scanx.trade</t>
+          <t>Yasho Industries Q1 FY27 Results: PAT Rs 36 Cr, Revenue Rs 307 Cr - Univest</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2720,60 +2720,56 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>KEEPLEARN.NS</t>
+          <t>KRISHNADEF.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DSJ Keep Learning Limited</t>
+          <t>Krishna Defence And Allied Industries Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.919999957084656</v>
+        <v>1083.900024414062</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2</v>
+        <v>1094.900024414062</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1.75</v>
+        <v>1026</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.809999942779541</v>
+        <v>1037.900024414062</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.909999966621399</v>
+        <v>1077.800048828125</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.809999942779541</v>
+        <v>1037.900024414062</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>65231</v>
+        <v>152475</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5.24</v>
+        <v>-3.7</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>DSJ Keep Learning Q1 Results: Net profit rises 66% YoY to ₹10 lakh - scanx.trade</t>
+          <t>Krishna Defence and Allied Industries Ltd. (KRISHNADEF) Share Price Falls 8.3% Today - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
-        </is>
-      </c>
+          <t>Krishna Defence and Allied Industries Ltd. (KRISHNADEF) Share Price Falls 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2781,56 +2777,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT.NS</t>
+          <t>CHENNPETRO.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>California Software Company Limited</t>
+          <t>Chennai Petroleum Corporation Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29.88999938964844</v>
+        <v>1457</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>29.88999938964844</v>
+        <v>1466</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>27.04999923706055</v>
+        <v>1379.599975585938</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>27.04999923706055</v>
+        <v>1390.5</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28.46999931335449</v>
+        <v>1440.300048828125</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>27.04999923706055</v>
+        <v>1390.5</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1227668</v>
+        <v>2227820</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.99</v>
+        <v>-3.46</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
+          <t>Chennai Petroleum Corporation Limited (NSE:CHENNPETRO) Looks Interesting, And It's About To Pay A Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Rises 5.01% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. Stock News: Price Up 5.8% - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2838,60 +2846,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>Syrma SGS Technology Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>1504.800048828125</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>1525.800048828125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>1415.699951171875</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>1443.699951171875</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>66.09999847412109</v>
+        <v>1494.800048828125</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>1443.699951171875</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>44689</v>
+        <v>1342162</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.99</v>
+        <v>-3.42</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+          <t>Syrma SGS Technology Ltd. Share Price Today After 3.43% Fall - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+          <t>Syrma SGS Technology Ltd. Share Price Today After 3.43% Fall - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Syrma SGS, Dixon, other EMS companies' shares rise as govt clears 31 electronics component projects worth... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Syrma SGS Technology Stock Surges Over 3% After ECMS Application Gets Approved By Govt - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Govt clears ₹7,877 crore ECMS investments; Wipro, PCBL Chemical, Syrma SGS shares in focus - CNBC TV18</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2899,68 +2915,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SVGLOBAL.NS</t>
+          <t>AIIL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Limited</t>
+          <t>Authum Investment &amp; Infrastructure Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>139.5</v>
+        <v>551</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>143.4900054931641</v>
+        <v>553.75</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>120.9300003051758</v>
+        <v>527.25</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>123.5299987792969</v>
+        <v>532.2999877929688</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>130</v>
+        <v>550.5</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>123.5299987792969</v>
+        <v>532.2999877929688</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>363</v>
+        <v>966550</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.98</v>
+        <v>-3.31</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of S V Global Mill Ltd. – NSE:SVGLOBAL - TradingView</t>
+          <t>AIIL Share Price | Authum Investment &amp; Infrastructure Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>SVGLOBAL Share Price Today - S V Global Mill Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>S V Global Mill Limited Announces Resignation of B. Parameswar as Key Managerial Personnel, Effective August 3, 2026 - marketscreener.com</t>
-        </is>
-      </c>
+          <t>AIIL Share Price | Authum Investment &amp; Infrastructure Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2968,68 +2972,56 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ABANSENT.NS</t>
+          <t>NOVARTIND.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Abans Enterprises Limited</t>
+          <t>Novartis India Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>28.79000091552734</v>
+        <v>1540</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>29.98999977111816</v>
+        <v>1574.900024414062</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>27.36000061035156</v>
+        <v>1476</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>27.36000061035156</v>
+        <v>1482.199951171875</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.79000091552734</v>
+        <v>1531.699951171875</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27.36000061035156</v>
+        <v>1482.199951171875</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>22519</v>
+        <v>16240</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.97</v>
+        <v>-3.23</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Abans Enterprises (ABANSENT.NS) Gains 1.63%: Support Holds Near ₹26.07 - Channel Breakout - Vinanet</t>
+          <t>Novartis India Ltd. Share Price News: New 52-Week Trough - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>ABANSENT.NS Mar 2026 Earnings: Modest EPS of ₹0.15 Despite Revenue Decline - Revenue Surprise History - Vinanet</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Abans Enterprises Gains 3% as Stock Approaches Key Resistance — ABANSENT.NS - Zero Lag EMA - Vinanet</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Abans Enterprises (ABANSENT.NS) Surges 3.96% – Support and Resistance Levels in Focus - Zero Gamma Level - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Abans Enterprises Slips 5% as Stock Tests Crucial Support Levels - Earnings Sentiment - Vinanet</t>
-        </is>
-      </c>
+          <t>Novartis India Ltd. Share Price News: New 52-Week Trough - Univest</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3037,68 +3029,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>KSR.NS</t>
+          <t>NEOGEN.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Limited</t>
+          <t>Neogen Chemicals Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>28.51000022888184</v>
+        <v>2358.89990234375</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>30</v>
+        <v>2368.699951171875</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>27</v>
+        <v>2250</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>27.42000007629395</v>
+        <v>2259.10009765625</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>28.84000015258789</v>
+        <v>2328.800048828125</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>27.42000007629395</v>
+        <v>2259.10009765625</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>77833</v>
+        <v>137421</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.92</v>
+        <v>-2.99</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Standalone June 2026 Net Sales at Rs 52.25 crore, up 0.36% Y-o-Y - Moneycontrol.com</t>
+          <t>SBI Mutual Fund reduces Neogen Chemicals stake to 6.03% under SAST Reg 29 - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+          <t>Neogen Corp CEO Mikheal Nassif Executes RSU Tax Withholding on August 19, 2026 - Kalkine Media</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Q1 Results: Net profit turns positive at ₹3.17 million - scanx.trade</t>
+          <t>Neogen (NEOG) CEO uses 20K shares to cover RSU taxes - Stock Titan</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear dispatches FY26 annual report, sets August 24 AGM date - scanx.trade</t>
+          <t>Neogen Chemicals Limited (NEOGEN.BO) stock price, news, quote and history - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+          <t>Neogen Corporation (NASDAQ:NEOG) Given Average Rating of "Hold" by Brokerages - MarketBeat</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3106,68 +3098,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ALPHAGEO.NS</t>
+          <t>MMFL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Alphageo (India) Limited</t>
+          <t>MM Forgings Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>359.5</v>
+        <v>660.0999755859375</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>359.5</v>
+        <v>669.4500122070312</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>328.1400146484375</v>
+        <v>635</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>328.6600036621094</v>
+        <v>638.9500122070312</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>345.4100036621094</v>
+        <v>657.7999877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>328.6600036621094</v>
+        <v>638.9500122070312</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>34455</v>
+        <v>176799</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.85</v>
+        <v>-2.87</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Alphageo Standalone June 2026 Net Sales at Rs 54.38 crore, up 33.14% Y-o-Y - Moneycontrol.com</t>
+          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Alphageo (India) Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Alphageo (India) Ltd. Share Price News and Price Action - Univest</t>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Alphageo promoter Anisha Alla sells 2,100 shares on market - scanx.trade</t>
+          <t>M M Forgings Limited Announces Resignation of Chandrasekar S from Company Secretary and Compliance Officer, Effective August 14, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Alphageo promoter Sashank Alla sells 1,500 equity shares on market - scanx.trade</t>
+          <t>M M Forgings postpones Q1FY26 board meeting to Aug 14 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3175,68 +3167,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>LAOPALA.NS</t>
+          <t>PFC.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>La Opala RG Limited</t>
+          <t>Power Finance Corporation Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>182.0500030517578</v>
+        <v>374.4500122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>182.0500030517578</v>
+        <v>375.1000061035156</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>176.5</v>
+        <v>363.2000122070312</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>178.3500061035156</v>
+        <v>363.7999877929688</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>187.2400054931641</v>
+        <v>374.4500122070312</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>178.3500061035156</v>
+        <v>363.7999877929688</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>395733</v>
+        <v>13375984</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.75</v>
+        <v>-2.84</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Interested In La Opala RG's (NSE:LAOPALA) Upcoming ₹5.00 Dividend? You Have Two Days Left - simplywall.st</t>
+          <t>PFC, REC shares decline up to 3% after Morgan Stanley cuts growth estimates - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Mazagon Dock and 9 Other Stocks in Focus as They Turn Ex-Dividend Tomorrow - Trade Brains</t>
+          <t>PFC, REC Shares Fall Up To 3% As Morgan Stanley Cuts Growth Estimates - outlookbusiness.com</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>La Opala RG's (NSE:LAOPALA) Anemic Earnings Might Be Worse Than You Think - webull.com</t>
+          <t>PFC, REC Shares Fall As Morgan Stanley Downgrades Both Stocks — Check Target Price, Potential Upside - NDTV Profit</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>La Opala RG Limited Releases Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+          <t>'Consensus buy' PFC, 'no sell' REC get downgraded; Check rationale and new targets - CNBC TV18</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>La Opala RG sets Aug 20 record date for ₹5 dividend - scanx.trade</t>
+          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:27:52 IST</t>
+          <t>2026-08-21 09:00:58 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3244,61 +3236,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TAKE.NS</t>
+          <t>BAJAJCON.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TAKE Limited</t>
+          <t>Bajaj Consumer Care Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>23.3700008392334</v>
+        <v>501</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>23.3700008392334</v>
+        <v>502</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>21.75</v>
+        <v>485</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>21.84000015258789</v>
+        <v>486.9500122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.88999938964844</v>
+        <v>500.7000122070312</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21.84000015258789</v>
+        <v>486.9500122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>611881</v>
+        <v>387003</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.59</v>
+        <v>-2.75</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>GTA 6 leaks cause minor Take-Two stock jump; fo... - Pluang</t>
+          <t>Optimistic Investors Push Bajaj Consumer Care Limited (NSE:BAJAJCON) Shares Up 26% But Growth Is Lacking - simplywall.st</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Take-Two Interactive stock steadies as GTA VI launch and fresh guidance shape 2026 outlook - Ad-hoc-news.de</t>
+          <t>Bajaj Consumer Care Limited (NSE:BAJAJCON) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹696 - simplywall.st</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Wall Street analysts just called this healthcare stock a buy — here’s our take - CNBC</t>
+          <t>BAJAJCON Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Take-Two director Michael Sheresky sells $31,116 in shares By Investing.com - Investing.com India</t>
+          <t>Bajaj Consumer Care Limited (NSE:BAJAJCON) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹696 - simplywall.st</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>LLY Stock: Where Compounding Could Take The Price - Trefis</t>
+          <t>Bajaj Consumer Care (BAJAJCON.NS): Stock Hovers Near Key Levels Amid Thin Trading - BPI Bull Correction - Vinanet</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KRONOX.NS</t>
+          <t>VIRAT.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Limited</t>
+          <t>Virat Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>155.0099945068359</v>
+        <v>335</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>186.1900024414062</v>
+        <v>401.7000122070312</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>155.0099945068359</v>
+        <v>330</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>186.1900024414062</v>
+        <v>401.7000122070312</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>155.1600036621094</v>
+        <v>334.75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>186.1900024414062</v>
+        <v>401.7000122070312</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5889347</v>
+        <v>51714</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Vadodara-based Kronox Lab Sciences to change hands 2 yrs after listing - BusinessLine</t>
+          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+          <t>Virat Industries seeks 70.28% stake in Brahm Lifestyle for ₹95 crore - scanx.trade</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+          <t>Gayan Senanayake: Sri Lankan superfan who shares a special bond with Virat and Rohit - Revsportz</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences promoters sell 64.26% stake to Indo Borax - scanx.trade</t>
+          <t>"He Is Like My Brother": PV Sindhu Shares How Virat Kohli Motivated Her During Tough Phase - Sportscape Magazine</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,60 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SOLARA.NS</t>
+          <t>QUADFUTURE.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Limited</t>
+          <t>Quadrant Future Tek Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>551.9500122070312</v>
+        <v>340</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>654.4000244140625</v>
+        <v>405.3500061035156</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>551.9500122070312</v>
+        <v>339</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>640</v>
+        <v>405.3500061035156</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>550.0499877929688</v>
+        <v>337.7999877929688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>640</v>
+        <v>405.3500061035156</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>6915687</v>
+        <v>7457265</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>16.35</v>
+        <v>20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+          <t>Quadrant Future Tek Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>SOLARA ACTIVE P Consolidated June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Solara Active Pharma Sciences revises CIO Ajit Manocha’s joining date - scanx.trade</t>
-        </is>
-      </c>
+          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +683,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KWIL.NS</t>
+          <t>MPDL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (India) Limited</t>
+          <t>MPDL Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>38</v>
+        <v>39.9900016784668</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>44.29999923706055</v>
+        <v>41.18000030517578</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>37.75</v>
+        <v>39.20000076293945</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>43.47000122070312</v>
+        <v>41.18000030517578</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>37.70999908447266</v>
+        <v>34.31999969482422</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43.47000122070312</v>
+        <v>41.18000030517578</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>101299688</v>
+        <v>14902</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>15.27</v>
+        <v>19.99</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (KWIL) Consolidates Near Support as Price Action Remains Range-Bound - Technical Analysis Picks - Vinanet</t>
+          <t>Oriental Rail Infrastructure Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
+          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
+          <t>Oriental Rail Infrastructure Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
+          <t>MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +752,60 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX.NS</t>
+          <t>KJMCFIN.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals Limited</t>
+          <t>KJMC Financial Services Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>439</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>509.8999938964844</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>431</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>498.1499938964844</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>433.8500061035156</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>498.1499938964844</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>6099644</v>
+        <v>3747</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14.82</v>
+        <v>19.99</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals Limited Shareholders Approve All Board Appointments Through Postal Ballot - scanx.trade</t>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX Q2 2026 Earnings: Revenue Surges 22.93% YoY, EPS Stands at ₹15.67 - High Growth Earnings - Vinanet</t>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
-        </is>
-      </c>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,56 +813,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>SUPTANERY.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited</t>
+          <t>Super Tannery Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.73999977111816</v>
+        <v>7.730000019073486</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>23.97999954223633</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20.59000015258789</v>
+        <v>7.309999942779541</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>23.32999992370605</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.3799991607666</v>
+        <v>7.309999942779541</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>23.32999992370605</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>256556792</v>
+        <v>2047504</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>14.47</v>
+        <v>19.97</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>SUPTANERY Share Price Today - Super Tannery Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>SUPTANERY Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Super Tannery Ltd. – NSE:SUPTANERY - TradingView</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SUPTANERY Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Super Tannery Ltd. Statistics – NSE:SUPTANERY - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,56 +882,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR.NS</t>
+          <t>NDL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Limited</t>
+          <t>Nandan Denim Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>303.0899963378906</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>344</v>
+        <v>2.710000038146973</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>301.8500061035156</v>
+        <v>2.25</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>336.2200012207031</v>
+        <v>2.710000038146973</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>300.989990234375</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>336.2200012207031</v>
+        <v>2.710000038146973</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2301215</v>
+        <v>5991494</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>11.7</v>
+        <v>19.91</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
+          <t>Next Digital probe halted - news.gov.hk</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -943,7 +939,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -951,68 +947,60 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR.NS</t>
+          <t>NKIND.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Limited</t>
+          <t>NK Industries Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32.09999847412109</v>
+        <v>60</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35.75</v>
+        <v>67.91999816894531</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30.95000076293945</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>34.81000137329102</v>
+        <v>67.62000274658203</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>56.59999847412109</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>34.81000137329102</v>
+        <v>67.62000274658203</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1740167</v>
+        <v>327876</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>11.32</v>
+        <v>19.47</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Textile to install 48MW battery storage amid 9MW solar expansion - Business Recorder</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
-        </is>
-      </c>
+          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - Vinanet</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1020,56 +1008,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RANASUG.NS</t>
+          <t>ALLCARGO.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Limited</t>
+          <t>Allcargo Logistics Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13.85999965667725</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>15.5</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13.85999965667725</v>
+        <v>10.47000026702881</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>15.21000003814697</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13.76000022888184</v>
+        <v>10.51000022888184</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>15.21000003814697</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3647306</v>
+        <v>110039625</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10.54</v>
+        <v>15.79</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+          <t>Allcargo Logistics shares up 20% in three sessions, could well have their best month on record - CNBC TV18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Allcargo Logistics shares up 20% in three sessions, could well have their best month on record - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics Share Price Update With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics shares rally 15% after Q1 profit jumps 258% YoY to Rs 31 crore - The Economic Times</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1077,68 +1077,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KAYA.NS</t>
+          <t>KRONOX.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kaya Limited</t>
+          <t>Kronox Lab Sciences Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>339.9500122070312</v>
+        <v>191</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>385</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>336.5499877929688</v>
+        <v>191</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>374.1000061035156</v>
+        <v>215.1799926757812</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>338.4500122070312</v>
+        <v>186.1900024414062</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>374.1000061035156</v>
+        <v>215.1799926757812</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>245362</v>
+        <v>24328538</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10.53</v>
+        <v>15.57</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Scholastic director Kaya Henderson sells $130,812 in stock - Investing.com</t>
+          <t>Indo Borax to acquire 64.26% stake in Kronox Lab Sciences in Rs 246-crore deal - Indian Chemical News</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+          <t>Why Did Kronox Lab Sciences Shares Surge by Up to 39% in Two Days? Here’s the Reason - Trade Brains</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+          <t>Kronox Lab Sciences shares rally 32% in 2 days as Indo Borax, Zenrock Chemicals eye stake acquisition - The Economic Times</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Kaya To Issue 1.82 Million Equity Shares At 274.10 Rupees Per Share For Aggregate Cash Consideration Of Approx 500 Million Rupees - TradingView</t>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Kaya Standalone June 2026 Net Sales at Rs 60.14 crore, up 13.91% Y-o-Y - Moneycontrol.com</t>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1146,68 +1146,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HUBTOWN.NS</t>
+          <t>BIRLAPREC.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Limited</t>
+          <t>Birla Precision Technologies Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>180.4499969482422</v>
+        <v>39.11999893188477</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>205.6999969482422</v>
+        <v>45.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>180.0099945068359</v>
+        <v>38.13000106811523</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>198.8099975585938</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>180.1199951171875</v>
+        <v>39.11000061035156</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>198.8099975585938</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4731451</v>
+        <v>986260</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10.38</v>
+        <v>13.53</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Ltd. Share Price Up 9.01%: Price, Valuation View - Univest</t>
+          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - Vinanet</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Ltd. Share Price Up 9.01%: Price, Valuation View - Univest</t>
+          <t>Birla Precision Technologies (BIRLAPREC.NS) Holds Support Near ₹36.1, Resistance at ₹39.9 in Focus - Gamma Flip Level - Vinanet</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Q1 PAT slides 69% YoY to Rs 25 crore - Business Standard</t>
+          <t>BIRLAPREC Share Price Today - Birla Precision Technologies Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Hubtown Consolidated June 2026 Net Sales at Rs 155.62 crore, down 16.96% Y-o-Y - Moneycontrol.com</t>
+          <t>Birla Precision Technologies (BIRLAPREC.NS) Holds Support Near ₹36.1, Resistance at ₹39.9 in Focus - Gamma Flip Level - Vinanet</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Hubtown makes Q1 FY27 earnings call audio available online - scanx.trade</t>
+          <t>BIRLAPREC.NS Mar 2026 Earnings: Marginal EPS of ₹0.39 on Modest Revenue of ₹63.91 crore; Stock Slides 0.71% - ROA Comparison - Vinanet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1215,51 +1215,51 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CORDELIA.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Waterways Leisure Tourism Limited</t>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>820.5499877929688</v>
+        <v>252.5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>907.75</v>
+        <v>291</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>820.5499877929688</v>
+        <v>250.1999969482422</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>907.75</v>
+        <v>279.5</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>825.25</v>
+        <v>248.8500061035156</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>907.75</v>
+        <v>279.5</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>700284</v>
+        <v>7128163</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10</v>
+        <v>12.32</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Cordelia Cruises Share Price Falls 7.71% to Rs 842.25 After Q1 Results - Univest</t>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
+          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1276,68 +1276,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VERANDA.NS</t>
+          <t>MODIRUBBER.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions Limited</t>
+          <t>Modi Rubber Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>236.8999938964844</v>
+        <v>119</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>265.8500061035156</v>
+        <v>144</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>236</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>255.8999938964844</v>
+        <v>134.2400054931641</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>233.6999969482422</v>
+        <v>120.0699996948242</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>255.8999938964844</v>
+        <v>134.2400054931641</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>9972226</v>
+        <v>40792</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>9.5</v>
+        <v>11.8</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions shareholders approve CMD reappointment - scanx.trade</t>
+          <t>Modi Rubber Ltd. Share Price Today Up 20%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Why are Crizac, Jaro, Veranda Learning and other e-learning stocks down today? Explained - Zee Business</t>
+          <t>SBEV Q2 2025 Earnings: Wider-than-Expected Loss Sends Shares Down 14.63% - High Growth Earnings - Vinanet</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+          <t>Modi Rubber seeks shareholder approval to appoint Ajay Kumar Jain as Independent Director - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Veranda Learning Solutions discloses JSCEL scheme compliance updates - scanx.trade</t>
+          <t>Modi Rubber approves comfort letter for Gujarat Guardian expansion project - scanx.trade</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>NCLT approves Veranda Learning Solutions subsidiary amalgamation - scanx.trade</t>
+          <t>Modi Rubber Ltd. (MODIRUBBER) Share Price Rises 11.8% Today - Univest</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1345,68 +1345,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCER.NS</t>
+          <t>THOMASCOOK.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ORIENT CERATECH LIMITED</t>
+          <t>Thomas Cook  (India)  Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>43</v>
+        <v>101.9899978637695</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>47.22999954223633</v>
+        <v>115.6999969482422</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>42.52000045776367</v>
+        <v>101.9899978637695</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46.72999954223633</v>
+        <v>113.1699981689453</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>43.11999893188477</v>
+        <v>101.5800018310547</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46.72999954223633</v>
+        <v>113.1699981689453</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>353057</v>
+        <v>25566022</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>11.41</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Do Its Financials Have Any Role To Play In Driving Orient Ceratech Limited's (NSE:ORIENTCER) Stock Up Recently? - simplywall.st</t>
+          <t>Thomas Cook Q1 Results: Earnings call recording now available for investors - scanx.trade</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCER.NS Mar 2026 Earnings: EPS of ₹0.43 on Revenue of ₹95.24 Crore; Stock Gains 2.37% - Post-Earnings Reaction - Vinanet</t>
+          <t>Thomas Cook India Sets Virtual AGM to Approve Dividend, Financials and Board Changes - TipRanks</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCER.NS Mar 2026 Earnings: EPS of ₹0.43 on Revenue of ₹95.24 Crore; Stock Gains 2.37% - Post-Earnings Reaction - Vinanet</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Ashapura International Limited Increases Shareholding in Orient Ceratech Limited to 8.35% - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>ORIENT CERATECH Limited (ORIENTCER.NS): Modest Uptick Amid Range-Bound Trading - OBV Trend Line - Vinanet</t>
-        </is>
-      </c>
+          <t>Thomas Cook India Sets Virtual AGM to Approve Dividend, Financials and Board Changes - TipRanks</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1414,68 +1406,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>KRYSTAL.NS</t>
+          <t>ORIRAIL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Krystal Integrated Services Limited</t>
+          <t>Oriental Rail Infrastructure Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>635</v>
+        <v>106.8899993896484</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>689</v>
+        <v>124.3499984741211</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>620.7000122070312</v>
+        <v>104.25</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>681.3499755859375</v>
+        <v>114.7799987792969</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>629.4500122070312</v>
+        <v>103.629997253418</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>681.3499755859375</v>
+        <v>114.7799987792969</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>688365</v>
+        <v>1142107</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>8.25</v>
+        <v>10.76</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Krystal Integrated Services Shares Gain 4% on Rs 134 Crore Order - Equitypandit</t>
+          <t>Oriental Rail uploads Q1FY27 earnings call audio recording - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Krystal Integrated Services Ltd (KRYSTAL) Share Price Rises 8.53% Today - Univest</t>
+          <t>Oriental Rail uploads Q1FY27 earnings call audio recording - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Krystal Integrated Services Ltd (KRYSTAL) Share Price Rises 8.53% Today - Univest</t>
+          <t>Oriental Rail Infrastructure shares permitted to trade on NSE - scanx.trade</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock jumps after receipt of ₹134 crore order from Maharashtra Road Transport - livemint.com</t>
+          <t>Free float of Oriental Rail Infrastructure Ltd. – NSE:ORIRAIL - TradingView</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Krystal Integrated Services makes decent debut, lists at 9.7% premium on NSE - Upstox</t>
+          <t>Oriental Rail Infrastructure seeks ratification for ₹42.04 crore fund variation - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1483,68 +1475,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GENUSPOWER.NS</t>
+          <t>QUINT.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Genus Power Infrastructures Limited</t>
+          <t>Quint Digital Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>310.8999938964844</v>
+        <v>38</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>340.8999938964844</v>
+        <v>41.79999923706055</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>310.8999938964844</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>334.25</v>
+        <v>40.34000015258789</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>309.2999877929688</v>
+        <v>36.5099983215332</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>334.25</v>
+        <v>40.34000015258789</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>16393463</v>
+        <v>65255</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8.07</v>
+        <v>10.49</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>GENUSPOWER Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Genus Power Q2 2026 Earnings: Revenue Surges 94.55% YoY, EPS at ₹21.29 - Revenue Warning Signal - Vinanet</t>
+          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Genus Power Infrastructures (NSE:GENUSPOWER) Strong Profits May Be Masking Some Underlying Issues - simplywall.st</t>
+          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Genus Power Infrastructures Limited (GENUSPOWER.NS) – Moderate Decline on Profit Booking Amid Sector Headwinds - Symmetrical Triangle - Vinanet</t>
+          <t>Quint Digital Consolidated June 2026 Net Sales at Rs 34.80 crore, up 335.77% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Genus Power Infrastructures Limited's (NSE:GENUSPOWER) Stock Has Been Sliding But Fundamentals Look Strong: Is The Market Wrong? - simplywall.st</t>
+          <t>BJP Shares Video From Bihar as One of Police Action on Jharkhand Protester - The Quint</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1552,68 +1544,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>JNPR.NS</t>
+          <t>RHETAN.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Juniper Green Energy Limited</t>
+          <t>Rhetan TMT Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>252.8099975585938</v>
+        <v>21.75</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>275.5199890136719</v>
+        <v>24.22999954223633</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>251.7299957275391</v>
+        <v>20.61000061035156</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>273.760009765625</v>
+        <v>24.21999931335449</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>253.7100067138672</v>
+        <v>22.03000068664551</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>273.760009765625</v>
+        <v>24.21999931335449</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>7029425</v>
+        <v>38609598</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7.9</v>
+        <v>9.94</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>JNPR Share Price Today - Juniper Green Energy Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>Iron, steel stock Rhetan TMT retraces after inching close to 52-week high. Do you own? - livemint.com</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+          <t>Rhetan TMT Ltd Surges 9.75% to Day's High of Rs 24.2 — Outperforms Sector by 8.98 Percentage Points - MarketsMojo</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>JNPR Share Price Today - Juniper Green Energy Stock Analysis - Equitypandit</t>
+          <t>Rhetan TMT Ltd. Share Price Jumps to Fresh One-Year High - Univest</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Juniper Green Energy Ltd Share Price Today,, JNPR Share Price NSE, BSE - Business Today</t>
+          <t>Rhetan TMT Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+          <t>Momentum Stocks: HLE Glascoat, Rhetan TMT, Identical Brain under pressure; stocks trade below key moving... - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1621,68 +1613,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RENUKA.NS</t>
+          <t>CRSL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Shree Renuka Sugars Limited</t>
+          <t>Cressanda Railway Solutions Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>24.70000076293945</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>26.43000030517578</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24.5</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>26.1299991607666</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.23999977111816</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>26.1299991607666</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>95136169</v>
+        <v>4264848</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.8</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Shree Renuka Sugars Ltd. Share Price: 8.7% Gain Analysis - Univest</t>
+          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Shree Renuka Sugars Ltd. Share Price: 8.7% Gain Analysis - Univest</t>
+          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini, Bajaj Hind, Shree Renuka shares rise up to 13%; here's why - Business Today</t>
+          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hind, Dwarikesh, Renuka rally up to 14%; what's driving sugar stocks? - Business Standard</t>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Sweet Gains Continue: Shree Renuka, Dalmia Bharat Rally Up To 7% Despite Govt's Inventory Clampdown - NDTV Profit</t>
+          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1690,68 +1682,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DHAMPURSUG.NS</t>
+          <t>LAMBODHARA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Limited</t>
+          <t>Lambodhara Textiles Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>179.6999969482422</v>
+        <v>107.629997253418</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>192.8899993896484</v>
+        <v>124</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>178.9700012207031</v>
+        <v>105.5</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>189.7599945068359</v>
+        <v>118.0800018310547</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>176.1799926757812</v>
+        <v>107.629997253418</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>189.7599945068359</v>
+        <v>118.0800018310547</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>6615935</v>
+        <v>83132</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+          <t>MDS &amp; Associates LLP resigns as Lambodhara Textiles secretarial auditor - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
+          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
+          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills sets book closure dates for 91st AGM - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Dhampur Sugar Mills settles ₹100 crore commercial paper - scanx.trade</t>
-        </is>
-      </c>
+          <t>Lambodhara Textiles net profit rises 66% in Q1FY26 on lower finance costs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1759,68 +1747,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EPL.NS</t>
+          <t>ATLANTAELE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>EPL Limited</t>
+          <t>Atlanta Electricals Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>252</v>
+        <v>1712.900024414062</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>273</v>
+        <v>1857.400024414062</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>251</v>
+        <v>1700</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>270.1000061035156</v>
+        <v>1846.900024414062</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>250.8000030517578</v>
+        <v>1688.599975585938</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>270.1000061035156</v>
+        <v>1846.900024414062</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>6480002</v>
+        <v>402648</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.7</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>EPL Ltd. Share Price Reaches One-Year High: Stock Analysis - Univest</t>
+          <t>Atlanta Electricals Schedules Investor and Analyst Meetings in Mumbai - TipRanks</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>EPL Ltd. Share Price Reaches One-Year High: Stock Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>EPL Standalone June 2026 Net Sales at Rs 400.30 crore, up 19.85% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>EPL Limited Q1FY27 results: Consolidated revenue up 25% to ₹13,879mn - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Old Namibia uranium data guides Skeleton Coast's planned fieldwork - Stock Titan</t>
-        </is>
-      </c>
+          <t>Atlanta Electricals Schedules Investor and Analyst Meetings in Mumbai - TipRanks</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1828,61 +1804,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER.NS</t>
+          <t>BLUSPRING.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Limited</t>
+          <t>Bluspring Enterprises Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>253.2299957275391</v>
+        <v>118</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>270.5</v>
+        <v>129.75</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>252</v>
+        <v>117.7200012207031</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>269.239990234375</v>
+        <v>128.9799957275391</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>250.3999938964844</v>
+        <v>117.9599990844727</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>269.239990234375</v>
+        <v>128.9799957275391</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>11344542</v>
+        <v>2549295</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7.52</v>
+        <v>9.34</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
+          <t>BLUSPRING Share Price Rise: Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering appoints Seema Sanghavi as WTD - scanx.trade</t>
+          <t>BLUSPRING Share Price Rise: Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision approves rights issue of 1.25 crore shares at ₹264 each - scanx.trade</t>
+          <t>BLUSPRING ENTERPRISES LTD Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Press Release Distribution India - Business Wire India</t>
+          <t>Bluspring revenue rises 20% to ₹930 crore in Q1 FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Standalone June 2026 Net Sales at Rs 314.64 crore, up 18.9% Y-o-Y - Moneycontrol.com</t>
+          <t>Bluspring subsidiary secures ₹125 Cr term loan for LSG acquisition - scanx.trade</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1879,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2009,7 +1985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2017,68 +1993,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GCSL.NS</t>
+          <t>SHAH.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Limited</t>
+          <t>Shah Metacorp Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>526.2999877929688</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>540.9500122070312</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>470</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>482.0499877929688</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>521.7000122070312</v>
+        <v>3.950000047683716</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>482.0499877929688</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>615899</v>
+        <v>4422848</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-7.6</v>
+        <v>-15.7</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
+          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
+          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
+          <t>New-age stocks, IPOs and valuations: Envision's Nilesh Shah shares his investment playbook - CNBC TV18</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
+          <t>'Does True Love Exist?' Kashmera Shah Shares Cryptic Post Amid Govinda-Sunita Ahuja Spat - NDTV</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
+          <t>Sunshine Pictures IPO day 2 LIVE: GMP, subscription status to review. Should you apply for Vipul Shah's company shares? - TradingView</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2086,60 +2062,64 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HSCL.NS</t>
+          <t>AVROIND.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Limited</t>
+          <t>AVRO INDIA LIMITED</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>755</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>767.5999755859375</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>695.5</v>
+        <v>8.409999847412109</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>704.2000122070312</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>750.25</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>704.2000122070312</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>12482496</v>
+        <v>1274488</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-6.14</v>
+        <v>-8.42</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox</t>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
+          <t>Avro India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Protalix BioTherapeutics (PLX) Edges Higher Amid Consolidation Near Support - Retail Driven Moves - Vinanet</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2147,56 +2127,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DREDGECORP.NS</t>
+          <t>UMESLTD.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation of India Limited</t>
+          <t>Usha Martin Education &amp; Solutions Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1199</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1204</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1111.5</v>
+        <v>5.369999885559082</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1118.300048828125</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1189.199951171875</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1118.300048828125</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>253900</v>
+        <v>111981</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-5.96</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+          <t>Do Usha Martin Education &amp; Solutions' (NSE:UMESLTD) Earnings Warrant Your Attention? - simplywall.st</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: Modest profit amid low revenue base - Earnings Per Share - Vinanet</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Declines 3.66%: Testing Support at ₹5.24 - Retail Driven Moves - Vinanet</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions (UMESLTD.NS) Inches Lower Amidst Range-Bound Trading on the NSE - Insider Selling Alerts - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions (UMESLTD.NS): Stock Slips 1.03% as Support Levels Come Into Focus - Wave Extension - Vinanet</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2204,60 +2196,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SHREEJISPG.NS</t>
+          <t>SHERVANI.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Limited</t>
+          <t>Shervani Industrial Syndicate Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>657</v>
+        <v>340</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>661.9500122070312</v>
+        <v>340</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>609.8499755859375</v>
+        <v>319.5499877929688</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>613.3499755859375</v>
+        <v>321.1499938964844</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>649.4500122070312</v>
+        <v>349.9500122070312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>613.3499755859375</v>
+        <v>321.1499938964844</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1441163</v>
+        <v>421</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-5.56</v>
+        <v>-8.23</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Ltd. (SHREEJISPG) Share Price Hits 52-Week High - Univest</t>
+          <t>SHERVANI Share Price Today - Shervani Industrial Syndicate Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
+          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2265,68 +2265,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>UEL.NS</t>
+          <t>KPL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Limited</t>
+          <t>Kwality Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>190.7599945068359</v>
+        <v>3604.10009765625</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>190.7599945068359</v>
+        <v>3634.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>190.7599945068359</v>
+        <v>3327</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>190.7599945068359</v>
+        <v>3361.10009765625</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>200.8000030517578</v>
+        <v>3630.300048828125</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>190.7599945068359</v>
+        <v>3361.10009765625</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6358</v>
+        <v>113689</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-5</v>
+        <v>-7.42</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Ltd. Share Price Shows Strong Price Action - Univest</t>
+          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+          <t>KPL Share Price | Kwality Pharmaceuticals Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+          <t>Kino Polska TV S.A. Revenue Breakdown – GPW:KPL - TradingView</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Ltd. Share Price Jumps to New 52-Week Peak - Univest</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
-        </is>
-      </c>
+          <t>KPL Share Price | Kwality Pharmaceuticals Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2334,68 +2330,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>SIYSIL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>Siyaram Silk Mills Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>635</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>645.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>599.9500122070312</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>606.3499755859375</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>66.09999847412109</v>
+        <v>647.5499877929688</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>606.3499755859375</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>45140</v>
+        <v>198647</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-4.99</v>
+        <v>-6.36</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
+          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
+          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+          <t>Siyaram Silk Mills Limited Reports Q1 FY27 Results: Total Income Rises 16.4% YoY to ₹466 Crore; PAT Surges to ₹11 Crore - EquityBulls</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities unsecured creditors approve broking demerger - scanx.trade</t>
+          <t>Siyaram Silk Mills Expands Authorised Share Capital After Scheme Approval - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2403,68 +2399,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KSR.NS</t>
+          <t>BANARISUG.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Limited</t>
+          <t>Bannari Amman Sugars Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>28.51000022888184</v>
+        <v>4114.89990234375</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>30</v>
+        <v>4199</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>27</v>
+        <v>3950</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>27.42000007629395</v>
+        <v>4019.699951171875</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>28.84000015258789</v>
+        <v>4240.7001953125</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>27.42000007629395</v>
+        <v>4019.699951171875</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>77843</v>
+        <v>22810</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.92</v>
+        <v>-5.21</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Standalone June 2026 Net Sales at Rs 52.25 crore, up 0.36% Y-o-Y - Moneycontrol.com</t>
+          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Q1 Results: Net profit turns positive at ₹3.17 million - scanx.trade</t>
+          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear dispatches FY26 annual report, sets August 24 AGM date - scanx.trade</t>
+          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2472,56 +2468,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE.NS</t>
+          <t>UEL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging Limited</t>
+          <t>Ujaas Energy Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>181.2299957275391</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>181.2299957275391</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>181.2299957275391</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>181.2299957275391</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2.259999990463257</v>
+        <v>190.7599945068359</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>181.2299957275391</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>968342</v>
+        <v>8804</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.87</v>
+        <v>-5</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Q1 Standalone Net Profit Rises to 33M Rupees on Revenue of 30M Rupees - Sahi</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Ltd. Share Price Shows Strong Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Ltd. Share Price Jumps to New 52-Week Peak - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2529,60 +2537,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ASTERDM.NS</t>
+          <t>INDOTHAI.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Quality Care Limited</t>
+          <t>Indo Thai Securities Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>798.3499755859375</v>
+        <v>59.65999984741211</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>798.3499755859375</v>
+        <v>59.65999984741211</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>756.0499877929688</v>
+        <v>59.65999984741211</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>765.6500244140625</v>
+        <v>59.65999984741211</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>800.2000122070312</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>765.6500244140625</v>
+        <v>59.65999984741211</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>9884475</v>
+        <v>84649</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4.32</v>
+        <v>-5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Healthcare to rename as Aster DM Quality Care Limited - scanx.trade</t>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
+          <t>how InvestingPro’s fair value predicted 56% drop in Indo Thai Securities By Investing.com - Investing.com India</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>how InvestingPro’s fair value predicted 56% drop in Indo Thai Securities By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2590,60 +2606,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>KPEL.NS</t>
+          <t>NATIONSTD.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>K.P. Energy Limited</t>
+          <t>National Standard (India) Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>268.2000122070312</v>
+        <v>128</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>271</v>
+        <v>140.3399963378906</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>255.1499938964844</v>
+        <v>126.9800033569336</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>256.6499938964844</v>
+        <v>126.9800033569336</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>268.2000122070312</v>
+        <v>133.6600036621094</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>256.6499938964844</v>
+        <v>126.9800033569336</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>442666</v>
+        <v>464929</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.31</v>
+        <v>-5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>K.P. Energy Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>K.P. Energy Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>K.P. Energy Q1FY27 revenue surges 137% to ₹519.46 crore - scanx.trade</t>
-        </is>
-      </c>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2651,68 +2663,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>YASHO.NS</t>
+          <t>SIEL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Limited</t>
+          <t>Superior Industrial Enterprises Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4500</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>4500</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4230</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>4284.2001953125</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4470.7998046875</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4284.2001953125</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>123163</v>
+        <v>7981</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.17</v>
+        <v>-4.99</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Share Price Today, Yasho Industries Stock Price Live NSE/BSE Updates - The Economic Times</t>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Ind. Standalone June 2026 Net Sales at Rs 314.09 crore, up 58.73% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Yasho Industries Q1 FY27 Results: PAT Rs 36 Cr, Revenue Rs 307 Cr - Univest</t>
-        </is>
-      </c>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2720,56 +2728,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>KRISHNADEF.NS</t>
+          <t>STYLEBAAZA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Krishna Defence And Allied Industries Limited</t>
+          <t>Baazar Style Retail Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1083.900024414062</v>
+        <v>437.8500061035156</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1094.900024414062</v>
+        <v>447.1000061035156</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1026</v>
+        <v>417.6499938964844</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1037.900024414062</v>
+        <v>417.6499938964844</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1077.800048828125</v>
+        <v>439.6000061035156</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1037.900024414062</v>
+        <v>417.6499938964844</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>152475</v>
+        <v>2692008</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-3.7</v>
+        <v>-4.99</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Krishna Defence and Allied Industries Ltd. (KRISHNADEF) Share Price Falls 8.3% Today - Univest</t>
+          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Krishna Defence and Allied Industries Ltd. (KRISHNADEF) Share Price Falls 8.3% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Baazar Style Retail Independent Directors Step Down, Triggering Board Reshuffle - TipRanks</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Limited Announces Redesignation of Siddhant Khemani from Chief Marketing Officer to Head E-Commerce, Effective August 13, 2026 - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2777,68 +2797,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CHENNPETRO.NS</t>
+          <t>KMSUGAR.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Limited</t>
+          <t>K.M.Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1457</v>
+        <v>35.0099983215332</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1466</v>
+        <v>35.29999923706055</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1379.599975585938</v>
+        <v>32.84999847412109</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1390.5</v>
+        <v>33.54999923706055</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1440.300048828125</v>
+        <v>35.29999923706055</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1390.5</v>
+        <v>33.54999923706055</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2227820</v>
+        <v>1436244</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-3.46</v>
+        <v>-4.96</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Limited (NSE:CHENNPETRO) Looks Interesting, And It's About To Pay A Dividend - simplywall.st</t>
+          <t>K.M. Sugar Mills Ltd. Share Price Rise With Valuation View - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+          <t>NCLT Allahabad sanctions KM Sugar Mills distillery demerger scheme - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Rises 5.01% Today - Univest</t>
+          <t>K.M. Sugar Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+          <t>K.M. Sugar Mills Ltd. Share Price Today With Fundamentals - Univest</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. Stock News: Price Up 5.8% - Univest</t>
+          <t>NCLT Allahabad sanctions KM Sugar Mills distillery demerger scheme - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2846,68 +2866,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Limited</t>
+          <t>Balrampur Chini Mills Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1504.800048828125</v>
+        <v>747.3499755859375</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1525.800048828125</v>
+        <v>765</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1415.699951171875</v>
+        <v>714</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1443.699951171875</v>
+        <v>729.3499755859375</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1494.800048828125</v>
+        <v>767.0999755859375</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1443.699951171875</v>
+        <v>729.3499755859375</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1342162</v>
+        <v>19992314</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-3.42</v>
+        <v>-4.92</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Ltd. Share Price Today After 3.43% Fall - Univest</t>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Ltd. Share Price Today After 3.43% Fall - Univest</t>
+          <t>Balrampur Chini Mills Stock Update: Shares Slip on Duty-Free Sugar Imports - LatestLY</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS, Dixon, other EMS companies' shares rise as govt clears 31 electronics component projects worth... - Moneycontrol.com</t>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Stock Surges Over 3% After ECMS Application Gets Approved By Govt - NDTV Profit</t>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Govt clears ₹7,877 crore ECMS investments; Wipro, PCBL Chemical, Syrma SGS shares in focus - CNBC TV18</t>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2915,56 +2935,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AIIL.NS</t>
+          <t>MODIS.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Authum Investment &amp; Infrastructure Limited</t>
+          <t>Modis Navnirman Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>551</v>
+        <v>400</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>553.75</v>
+        <v>404.4500122070312</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>527.25</v>
+        <v>377.5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>532.2999877929688</v>
+        <v>383.1499938964844</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>550.5</v>
+        <v>402.7000122070312</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>532.2999877929688</v>
+        <v>383.1499938964844</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>966550</v>
+        <v>142116</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-3.31</v>
+        <v>-4.85</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>AIIL Share Price | Authum Investment &amp; Infrastructure Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>AIIL Share Price | Authum Investment &amp; Infrastructure Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Modis Navnirman reappoints Dinesh Modi at AGM; reports record FY26 growth - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Standalone June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2972,46 +3004,46 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>NOVARTIND.NS</t>
+          <t>GANGAFORGE.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Limited</t>
+          <t>Ganga Forging Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1540</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1574.900024414062</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1476</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1482.199951171875</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1531.699951171875</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1482.199951171875</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>16240</v>
+        <v>846238</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-3.23</v>
+        <v>-4.65</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Ltd. Share Price News: New 52-Week Trough - Univest</t>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Ltd. Share Price News: New 52-Week Trough - Univest</t>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
@@ -3021,7 +3053,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3029,68 +3061,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN.NS</t>
+          <t>PRAJIND.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Neogen Chemicals Limited</t>
+          <t>Praj Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2358.89990234375</v>
+        <v>358</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2368.699951171875</v>
+        <v>358</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2250</v>
+        <v>341.1499938964844</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2259.10009765625</v>
+        <v>344.3500061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2328.800048828125</v>
+        <v>358.4500122070312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2259.10009765625</v>
+        <v>344.3500061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>137421</v>
+        <v>1661248</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-2.99</v>
+        <v>-3.93</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SBI Mutual Fund reduces Neogen Chemicals stake to 6.03% under SAST Reg 29 - scanx.trade</t>
+          <t>Praj Industries Stock And Two India Energy Names Tied To Higher Oil Prices - simplywall.st</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Neogen Corp CEO Mikheal Nassif Executes RSU Tax Withholding on August 19, 2026 - Kalkine Media</t>
+          <t>Praj Industries Ltd. Share Price Up 5.18%: Price Analysis - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Neogen (NEOG) CEO uses 20K shares to cover RSU taxes - Stock Titan</t>
+          <t>Praj Industries Limited Beat Analyst Estimates: See What The Consensus Is Forecasting For This Year - simplywall.st</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Neogen Chemicals Limited (NEOGEN.BO) stock price, news, quote and history - Yahoo Finance UK</t>
+          <t>Praj Industries Ltd. (PRAJIND) Share Price Rises 6.1% Today - Univest</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Neogen Corporation (NASDAQ:NEOG) Given Average Rating of "Hold" by Brokerages - MarketBeat</t>
+          <t>Praj Industries Ltd. Share Price Up 5.18%: Price Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3098,68 +3130,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>MMFL.NS</t>
+          <t>JAIBALAJI.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MM Forgings Limited</t>
+          <t>Jai Balaji Industries Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>660.0999755859375</v>
+        <v>65.5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>669.4500122070312</v>
+        <v>65.95999908447266</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>635</v>
+        <v>63.11000061035156</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>638.9500122070312</v>
+        <v>63.56999969482422</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>657.7999877929688</v>
+        <v>66.08000183105469</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>638.9500122070312</v>
+        <v>63.56999969482422</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>176799</v>
+        <v>611558</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-2.87</v>
+        <v>-3.8</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
+          <t>Jai Balaji Industries Limited Announces Cessation of Bimal Kumar Choudhary as Whole-Time Director, Effective September 14, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
+          <t>Jai Balaji Industries Limited Announces Cessation of Bimal Kumar Choudhary as Whole-Time Director, Effective September 14, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>M M Forgings Limited Announces Resignation of Chandrasekar S from Company Secretary and Compliance Officer, Effective August 14, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>M M Forgings postpones Q1FY26 board meeting to Aug 14 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Jai Balaji Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3167,68 +3191,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>PFC.NS</t>
+          <t>MATRIMONY.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Limited</t>
+          <t>Matrimony.Com Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>374.4500122070312</v>
+        <v>551.7999877929688</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>375.1000061035156</v>
+        <v>560.8499755859375</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>363.2000122070312</v>
+        <v>532</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>363.7999877929688</v>
+        <v>537.0499877929688</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>374.4500122070312</v>
+        <v>558.2000122070312</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>363.7999877929688</v>
+        <v>537.0499877929688</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>13375984</v>
+        <v>26974</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-2.84</v>
+        <v>-3.79</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>PFC, REC shares decline up to 3% after Morgan Stanley cuts growth estimates - Moneycontrol.com</t>
+          <t>Matrimony.com relieves CFO Harigovind Krishnasamy effective Aug 17 - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>PFC, REC Shares Fall Up To 3% As Morgan Stanley Cuts Growth Estimates - outlookbusiness.com</t>
+          <t>Matrimony.com relieves CFO Harigovind Krishnasamy effective Aug 17 - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>PFC, REC Shares Fall As Morgan Stanley Downgrades Both Stocks — Check Target Price, Potential Upside - NDTV Profit</t>
+          <t>Income Investors Should Know That Matrimony.com Limited (NSE:MATRIMONY) Goes Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>'Consensus buy' PFC, 'no sell' REC get downgraded; Check rationale and new targets - CNBC TV18</t>
+          <t>Matrimony.com soars after Q1 PAT spurts 127.5% YoY - Business Standard</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
+          <t>Matrimony.com Shares Rally 10% After Q1 Net Profit Jumps 127.5% Year-on-Year - Margin Expansion Trends - Vinanet</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:00:58 IST</t>
+          <t>2026-08-21 16:29:09 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3236,61 +3260,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BAJAJCON.NS</t>
+          <t>SALONA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Consumer Care Limited</t>
+          <t>Salona Cotspin Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>501</v>
+        <v>272.989990234375</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>502</v>
+        <v>273</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>485</v>
+        <v>260.0499877929688</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>486.9500122070312</v>
+        <v>263.2999877929688</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>500.7000122070312</v>
+        <v>273.5299987792969</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>486.9500122070312</v>
+        <v>263.2999877929688</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>387003</v>
+        <v>331</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-2.75</v>
+        <v>-3.74</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Optimistic Investors Push Bajaj Consumer Care Limited (NSE:BAJAJCON) Shares Up 26% But Growth Is Lacking - simplywall.st</t>
+          <t>Salona Cotspin Share Price Forecast to 2030 - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Consumer Care Limited (NSE:BAJAJCON) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹696 - simplywall.st</t>
+          <t>RRP Semiconductor reports standalone net loss of Rs 0.33 crore in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>BAJAJCON Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>Salona Cotspin standalone net profit rises 47.71% in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Consumer Care Limited (NSE:BAJAJCON) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹696 - simplywall.st</t>
+          <t>RRP Semiconductor reports standalone net loss of Rs 0.33 crore in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Consumer Care (BAJAJCON.NS): Stock Hovers Near Key Levels Amid Thin Trading - BPI Bull Correction - Vinanet</t>
+          <t>STL Global reports standalone net loss of Rs 1.25 crore in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -446,7 +446,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>VIRAT.NS</t>
+          <t>MINALIND.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Virat Industries Limited</t>
+          <t>Minal Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>335</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>401.7000122070312</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>330</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>401.7000122070312</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>334.75</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>401.7000122070312</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>51714</v>
+        <v>148926</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
+          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
+          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Virat Industries seeks 70.28% stake in Brahm Lifestyle for ₹95 crore - scanx.trade</t>
+          <t>Free float of Minal Industries Limited – NSE:MINALIND - TradingView</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Gayan Senanayake: Sri Lankan superfan who shares a special bond with Virat and Rohit - Revsportz</t>
+          <t>Minal Industries Limited Announces Appointment of Saket Rajendra Sugandh as Company Secretary and Compliance Officer, Effective August 5, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>"He Is Like My Brother": PV Sindhu Shares How Virat Kohli Motivated Her During Tough Phase - Sportscape Magazine</t>
+          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -649,19 +649,19 @@
         <v>405.3500061035156</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>7457265</v>
+        <v>7504777</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +683,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MPDL.NS</t>
+          <t>SHANTIGEAR.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MPDL Limited</t>
+          <t>Shanthi Gears Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39.9900016784668</v>
+        <v>395</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>41.18000030517578</v>
+        <v>464.25</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>39.20000076293945</v>
+        <v>395</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>41.18000030517578</v>
+        <v>464.25</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.31999969482422</v>
+        <v>386.8999938964844</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>41.18000030517578</v>
+        <v>464.25</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>14902</v>
+        <v>1972065</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>19.99</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+          <t>Shanthi Gears Ltd. (SHANTIGEAR) Share Price Hits Fresh 52-Week Low - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Shanthi Gears Share: பெற்றோர் கம்பெனி நம்பிக்கை! **18%** குதித்தது ஷேர் விலை! - Whalesbook</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
+          <t>Shanthi Gears Share Price at Fresh 52-Week Low - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Tube Investments of India acquires 2.69% stake in Shanthi Gears - scanx.trade</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade</t>
+          <t>Tube Investments of India Increases Stake in Shanthi Gears - InvestyWise</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,60 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KJMCFIN.NS</t>
+          <t>MPDL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited</t>
+          <t>MPDL Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>79.69999694824219</v>
+        <v>39.9900016784668</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>79.69999694824219</v>
+        <v>41.18000030517578</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>79.69999694824219</v>
+        <v>39.20000076293945</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>79.69999694824219</v>
+        <v>41.18000030517578</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>66.41999816894531</v>
+        <v>34.31999969482422</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>79.69999694824219</v>
+        <v>41.18000030517578</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3747</v>
+        <v>14902</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>19.99</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>MPDL reports consolidated net loss of Rs 4.20 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -813,68 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY.NS</t>
+          <t>NDL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Limited</t>
+          <t>Nandan Denim Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7.730000019073486</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8.770000457763672</v>
+        <v>2.710000038146973</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7.309999942779541</v>
+        <v>2.25</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8.770000457763672</v>
+        <v>2.710000038146973</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7.309999942779541</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8.770000457763672</v>
+        <v>2.710000038146973</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2047504</v>
+        <v>5991494</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>19.97</v>
+        <v>19.91</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Share Price Today - Super Tannery Stock Analysis - Equitypandit</t>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Historical Data - Equitypandit</t>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of Super Tannery Ltd. – NSE:SUPTANERY - TradingView</t>
+          <t>Next Digital probe halted - news.gov.hk</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Historical Data - Equitypandit</t>
+          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Ltd. Statistics – NSE:SUPTANERY - TradingView</t>
+          <t>NDL Ventures Q1 FY27 Results: Revenue, PAT &amp; Key Highlights - Univest</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -882,64 +890,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NDL.NS</t>
+          <t>NKIND.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Nandan Denim Limited</t>
+          <t>NK Industries Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.279999971389771</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2.710000038146973</v>
+        <v>67.91999816894531</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2.25</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2.710000038146973</v>
+        <v>67.62000274658203</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2.259999990463257</v>
+        <v>56.59999847412109</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.710000038146973</v>
+        <v>67.62000274658203</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5991494</v>
+        <v>327876</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>19.91</v>
+        <v>19.47</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+          <t>NK Industries Limited (NKIND.NS) Holds Near Support as Modest Uptick Stalls at Resistance - High Conviction Picks - vinanet.vn</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - vinanet.vn</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
+          <t>NK Industries (NKIND.NS) Hovers Near ₹59 Amid Narrow Range, Support at ₹56.16 in Focus - Monthly Profile - vinanet.vn</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Next Digital probe halted - news.gov.hk</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>NK Industries Limited Q2 2026 Earnings: Revenue Declines Sharply on Weak Operational Environment; EPS Turns Negative - Performance Review - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>NK Industries Limited (NKIND.NS): Marginal Gain Amid Consolidation Near Key Resistance - Dark Pool Prints - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -947,60 +959,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>NKIND.NS</t>
+          <t>BIRLAPREC.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited</t>
+          <t>Birla Precision Technologies Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60</v>
+        <v>39.11999893188477</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>67.91999816894531</v>
+        <v>45.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>58.09999847412109</v>
+        <v>38.13000106811523</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.62000274658203</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>56.59999847412109</v>
+        <v>39.11000061035156</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>67.62000274658203</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>327876</v>
+        <v>986460</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>19.47</v>
+        <v>13.53</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - vinanet.vn</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - Vinanet</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>BIRLAPREC Share Price Today - Birla Precision Technologies Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS Dec 2025 Earnings: Modest EPS of ₹0.19 on Stable Revenues - Segment Revenue Breakdown - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1008,68 +1028,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO.NS</t>
+          <t>MODIRUBBER.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Allcargo Logistics Limited</t>
+          <t>Modi Rubber Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10.55000019073486</v>
+        <v>119</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>144</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>10.47000026702881</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>12.17000007629395</v>
+        <v>134.2400054931641</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10.51000022888184</v>
+        <v>120.0699996948242</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12.17000007629395</v>
+        <v>134.2400054931641</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>110039625</v>
+        <v>40792</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>15.79</v>
+        <v>11.8</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Allcargo Logistics shares up 20% in three sessions, could well have their best month on record - CNBC TV18</t>
+          <t>Modi Rubber Ltd. Share Price Update: Fundamentals Check - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Allcargo Logistics shares up 20% in three sessions, could well have their best month on record - CNBC TV18</t>
+          <t>Modi Rubber Ltd. Share Price Update: Fundamentals Check - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Allcargo Logistics Share Price Update With Valuation View - Univest</t>
+          <t>Modi Rubber seeks shareholder approval to appoint Ajay Kumar Jain as Independent Director - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
+          <t>Modi Rubber Ltd. Share Price Today Up 20%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Allcargo Logistics shares rally 15% after Q1 profit jumps 258% YoY to Rs 31 crore - The Economic Times</t>
+          <t>Modi Rubber approves comfort letter for Gujarat Guardian expansion project - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1077,68 +1097,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KRONOX.NS</t>
+          <t>KLBRENG-B.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Limited</t>
+          <t>Kilburn Engineering Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>191</v>
+        <v>364</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>223.4199981689453</v>
+        <v>408.6000061035156</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>191</v>
+        <v>361.7000122070312</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>215.1799926757812</v>
+        <v>397.3999938964844</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>186.1900024414062</v>
+        <v>357.6499938964844</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>215.1799926757812</v>
+        <v>397.3999938964844</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>24328538</v>
+        <v>3833782</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>15.57</v>
+        <v>11.11</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax to acquire 64.26% stake in Kronox Lab Sciences in Rs 246-crore deal - Indian Chemical News</t>
+          <t>Kilburn Engineering Ltd. Share Price Rises 9.96% Today - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Why Did Kronox Lab Sciences Shares Surge by Up to 39% in Two Days? Here’s the Reason - Trade Brains</t>
+          <t>Kilburn Engineering (NSE:KLBRENG-B) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences shares rally 32% in 2 days as Indo Borax, Zenrock Chemicals eye stake acquisition - The Economic Times</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Kilburn Engineering (NSE:KLBRENG-B) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1146,68 +1158,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC.NS</t>
+          <t>ORIRAIL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Limited</t>
+          <t>Oriental Rail Infrastructure Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>39.11999893188477</v>
+        <v>106.8899993896484</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45.5</v>
+        <v>124.3499984741211</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>38.13000106811523</v>
+        <v>104.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>44.40000152587891</v>
+        <v>114.7799987792969</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>39.11000061035156</v>
+        <v>103.629997253418</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>44.40000152587891</v>
+        <v>114.7799987792969</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>986260</v>
+        <v>1142227</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>13.53</v>
+        <v>10.76</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - Vinanet</t>
+          <t>Average basic shares outstanding of Oriental Rail Infrastructure Ltd. – NSE:ORIRAIL - TradingView</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies (BIRLAPREC.NS) Holds Support Near ₹36.1, Resistance at ₹39.9 in Focus - Gamma Flip Level - Vinanet</t>
+          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC Share Price Today - Birla Precision Technologies Stock Analysis - Equitypandit</t>
+          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies (BIRLAPREC.NS) Holds Support Near ₹36.1, Resistance at ₹39.9 in Focus - Gamma Flip Level - Vinanet</t>
+          <t>Oriental Rail Infrastructure shares permitted to trade on NSE - scanx.trade</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC.NS Mar 2026 Earnings: Marginal EPS of ₹0.39 on Modest Revenue of ₹63.91 crore; Stock Slides 0.71% - ROA Comparison - Vinanet</t>
+          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Cyclically Adjus - GuruFocus</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1215,60 +1227,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>QUINT.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>Quint Digital Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>252.5</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>291</v>
+        <v>41.79999923706055</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>250.1999969482422</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>279.5</v>
+        <v>40.34000015258789</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>248.8500061035156</v>
+        <v>36.5099983215332</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>279.5</v>
+        <v>40.34000015258789</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>7128163</v>
+        <v>65255</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>12.32</v>
+        <v>10.49</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Quint Digital Ltd. Share Price Up 10.53%: Full Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1276,68 +1296,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MODIRUBBER.NS</t>
+          <t>S&amp;SPOWER.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber Limited</t>
+          <t>S&amp;S Power Switchgears Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>119</v>
+        <v>286</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>144</v>
+        <v>298.8500061035156</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>117.8000030517578</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>134.2400054931641</v>
+        <v>298.8500061035156</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>120.0699996948242</v>
+        <v>271.7000122070312</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>134.2400054931641</v>
+        <v>298.8500061035156</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>40792</v>
+        <v>12178</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>11.8</v>
+        <v>9.99</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber Ltd. Share Price Today Up 20%: Stock Analysis - Univest</t>
+          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>SBEV Q2 2025 Earnings: Wider-than-Expected Loss Sends Shares Down 14.63% - High Growth Earnings - Vinanet</t>
+          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber seeks shareholder approval to appoint Ajay Kumar Jain as Independent Director - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Modi Rubber approves comfort letter for Gujarat Guardian expansion project - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Modi Rubber Ltd. (MODIRUBBER) Share Price Rises 11.8% Today - Univest</t>
-        </is>
-      </c>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1345,60 +1357,56 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK.NS</t>
+          <t>LEENEE.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Thomas Cook  (India)  Limited</t>
+          <t>Lee &amp; Nee Softwares Exports Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>101.9899978637695</v>
+        <v>8.439999580383301</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>115.6999969482422</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>101.9899978637695</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>113.1699981689453</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>101.5800018310547</v>
+        <v>8.359999656677246</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>113.1699981689453</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>25566022</v>
+        <v>99370</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>11.41</v>
+        <v>9.93</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Thomas Cook Q1 Results: Earnings call recording now available for investors - scanx.trade</t>
+          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Thomas Cook India Sets Virtual AGM to Approve Dividend, Financials and Board Changes - TipRanks</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Cook India Sets Virtual AGM to Approve Dividend, Financials and Board Changes - TipRanks</t>
-        </is>
-      </c>
+          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1406,68 +1414,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ORIRAIL.NS</t>
+          <t>LAMBODHARA.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure Limited</t>
+          <t>Lambodhara Textiles Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>106.8899993896484</v>
+        <v>107.629997253418</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>124.3499984741211</v>
+        <v>124</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>104.25</v>
+        <v>105.5</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>114.7799987792969</v>
+        <v>118.0800018310547</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>103.629997253418</v>
+        <v>107.629997253418</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>114.7799987792969</v>
+        <v>118.0800018310547</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1142107</v>
+        <v>83175</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10.76</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail uploads Q1FY27 earnings call audio recording - scanx.trade</t>
+          <t>Lambodhara Textiles Share Price Today: 8.85% Price Rise - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail uploads Q1FY27 earnings call audio recording - scanx.trade</t>
+          <t>Lambodhara Textiles Share Price Today: 8.85% Price Rise - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure shares permitted to trade on NSE - scanx.trade</t>
+          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Free float of Oriental Rail Infrastructure Ltd. – NSE:ORIRAIL - TradingView</t>
+          <t>MDS &amp; Associates LLP resigns as Lambodhara Textiles secretarial auditor - scanx.trade</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure seeks ratification for ₹42.04 crore fund variation - scanx.trade</t>
+          <t>Lambodhara Textiles Q1 FY27 Results: Revenue, PAT &amp; Key Highlight - Univest</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1475,68 +1483,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>QUINT.NS</t>
+          <t>CRSL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Limited</t>
+          <t>Cressanda Railway Solutions Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>41.79999923706055</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>40.34000015258789</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>36.5099983215332</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>40.34000015258789</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>65255</v>
+        <v>4265503</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>10.49</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
+          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Quint Digital Consolidated June 2026 Net Sales at Rs 34.80 crore, up 335.77% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>BJP Shares Video From Bihar as One of Police Action on Jharkhand Protester - The Quint</t>
-        </is>
-      </c>
+          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1544,68 +1540,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>RHETAN.NS</t>
+          <t>ATLANTAELE.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Limited</t>
+          <t>Atlanta Electricals Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>21.75</v>
+        <v>1712.900024414062</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>24.22999954223633</v>
+        <v>1857.400024414062</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>20.61000061035156</v>
+        <v>1700</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>24.21999931335449</v>
+        <v>1846.900024414062</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.03000068664551</v>
+        <v>1688.599975585938</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>24.21999931335449</v>
+        <v>1846.900024414062</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>38609598</v>
+        <v>402945</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.94</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Iron, steel stock Rhetan TMT retraces after inching close to 52-week high. Do you own? - livemint.com</t>
+          <t>ATLANTAELE Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Ltd Surges 9.75% to Day's High of Rs 24.2 — Outperforms Sector by 8.98 Percentage Points - MarketsMojo</t>
+          <t>Atlanta Electricals shares slide 5% despite strong Q1 results; stock hits lower band - BusinessLine</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Ltd. Share Price Jumps to Fresh One-Year High - Univest</t>
+          <t>Atlanta Electricals Limited (NSE:ATLANTAELE) Stock Has Shown Weakness Lately But Financials Look Strong: Should Prospective Shareholders Make The Leap? - simplywall.st</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Atlanta Electricals shares slide 5% despite strong Q1 results; stock hits lower band - BusinessLine</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Momentum Stocks: HLE Glascoat, Rhetan TMT, Identical Brain under pressure; stocks trade below key moving... - Moneycontrol.com</t>
+          <t>Atlanta Electricals Ltd. | Stock Share Price Live - MarketSmith India</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1613,68 +1609,56 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CRSL.NS</t>
+          <t>SUBEXLTD.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Limited</t>
+          <t>Subex Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3.369999885559082</v>
+        <v>17.23999977111816</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3.390000104904175</v>
+        <v>19.38999938964844</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3.200000047683716</v>
+        <v>17.14999961853027</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3.390000104904175</v>
+        <v>18.65999984741211</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3.089999914169312</v>
+        <v>17.07999992370605</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.390000104904175</v>
+        <v>18.65999984741211</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4264848</v>
+        <v>24036145</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
+          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
-        </is>
-      </c>
+          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1682,64 +1666,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>LAMBODHARA.NS</t>
+          <t>SIL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Limited</t>
+          <t>Standard Industries Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>107.629997253418</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>124</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>105.5</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>118.0800018310547</v>
+        <v>20.84000015258789</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>107.629997253418</v>
+        <v>19.11000061035156</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>118.0800018310547</v>
+        <v>20.84000015258789</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>83132</v>
+        <v>592621</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>MDS &amp; Associates LLP resigns as Lambodhara Textiles secretarial auditor - scanx.trade</t>
+          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - kalkine.ca</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
+          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - kalkine.ca</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
+          <t>(SIL) Equity Trading Insights (SIL:CA) - Stock Traders Daily</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles net profit rises 66% in Q1FY26 on lower finance costs - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>SIL News | GLOBAL X SILVER MINERS ETF (NYSEARCA:SIL) - ChartMill</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - Kalkine</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1747,48 +1735,40 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE.NS</t>
+          <t>WHBRADY.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Electricals Limited</t>
+          <t>WH Brady &amp; Company Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1712.900024414062</v>
+        <v>502</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1857.400024414062</v>
+        <v>539.8499755859375</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1700</v>
+        <v>502</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1846.900024414062</v>
+        <v>534.5</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1688.599975585938</v>
+        <v>490.2000122070312</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1846.900024414062</v>
+        <v>534.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>402648</v>
+        <v>148</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Atlanta Electricals Schedules Investor and Analyst Meetings in Mumbai - TipRanks</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Atlanta Electricals Schedules Investor and Analyst Meetings in Mumbai - TipRanks</t>
-        </is>
-      </c>
+        <v>9.039999999999999</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -1796,7 +1776,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1804,61 +1784,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING.NS</t>
+          <t>FCL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bluspring Enterprises Limited</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>118</v>
+        <v>43.68000030517578</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>129.75</v>
+        <v>47.90000152587891</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>117.7200012207031</v>
+        <v>43.43000030517578</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>128.9799957275391</v>
+        <v>47.43000030517578</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>117.9599990844727</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>128.9799957275391</v>
+        <v>47.43000030517578</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2549295</v>
+        <v>34486545</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9.34</v>
+        <v>8.91</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING Share Price Rise: Price, Valuation, Sector View - Univest</t>
+          <t>Fineos (ASX:FCL) Shares Edge Lower Amid Weaker Technology Sector Sentiment - Kalkine</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING Share Price Rise: Price, Valuation, Sector View - Univest</t>
+          <t>ETFs Investing in Fineotex Chemical Limited Stocks - TradingView</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING ENTERPRISES LTD Share Price: Price Rise Analysis - Univest</t>
+          <t>Why Are Investors Watching Fineos (ASX:FCL) After Its Latest Share Price Decline? - Kalkine</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Bluspring revenue rises 20% to ₹930 crore in Q1 FY27 - scanx.trade</t>
+          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Bluspring subsidiary secures ₹125 Cr term loan for LSG acquisition - scanx.trade</t>
+          <t>Fineos (ASX: FCL) Crosses Profitability Inflection Point In H1 FY 2026 - A Rich Life</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1965,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2020,41 +2000,41 @@
         <v>3.329999923706055</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4422848</v>
+        <v>5879851</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>-15.7</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Yash Chemex promoter Paxal Shah buys 3500 shares on BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>New-age stocks, IPOs and valuations: Envision's Nilesh Shah shares his investment playbook - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>'Does True Love Exist?' Kashmera Shah Shares Cryptic Post Amid Govinda-Sunita Ahuja Spat - NDTV</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Sunshine Pictures IPO day 2 LIVE: GMP, subscription status to review. Should you apply for Vipul Shah's company shares? - TradingView</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2062,64 +2042,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AVROIND.NS</t>
+          <t>UMESLTD.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>AVRO INDIA LIMITED</t>
+          <t>Usha Martin Education &amp; Solutions Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9.479999542236328</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9.479999542236328</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8.409999847412109</v>
+        <v>5.369999885559082</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8.590000152587891</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9.380000114440918</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.590000152587891</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1274488</v>
+        <v>111981</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.42</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
+          <t>Usha Martin Education &amp; Solutions Declines 3.66%: Testing Support at ₹5.24 - Retail Driven Moves - vinanet.vn</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
+          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: Modest profit amid low revenue base - Earnings Per Share - vinanet.vn</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Avro India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>KASTURI Stock Price and Chart — BSE:KASTURI - TradingView</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Protalix BioTherapeutics (PLX) Edges Higher Amid Consolidation Near Support - Retail Driven Moves - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: EPS of ₹0.07 on Revenue of ₹0.32 Cr; Stock Declines Marginally - Strong Earnings Momentum - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Share Price - Upstox</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2127,68 +2111,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UMESLTD.NS</t>
+          <t>SHERVANI.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Limited</t>
+          <t>Shervani Industrial Syndicate Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.079999923706055</v>
+        <v>340</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6.079999923706055</v>
+        <v>340</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5.369999885559082</v>
+        <v>319.5499877929688</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5.460000038146973</v>
+        <v>321.1499938964844</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5.960000038146973</v>
+        <v>349.9500122070312</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.460000038146973</v>
+        <v>321.1499938964844</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>111981</v>
+        <v>421</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.23</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Do Usha Martin Education &amp; Solutions' (NSE:UMESLTD) Earnings Warrant Your Attention? - simplywall.st</t>
+          <t>SHERVANI Share Price Today - Shervani Industrial Syndicate Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: Modest profit amid low revenue base - Earnings Per Share - Vinanet</t>
+          <t>Shervani Industrial Syndicate (NSE:SHERVANI) Cyclically Adj - GuruFocus</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Declines 3.66%: Testing Support at ₹5.24 - Retail Driven Moves - Vinanet</t>
+          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions (UMESLTD.NS) Inches Lower Amidst Range-Bound Trading on the NSE - Insider Selling Alerts - Vinanet</t>
+          <t>Shervani Industrial Syndicate (NSE:SHERVANI) Cyclically Adj - GuruFocus</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions (UMESLTD.NS): Stock Slips 1.03% as Support Levels Come Into Focus - Wave Extension - Vinanet</t>
+          <t>Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2196,68 +2180,56 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SHERVANI.NS</t>
+          <t>KPL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate Limited</t>
+          <t>Kwality Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>340</v>
+        <v>3604.10009765625</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>340</v>
+        <v>3634.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>319.5499877929688</v>
+        <v>3327</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>321.1499938964844</v>
+        <v>3361.10009765625</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>349.9500122070312</v>
+        <v>3630.300048828125</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>321.1499938964844</v>
+        <v>3361.10009765625</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>421</v>
+        <v>113735</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-8.23</v>
+        <v>-7.42</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHERVANI Share Price Today - Shervani Industrial Syndicate Stock Analysis - Equitypandit</t>
+          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard</t>
-        </is>
-      </c>
+          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2265,56 +2237,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>KPL.NS</t>
+          <t>HSCL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kwality Pharmaceuticals Limited</t>
+          <t>Himadri Speciality Chemical Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3604.10009765625</v>
+        <v>705.0999755859375</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3634.5</v>
+        <v>711</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3327</v>
+        <v>650</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3361.10009765625</v>
+        <v>654.4000244140625</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3630.300048828125</v>
+        <v>704.2000122070312</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3361.10009765625</v>
+        <v>654.4000244140625</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>113689</v>
+        <v>17256079</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-7.42</v>
+        <v>-7.07</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 3.13% Today - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>KPL Share Price | Kwality Pharmaceuticals Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>HSCL Share Price | Himadri Speciality Chemical Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Kino Polska TV S.A. Revenue Breakdown – GPW:KPL - TradingView</t>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>KPL Share Price | Kwality Pharmaceuticals Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>HSCL Share Price | Himadri Speciality Chemical Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -2322,7 +2294,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2330,68 +2302,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SIYSIL.NS</t>
+          <t>KSE.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills Limited</t>
+          <t>KSE Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>635</v>
+        <v>192.0099945068359</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>645.5</v>
+        <v>192.8600006103516</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>599.9500122070312</v>
+        <v>183.3000030517578</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>606.3499755859375</v>
+        <v>183.8399963378906</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>647.5499877929688</v>
+        <v>196.8000030517578</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>606.3499755859375</v>
+        <v>183.8399963378906</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>198647</v>
+        <v>71756</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.36</v>
+        <v>-6.59</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>KSE Q1 FY27 Results: Revenue grew to Rs 454 Cr, PAT -97% - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
+          <t>Stock market slips 1.6% on Hormuz uncertainty - The Express Tribune</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
+          <t>Stock market slips 1.6% on Hormuz uncertainty - The Express Tribune</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills Limited Reports Q1 FY27 Results: Total Income Rises 16.4% YoY to ₹466 Crore; PAT Surges to ₹11 Crore - EquityBulls</t>
+          <t>KSE-100 Index gains 575 points as buying returns to PSX - Business Recorder</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills Expands Authorised Share Capital After Scheme Approval - TipRanks</t>
+          <t>KSE Ltd Q1 Results: Unaudited financials filed for June 2026 quarter - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2399,68 +2371,60 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>BANARISUG.NS</t>
+          <t>SIYSIL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Limited</t>
+          <t>Siyaram Silk Mills Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4114.89990234375</v>
+        <v>635</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4199</v>
+        <v>645.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>3950</v>
+        <v>599.9500122070312</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4019.699951171875</v>
+        <v>606.3499755859375</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4240.7001953125</v>
+        <v>647.5499877929688</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4019.699951171875</v>
+        <v>606.3499755859375</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>22810</v>
+        <v>198798</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.21</v>
+        <v>-6.36</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
+          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
-        </is>
-      </c>
+          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2468,68 +2432,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>UEL.NS</t>
+          <t>ABINFRA.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Limited</t>
+          <t>A B Infrabuild Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>181.2299957275391</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>181.2299957275391</v>
+        <v>13.72999954223633</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>181.2299957275391</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>181.2299957275391</v>
+        <v>12.63000011444092</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>190.7599945068359</v>
+        <v>13.34000015258789</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>181.2299957275391</v>
+        <v>12.63000011444092</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>8804</v>
+        <v>14180685</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5</v>
+        <v>-5.32</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+          <t>AB Infrabuild Ltd. Share Price News: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Q1 Standalone Net Profit Rises to 33M Rupees on Revenue of 30M Rupees - Sahi</t>
+          <t>AB Infrabuild Ltd. Share Price News: Price Action Check - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Ltd. Share Price Shows Strong Price Action - Univest</t>
+          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Ltd. Share Price Jumps to New 52-Week Peak - Univest</t>
+          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2537,68 +2501,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>RTSPOWR.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>RTS Power Corporation Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>59.65999984741211</v>
+        <v>94.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>59.65999984741211</v>
+        <v>99.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>59.65999984741211</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>59.65999984741211</v>
+        <v>93.33000183105469</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>62.79999923706055</v>
+        <v>98.51999664306641</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>59.65999984741211</v>
+        <v>93.33000183105469</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>84649</v>
+        <v>10016</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5</v>
+        <v>-5.27</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+          <t>RTS Power Corporation Ltd Income Statement – NSE:RTSPOWR - TradingView</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>how InvestingPro’s fair value predicted 56% drop in Indo Thai Securities By Investing.com - Investing.com India</t>
+          <t>RTS Power (NSE:RTSPOWR) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>how InvestingPro’s fair value predicted 56% drop in Indo Thai Securities By Investing.com - Investing.com India</t>
+          <t>RTS Power Corporation Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
-        </is>
-      </c>
+          <t>RTS Power (NSE:RTSPOWR) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2606,56 +2566,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NATIONSTD.NS</t>
+          <t>BANARISUG.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) Limited</t>
+          <t>Bannari Amman Sugars Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>128</v>
+        <v>4114.89990234375</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>140.3399963378906</v>
+        <v>4199</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>126.9800033569336</v>
+        <v>3950</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>126.9800033569336</v>
+        <v>4019.699951171875</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>133.6600036621094</v>
+        <v>4240.7001953125</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>126.9800033569336</v>
+        <v>4019.699951171875</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>464929</v>
+        <v>22815</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5</v>
+        <v>-5.21</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Q1FY26 net loss widens to ₹109 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2663,64 +2631,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SIEL.NS</t>
+          <t>HAPPYFORGE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises Limited</t>
+          <t>Happy Forgings Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>38.29000091552734</v>
+        <v>2318.10009765625</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>2318.10009765625</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>38.29000091552734</v>
+        <v>2211.800048828125</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>38.29000091552734</v>
+        <v>2211.800048828125</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>2328.199951171875</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>38.29000091552734</v>
+        <v>2211.800048828125</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>7981</v>
+        <v>91079</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+          <t>Happy Forgings Limited Just Beat EPS By 10.0%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Happy Forgings Limited Just Beat EPS By 10.0%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2728,68 +2688,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>STYLEBAAZA.NS</t>
+          <t>NATIONSTD.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Limited</t>
+          <t>National Standard (India) Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>437.8500061035156</v>
+        <v>128</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>447.1000061035156</v>
+        <v>140.3399963378906</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>417.6499938964844</v>
+        <v>126.9800033569336</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>417.6499938964844</v>
+        <v>126.9800033569336</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>439.6000061035156</v>
+        <v>133.6600036621094</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>417.6499938964844</v>
+        <v>126.9800033569336</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2692008</v>
+        <v>464929</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Independent Directors Step Down, Triggering Board Reshuffle - TipRanks</t>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Baazar Style Retail Limited Announces Redesignation of Siddhant Khemani from Chief Marketing Officer to Head E-Commerce, Effective August 13, 2026 - marketscreener.com</t>
-        </is>
-      </c>
+          <t>National Standard (India) sets Aug 28 date for 63rd AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2797,68 +2753,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>KMSUGAR.NS</t>
+          <t>STYLEBAAZA.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>K.M.Sugar Mills Limited</t>
+          <t>Baazar Style Retail Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>35.0099983215332</v>
+        <v>437.8500061035156</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>35.29999923706055</v>
+        <v>447.1000061035156</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>32.84999847412109</v>
+        <v>417.6499938964844</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>33.54999923706055</v>
+        <v>417.6499938964844</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35.29999923706055</v>
+        <v>439.6000061035156</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>33.54999923706055</v>
+        <v>417.6499938964844</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1436244</v>
+        <v>2692014</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.96</v>
+        <v>-4.99</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Ltd. Share Price Rise With Valuation View - Univest</t>
+          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>NCLT Allahabad sanctions KM Sugar Mills distillery demerger scheme - scanx.trade</t>
+          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Ltd. Share Price Today With Fundamentals - Univest</t>
+          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>NCLT Allahabad sanctions KM Sugar Mills distillery demerger scheme - scanx.trade</t>
+          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2866,68 +2822,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BALRAMCHIN.NS</t>
+          <t>ONIXSOLAR.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Limited</t>
+          <t>Onix Solar Energy Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>747.3499755859375</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>765</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>714</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>729.3499755859375</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>767.0999755859375</v>
+        <v>321.9500122070312</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>729.3499755859375</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>19992314</v>
+        <v>11633</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.92</v>
+        <v>-4.99</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Stock Update: Shares Slip on Duty-Free Sugar Imports - LatestLY</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
+          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2935,68 +2879,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MODIS.NS</t>
+          <t>AMBALALSA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Modis Navnirman Limited</t>
+          <t>Ambalal Sarabhai Enterprises Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>400</v>
+        <v>46.5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>404.4500122070312</v>
+        <v>48</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>377.5</v>
+        <v>45.36000061035156</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>383.1499938964844</v>
+        <v>45.36000061035156</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>402.7000122070312</v>
+        <v>47.7400016784668</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>383.1499938964844</v>
+        <v>45.36000061035156</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>142116</v>
+        <v>86066</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.85</v>
+        <v>-4.99</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+          <t>Issuance/retirement of stock (net) of Ambalal Sarabhai Enterprises Limited – NSE:AMBALALSA - TradingView</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+          <t>Issuance/retirement of stock (net) of Ambalal Sarabhai Enterprises Limited – NSE:AMBALALSA - TradingView</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Modis Navnirman reappoints Dinesh Modi at AGM; reports record FY26 growth - scanx.trade</t>
+          <t>Ambalal Sarabhai Share Price Gains 10.31% in Today's Trading - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Modis Navnirman Standalone June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+          <t>Ambalal Sarabhai Enterprises Ltd. Stock: 11.62% Price Rise - Univest</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Modis Navnirman Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+          <t>Ambalal Sarabhai Enterprises shareholders approve director reappointments - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3004,56 +2948,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE.NS</t>
+          <t>SIEL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging Limited</t>
+          <t>Superior Industrial Enterprises Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>846238</v>
+        <v>7981</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.65</v>
+        <v>-4.99</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3061,68 +3013,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND.NS</t>
+          <t>BALRAMCHIN.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Praj Industries Limited</t>
+          <t>Balrampur Chini Mills Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>358</v>
+        <v>747.3499755859375</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>358</v>
+        <v>765</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>341.1499938964844</v>
+        <v>714</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>344.3500061035156</v>
+        <v>729.3499755859375</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>358.4500122070312</v>
+        <v>767.0999755859375</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>344.3500061035156</v>
+        <v>729.3499755859375</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1661248</v>
+        <v>19995747</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.93</v>
+        <v>-4.92</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Praj Industries Stock And Two India Energy Names Tied To Higher Oil Prices - simplywall.st</t>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Praj Industries Ltd. Share Price Up 5.18%: Price Analysis - Univest</t>
+          <t>Balrampur Exceeds Analyst Target by 5% After India Reverses Sugar Import Policy - TechStock²</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Praj Industries Limited Beat Analyst Estimates: See What The Consensus Is Forecasting For This Year - simplywall.st</t>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Praj Industries Ltd. (PRAJIND) Share Price Rises 6.1% Today - Univest</t>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Praj Industries Ltd. Share Price Up 5.18%: Price Analysis - Univest</t>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3130,60 +3082,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI.NS</t>
+          <t>PAKKA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Jai Balaji Industries Limited</t>
+          <t>PAKKA LIMITED</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>65.5</v>
+        <v>88.65000152587891</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>65.95999908447266</v>
+        <v>89.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>63.11000061035156</v>
+        <v>83.5</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.56999969482422</v>
+        <v>84.51999664306641</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>66.08000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>63.56999969482422</v>
+        <v>84.51999664306641</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>611558</v>
+        <v>190999</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.8</v>
+        <v>-4.7</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Jai Balaji Industries Limited Announces Cessation of Bimal Kumar Choudhary as Whole-Time Director, Effective September 14, 2026 - marketscreener.com</t>
+          <t>Earnings call transcript: Pakka posts record Q1 2026 revenue, shares jump 8% - Investing.com India</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Jai Balaji Industries Limited Announces Cessation of Bimal Kumar Choudhary as Whole-Time Director, Effective September 14, 2026 - marketscreener.com</t>
+          <t>Pakka Limited Confirms No Deviation in Preferential Issue Fund Use - TipRanks</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Jai Balaji Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Pakka Ltd. Share Price Decline: Technicals, Peers, Sector - Univest</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SBI Mutual Fund sells 71,698 Pakka Ltd shares, stake falls to 6.45% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Pakka Ltd. Share Price Rise: Paper Stock Price and Analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3191,68 +3151,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MATRIMONY.NS</t>
+          <t>GANGAFORGE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Matrimony.Com Limited</t>
+          <t>Ganga Forging Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>551.7999877929688</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>560.8499755859375</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>532</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>537.0499877929688</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>558.2000122070312</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>537.0499877929688</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>26974</v>
+        <v>846239</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.79</v>
+        <v>-4.65</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Matrimony.com relieves CFO Harigovind Krishnasamy effective Aug 17 - scanx.trade</t>
+          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Matrimony.com relieves CFO Harigovind Krishnasamy effective Aug 17 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Income Investors Should Know That Matrimony.com Limited (NSE:MATRIMONY) Goes Ex-Dividend Soon - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Matrimony.com soars after Q1 PAT spurts 127.5% YoY - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Matrimony.com Shares Rally 10% After Q1 Net Profit Jumps 127.5% Year-on-Year - Margin Expansion Trends - Vinanet</t>
-        </is>
-      </c>
+          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:29:09 IST</t>
+          <t>2026-08-24 09:02:59 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3260,61 +3208,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SALONA.NS</t>
+          <t>TAKE.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Salona Cotspin Limited</t>
+          <t>TAKE Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>272.989990234375</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>273</v>
+        <v>22.18000030517578</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>260.0499877929688</v>
+        <v>20.75</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>263.2999877929688</v>
+        <v>20.82999992370605</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>273.5299987792969</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>263.2999877929688</v>
+        <v>20.82999992370605</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>331</v>
+        <v>515661</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.74</v>
+        <v>-4.62</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Salona Cotspin Share Price Forecast to 2030 - Univest</t>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>RRP Semiconductor reports standalone net loss of Rs 0.33 crore in the June 2026 quarter - Business Standard</t>
+          <t>Take-Two Shares Rebound by 50% From GTA 6 Leak Decline Before Preview Reveal - TechStock²</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Salona Cotspin standalone net profit rises 47.71% in the June 2026 quarter - Business Standard</t>
+          <t>It Won’t Take Much to Burst the Stock Market Bubble - Advisor Perspectives</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>RRP Semiconductor reports standalone net loss of Rs 0.33 crore in the June 2026 quarter - Business Standard</t>
+          <t>Buy or rent a house? Niranjan Hiranandani shares his take on India's housing market: 'Home will never become obsolete' - livemint.com</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>STL Global reports standalone net loss of Rs 1.25 crore in the June 2026 quarter - Business Standard</t>
+          <t>Govt to take stock of H1N1 as Karnataka cases cross 4,000 - The Times of India</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -446,7 +446,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,56 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MINALIND.NS</t>
+          <t>RAMBHAJO.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries Limited</t>
+          <t>Advit Jewels Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.089999914169312</v>
+        <v>180.8500061035156</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.180000066757202</v>
+        <v>212.8899993896484</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.089999914169312</v>
+        <v>180.8500061035156</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>3.180000066757202</v>
+        <v>212.8899993896484</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.650000095367432</v>
+        <v>177.4100036621094</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.180000066757202</v>
+        <v>212.8899993896484</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>148926</v>
+        <v>2520932</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
+          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Free float of Minal Industries Limited – NSE:MINALIND - TradingView</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Minal Industries Limited Announces Appointment of Saket Rajendra Sugandh as Company Secretary and Compliance Officer, Effective August 5, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
-        </is>
-      </c>
+          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,60 +610,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE.NS</t>
+          <t>VIRAT.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited</t>
+          <t>Virat Industries Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>340</v>
+        <v>465</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>405.3500061035156</v>
+        <v>482</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>339</v>
+        <v>452.7999877929688</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>405.3500061035156</v>
+        <v>482</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>337.7999877929688</v>
+        <v>401.7000122070312</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>405.3500061035156</v>
+        <v>482</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>7504777</v>
+        <v>125540</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>20</v>
+        <v>19.99</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+          <t>Sanat Sangwan shares a partnership with Virat Kohli in the Ranji Trophy - Cricinfo</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+          <t>Sanat Sangwan shares a partnership with Virat Kohli in the Ranji Trophy - Cricinfo</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>"He Is Like My Brother": PV Sindhu Shares How Virat Kohli Motivated Her During Tough Phase - Sportscape Magazine</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Virat Industries Approves Acquisition Of 70.28% Shares In Brahm Lifestyle Products - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +679,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGEAR.NS</t>
+          <t>MARATHON.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Shanthi Gears Limited</t>
+          <t>Marathon Nextgen Realty Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>464.25</v>
+        <v>422.7999877929688</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>395</v>
+        <v>361.6000061035156</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>464.25</v>
+        <v>422.7999877929688</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>386.8999938964844</v>
+        <v>352.3500061035156</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>464.25</v>
+        <v>422.7999877929688</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1972065</v>
+        <v>3183615</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>19.99</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Shanthi Gears Ltd. (SHANTIGEAR) Share Price Hits Fresh 52-Week Low - Univest</t>
+          <t>Why is Marathon Digital stock surging today? By Investing.com - Investing.com India</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Shanthi Gears Share: பெற்றோர் கம்பெனி நம்பிக்கை! **18%** குதித்தது ஷேர் விலை! - Whalesbook</t>
+          <t>Landscape Capital Management L.L.C. Purchases Shares of 5,091 Marathon Petroleum Corporation $MPC - MarketBeat</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Shanthi Gears Share Price at Fresh 52-Week Low - Univest</t>
+          <t>Marathon Nextgen Realty confirms no new encumbrance by promoters - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Tube Investments of India acquires 2.69% stake in Shanthi Gears - scanx.trade</t>
+          <t>Bank of Nova Scotia Acquires Shares of 113,403 Marathon Petroleum Corporation $MPC - MarketBeat</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Tube Investments of India Increases Stake in Shanthi Gears - InvestyWise</t>
+          <t>Marathon Petroleum SVP Log &amp; Storage, MPLX GP LLC Sold Shares Worth Over $875K - TradingView</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +748,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MPDL.NS</t>
+          <t>SUPTANERY.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>MPDL Limited</t>
+          <t>Super Tannery Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>39.9900016784668</v>
+        <v>9.170000076293945</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>41.18000030517578</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>39.20000076293945</v>
+        <v>9.170000076293945</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>41.18000030517578</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.31999969482422</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41.18000030517578</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>14902</v>
+        <v>1630102</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>19.99</v>
+        <v>19.95</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+          <t>SUPTANERY Share Price Today - Super Tannery Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
+          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>SUPTANERY Historical Data - Equitypandit</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>MPDL reports consolidated net loss of Rs 4.20 crore in the June 2026 quarter - Business Standard</t>
+          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,68 +817,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NDL.NS</t>
+          <t>SHAH.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Nandan Denim Limited</t>
+          <t>Shah Metacorp Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.279999971389771</v>
+        <v>3.670000076293945</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.710000038146973</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.710000038146973</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2.259999990463257</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.710000038146973</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5991494</v>
+        <v>7806929</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>19.91</v>
+        <v>19.82</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+          <t>What Is Changing At Shah Rukh Khan's Rs 300-Crore Mannat? Anand Pandit Shares Renovation Details - NDTV</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+          <t>Hipolin promoter Rajasvee Sagar Shah sells 9.38% stake in open market - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Next Digital probe halted - news.gov.hk</t>
+          <t>Hipolin promoter Rajasvee Sagar Shah sells 9.38% stake in open market - scanx.trade</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
+          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>NDL Ventures Q1 FY27 Results: Revenue, PAT &amp; Key Highlights - Univest</t>
+          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -890,68 +886,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NKIND.NS</t>
+          <t>KOTARISUG.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited</t>
+          <t>Kothari Sugars And Chemicals Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>60</v>
+        <v>34.47999954223633</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>67.91999816894531</v>
+        <v>39.93999862670898</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>58.09999847412109</v>
+        <v>33.95999908447266</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>67.62000274658203</v>
+        <v>39.15999984741211</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>56.59999847412109</v>
+        <v>33.29000091552734</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>67.62000274658203</v>
+        <v>39.15999984741211</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>327876</v>
+        <v>3630571</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>19.47</v>
+        <v>17.63</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited (NKIND.NS) Holds Near Support as Modest Uptick Stalls at Resistance - High Conviction Picks - vinanet.vn</t>
+          <t>Kothari Sugars And Chemicals Share Price Today at Rs 36.35 - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - vinanet.vn</t>
+          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries (NKIND.NS) Hovers Near ₹59 Amid Narrow Range, Support at ₹56.16 in Focus - Monthly Profile - vinanet.vn</t>
+          <t>Kothari Sugars and Chemicals gets NSE no objection for merger with Kothari Petrochemicals - ChiniMandi</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited Q2 2026 Earnings: Revenue Declines Sharply on Weak Operational Environment; EPS Turns Negative - Performance Review - vinanet.vn</t>
+          <t>Kothari Sugars And Chemicals Ltd. (KOTARISUG) Share Price Rises 13.52% Today - Univest</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited (NKIND.NS): Marginal Gain Amid Consolidation Near Key Resistance - Dark Pool Prints - vinanet.vn</t>
+          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -959,68 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC.NS</t>
+          <t>NAHARINDUS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Limited</t>
+          <t>Nahar Industrial Enterprises Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>39.11999893188477</v>
+        <v>127.3499984741211</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45.5</v>
+        <v>150.7299957275391</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>38.13000106811523</v>
+        <v>125.8000030517578</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>44.40000152587891</v>
+        <v>147.6000061035156</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>39.11000061035156</v>
+        <v>125.6100006103516</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44.40000152587891</v>
+        <v>147.6000061035156</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>986460</v>
+        <v>570317</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>13.53</v>
+        <v>17.51</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - vinanet.vn</t>
+          <t>Nahar Industrial Enterprises Share Price after 10.58% gain - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+          <t>Nahar Industrial Enterprises Share Price after 10.58% gain - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC Share Price Today - Birla Precision Technologies Stock Analysis - Equitypandit</t>
+          <t>Nahar Industrial Enterprises Ltd. (NAHARINDUS) Share Price Rises 8.91% Today - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC.NS Dec 2025 Earnings: Modest EPS of ₹0.19 on Stable Revenues - Segment Revenue Breakdown - vinanet.vn</t>
+          <t>Nahar Industrial Enterprises Limited acquired Emerald Logipark Private Limited for INR 0.10 million. - marketscreener.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+          <t>Nahar Industrial Enterprises Acquires 100% Stake in Emerald Logipark for ₹1,00,000 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1028,68 +1024,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MODIRUBBER.NS</t>
+          <t>RATNAMANI.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber Limited</t>
+          <t>Ratnamani Metals &amp; Tubes Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>119</v>
+        <v>2354.39990234375</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>144</v>
+        <v>2777</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>117.8000030517578</v>
+        <v>2323</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>134.2400054931641</v>
+        <v>2697</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>120.0699996948242</v>
+        <v>2354.39990234375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>134.2400054931641</v>
+        <v>2697</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>40792</v>
+        <v>903479</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>11.8</v>
+        <v>14.55</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber Ltd. Share Price Update: Fundamentals Check - Univest</t>
+          <t>Ratnamani Metals &amp; Tubes shares jump 18% on securing export orders worth ₹2,700 crore - Upstox</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber Ltd. Share Price Update: Fundamentals Check - Univest</t>
+          <t>This mid-cap metal stock zooms 15% on Rs 2,700 crore order announcement; do you own? - Business Today</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber seeks shareholder approval to appoint Ajay Kumar Jain as Independent Director - scanx.trade</t>
+          <t>Ratnamani Subsidiary Wins ₹2,700 Crore Orders - HDFC Sky</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber Ltd. Share Price Today Up 20%: Stock Analysis - Univest</t>
+          <t>Buzzing stocks: Ratnamani, Quadrant, Shanthi Gears zoom up to 42% in 2 days - Business Standard</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Modi Rubber approves comfort letter for Gujarat Guardian expansion project - scanx.trade</t>
+          <t>Ratnamani Metals shareholders approve ₹10 dividend, reappoint directors - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1097,60 +1093,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KLBRENG-B.NS</t>
+          <t>LEENEE.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kilburn Engineering Limited</t>
+          <t>Lee &amp; Nee Softwares Exports Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>364</v>
+        <v>10.75</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>408.6000061035156</v>
+        <v>11.02000045776367</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>361.7000122070312</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>397.3999938964844</v>
+        <v>10.5</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>357.6499938964844</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>397.3999938964844</v>
+        <v>10.5</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3833782</v>
+        <v>360638</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>11.11</v>
+        <v>14.25</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Kilburn Engineering Ltd. Share Price Rises 9.96% Today - Univest</t>
+          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Kilburn Engineering (NSE:KLBRENG-B) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Kilburn Engineering (NSE:KLBRENG-B) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
-        </is>
-      </c>
+          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1158,68 +1150,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ORIRAIL.NS</t>
+          <t>BALUFORGE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure Limited</t>
+          <t>Balu Forge Industries Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>106.8899993896484</v>
+        <v>568</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>124.3499984741211</v>
+        <v>638</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>104.25</v>
+        <v>568</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>114.7799987792969</v>
+        <v>632.2000122070312</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>103.629997253418</v>
+        <v>555.4000244140625</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>114.7799987792969</v>
+        <v>632.2000122070312</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1142227</v>
+        <v>15539622</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10.76</v>
+        <v>13.83</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Oriental Rail Infrastructure Ltd. – NSE:ORIRAIL - TradingView</t>
+          <t>Solid Earnings May Not Tell The Whole Story For Balu Forge Industries (NSE:BALUFORGE) - simplywall.st</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Balu Forge Industries Declines 3.98%: Stock Approaches Key Support Level - Dark Pool Prints - vinanet.vn</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Balu Forge Industries Share Price Rise 8.69% As Company Signs 5-Year MoU For Large Calibre Ammunition Supply - HDFC Sky</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure shares permitted to trade on NSE - scanx.trade</t>
+          <t>Balu Forge Industries Limited (NSE:BALUFORGE) Stock's 29% Dive Might Signal An Opportunity But It Requires Some Scrutiny - simplywall.st</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Cyclically Adjus - GuruFocus</t>
+          <t>BALUFORGE Q2 2026 Earnings: Revenue Surges 20% YoY, EPS at ₹23.9 - Energy Earnings Report - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1227,68 +1219,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>QUINT.NS</t>
+          <t>NDL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Limited</t>
+          <t>Nandan Denim Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>38</v>
+        <v>2.890000104904175</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>41.79999923706055</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>40.34000015258789</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.5099983215332</v>
+        <v>2.710000038146973</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>40.34000015258789</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>65255</v>
+        <v>15635199</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.49</v>
+        <v>12.18</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Ltd. Share Price Up 10.53%: Full Analysis - Univest</t>
+          <t>Next Digital probe halted - news.gov.hk</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
+          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
+          <t>NDL Ventures Q1 FY27 Results: Revenue, PAT &amp; Key Highlights - Univest</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1296,60 +1288,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER.NS</t>
+          <t>ATL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgears Limited</t>
+          <t>Allcargo Terminals Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>286</v>
+        <v>25.3799991607666</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>298.8500061035156</v>
+        <v>28.18000030517578</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>271.7000122070312</v>
+        <v>24.55999946594238</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>298.8500061035156</v>
+        <v>27.59000015258789</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>271.7000122070312</v>
+        <v>24.86000061035156</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>298.8500061035156</v>
+        <v>27.59000015258789</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>12178</v>
+        <v>1310266</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>9.99</v>
+        <v>10.98</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
+          <t>Enterprise value to EBIT forward of Arab Tunisian Lease SA – BVMT:ATL - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
+          <t>Taking Stock - Adam Stewart On Sandals, Jamaica’s Tourism Industry &amp; ATL’s Caribbean Expansion Rocket Launch Today (fXoWngxf0m) - Mshale</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Reimagining the passenger journey: ATL Airport on AI, human-centred experiences and the airport as a destination - Future Travel Experience</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Taking Stock - Adam Stewart On Sandals, Jamaica’s Tourism Industry &amp; ATL’s Caribbean Expansion Rocket Launch Today (fXoWngxf0m) - Mshale</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>AtlantaSanad Revenue Breakdown – CSEMA:ATL - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1357,56 +1357,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>LEENEE.NS</t>
+          <t>MAXESTATES.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Lee &amp; Nee Softwares Exports Limited</t>
+          <t>Max Estates Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8.439999580383301</v>
+        <v>495.3999938964844</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>9.510000228881836</v>
+        <v>559.7999877929688</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>7.559999942779541</v>
+        <v>495.3999938964844</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.189999580383301</v>
+        <v>549.1500244140625</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8.359999656677246</v>
+        <v>494.8500061035156</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.189999580383301</v>
+        <v>549.1500244140625</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>99370</v>
+        <v>1963922</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>9.93</v>
+        <v>10.97</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
+          <t>Max Estates Ltd. (MAXESTATES) Share Price Hits Fresh 52-Week Low - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>You were invited to TradingView - TradingView</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>WEWORK Stock Price and Chart — NSE:WEWORK - TradingView</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Max Estates Ltd. Share Price: Fresh 52-Week High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>You were invited to TradingView - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1414,68 +1426,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>LAMBODHARA.NS</t>
+          <t>QUADFUTURE.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Limited</t>
+          <t>Quadrant Future Tek Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>107.629997253418</v>
+        <v>410.0499877929688</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>124</v>
+        <v>464.7999877929688</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>105.5</v>
+        <v>395.5</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>118.0800018310547</v>
+        <v>447.2999877929688</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>107.629997253418</v>
+        <v>405.3500061035156</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>118.0800018310547</v>
+        <v>447.2999877929688</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>83175</v>
+        <v>23856274</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Share Price Today: 8.85% Price Rise - Univest</t>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Share Price Today: 8.85% Price Rise - Univest</t>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>MDS &amp; Associates LLP resigns as Lambodhara Textiles secretarial auditor - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Lambodhara Textiles Q1 FY27 Results: Revenue, PAT &amp; Key Highlight - Univest</t>
-        </is>
-      </c>
+          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1483,56 +1487,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CRSL.NS</t>
+          <t>S&amp;SPOWER.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Limited</t>
+          <t>S&amp;S Power Switchgears Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3.369999885559082</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3.390000104904175</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3.200000047683716</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3.390000104904175</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3.089999914169312</v>
+        <v>298.8500061035156</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.390000104904175</v>
+        <v>328.7000122070312</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4265503</v>
+        <v>4808</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
+          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+          <t>S&amp;S Power Arm Wins Hitachi Energy Order, Contract Valued At Over ₹8-10 Crore - Free Press Journal</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Arm Wins Hitachi Energy Order, Contract Valued At Over ₹8-10 Crore - Free Press Journal</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1540,68 +1552,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE.NS</t>
+          <t>MINALIND.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Electricals Limited</t>
+          <t>Minal Industries Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1712.900024414062</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1857.400024414062</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1700</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1846.900024414062</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1688.599975585938</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1846.900024414062</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>402945</v>
+        <v>220880</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Electricals shares slide 5% despite strong Q1 results; stock hits lower band - BusinessLine</t>
+          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Electricals Limited (NSE:ATLANTAELE) Stock Has Shown Weakness Lately But Financials Look Strong: Should Prospective Shareholders Make The Leap? - simplywall.st</t>
+          <t>Free float of Minal Industries Limited – NSE:MINALIND - TradingView</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Electricals shares slide 5% despite strong Q1 results; stock hits lower band - BusinessLine</t>
+          <t>Minal Industries Limited Announces Appointment of Saket Rajendra Sugandh as Company Secretary and Compliance Officer, Effective August 5, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Electricals Ltd. | Stock Share Price Live - MarketSmith India</t>
+          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1609,56 +1621,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SUBEXLTD.NS</t>
+          <t>MOLBIO.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Subex Limited</t>
+          <t>Molbio Diagnostics Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>17.23999977111816</v>
+        <v>1125</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>19.38999938964844</v>
+        <v>1219.949951171875</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>17.14999961853027</v>
+        <v>1125</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>18.65999984741211</v>
+        <v>1199.300048828125</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.07999992370605</v>
+        <v>1098.449951171875</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18.65999984741211</v>
+        <v>1199.300048828125</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>24036145</v>
+        <v>4088665</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9.25</v>
+        <v>9.18</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
+          <t>MOLBIO DIAGNOSTICS LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Molbio Diagnostics Ltd. Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics Ltd. Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics' shares jump over 21 pc in market debut trade - ET HealthWorld</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1666,68 +1690,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SIL.NS</t>
+          <t>PCJEWELLER.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Standard Industries Limited</t>
+          <t>PC Jeweller Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>19.20000076293945</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>22.29999923706055</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>10.1899995803833</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>20.84000015258789</v>
+        <v>11.11999988555908</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19.11000061035156</v>
+        <v>10.22000026702881</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20.84000015258789</v>
+        <v>11.11999988555908</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>592621</v>
+        <v>686804747</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - kalkine.ca</t>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - kalkine.ca</t>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>(SIL) Equity Trading Insights (SIL:CA) - Stock Traders Daily</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>SIL News | GLOBAL X SILVER MINERS ETF (NYSEARCA:SIL) - ChartMill</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - Kalkine</t>
-        </is>
-      </c>
+          <t>Penny Stock in Focus: Jewellery Stock Ends Higher After Key Business Update; Should Investors Watch? - Goodreturns</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1735,48 +1751,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WHBRADY.NS</t>
+          <t>SHIVAAGRO.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>WH Brady &amp; Company Limited</t>
+          <t>Shiva Global Agro Industries Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>502</v>
+        <v>41.9900016784668</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>539.8499755859375</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>502</v>
+        <v>38.65000152587891</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>534.5</v>
+        <v>42.7599983215332</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>490.2000122070312</v>
+        <v>39.40000152587891</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>534.5</v>
+        <v>42.7599983215332</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>148</v>
+        <v>18088</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+        <v>8.529999999999999</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>SHIVAAGRO Share Price Today - Shiva Global Agro Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Shiva Global Agro Industries Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Shiva Global Agro Industries Limited Statistics – NSE:SHIVAAGRO - TradingView</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Shiva Global Agro Industries Ltd - Equitypandit</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1784,63 +1816,51 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>FCL.NS</t>
+          <t>CLSEL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Fineotex Chemical Limited</t>
+          <t>Chaman Lal Setia Exports Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>43.68000030517578</v>
+        <v>288.8999938964844</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>47.90000152587891</v>
+        <v>321</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>43.43000030517578</v>
+        <v>288.8999938964844</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>47.43000030517578</v>
+        <v>312.75</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43.54999923706055</v>
+        <v>288.3500061035156</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>47.43000030517578</v>
+        <v>312.75</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>34486545</v>
+        <v>2814060</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8.91</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Fineos (ASX:FCL) Shares Edge Lower Amid Weaker Technology Sector Sentiment - Kalkine</t>
+          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>ETFs Investing in Fineotex Chemical Limited Stocks - TradingView</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Why Are Investors Watching Fineos (ASX:FCL) After Its Latest Share Price Decline? - Kalkine</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Fineos (ASX: FCL) Crosses Profitability Inflection Point In H1 FY 2026 - A Rich Life</t>
-        </is>
-      </c>
+          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1859,7 +1879,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1965,7 +1985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1973,68 +1993,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SHAH.NS</t>
+          <t>BLS.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Shah Metacorp Limited</t>
+          <t>BLS International Services Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.980000019073486</v>
+        <v>272</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.050000190734863</v>
+        <v>280.1400146484375</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.160000085830688</v>
+        <v>233.4700012207031</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>3.329999923706055</v>
+        <v>241.5099945068359</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3.950000047683716</v>
+        <v>271.2900085449219</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.329999923706055</v>
+        <v>241.5099945068359</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5879851</v>
+        <v>29676902</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-15.7</v>
+        <v>-10.98</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
+          <t>BLS International Share Price Slumps 12% Even As Company Rejects Role In Allegations Of Visa Irregularities - NDTV Profit</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
+          <t>BLS International shares fall up to 14% after reports of visa fraud; company rejects claims - TradingView</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
+          <t>BLS International shares slump nearly 13% after reports of visa fraud; company rejects claims - CNBC TV18</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Yash Chemex promoter Paxal Shah buys 3500 shares on BSE - scanx.trade</t>
+          <t>Visa fraud case: Why BLS International shares tanked 13% today; clarification issued - Business Today</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>New-age stocks, IPOs and valuations: Envision's Nilesh Shah shares his investment playbook - CNBC TV18</t>
+          <t>BLS International Shares Plunge 13% On Spanish Visa Probe Report - outlookbusiness.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2042,68 +2062,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UMESLTD.NS</t>
+          <t>KJMCFIN.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Limited</t>
+          <t>KJMC Financial Services Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6.079999923706055</v>
+        <v>82</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6.079999923706055</v>
+        <v>84.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5.369999885559082</v>
+        <v>71.73000335693359</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>5.460000038146973</v>
+        <v>71.73000335693359</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5.960000038146973</v>
+        <v>79.69999694824219</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5.460000038146973</v>
+        <v>71.73000335693359</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>111981</v>
+        <v>19958</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.390000000000001</v>
+        <v>-10</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Declines 3.66%: Testing Support at ₹5.24 - Retail Driven Moves - vinanet.vn</t>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: Modest profit amid low revenue base - Earnings Per Share - vinanet.vn</t>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>KASTURI Stock Price and Chart — BSE:KASTURI - TradingView</t>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: EPS of ₹0.07 on Revenue of ₹0.32 Cr; Stock Declines Marginally - Strong Earnings Momentum - vinanet.vn</t>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Share Price - Upstox</t>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2111,68 +2131,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SHERVANI.NS</t>
+          <t>CRSL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate Limited</t>
+          <t>Cressanda Railway Solutions Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>340</v>
+        <v>3.509999990463257</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>340</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>319.5499877929688</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>321.1499938964844</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>349.9500122070312</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>321.1499938964844</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>421</v>
+        <v>2362969</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-8.23</v>
+        <v>-9.73</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHERVANI Share Price Today - Shervani Industrial Syndicate Stock Analysis - Equitypandit</t>
+          <t>Cressanda Railway Solutions (CRSL) Share Price Falls 9.73% Today - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate (NSE:SHERVANI) Cyclically Adj - GuruFocus</t>
+          <t>Cressanda Railway Solutions (CRSL) Share Price Falls 9.73% Today - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
+          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate (NSE:SHERVANI) Cyclically Adj - GuruFocus</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2180,56 +2196,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KPL.NS</t>
+          <t>POLYSPIN.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Kwality Pharmaceuticals Limited</t>
+          <t>Polyspin Exports Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3604.10009765625</v>
+        <v>30.96999931335449</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3634.5</v>
+        <v>30.96999931335449</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3327</v>
+        <v>28.11000061035156</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3361.10009765625</v>
+        <v>28.29999923706055</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3630.300048828125</v>
+        <v>30.96999931335449</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3361.10009765625</v>
+        <v>28.29999923706055</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>113735</v>
+        <v>3255</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.42</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+          <t>Diluted shares outstanding of Polyspin Exports Limited – NSE:POLYSPIN - TradingView</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Polyspin Exports consolidated net profit rises 7.14% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Shubham Polyspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2237,64 +2265,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HSCL.NS</t>
+          <t>ORCHASP.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Limited</t>
+          <t>Orchasp Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>705.0999755859375</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>711</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>650</v>
+        <v>1.259999990463257</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>654.4000244140625</v>
+        <v>1.289999961853027</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>704.2000122070312</v>
+        <v>1.409999966621399</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>654.4000244140625</v>
+        <v>1.289999961853027</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>17256079</v>
+        <v>799128</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-7.07</v>
+        <v>-8.51</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 3.13% Today - Univest</t>
+          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>HSCL Share Price | Himadri Speciality Chemical Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>HSCL Share Price | Himadri Speciality Chemical Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
-        </is>
-      </c>
+          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2302,68 +2322,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>KSE.NS</t>
+          <t>NKIND.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>KSE Limited</t>
+          <t>NK Industries Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>192.0099945068359</v>
+        <v>67.58999633789062</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>192.8600006103516</v>
+        <v>67.58999633789062</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>183.3000030517578</v>
+        <v>62</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>183.8399963378906</v>
+        <v>62.0099983215332</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>196.8000030517578</v>
+        <v>67.62000274658203</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>183.8399963378906</v>
+        <v>62.0099983215332</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>71756</v>
+        <v>33161</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.59</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>KSE Q1 FY27 Results: Revenue grew to Rs 454 Cr, PAT -97% - Univest</t>
+          <t>NK Industries (NKIND.NS) Hovers Near ₹59 Amid Narrow Range, Support at ₹56.16 in Focus - Monthly Profile - vinanet.vn</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Stock market slips 1.6% on Hormuz uncertainty - The Express Tribune</t>
+          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - vinanet.vn</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Stock market slips 1.6% on Hormuz uncertainty - The Express Tribune</t>
+          <t>NK Industries Limited Q2 2026 Earnings: Revenue Declines Sharply on Weak Operational Environment; EPS Turns Negative - Performance Review - vinanet.vn</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>KSE-100 Index gains 575 points as buying returns to PSX - Business Recorder</t>
+          <t>NK Industries Limited (NKIND.NS): Marginal Gain Amid Consolidation Near Key Resistance - Dark Pool Prints - vinanet.vn</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>KSE Ltd Q1 Results: Unaudited financials filed for June 2026 quarter - scanx.trade</t>
+          <t>NK Industries Limited Slips 2.49% as Stock Tests Key Support at ₹62.89 - BPI Bear Correction - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2371,60 +2391,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SIYSIL.NS</t>
+          <t>MYSORPETRO.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills Limited</t>
+          <t>Mysore Petro Chemicals Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>635</v>
+        <v>165</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>645.5</v>
+        <v>165</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>599.9500122070312</v>
+        <v>150.6000061035156</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>606.3499755859375</v>
+        <v>153.5299987792969</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>647.5499877929688</v>
+        <v>166.1100006103516</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>606.3499755859375</v>
+        <v>153.5299987792969</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>198798</v>
+        <v>49408</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-6.36</v>
+        <v>-7.57</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Cyclically Adjusted PB Ratio : (As of Aug. 20, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2432,68 +2460,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA.NS</t>
+          <t>RVHL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild Limited</t>
+          <t>Ravinder Heights Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13.35000038146973</v>
+        <v>43.02000045776367</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>13.72999954223633</v>
+        <v>43.79999923706055</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12.19999980926514</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>12.63000011444092</v>
+        <v>39.91999816894531</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13.34000015258789</v>
+        <v>43.02000045776367</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12.63000011444092</v>
+        <v>39.91999816894531</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>14180685</v>
+        <v>40751</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.32</v>
+        <v>-7.21</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>AB Infrabuild Ltd. Share Price News: Price Rise Analysis - Univest</t>
+          <t>Ravinder Heights Q1 Results: Q1FY27 Financials Filed With Exchanges - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>AB Infrabuild Ltd. Share Price News: Price Action Check - Univest</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
-        </is>
-      </c>
+          <t>Ravinder Heights Q1 Results: Q1FY27 Financials Filed With Exchanges - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2501,64 +2517,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>RTSPOWR.NS</t>
+          <t>COMPUSOFT.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>RTS Power Corporation Limited</t>
+          <t>Compucom Software Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>94.5</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>99.5</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>92</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>93.33000183105469</v>
+        <v>13.03999996185303</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>98.51999664306641</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>93.33000183105469</v>
+        <v>13.03999996185303</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>10016</v>
+        <v>101907</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.27</v>
+        <v>-6.72</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>RTS Power Corporation Ltd Income Statement – NSE:RTSPOWR - TradingView</t>
+          <t>Compucom Software publishes 32nd AGM notice for Sept 9 meeting - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>RTS Power (NSE:RTSPOWR) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Compucom Software publishes 32nd AGM notice for Sept 9 meeting - scanx.trade</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>RTS Power Corporation Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>ROXHITECH Stock Price and Chart — NSE:ROXHITECH - TradingView</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>RTS Power (NSE:RTSPOWR) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Compucom Software Q1 Results: Unaudited financials approved by Board - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Compucom Software publishes 32nd AGM newspaper notice for September 9 - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2566,64 +2586,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>BANARISUG.NS</t>
+          <t>AHLUCONT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Limited</t>
+          <t>Ahluwalia Contracts (India) Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4114.89990234375</v>
+        <v>688</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4199</v>
+        <v>690</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3950</v>
+        <v>645.2999877929688</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>4019.699951171875</v>
+        <v>649.5999755859375</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4240.7001953125</v>
+        <v>696.2000122070312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4019.699951171875</v>
+        <v>649.5999755859375</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>22815</v>
+        <v>316763</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.21</v>
+        <v>-6.69</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
+          <t>Ahluwalia Contracts trades higher after winning orders worth ₹1,307 crore - Upstox</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+          <t>Stocks to Buy: 5 Stocks That Can Deliver Returns of Up to 54%; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bannari Amman Sugars Q1FY26 net loss widens to ₹109 million - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
-        </is>
-      </c>
+          <t>Stocks to Buy: 5 Stocks That Can Deliver Returns of Up to 54%; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2631,56 +2647,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE.NS</t>
+          <t>CRAVATEX.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited</t>
+          <t>Cravatex Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2318.10009765625</v>
+        <v>359</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2318.10009765625</v>
+        <v>359</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2211.800048828125</v>
+        <v>335</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2211.800048828125</v>
+        <v>337.1000061035156</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2328.199951171875</v>
+        <v>359</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2211.800048828125</v>
+        <v>337.1000061035156</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>91079</v>
+        <v>131</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5</v>
+        <v>-6.1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited Just Beat EPS By 10.0%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+          <t>CRAVATEX Share Price Today - Cravatex Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited Just Beat EPS By 10.0%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Cravatex (NSE:CRAVATEX) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Cravatex (NSE:CRAVATEX) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Cravatex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Cravatex Q1FY27 consolidated profit turns positive, revenue up 39% - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2688,64 +2716,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NATIONSTD.NS</t>
+          <t>BRAHMINFRA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) Limited</t>
+          <t>Brahmaputra Infrastructure Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>140.3399963378906</v>
+        <v>167.3800048828125</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>126.9800033569336</v>
+        <v>151.1999969482422</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>126.9800033569336</v>
+        <v>154.2400054931641</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>133.6600036621094</v>
+        <v>164.1499938964844</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>126.9800033569336</v>
+        <v>154.2400054931641</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>464929</v>
+        <v>78920</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5</v>
+        <v>-6.04</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Average basic shares outstanding of Brahmaputra Infrastructure Ltd. – NSE:BRAHMINFRA - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Brahmaputra Infrastructure Signs ₹70.18 Cr NH-502A Maintenance Contract in Mizoram - Trade Brains</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+          <t>Brahmaputra Infrastructure (NSE:BRAHMINFRA) Cyclically Adju - GuruFocus</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) sets Aug 28 date for 63rd AGM - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Brahmaputra Infrastructure Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Brahmaputra Infra Secures ₹71 Crore Contract with Market Capitalization at ₹470 Crore - Sahi</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2753,68 +2785,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STYLEBAAZA.NS</t>
+          <t>SVGLOBAL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Limited</t>
+          <t>S V Global Mill Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>437.8500061035156</v>
+        <v>125</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>447.1000061035156</v>
+        <v>125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>417.6499938964844</v>
+        <v>115.0100021362305</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>417.6499938964844</v>
+        <v>118</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>439.6000061035156</v>
+        <v>125.2600021362305</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>417.6499938964844</v>
+        <v>118</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2692014</v>
+        <v>345</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.8</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
+          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+          <t>SV Global Mill board to consider physical share cancellation scheme - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
+          <t>S V Global Mill (NSE:SVGLOBAL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+          <t>SV Global Mill board to consider physical share cancellation scheme - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
+          <t>S V Global Mill Limited Announces Resignation of B. Parameswar as Key Managerial Personnel, Effective August 3, 2026 - marketscreener.com</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2822,56 +2854,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ONIXSOLAR.NS</t>
+          <t>MPSLTD.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Onix Solar Energy Limited</t>
+          <t>MPS Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>2870</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>2903.89990234375</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>2705.89990234375</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>2734.800048828125</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>321.9500122070312</v>
+        <v>2897.89990234375</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>2734.800048828125</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>11633</v>
+        <v>42608</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.63</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
+          <t>MPS Limited Amends Share Subscription and Shareholders' Agreement with MPSi and Rodney Charles Beach - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>MPS Ltd shareholders approve ADI BPO amalgamation with 99.99% support - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Taurian MPS Limited Share Price Rises 8.16% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>MPS issues addendum on ADI BPO merger, confirms no public dilution - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>MPS Ltd Q1FY27 net profit rises 43% to ₹50.39 cr on margin expansion - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2879,68 +2923,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AMBALALSA.NS</t>
+          <t>DCMFINSERV.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ambalal Sarabhai Enterprises Limited</t>
+          <t>DCM Financial Services Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46.5</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>48</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>45.36000061035156</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45.36000061035156</v>
+        <v>5.130000114440918</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>47.7400016784668</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>45.36000061035156</v>
+        <v>5.130000114440918</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>86066</v>
+        <v>26143</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.52</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Issuance/retirement of stock (net) of Ambalal Sarabhai Enterprises Limited – NSE:AMBALALSA - TradingView</t>
+          <t>DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Issuance/retirement of stock (net) of Ambalal Sarabhai Enterprises Limited – NSE:AMBALALSA - TradingView</t>
+          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ambalal Sarabhai Share Price Gains 10.31% in Today's Trading - Univest</t>
+          <t>Dcm Financial Services Limited Announces Resignation of Richa Kathuria as Independent Director, Member of the Audit Committee, Nomination and Remuneration Committee and Stakeholders Relationship Committee, Effective August 11, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Ambalal Sarabhai Enterprises Ltd. Stock: 11.62% Price Rise - Univest</t>
+          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Ambalal Sarabhai Enterprises shareholders approve director reappointments - scanx.trade</t>
+          <t>Lagarde Leaves Door Open to Early ECB Exit Amid French Political Speculation - High Estimate Range - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2948,56 +2992,56 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SIEL.NS</t>
+          <t>REGENCERAM.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises Limited</t>
+          <t>Regency Ceramics Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>38.29000091552734</v>
+        <v>36</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>38.29000091552734</v>
+        <v>33.5099983215332</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>38.29000091552734</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>35.90999984741211</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>38.29000091552734</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>7981</v>
+        <v>6418</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.51</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+          <t>Regency Ceramics Ltd. Share Price Fall and Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+          <t>Regency Ceramics Ltd. Share Price Fall and Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+          <t>Regency Ceramics Q1 Results: Revenue up 173% YoY, net loss narrows - scanx.trade</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+          <t>Regency Ceramics Publishes June-Quarter Unaudited Results in Leading Dailies - TipRanks</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -3005,7 +3049,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3013,68 +3057,56 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BALRAMCHIN.NS</t>
+          <t>INTENTECH.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Limited</t>
+          <t>Intense Technologies Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>747.3499755859375</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>765</v>
+        <v>87</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>714</v>
+        <v>79</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>729.3499755859375</v>
+        <v>80.23999786376953</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>767.0999755859375</v>
+        <v>84.87999725341797</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>729.3499755859375</v>
+        <v>80.23999786376953</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>19995747</v>
+        <v>63360</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.92</v>
+        <v>-5.47</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+          <t>Intense Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Balrampur Exceeds Analyst Target by 5% After India Reverses Sugar Import Policy - TechStock²</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
-        </is>
-      </c>
+          <t>Intense Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3082,68 +3114,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PAKKA.NS</t>
+          <t>AEGISLOG.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PAKKA LIMITED</t>
+          <t>Aegis Logistics Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>88.65000152587891</v>
+        <v>1424.400024414062</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>89.5</v>
+        <v>1438.099975585938</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>83.5</v>
+        <v>1337</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>84.51999664306641</v>
+        <v>1341.5</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>88.69000244140625</v>
+        <v>1417.900024414062</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>84.51999664306641</v>
+        <v>1341.5</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>190999</v>
+        <v>928535</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.7</v>
+        <v>-5.39</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Pakka posts record Q1 2026 revenue, shares jump 8% - Investing.com India</t>
+          <t>Aegis Logistics Ltd. Share Price Today in Top Decliners - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Pakka Limited Confirms No Deviation in Preferential Issue Fund Use - TipRanks</t>
+          <t>Aegis Logistics Ltd. (AEGISLOG) Share Price Rises 3.1% in Today’s Move - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Pakka Ltd. Share Price Decline: Technicals, Peers, Sector - Univest</t>
+          <t>Aegis Logistics Ltd. Share Price Shows Strong Price Action - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>SBI Mutual Fund sells 71,698 Pakka Ltd shares, stake falls to 6.45% - scanx.trade</t>
+          <t>Aegis Logistics Ltd. (AEGISLOG) Share Price Rises 3.1% in Today’s Move - Univest</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Pakka Ltd. Share Price Rise: Paper Stock Price and Analysis - Univest</t>
+          <t>Aegis Logistics Share Price Update: Market Cap and Fall - Univest</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3151,56 +3183,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE.NS</t>
+          <t>STYLEBAAZA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging Limited</t>
+          <t>Baazar Style Retail Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>406.2000122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>425.0499877929688</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>396.7999877929688</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>396.7999877929688</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>417.6499938964844</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.049999952316284</v>
+        <v>396.7999877929688</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>846239</v>
+        <v>1673190</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.65</v>
+        <v>-4.99</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
+          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:02:59 IST</t>
+          <t>2026-08-24 16:33:12 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3208,63 +3252,51 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TAKE.NS</t>
+          <t>ONIXSOLAR.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TAKE Limited</t>
+          <t>Onix Solar Energy Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>22.14999961853027</v>
+        <v>290.6499938964844</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>22.18000030517578</v>
+        <v>290.6499938964844</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20.75</v>
+        <v>290.6499938964844</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>20.82999992370605</v>
+        <v>290.6499938964844</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.84000015258789</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20.82999992370605</v>
+        <v>290.6499938964844</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>515661</v>
+        <v>13015</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.62</v>
+        <v>-4.99</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Take-Two Shares Rebound by 50% From GTA 6 Leak Decline Before Preview Reveal - TechStock²</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>It Won’t Take Much to Burst the Stock Market Bubble - Advisor Perspectives</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Buy or rent a house? Niranjan Hiranandani shares his take on India's housing market: 'Home will never become obsolete' - livemint.com</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Govt to take stock of H1N1 as Karnataka cases cross 4,000 - The Times of India</t>
-        </is>
-      </c>
+          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,56 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RAMBHAJO.NS</t>
+          <t>GENESYS.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Limited</t>
+          <t>Genesys International Corporation Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>180.8500061035156</v>
+        <v>181.3000030517578</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>212.8899993896484</v>
+        <v>214.25</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>180.8500061035156</v>
+        <v>181.3000030517578</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>212.8899993896484</v>
+        <v>214.25</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>177.4100036621094</v>
+        <v>178.5500030517578</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>212.8899993896484</v>
+        <v>214.25</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2520932</v>
+        <v>4165927</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>20</v>
+        <v>19.99</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Genesys International Corp fixes rights issue price at ₹50 for 2.5Cr shares - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Taxes of Genesys International Corporation Limited Rights 2026-21.08.26 For Shares – BSE:GENESYS_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Ltd. Share Price Live Today - CNBC TV18</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -610,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>VIRAT.NS</t>
+          <t>DUCON.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Virat Industries Limited</t>
+          <t>Ducon Infratechnologies Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>465</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>482</v>
+        <v>2.539999961853027</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>452.7999877929688</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>482</v>
+        <v>2.430000066757202</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>401.7000122070312</v>
+        <v>2.175652027130127</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>482</v>
+        <v>2.430000066757202</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>125540</v>
+        <v>2870903</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.99</v>
+        <v>11.69</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Sanat Sangwan shares a partnership with Virat Kohli in the Ranji Trophy - Cricinfo</t>
+          <t>Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Sanat Sangwan shares a partnership with Virat Kohli in the Ranji Trophy - Cricinfo</t>
+          <t>Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
+          <t>Ducon Infratechnologies Wins Contract With India's Largest Aluminium Smelter - Sahi</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>"He Is Like My Brother": PV Sindhu Shares How Virat Kohli Motivated Her During Tough Phase - Sportscape Magazine</t>
+          <t>Ducon Infratechnologies Share Price and Valuation Check - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Virat Industries Approves Acquisition Of 70.28% Shares In Brahm Lifestyle Products - TradingView</t>
+          <t>Ducon Infratechnologies approves rights issue of up to ₹25 Crore - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -679,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MARATHON.NS</t>
+          <t>QUINT.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Marathon Nextgen Realty Limited</t>
+          <t>Quint Digital Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>364</v>
+        <v>42.79000091552734</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>422.7999877929688</v>
+        <v>46</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>361.6000061035156</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>422.7999877929688</v>
+        <v>44.97999954223633</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>352.3500061035156</v>
+        <v>40.5099983215332</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>422.7999877929688</v>
+        <v>44.97999954223633</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3183615</v>
+        <v>22466</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>19.99</v>
+        <v>11.03</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Why is Marathon Digital stock surging today? By Investing.com - Investing.com India</t>
+          <t>Quint Digital Ltd. Share Price Up 10.53%: Full Analysis - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Landscape Capital Management L.L.C. Purchases Shares of 5,091 Marathon Petroleum Corporation $MPC - MarketBeat</t>
+          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Marathon Nextgen Realty confirms no new encumbrance by promoters - scanx.trade</t>
+          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia Acquires Shares of 113,403 Marathon Petroleum Corporation $MPC - MarketBeat</t>
+          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Marathon Petroleum SVP Log &amp; Storage, MPLX GP LLC Sold Shares Worth Over $875K - TradingView</t>
+          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -748,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY.NS</t>
+          <t>APOLLOPIPE.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Limited</t>
+          <t>Apollo Pipes Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9.170000076293945</v>
+        <v>609.25</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>10.52000045776367</v>
+        <v>665</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>9.170000076293945</v>
+        <v>605.0999755859375</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.52000045776367</v>
+        <v>659.8499755859375</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8.770000457763672</v>
+        <v>609.25</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10.52000045776367</v>
+        <v>659.8499755859375</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1630102</v>
+        <v>1323174</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>19.95</v>
+        <v>8.31</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Share Price Today - Super Tannery Stock Analysis - Equitypandit</t>
+          <t>Apollo Pipes appoints Sanjay Gupta as Chairman after AGM approval - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Historical Data - Equitypandit</t>
+          <t>Apollo Pipes Ltd. (APOLLOPIPE) Share Price Within 2% of 52-Week High - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Apollo Pipes Ltd. Share Price Update on Fresh Yearly High - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -817,68 +829,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SHAH.NS</t>
+          <t>IDEA.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Shah Metacorp Limited</t>
+          <t>Vodafone Idea Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.670000076293945</v>
+        <v>14.09000015258789</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.990000009536743</v>
+        <v>15.18000030517578</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3.5</v>
+        <v>14.07999992370605</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3.990000009536743</v>
+        <v>15.09000015258789</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3.329999923706055</v>
+        <v>14.06999969482422</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.990000009536743</v>
+        <v>15.09000015258789</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>7806929</v>
+        <v>995891586</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>19.82</v>
+        <v>7.25</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>What Is Changing At Shah Rukh Khan's Rs 300-Crore Mannat? Anand Pandit Shares Renovation Details - NDTV</t>
+          <t>SBI approves loan share for Vodafone Idea's ₹45,000 crore funding - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Hipolin promoter Rajasvee Sagar Shah sells 9.38% stake in open market - scanx.trade</t>
+          <t>SBI approves loan share for Vodafone Idea's ₹45,000 crore funding - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Hipolin promoter Rajasvee Sagar Shah sells 9.38% stake in open market - scanx.trade</t>
+          <t>Vodafone Idea shares rise 2.04% to Rs 13.99 on Tuesday - TradingView</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
+          <t>Vodafone Idea shares rise nearly 11% in 3 sessions on buzz of tariff hike; should you buy, sell or hold? - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
+          <t>Vodafone Idea shares reverse early gains, Q1 loss narrows - BusinessLine</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,68 +898,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>KOTARISUG.NS</t>
+          <t>TARMAT.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Limited</t>
+          <t>Tarmat Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34.47999954223633</v>
+        <v>50.02999877929688</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39.93999862670898</v>
+        <v>54.93999862670898</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>33.95999908447266</v>
+        <v>49.59999847412109</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>39.15999984741211</v>
+        <v>53.65999984741211</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33.29000091552734</v>
+        <v>50.13999938964844</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>39.15999984741211</v>
+        <v>53.65999984741211</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3630571</v>
+        <v>41829</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>17.63</v>
+        <v>7.02</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Share Price Today at Rs 36.35 - Univest</t>
+          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
+          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars and Chemicals gets NSE no objection for merger with Kothari Petrochemicals - ChiniMandi</t>
+          <t>Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Ltd. (KOTARISUG) Share Price Rises 13.52% Today - Univest</t>
+          <t>Tarmat Ltd. Share Price Drop: Price Action and Sector View - Univest</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
+          <t>Tarmat Ltd announces demise of promoter group member holding 4.19% stake - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,68 +967,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>NAHARINDUS.NS</t>
+          <t>MANAKALUCO.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Nahar Industrial Enterprises Limited</t>
+          <t>Manaksia Aluminium Company Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>127.3499984741211</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>150.7299957275391</v>
+        <v>41.68000030517578</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>125.8000030517578</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>147.6000061035156</v>
+        <v>39.70000076293945</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>125.6100006103516</v>
+        <v>37.2599983215332</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>147.6000061035156</v>
+        <v>39.70000076293945</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>570317</v>
+        <v>127456</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>17.51</v>
+        <v>6.55</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Nahar Industrial Enterprises Share Price after 10.58% gain - Univest</t>
+          <t>Manaksia Aluminium Company Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Nahar Industrial Enterprises Share Price after 10.58% gain - Univest</t>
+          <t>Manaksia Aluminium Board Clears Q1 Results, Sets AGM and Dividend Record Dates - TipRanks</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Nahar Industrial Enterprises Ltd. (NAHARINDUS) Share Price Rises 8.91% Today - Univest</t>
+          <t>Manaksia Aluminium Q1 Results: Net profit rises 83% YoY to ₹2.85 crore - scanx.trade</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Nahar Industrial Enterprises Limited acquired Emerald Logipark Private Limited for INR 0.10 million. - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Nahar Industrial Enterprises Acquires 100% Stake in Emerald Logipark for ₹1,00,000 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Manaksia Aluminium Board Clears Q1 Results, Sets AGM and Dividend Record Dates - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1024,68 +1032,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ratnamani Metals &amp; Tubes Limited</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2354.39990234375</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2777</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2323</v>
+        <v>47.75</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2697</v>
+        <v>51.68000030517578</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2354.39990234375</v>
+        <v>48.59000015258789</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2697</v>
+        <v>51.68000030517578</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>903479</v>
+        <v>3517997</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>14.55</v>
+        <v>6.36</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Ratnamani Metals &amp; Tubes shares jump 18% on securing export orders worth ₹2,700 crore - Upstox</t>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>This mid-cap metal stock zooms 15% on Rs 2,700 crore order announcement; do you own? - Business Today</t>
+          <t>PVPFUN Price Today | Live PVP Price, Chart &amp; Market Data - Binance</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ratnamani Subsidiary Wins ₹2,700 Crore Orders - HDFC Sky</t>
+          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Buzzing stocks: Ratnamani, Quadrant, Shanthi Gears zoom up to 42% in 2 days - Business Standard</t>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Ratnamani Metals shareholders approve ₹10 dividend, reappoint directors - scanx.trade</t>
+          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1093,56 +1101,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>LEENEE.NS</t>
+          <t>RCF.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lee &amp; Nee Softwares Exports Limited</t>
+          <t>Rashtriya Chemicals and Fertilizers Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10.75</v>
+        <v>121</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>11.02000045776367</v>
+        <v>128.5500030517578</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>9.319999694824219</v>
+        <v>120.25</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.5</v>
+        <v>126.0999984741211</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>9.189999580383301</v>
+        <v>119.0299987792969</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10.5</v>
+        <v>126.0999984741211</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>360638</v>
+        <v>14586500</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>14.25</v>
+        <v>5.94</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>RCF Q1 PAT jumps 35% YoY to Rs 74 crore - Business Standard</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Stocks to Watch today: Bajaj Finance, Vedanta, Tata Steel, Dabur, PNB, RCF - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>GAIL and RCF sign MoU for 1.27 MMTPA gas-based fertilizer plant in Maharashtra - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1150,68 +1170,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE.NS</t>
+          <t>GIPCL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Balu Forge Industries Limited</t>
+          <t>Gujarat Industries Power Company Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>568</v>
+        <v>177.3999938964844</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>638</v>
+        <v>189.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>568</v>
+        <v>177.3999938964844</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>632.2000122070312</v>
+        <v>188.8999938964844</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>555.4000244140625</v>
+        <v>178.3899993896484</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>632.2000122070312</v>
+        <v>188.8999938964844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>15539622</v>
+        <v>2290986</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>13.83</v>
+        <v>5.89</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Solid Earnings May Not Tell The Whole Story For Balu Forge Industries (NSE:BALUFORGE) - simplywall.st</t>
+          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Balu Forge Industries Declines 3.98%: Stock Approaches Key Support Level - Dark Pool Prints - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Balu Forge Industries Share Price Rise 8.69% As Company Signs 5-Year MoU For Large Calibre Ammunition Supply - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Balu Forge Industries Limited (NSE:BALUFORGE) Stock's 29% Dive Might Signal An Opportunity But It Requires Some Scrutiny - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>BALUFORGE Q2 2026 Earnings: Revenue Surges 20% YoY, EPS at ₹23.9 - Energy Earnings Report - vinanet.vn</t>
-        </is>
-      </c>
+          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1219,68 +1227,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>NDL.NS</t>
+          <t>JARO.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Nandan Denim Limited</t>
+          <t>Jaro Institute of Technology Management and Research Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.890000104904175</v>
+        <v>450</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3.190000057220459</v>
+        <v>476.3999938964844</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2.859999895095825</v>
+        <v>445.8999938964844</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3.039999961853027</v>
+        <v>468</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2.710000038146973</v>
+        <v>445.2000122070312</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.039999961853027</v>
+        <v>468</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>15635199</v>
+        <v>231791</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>12.18</v>
+        <v>5.12</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+          <t>Jaro Institute of Technology Management and Research Limited Actuals &amp; Estimates (NSE:JARO) - TradingView</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+          <t>Jaro Inst promoter Balkrishna Salunkhe buys 7,390 shares in open market - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Next Digital probe halted - news.gov.hk</t>
+          <t>Jaro Inst promoter acquires 300 equity shares in open market - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
+          <t>Jaro Education shares make muted market debut; later tanks nearly 18 pc - News18</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>NDL Ventures Q1 FY27 Results: Revenue, PAT &amp; Key Highlights - Univest</t>
+          <t>Small-cap stock under ₹500 jumps 5% despite muted trend on Dalal Street - Livemint</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1288,68 +1296,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ATL.NS</t>
+          <t>AWL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Allcargo Terminals Limited</t>
+          <t>AWL Agri Business Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>25.3799991607666</v>
+        <v>194</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>28.18000030517578</v>
+        <v>204.8200073242188</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>24.55999946594238</v>
+        <v>192.9799957275391</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>27.59000015258789</v>
+        <v>203.3899993896484</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24.86000061035156</v>
+        <v>193.8800048828125</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27.59000015258789</v>
+        <v>203.3899993896484</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1310266</v>
+        <v>10755878</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10.98</v>
+        <v>4.91</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value to EBIT forward of Arab Tunisian Lease SA – BVMT:ATL - TradingView</t>
+          <t>Fortune maker AWL piles up edible oil stocks as Middle East, Ukraine wars rattle supply chains: CEO Shrikant Kanhere - ET Retail</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Taking Stock - Adam Stewart On Sandals, Jamaica’s Tourism Industry &amp; ATL’s Caribbean Expansion Rocket Launch Today (fXoWngxf0m) - Mshale</t>
+          <t>Bandhan Small Cap Fund July portfolio: 15 stocks added, 9 exited; HDFC Bank, AWL Agri see higher holdings - TradingView</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Reimagining the passenger journey: ATL Airport on AI, human-centred experiences and the airport as a destination - Future Travel Experience</t>
+          <t>Analyst Estimates: Here's What Brokers Think Of AWL Agri Business Limited (NSE:AWL) After Its First-Quarter Report - simplywall.st</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Taking Stock - Adam Stewart On Sandals, Jamaica’s Tourism Industry &amp; ATL’s Caribbean Expansion Rocket Launch Today (fXoWngxf0m) - Mshale</t>
+          <t>AWL Agri Business Shares Rise 5.82% to Rs 198.50, Among Nifty Midcap 150 Top Gainers - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>AtlantaSanad Revenue Breakdown – CSEMA:ATL - TradingView</t>
+          <t>AWL Agri Business Shares Rise 2.23%; Stock Among Top Gainers on Nifty Midcap 150 - TradingView</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1357,68 +1365,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES.NS</t>
+          <t>DELTACORP.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Max Estates Limited</t>
+          <t>Delta Corp Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>495.3999938964844</v>
+        <v>59.16999816894531</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>559.7999877929688</v>
+        <v>62.2400016784668</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>495.3999938964844</v>
+        <v>58.90000152587891</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>549.1500244140625</v>
+        <v>61.72000122070312</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>494.8500061035156</v>
+        <v>58.88000106811523</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>549.1500244140625</v>
+        <v>61.72000122070312</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1963922</v>
+        <v>2541358</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>10.97</v>
+        <v>4.82</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Max Estates Ltd. (MAXESTATES) Share Price Hits Fresh 52-Week Low - Univest</t>
+          <t>Why Delta's (NSE:DELTACORP) Earnings Are Weaker Than They Seem - simplywall.st</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>You were invited to TradingView - TradingView</t>
+          <t>DELTACORP Mar 2026 Earnings: Steady Performance Amidst Regulatory Landscape - Performance Review - vinanet.vn</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>WEWORK Stock Price and Chart — NSE:WEWORK - TradingView</t>
+          <t>Supreme Court Grants Interim Stay on Rs 1,752.37 crore GST Demand Against Delta Corp - StudyCafe</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Max Estates Ltd. Share Price: Fresh 52-Week High Analysis - Univest</t>
+          <t>Delta Corp's Marvel Resorts to Acquire 74% Stake in Easymile Parking and Shanta Infratech - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>You were invited to TradingView - TradingView</t>
+          <t>Delta Corp Shares Edge Higher at ₹67.15, Key Resistance at ₹70.51 in Focus - Leveraged ETF Flow - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,60 +1434,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE.NS</t>
+          <t>BVCL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited</t>
+          <t>Barak Valley Cements Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>410.0499877929688</v>
+        <v>41.20999908447266</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>464.7999877929688</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>395.5</v>
+        <v>41.20999908447266</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>447.2999877929688</v>
+        <v>43.43999862670898</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>405.3500061035156</v>
+        <v>41.63000106811523</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>447.2999877929688</v>
+        <v>43.43999862670898</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>23856274</v>
+        <v>232091</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10.35</v>
+        <v>4.35</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+          <t>Barak Valley Cements Q1 Results: Net profit rises 19% YoY to ₹3.02 crore - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
-        </is>
-      </c>
+          <t>Barak Valley Cements Q1 Results: Net profit rises 19% YoY to ₹3.02 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1487,64 +1491,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER.NS</t>
+          <t>ABDL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgears Limited</t>
+          <t>Allied Blenders and Distillers Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>328.7000122070312</v>
+        <v>615</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>328.7000122070312</v>
+        <v>643.9000244140625</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>328.7000122070312</v>
+        <v>613.4000244140625</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>328.7000122070312</v>
+        <v>636.1500244140625</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>298.8500061035156</v>
+        <v>610.3499755859375</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>328.7000122070312</v>
+        <v>636.1500244140625</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4808</v>
+        <v>826406</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.99</v>
+        <v>4.23</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
+          <t>ABDL announces its first overseas local production arrangement - Business Standard</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>S&amp;S Power Arm Wins Hitachi Energy Order, Contract Valued At Over ₹8-10 Crore - Free Press Journal</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>S&amp;S Power Arm Wins Hitachi Energy Order, Contract Valued At Over ₹8-10 Crore - Free Press Journal</t>
-        </is>
-      </c>
+          <t>ABDL announces its first overseas local production arrangement - Business Standard</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1552,68 +1548,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MINALIND.NS</t>
+          <t>PARADEEP.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries Limited</t>
+          <t>Paradeep Phosphates Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3.400000095367432</v>
+        <v>150.8000030517578</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3.490000009536743</v>
+        <v>160.6000061035156</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3.400000095367432</v>
+        <v>150.8000030517578</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>3.490000009536743</v>
+        <v>155.7100067138672</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3.180000066757202</v>
+        <v>149.3999938964844</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3.490000009536743</v>
+        <v>155.7100067138672</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>220880</v>
+        <v>31196247</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.75</v>
+        <v>4.22</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
+          <t>Fertiliser Stocks Jump Up To 10% — FACT, Paradeep Phosphates, NFL Gain. Here's Why - NDTV Profit</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+          <t>FACT, Rashtriya Chemicals and Fertilisers, Paradeep Phosphates: Fertiliser shares surge up to 15%; here is why - Upstox</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Free float of Minal Industries Limited – NSE:MINALIND - TradingView</t>
+          <t>FACT, Rashtriya Chemicals and Fertilisers, Paradeep Phosphates: Fertiliser shares surge up to 15%; here is why - Upstox</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries Limited Announces Appointment of Saket Rajendra Sugandh as Company Secretary and Compliance Officer, Effective August 5, 2026 - marketscreener.com</t>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+          <t>News by CNBC TV18 on TradingView, 2026-08-24 — cnbctv:1dafb002e094b:0 - TradingView</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1621,68 +1617,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO.NS</t>
+          <t>EMPOWER.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Limited</t>
+          <t>Empower India Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1125</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1219.949951171875</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1125</v>
+        <v>2.369999885559082</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1199.300048828125</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1098.449951171875</v>
+        <v>2.369999885559082</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1199.300048828125</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4088665</v>
+        <v>5668630</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9.18</v>
+        <v>4.22</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO DIAGNOSTICS LTD Share Price - Upstox</t>
+          <t>Empower India - 11 penny stocks surged up to 198% in 6 months. Do you own any? - The Economic Times</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Ltd. Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+          <t>Empower India shareholders approve Rajesh Chavan as managing director - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Ltd. Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Empower Q2 Results: Base earnings rise 34% to $332 million - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics' shares jump over 21 pc in market debut trade - ET HealthWorld</t>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1690,60 +1686,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER.NS</t>
+          <t>PITTIENG.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PC Jeweller Limited</t>
+          <t>Pitti Engineering Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10.27999973297119</v>
+        <v>1120</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>11.35000038146973</v>
+        <v>1149.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>10.1899995803833</v>
+        <v>1100.5</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>11.11999988555908</v>
+        <v>1143.650024414062</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10.22000026702881</v>
+        <v>1098.25</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>11.11999988555908</v>
+        <v>1143.650024414062</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>686804747</v>
+        <v>361017</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8.81</v>
+        <v>4.13</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+          <t>Pitti Engineering Ltd. Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+          <t>Pitti Engineering Publishes AGM and E-Voting Details for Shareholders - TipRanks</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Penny Stock in Focus: Jewellery Stock Ends Higher After Key Business Update; Should Investors Watch? - Goodreturns</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Pitti Engineering Publishes AGM and E-Voting Details for Shareholders - TipRanks</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Pitti Engineering షేర్: Q1లో అద్భుత వృద్ధి! రెవెన్యూ **16%** పెరిగి **₹529 కోట్లకు**, వాల్యూమ్ **19%** జంప్! - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Pitti Engineering Share Price: FY27ના પ્રથમ ક્વાર્ટરમાં રેવન્યુમાં **16%** નો વધારો, શેર હોલ્ડર્સની વધી દિશા - Whalesbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1751,64 +1755,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SHIVAAGRO.NS</t>
+          <t>DHARMAJ.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Shiva Global Agro Industries Limited</t>
+          <t>Dharmaj Crop Guard Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>41.9900016784668</v>
+        <v>260.6499938964844</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>44.40000152587891</v>
+        <v>271.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>38.65000152587891</v>
+        <v>256.8999938964844</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>42.7599983215332</v>
+        <v>271.2000122070312</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>39.40000152587891</v>
+        <v>260.6499938964844</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42.7599983215332</v>
+        <v>271.2000122070312</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>18088</v>
+        <v>30691</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>4.05</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>SHIVAAGRO Share Price Today - Shiva Global Agro Industries Stock Analysis - Equitypandit</t>
+          <t>Insecticides India vs Dharmaj Crop Guard: Which Agro Stock - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Shiva Global Agro Industries Ltd - Equitypandit</t>
+          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Shiva Global Agro Industries Limited Statistics – NSE:SHIVAAGRO - TradingView</t>
+          <t>Dharmaj Crop Consolidated June 2026 Net Sales at Rs 382.38 crore, up 4.08% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Shiva Global Agro Industries Ltd - Equitypandit</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Dharmaj Crop Standalone June 2026 Net Sales at Rs 384.10 crore, up 4.55% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1816,49 +1824,53 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CLSEL.NS</t>
+          <t>SREEL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Chaman Lal Setia Exports Limited</t>
+          <t>Sreeleathers Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>288.8999938964844</v>
+        <v>248.0500030517578</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>321</v>
+        <v>261.7799987792969</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>288.8999938964844</v>
+        <v>248.0500030517578</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>312.75</v>
+        <v>259.510009765625</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>288.3500061035156</v>
+        <v>249.7100067138672</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>312.75</v>
+        <v>259.510009765625</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2814060</v>
+        <v>28223</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>3.92</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
+          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
+          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Sreeleathers shareholders approve Bhaskar Chatterjee as independent director - scanx.trade</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
@@ -1879,7 +1891,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1985,7 +1997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1993,68 +2005,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>BLS.NS</t>
+          <t>RPTECH.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>BLS International Services Limited</t>
+          <t>Rashi Peripherals Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>272</v>
+        <v>868.3499755859375</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>280.1400146484375</v>
+        <v>878.4500122070312</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>233.4700012207031</v>
+        <v>703.7000122070312</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>241.5099945068359</v>
+        <v>743.1500244140625</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>271.2900085449219</v>
+        <v>867</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>241.5099945068359</v>
+        <v>743.1500244140625</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>29676902</v>
+        <v>1534524</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-10.98</v>
+        <v>-14.28</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>BLS International Share Price Slumps 12% Even As Company Rejects Role In Allegations Of Visa Irregularities - NDTV Profit</t>
+          <t>Rashi Peripherals Limited (NSE:RPTECH) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>BLS International shares fall up to 14% after reports of visa fraud; company rejects claims - TradingView</t>
+          <t>Rashi Peripherals Ltd. Share Price Today - Rashi Peripherals Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>BLS International shares slump nearly 13% after reports of visa fraud; company rejects claims - CNBC TV18</t>
+          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Visa fraud case: Why BLS International shares tanked 13% today; clarification issued - Business Today</t>
+          <t>Pros and Cons of Investing in Rashi Peripherals Share: IT Distributor Analysis 2026 - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>BLS International Shares Plunge 13% On Spanish Visa Probe Report - outlookbusiness.com</t>
+          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits New 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2062,68 +2074,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KJMCFIN.NS</t>
+          <t>KOTARISUG.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited</t>
+          <t>Kothari Sugars And Chemicals Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>82</v>
+        <v>38.59999847412109</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>84.5</v>
+        <v>38.59999847412109</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>71.73000335693359</v>
+        <v>35.25</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.73000335693359</v>
+        <v>35.25</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>79.69999694824219</v>
+        <v>39.15999984741211</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>71.73000335693359</v>
+        <v>35.25</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>19958</v>
+        <v>778688</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-10</v>
+        <v>-9.98</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+          <t>Kothari Sugars And Chemicals Share Price Today at Rs 36.35 - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
+          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
+          <t>Kothari Sugars And Chemicals Ltd. (KOTARISUG) Share Price Rises 13.52% Today - Univest</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+          <t>Kothari Sugars and Chemicals gets NSE no objection for merger with Kothari Petrochemicals - ChiniMandi</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services (NSE:KJMCFIN) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2131,64 +2143,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CRSL.NS</t>
+          <t>KRONOX.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Limited</t>
+          <t>Kronox Lab Sciences Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.509999990463257</v>
+        <v>205.3600006103516</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.559999942779541</v>
+        <v>205.3600006103516</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3.059999942779541</v>
+        <v>185.1000061035156</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3.059999942779541</v>
+        <v>188</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3.390000104904175</v>
+        <v>205.3600006103516</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.059999942779541</v>
+        <v>188</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2362969</v>
+        <v>791879</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.73</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions (CRSL) Share Price Falls 9.73% Today - Univest</t>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions (CRSL) Share Price Falls 9.73% Today - Univest</t>
+          <t>Kronox Lab Sciences schedules 17th AGM for September 16, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Indo Borax to acquire 64.26% stake in Kronox Lab Sciences in Rs 246-crore deal - Indian Chemical News</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Indo Borax to Acquire Stakes in Kronox Lab Sciences - Entrepreneur India</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2196,68 +2212,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>POLYSPIN.NS</t>
+          <t>HINDCOPPER.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Polyspin Exports Limited</t>
+          <t>Hindustan Copper Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>30.96999931335449</v>
+        <v>542</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>30.96999931335449</v>
+        <v>551.8499755859375</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>28.11000061035156</v>
+        <v>529.3499755859375</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>28.29999923706055</v>
+        <v>531.9500122070312</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>30.96999931335449</v>
+        <v>574.1500244140625</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28.29999923706055</v>
+        <v>531.9500122070312</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3255</v>
+        <v>27269605</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-8.619999999999999</v>
+        <v>-7.35</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Polyspin Exports Limited – NSE:POLYSPIN - TradingView</t>
+          <t>Hindustan Copper: Govt to sell up to 6% stake via OFS; check floor price details - Upstox</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+          <t>Govt''s 6% HindCopper Share Sale Begins - Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+          <t>Top stocks in news: TCS, Suzlon, ICICI Bank, HindCopper, Sunshine, Kotak Bank, Afcons, Shankesh - Business Today</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Polyspin Exports consolidated net profit rises 7.14% in the June 2026 quarter - Business Standard</t>
+          <t>Hindustan Copper Share Price Up 3.13% Today - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Shubham Polyspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>HINDCOPPER Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2265,56 +2281,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ORCHASP.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Orchasp Limited</t>
+          <t>Bajaj Hindusthan Sugar Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.440000057220459</v>
+        <v>24.10000038146973</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.440000057220459</v>
+        <v>24.35000038146973</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.259999990463257</v>
+        <v>22.42000007629395</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.289999961853027</v>
+        <v>22.55999946594238</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.409999966621399</v>
+        <v>24.22999954223633</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.289999961853027</v>
+        <v>22.55999946594238</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>799128</v>
+        <v>72632672</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-8.51</v>
+        <v>-6.89</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
+          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Most Active Equities on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2322,68 +2350,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NKIND.NS</t>
+          <t>SAKHTISUG.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited</t>
+          <t>Sakthi Sugars Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>67.58999633789062</v>
+        <v>22</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>67.58999633789062</v>
+        <v>22.56999969482422</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.0099983215332</v>
+        <v>21.14999961853027</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>67.62000274658203</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62.0099983215332</v>
+        <v>21.14999961853027</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>33161</v>
+        <v>353444</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.58</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries (NKIND.NS) Hovers Near ₹59 Amid Narrow Range, Support at ₹56.16 in Focus - Monthly Profile - vinanet.vn</t>
+          <t>Sakthi Sugars Share Price news with sector and peer view - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - vinanet.vn</t>
+          <t>Sakthi Sugars Share Price news with sector and peer view - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited Q2 2026 Earnings: Revenue Declines Sharply on Weak Operational Environment; EPS Turns Negative - Performance Review - vinanet.vn</t>
+          <t>Sakthi Sugars Limited Appoints R. Jeysree to Head the Internal Audit Department(In-House), Effective August 13, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited (NKIND.NS): Marginal Gain Amid Consolidation Near Key Resistance - Dark Pool Prints - vinanet.vn</t>
+          <t>Sakthi Sugars Ltd. Share Price Up 10.82%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited Slips 2.49% as Stock Tests Key Support at ₹62.89 - BPI Bear Correction - vinanet.vn</t>
+          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2391,68 +2419,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO.NS</t>
+          <t>TDPOWERSYS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Limited</t>
+          <t>TD Power Systems Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>165</v>
+        <v>780.2000122070312</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>165</v>
+        <v>782.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>150.6000061035156</v>
+        <v>733.4000244140625</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>153.5299987792969</v>
+        <v>739</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>166.1100006103516</v>
+        <v>780.0999755859375</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>153.5299987792969</v>
+        <v>739</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>49408</v>
+        <v>1130167</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.57</v>
+        <v>-5.27</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
+          <t>Why Did TD Power Systems Shares Crash 50% Today? Check the Reason - Trade Brains</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>TDPOWERSYS: Revenue and profit surged year-over-year, with robust EPS and improved margins - TradingView</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Cyclically Adjusted PB Ratio : (As of Aug. 20, 2026) - GuruFocus</t>
+          <t>Interested In TD Power Systems' (NSE:TDPOWERSYS) Upcoming ₹1.10 Dividend? You Have One Day Left - simplywall.st</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
+          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2460,56 +2488,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RVHL.NS</t>
+          <t>ELITECON.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ravinder Heights Limited</t>
+          <t>Elitecon International Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>43.02000045776367</v>
+        <v>15.19999980926514</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>43.79999923706055</v>
+        <v>15.47999954223633</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39</v>
+        <v>14.39999961853027</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>39.91999816894531</v>
+        <v>14.39999961853027</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>43.02000045776367</v>
+        <v>15.1899995803833</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39.91999816894531</v>
+        <v>14.39999961853027</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>40751</v>
+        <v>1197314</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-7.21</v>
+        <v>-5.2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Ravinder Heights Q1 Results: Q1FY27 Financials Filed With Exchanges - scanx.trade</t>
+          <t>Elitecon appoints Vipin Sharma and Pradeep Kumar as Executive Directors - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Ravinder Heights Q1 Results: Q1FY27 Financials Filed With Exchanges - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Elitecon appoints Vipin Sharma and Pradeep Kumar as Executive Directors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Small-cap stock under ₹50 Elitecon International hits 10% upper circuit for second day in a row - Livemint</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Elitecon International: Kumar Anubhav Upadhyay ceases as Additional Director - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2517,68 +2557,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COMPUSOFT.NS</t>
+          <t>TAKE.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Compucom Software Limited</t>
+          <t>TAKE Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.97999954223633</v>
+        <v>19.04999923706055</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>14.10000038146973</v>
+        <v>19.29000091552734</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>12.3100004196167</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>13.03999996185303</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13.97999954223633</v>
+        <v>19.79000091552734</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13.03999996185303</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>101907</v>
+        <v>123313</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-6.72</v>
+        <v>-4.95</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Compucom Software publishes 32nd AGM notice for Sept 9 meeting - scanx.trade</t>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Compucom Software publishes 32nd AGM notice for Sept 9 meeting - scanx.trade</t>
+          <t>Take-Two's Twin Headwinds: A Leak Offensive and a Stock That Analysts Refuse to Abandon - Ad-hoc-news.de</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ROXHITECH Stock Price and Chart — NSE:ROXHITECH - TradingView</t>
+          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Compucom Software Q1 Results: Unaudited financials approved by Board - scanx.trade</t>
+          <t>Woman shares emotional moment as parents take first-ever flight: ‘Life has come full circle’ | Trending - Hindustan Times</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Compucom Software publishes 32nd AGM newspaper notice for September 9 - scanx.trade</t>
+          <t>Delhi: Swine Flu Cases On The Rise, High-level Meeting To Take Stock - ETV Bharat</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2586,60 +2626,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT.NS</t>
+          <t>ATLANTAELE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Ahluwalia Contracts (India) Limited</t>
+          <t>Atlanta Electricals Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>688</v>
+        <v>1801</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>690</v>
+        <v>1812</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>645.2999877929688</v>
+        <v>1725.099975585938</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>649.5999755859375</v>
+        <v>1733.699951171875</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>696.2000122070312</v>
+        <v>1819.5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>649.5999755859375</v>
+        <v>1733.699951171875</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>316763</v>
+        <v>68111</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-6.69</v>
+        <v>-4.72</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Ahluwalia Contracts trades higher after winning orders worth ₹1,307 crore - Upstox</t>
+          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Stocks to Buy: 5 Stocks That Can Deliver Returns of Up to 54%; Do You Own Any? - Trade Brains</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Stocks to Buy: 5 Stocks That Can Deliver Returns of Up to 54%; Do You Own Any? - Trade Brains</t>
-        </is>
-      </c>
+          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2647,68 +2683,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CRAVATEX.NS</t>
+          <t>GRADIENTE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Cravatex Limited</t>
+          <t>Gradiente Infotainment Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>359</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>359</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>335</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>337.1000061035156</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>359</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>337.1000061035156</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>131</v>
+        <v>1949939</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.1</v>
+        <v>-4.7</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>CRAVATEX Share Price Today - Cravatex Stock Analysis - Equitypandit</t>
+          <t>Gradiente Infotainment Considers Capital Raising Initiatives in Board Meeting - Sahi</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Cravatex (NSE:CRAVATEX) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Gradiente Asian Fashion Tour India - Mumbai Curtain Raiser Marks the 25th Season with Fashion, Glamour and New Talent - Big News Network.com</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Cravatex (NSE:CRAVATEX) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Gradiente Infotainment approves ₹65 Cr capex for micro dramas and music videos - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Cravatex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Price Band Hitters, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Cravatex Q1FY27 consolidated profit turns positive, revenue up 39% - scanx.trade</t>
+          <t>Major Push for the Orange Economy: Gradiente Infotainment Unveils ₹5,000 Crore Mega Investment Roadmap - The Tribune</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2716,68 +2752,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BRAHMINFRA.NS</t>
+          <t>GANGAFORGE.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Brahmaputra Infrastructure Limited</t>
+          <t>Ganga Forging Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>160</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>167.3800048828125</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>151.1999969482422</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>154.2400054931641</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>164.1499938964844</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>154.2400054931641</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>78920</v>
+        <v>18057141</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.04</v>
+        <v>-4.62</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Brahmaputra Infrastructure Ltd. – NSE:BRAHMINFRA - TradingView</t>
+          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Brahmaputra Infrastructure Signs ₹70.18 Cr NH-502A Maintenance Contract in Mizoram - Trade Brains</t>
+          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Brahmaputra Infrastructure (NSE:BRAHMINFRA) Cyclically Adju - GuruFocus</t>
+          <t>Ganga Forging opens Rights Issue at ₹1.63 per share - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Brahmaputra Infrastructure Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Brahmaputra Infra Secures ₹71 Crore Contract with Market Capitalization at ₹470 Crore - Sahi</t>
-        </is>
-      </c>
+          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2785,68 +2817,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SVGLOBAL.NS</t>
+          <t>DATAPATTNS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Limited</t>
+          <t>Data Patterns (India) Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>125</v>
+        <v>4730</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>125</v>
+        <v>4768.7001953125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>115.0100021362305</v>
+        <v>4500.10009765625</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>118</v>
+        <v>4522</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>125.2600021362305</v>
+        <v>4736.2001953125</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>118</v>
+        <v>4522</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>345</v>
+        <v>845786</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.8</v>
+        <v>-4.52</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
+          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill board to consider physical share cancellation scheme - scanx.trade</t>
+          <t>Defence stock with Rs 2,654-crore order book hits record high; here's why - Business Today</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill (NSE:SVGLOBAL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Data Patterns shares collapse 7% as Q1FY27 earnings show subdued performance - Upstox</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill board to consider physical share cancellation scheme - scanx.trade</t>
+          <t>Data Patterns Share Price Today: Stock Rises 3.11% - Univest</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Limited Announces Resignation of B. Parameswar as Key Managerial Personnel, Effective August 3, 2026 - marketscreener.com</t>
+          <t>Data Patterns (India) Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2854,68 +2886,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>MPSLTD.NS</t>
+          <t>RANASUG.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MPS Limited</t>
+          <t>Rana Sugars Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2870</v>
+        <v>15.77999973297119</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2903.89990234375</v>
+        <v>16.19000053405762</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2705.89990234375</v>
+        <v>15.01000022888184</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>2734.800048828125</v>
+        <v>15.19999980926514</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2897.89990234375</v>
+        <v>15.92000007629395</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2734.800048828125</v>
+        <v>15.19999980926514</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>42608</v>
+        <v>670550</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5.63</v>
+        <v>-4.52</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>MPS Limited Amends Share Subscription and Shareholders' Agreement with MPSi and Rodney Charles Beach - scanx.trade</t>
+          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>MPS Ltd shareholders approve ADI BPO amalgamation with 99.99% support - scanx.trade</t>
+          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Taurian MPS Limited Share Price Rises 8.16% Today - Univest</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>MPS issues addendum on ADI BPO merger, confirms no public dilution - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>MPS Ltd Q1FY27 net profit rises 43% to ₹50.39 cr on margin expansion - scanx.trade</t>
-        </is>
-      </c>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2923,68 +2947,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DCMFINSERV.NS</t>
+          <t>KMSUGAR.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DCM Financial Services Limited</t>
+          <t>K.M.Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5.429999828338623</v>
+        <v>34.04000091552734</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>5.429999828338623</v>
+        <v>35</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5.099999904632568</v>
+        <v>31.1200008392334</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>5.130000114440918</v>
+        <v>32.54999923706055</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5.429999828338623</v>
+        <v>34.04999923706055</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.130000114440918</v>
+        <v>32.54999923706055</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>26143</v>
+        <v>370950</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.52</v>
+        <v>-4.41</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>K.M. Sugar Mills Share Price rises 8.17%: valuation, peers - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
+          <t>K.M. Sugar Mills Share Price rises 8.17%: valuation, peers - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Dcm Financial Services Limited Announces Resignation of Richa Kathuria as Independent Director, Member of the Audit Committee, Nomination and Remuneration Committee and Stakeholders Relationship Committee, Effective August 11, 2026 - marketscreener.com</t>
+          <t>K.M. Sugar Mills Ltd. Share Price Today With Fundamentals - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
+          <t>K.M. Sugar Mills Ltd. Share Price Rise With Valuation View - Univest</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Lagarde Leaves Door Open to Early ECB Exit Amid French Political Speculation - High Estimate Range - vinanet.vn</t>
+          <t>Keysight Technologies (KEYS) Slips 1.5% as Shares Hold Above Key Support - Earnings Breakout Stocks - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2992,64 +3016,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>REGENCERAM.NS</t>
+          <t>NETWEB.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Regency Ceramics Limited</t>
+          <t>Netweb Technologies India Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>36</v>
+        <v>5400</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>36.09999847412109</v>
+        <v>5413.2001953125</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>33.5099983215332</v>
+        <v>5208</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>5220</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>35.90999984741211</v>
+        <v>5454.5</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>33.93000030517578</v>
+        <v>5220</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>6418</v>
+        <v>1241468</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.51</v>
+        <v>-4.3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Regency Ceramics Ltd. Share Price Fall and Stock Analysis - Univest</t>
+          <t>Netweb Technologies shares fall over 3% after Rs 1,200 crore QIP - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Regency Ceramics Ltd. Share Price Fall and Stock Analysis - Univest</t>
+          <t>Netweb Technologies shares fall 4% after raising Rs 1,200 crore through QIP - The Economic Times</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Regency Ceramics Q1 Results: Revenue up 173% YoY, net loss narrows - scanx.trade</t>
+          <t>Netweb Technologies shares fall 4% after raising Rs 1,200 crore through QIP - The Economic Times</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Regency Ceramics Publishes June-Quarter Unaudited Results in Leading Dailies - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Netweb Tech raises Rs 1,200 crore via QIP; stock falls for 2nd day, down 4% - Business Today</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Netweb Tech Raises ₹1,200 Crore By Issuing 25,05,219 Equity Shares At ₹4,790 Each - Sahi</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3057,56 +3085,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>INTENTECH.NS</t>
+          <t>IIFL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Intense Technologies Limited</t>
+          <t>IIFL Finance Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>83.19999694824219</v>
+        <v>667</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>87</v>
+        <v>681.0999755859375</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>79</v>
+        <v>643.5499877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>80.23999786376953</v>
+        <v>670.2999877929688</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>84.87999725341797</v>
+        <v>696.4000244140625</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>80.23999786376953</v>
+        <v>670.2999877929688</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>63360</v>
+        <v>6270881</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.47</v>
+        <v>-3.75</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Intense Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>IIFL Finance shares decline over 7% after home finance arm receives ₹963 crore income tax demand notice; here's why - Upstox</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Intense Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>IFL Finance shares drop 8% as IIFL Home Finance gets Rs 963 crore tax demand - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares fall 4% after subsidiary faces Rs 963 crore tax demand - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares crack 8% after ₹963-crore tax demand for subsidiary - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares fall nearly 8% after receiving tax demand of ₹963 crore for home finance arm - CNBC TV18</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3114,68 +3154,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AEGISLOG.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Aegis Logistics Limited</t>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1424.400024414062</v>
+        <v>285</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1438.099975585938</v>
+        <v>285.3999938964844</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1337</v>
+        <v>274.0499877929688</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1341.5</v>
+        <v>275.5</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1417.900024414062</v>
+        <v>286.2000122070312</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1341.5</v>
+        <v>275.5</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>928535</v>
+        <v>498776</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.39</v>
+        <v>-3.74</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd. Share Price Today in Top Decliners - Univest</t>
+          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd. (AEGISLOG) Share Price Rises 3.1% in Today’s Move - Univest</t>
+          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd. Share Price Shows Strong Price Action - Univest</t>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd. (AEGISLOG) Share Price Rises 3.1% in Today’s Move - Univest</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Aegis Logistics Share Price Update: Market Cap and Fall - Univest</t>
-        </is>
-      </c>
+          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3183,68 +3219,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>STYLEBAAZA.NS</t>
+          <t>VOLTAMP.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Limited</t>
+          <t>Voltamp Transformers Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>406.2000122070312</v>
+        <v>11382.5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>425.0499877929688</v>
+        <v>11400</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>396.7999877929688</v>
+        <v>10670</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>396.7999877929688</v>
+        <v>10875</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>417.6499938964844</v>
+        <v>11292</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>396.7999877929688</v>
+        <v>10875</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1673190</v>
+        <v>41420</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.99</v>
+        <v>-3.69</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
+          <t>Voltamp Transformers Share Price today: price, valuation - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+          <t>Voltamp Transformers Share Price today: price, valuation - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+          <t>Voltamp Transformers posts ₹912M profit in Q1FY27, updates capex plan - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
+          <t>Voltamp Trans Standalone June 2026 Net Sales at Rs 543.78 crore, up 28.38% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
+          <t>Voltamp Transformers declares ₹100 final dividend per share for FY26 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:33:12 IST</t>
+          <t>2026-08-25 12:50:15 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3252,51 +3288,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ONIXSOLAR.NS</t>
+          <t>RAIN.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Onix Solar Energy Limited</t>
+          <t>Rain Industries Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>290.6499938964844</v>
+        <v>213.8899993896484</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>290.6499938964844</v>
+        <v>213.8899993896484</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>290.6499938964844</v>
+        <v>204.0099945068359</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>290.6499938964844</v>
+        <v>205.8999938964844</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>213.6900024414062</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>290.6499938964844</v>
+        <v>205.8999938964844</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>13015</v>
+        <v>2272466</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.99</v>
+        <v>-3.65</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
+          <t>"2 Hours 15 Minutes In Traffic": Man Shares How Rain Affected His Commute To Bengaluru Airport - NDTV</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>RAIN Should I Buy - Intellectia AI</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Just Three Days Till Rain Industries Limited (NSE:RAIN) Will Be Trading Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -446,7 +446,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -580,41 +580,41 @@
         <v>214.25</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4165927</v>
+        <v>4189199</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>19.99</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Genesys International Corp fixes rights issue price at ₹50 for 2.5Cr shares - scanx.trade</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
-        </is>
-      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
+          <t>Genesys International Corporation Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
           <t>Taxes of Genesys International Corporation Limited Rights 2026-21.08.26 For Shares – BSE:GENESYS_RE - TradingView</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Genesys International Corporation Ltd. Share Price Live Today - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -640,38 +640,38 @@
         <v>2.210000038146973</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.430000066757202</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>2.175652027130127</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.430000066757202</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2870903</v>
+        <v>3670210</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>11.69</v>
+        <v>10.31</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
+          <t>Ducon Infratechnologies Ltd. Share Price Today: 11.98% Gain - Univest</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Ltd. Share Price Today: 11.98% Gain - Univest</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
           <t>Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Ducon Infratechnologies Wins Contract With India's Largest Aluminium Smelter - Sahi</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Ducon Infratechnologies Share Price and Valuation Check - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>QUINT.NS</t>
+          <t>TARMAT.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Limited</t>
+          <t>Tarmat Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>42.79000091552734</v>
+        <v>50.02999877929688</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46</v>
+        <v>55.45000076293945</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>39.97000122070312</v>
+        <v>49.59999847412109</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>44.97999954223633</v>
+        <v>54.22999954223633</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40.5099983215332</v>
+        <v>50.13999938964844</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>44.97999954223633</v>
+        <v>54.22999954223633</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>22466</v>
+        <v>96996</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>11.03</v>
+        <v>8.16</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Ltd. Share Price Up 10.53%: Full Analysis - Univest</t>
+          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
+          <t>Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
+          <t>Tarmat Ltd Downgraded to Sell by MarketsMOJO Amid Mixed Financial and Technical Signals - marketsmojo.com</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+          <t>Tarmat Ltd. Share Price Drop: Price Action and Sector View - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>APOLLOPIPE.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes Limited</t>
+          <t>Cyient Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>609.25</v>
+        <v>909</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>665</v>
+        <v>989</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>605.0999755859375</v>
+        <v>898.6500244140625</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>659.8499755859375</v>
+        <v>979.0499877929688</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>609.25</v>
+        <v>909.0499877929688</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>659.8499755859375</v>
+        <v>979.0499877929688</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1323174</v>
+        <v>4712452</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>8.31</v>
+        <v>7.7</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes appoints Sanjay Gupta as Chairman after AGM approval - scanx.trade</t>
+          <t>Cyient DLM Ltd. (CYIENTDLM) Share Price Hits Fresh 52-Week High at Rs 768.95 - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
+          <t>Top Gainers &amp; Losers on 25 Aug: FACT, Vodafone Idea, Cyient, Paytm, Angel One, Pine Labs among top gainers - Livemint</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
+          <t>Top Gainers &amp; Losers on 25 Aug: FACT, Vodafone Idea, Cyient, Paytm, Angel One, Pine Labs among top gainers - Livemint</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes Ltd. (APOLLOPIPE) Share Price Within 2% of 52-Week High - Univest</t>
+          <t>Stocks to Watch Today, August 25, 2026: Cyient, Great Eastern Shipping Company, Tata Consultancy Services, Pace Digitek and Chemplast Sanmar - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes Ltd. Share Price Update on Fresh Yearly High - Univest</t>
+          <t>HAL shares gain up to 1% after NCLT dissolves joint venture with Cyient - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,68 +829,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IDEA.NS</t>
+          <t>INVENTURE.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea Limited</t>
+          <t>Inventure Growth &amp; Securities Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.09000015258789</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15.18000030517578</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>14.07999992370605</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>15.09000015258789</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14.06999969482422</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15.09000015258789</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>995891586</v>
+        <v>2156001</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>7.25</v>
+        <v>7.06</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SBI approves loan share for Vodafone Idea's ₹45,000 crore funding - scanx.trade</t>
+          <t>Inventure Grow Standalone June 2026 Net Sales at Rs 10.67 crore, down 26.91% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>SBI approves loan share for Vodafone Idea's ₹45,000 crore funding - scanx.trade</t>
+          <t>Inventure Growth &amp; Securities posts ₹4.61 crore profit in Q1FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea shares rise 2.04% to Rs 13.99 on Tuesday - TradingView</t>
+          <t>Inventure Growth &amp; Securities withdraws scheme after RBI denial - scanx.trade</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea shares rise nearly 11% in 3 sessions on buzz of tariff hike; should you buy, sell or hold? - Moneycontrol.com</t>
+          <t>Inventure Grow Consolidated June 2026 Net Sales at Rs 13.16 crore, down 23.98% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea shares reverse early gains, Q1 loss narrows - BusinessLine</t>
+          <t>Andriy Verevskyi Begins Kernel Share Buyout Ahead of Warsaw Stock Exchange Delisting - Inventure.com.ua.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -898,68 +898,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TARMAT.NS</t>
+          <t>GIPCL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Limited</t>
+          <t>Gujarat Industries Power Company Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50.02999877929688</v>
+        <v>177.3999938964844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>54.93999862670898</v>
+        <v>191.25</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>49.59999847412109</v>
+        <v>177.3999938964844</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>53.65999984741211</v>
+        <v>190.7200012207031</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>50.13999938964844</v>
+        <v>178.3899993896484</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>53.65999984741211</v>
+        <v>190.7200012207031</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>41829</v>
+        <v>3502664</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>7.02</v>
+        <v>6.91</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
+          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Tarmat Ltd. Share Price Drop: Price Action and Sector View - Univest</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Tarmat Ltd announces demise of promoter group member holding 4.19% stake - scanx.trade</t>
-        </is>
-      </c>
+          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -967,64 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MANAKALUCO.NS</t>
+          <t>PARADEEP.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Aluminium Company Limited</t>
+          <t>Paradeep Phosphates Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>150.8000030517578</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41.68000030517578</v>
+        <v>160.6000061035156</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>150.8000030517578</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>39.70000076293945</v>
+        <v>159.6300048828125</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37.2599983215332</v>
+        <v>149.3999938964844</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>39.70000076293945</v>
+        <v>159.6300048828125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>127456</v>
+        <v>51528268</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.55</v>
+        <v>6.85</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Aluminium Company Share Price: Price Rise Analysis - Univest</t>
+          <t>Fertiliser Stocks Jump Up To 10% — FACT, Paradeep Phosphates, NFL Gain. Here's Why - NDTV Profit</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Aluminium Board Clears Q1 Results, Sets AGM and Dividend Record Dates - TipRanks</t>
+          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - BusinessToday - India IPO</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Aluminium Q1 Results: Net profit rises 83% YoY to ₹2.85 crore - scanx.trade</t>
+          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - Business Today</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Aluminium Board Clears Q1 Results, Sets AGM and Dividend Record Dates - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - BusinessToday - India IPO</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1032,68 +1024,64 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>SHREEPUSHK.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Limited</t>
+          <t>Shree Pushkar Chemicals &amp; Fertilisers Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>48</v>
+        <v>427.5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>52</v>
+        <v>459.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>47.75</v>
+        <v>424.0499877929688</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>51.68000030517578</v>
+        <v>454.1000061035156</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>48.59000015258789</v>
+        <v>426.8999938964844</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.68000030517578</v>
+        <v>454.1000061035156</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3517997</v>
+        <v>258193</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6.36</v>
+        <v>6.37</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+          <t>Shree Pushkar Chemicals &amp; Fertilisers Limited Announces Board Changes, Effective August 13, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>PVPFUN Price Today | Live PVP Price, Chart &amp; Market Data - Binance</t>
+          <t>Shree Pushkar Chemicals &amp; Fertilisers Adds 10 MW Solar Capacity in Maharashtra - marketscreener.com</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+          <t>Shree Pushkar Chemicals Q1 Results: Earnings call set for Aug 13 - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
-        </is>
-      </c>
+          <t>Shree Pushkar Chemicals &amp; Fertilisers Adds 10 MW Solar Capacity in Maharashtra - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1101,68 +1089,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>RCF.NS</t>
+          <t>TFCILTD.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Rashtriya Chemicals and Fertilizers Limited</t>
+          <t>Tourism Finance Corporation of India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>128.5500030517578</v>
+        <v>137.9400024414062</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>120.25</v>
+        <v>129.2200012207031</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>126.0999984741211</v>
+        <v>137.0200042724609</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>119.0299987792969</v>
+        <v>129.5599975585938</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>126.0999984741211</v>
+        <v>137.0200042724609</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>14586500</v>
+        <v>20325175</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5.94</v>
+        <v>5.76</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+          <t>LIC confirms no fresh encumbrance on TFCI shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+          <t>LIC confirms no fresh encumbrance on TFCI shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>RCF Q1 PAT jumps 35% YoY to Rs 74 crore - Business Standard</t>
+          <t>Tourism Finance Corporation Of India Ltd. (TFCILTD) Share Price Hits Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Stocks to Watch today: Bajaj Finance, Vedanta, Tata Steel, Dabur, PNB, RCF - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>GAIL and RCF sign MoU for 1.27 MMTPA gas-based fertilizer plant in Maharashtra - scanx.trade</t>
-        </is>
-      </c>
+          <t>Tourism Finance Corporation Of India Ltd. Share Price Near - Univest</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1170,56 +1154,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>GIPCL.NS</t>
+          <t>NECLIFE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Industries Power Company Limited</t>
+          <t>Nectar Lifesciences Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>177.3999938964844</v>
+        <v>10.72000026702881</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>189.5</v>
+        <v>11.4399995803833</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>177.3999938964844</v>
+        <v>10.72000026702881</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>188.8999938964844</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>178.3899993896484</v>
+        <v>10.72000026702881</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>188.8999938964844</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2290986</v>
+        <v>317808</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5.89</v>
+        <v>5.69</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
+          <t>Nectar Lifesciences Limited Changes Its Corporate Office in Chandigarh - marketscreener.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1227,68 +1219,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>JARO.NS</t>
+          <t>BALAMINES.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Jaro Institute of Technology Management and Research Limited</t>
+          <t>Balaji Amines Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>450</v>
+        <v>2241.60009765625</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>476.3999938964844</v>
+        <v>2390</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>445.8999938964844</v>
+        <v>2205.300048828125</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>468</v>
+        <v>2343.60009765625</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>445.2000122070312</v>
+        <v>2224.5</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>468</v>
+        <v>2343.60009765625</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>231791</v>
+        <v>600301</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.12</v>
+        <v>5.35</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Jaro Institute of Technology Management and Research Limited Actuals &amp; Estimates (NSE:JARO) - TradingView</t>
+          <t>Balaji Amines Share Price news: Rs 2,210.70 and sector view - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Jaro Inst promoter Balkrishna Salunkhe buys 7,390 shares in open market - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Jaro Inst promoter acquires 300 equity shares in open market - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Jaro Education shares make muted market debut; later tanks nearly 18 pc - News18</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Small-cap stock under ₹500 jumps 5% despite muted trend on Dalal Street - Livemint</t>
-        </is>
-      </c>
+          <t>Balaji Amines Share Price news: Rs 2,210.70 and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1296,68 +1276,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AWL.NS</t>
+          <t>JARO.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AWL Agri Business Limited</t>
+          <t>Jaro Institute of Technology Management and Research Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>194</v>
+        <v>450</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>204.8200073242188</v>
+        <v>476.3999938964844</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>192.9799957275391</v>
+        <v>445.8999938964844</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>203.3899993896484</v>
+        <v>468.5499877929688</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>193.8800048828125</v>
+        <v>445.2000122070312</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>203.3899993896484</v>
+        <v>468.5499877929688</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>10755878</v>
+        <v>344015</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>4.91</v>
+        <v>5.24</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Fortune maker AWL piles up edible oil stocks as Middle East, Ukraine wars rattle supply chains: CEO Shrikant Kanhere - ET Retail</t>
+          <t>Jaro Institute of Technology Management and Research Limited Actuals &amp; Estimates (NSE:JARO) - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bandhan Small Cap Fund July portfolio: 15 stocks added, 9 exited; HDFC Bank, AWL Agri see higher holdings - TradingView</t>
+          <t>Jaro Inst promoter Balkrishna Salunkhe buys 7,390 shares in open market - scanx.trade</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Analyst Estimates: Here's What Brokers Think Of AWL Agri Business Limited (NSE:AWL) After Its First-Quarter Report - simplywall.st</t>
+          <t>Jaro Inst promoter acquires 300 equity shares in open market - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>AWL Agri Business Shares Rise 5.82% to Rs 198.50, Among Nifty Midcap 150 Top Gainers - Moneycontrol.com</t>
+          <t>Jaro Education shares make muted market debut; later tanks nearly 18 pc - News18</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>AWL Agri Business Shares Rise 2.23%; Stock Among Top Gainers on Nifty Midcap 150 - TradingView</t>
+          <t>Small-cap stock under ₹500 jumps 5% despite muted trend on Dalal Street - Livemint</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1365,68 +1345,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP.NS</t>
+          <t>CEWATER.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited</t>
+          <t>Concord Enviro Systems Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>59.16999816894531</v>
+        <v>253.5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>62.2400016784668</v>
+        <v>271.3999938964844</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>58.90000152587891</v>
+        <v>251.9499969482422</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.72000122070312</v>
+        <v>265.4500122070312</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>58.88000106811523</v>
+        <v>253.1499938964844</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>61.72000122070312</v>
+        <v>265.4500122070312</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2541358</v>
+        <v>219118</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4.82</v>
+        <v>4.86</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Why Delta's (NSE:DELTACORP) Earnings Are Weaker Than They Seem - simplywall.st</t>
+          <t>Investors Aren't Entirely Convinced By Concord Enviro Systems Limited's (NSE:CEWATER) Earnings - simplywall.st</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP Mar 2026 Earnings: Steady Performance Amidst Regulatory Landscape - Performance Review - vinanet.vn</t>
+          <t>Concord Enviro Systems (CEWATER.NS) Gains 3.43% – Bulls Defend Key Support at ₹366.8 - Double Bottom - vinanet.vn</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Supreme Court Grants Interim Stay on Rs 1,752.37 crore GST Demand Against Delta Corp - StudyCafe</t>
+          <t>CONCORD ENVIRO SYSTEMS L Share Price - Upstox</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp's Marvel Resorts to Acquire 74% Stake in Easymile Parking and Shanta Infratech - scanx.trade</t>
+          <t>Concord Enviro Systems Limited Announces Equity Shareholders Meeting for Scheme of Arrangement Approval - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Shares Edge Higher at ₹67.15, Key Resistance at ₹70.51 in Focus - Leveraged ETF Flow - vinanet.vn</t>
+          <t>CEWATER Mar 2026 Earnings: Strong EPS of ₹2.06 on Revenue of ₹17.64 Crore; Stock Gains 3.35% - Mid-Term Outlook - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1434,56 +1414,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BVCL.NS</t>
+          <t>RCF.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Barak Valley Cements Limited</t>
+          <t>Rashtriya Chemicals and Fertilizers Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>41.20999908447266</v>
+        <v>121</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>44.40000152587891</v>
+        <v>128.5500030517578</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>41.20999908447266</v>
+        <v>120.25</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>43.43999862670898</v>
+        <v>124.4700012207031</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>41.63000106811523</v>
+        <v>119.0299987792969</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>43.43999862670898</v>
+        <v>124.4700012207031</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>232091</v>
+        <v>18084974</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4.35</v>
+        <v>4.57</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Barak Valley Cements Q1 Results: Net profit rises 19% YoY to ₹3.02 crore - scanx.trade</t>
+          <t>Why did FACT, RCF, NFL and other fertiliser stocks rally up to 14% today? Explained - Livemint</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Barak Valley Cements Q1 Results: Net profit rises 19% YoY to ₹3.02 crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Why did FACT, RCF, NFL and other fertiliser stocks rally up to 14% today? Explained - Livemint</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>RCF Q1 PAT jumps 35% YoY to Rs 74 crore - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Stocks to Watch today: Bajaj Finance, Vedanta, Tata Steel, Dabur, PNB, RCF - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1491,56 +1483,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ABDL.NS</t>
+          <t>IREDA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Allied Blenders and Distillers Limited</t>
+          <t>Indian Renewable Energy Development Agency Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>615</v>
+        <v>115</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>643.9000244140625</v>
+        <v>121.1399993896484</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>613.4000244140625</v>
+        <v>114.4000015258789</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>636.1500244140625</v>
+        <v>120.6100006103516</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>610.3499755859375</v>
+        <v>115.4000015258789</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>636.1500244140625</v>
+        <v>120.6100006103516</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>826406</v>
+        <v>11092821</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.23</v>
+        <v>4.51</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>ABDL announces its first overseas local production arrangement - Business Standard</t>
+          <t>Stocks to watch: Reliance Industries, Power Grid, IREDA among shares to be in focus today. Details here - Livemint</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>ABDL announces its first overseas local production arrangement - Business Standard</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Stocks to watch: Reliance Industries, Power Grid, IREDA among shares to be in focus today. Details here - Livemint</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>IREDA Q1 Results 2027: Revenue Rises 16% YoY to ₹2,249 Cr, PAT Jumps 37% to ₹339 Cr - Sahi</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Dividend Delight! THIS Navratna PSU To Pay 6% Dividend; Stock Up 4%: How To Get Eligible Before Record Date? - Goodreturns</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Buy, Sell Or Hold: Suzlon, HDFC Bank, Colgate, Torrent Pharma And IREDA — Ask Profit - NDTV Profit</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1548,68 +1552,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP.NS</t>
+          <t>DELTACORP.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Paradeep Phosphates Limited</t>
+          <t>Delta Corp Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>150.8000030517578</v>
+        <v>59.16999816894531</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>160.6000061035156</v>
+        <v>62.2400016784668</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>150.8000030517578</v>
+        <v>58.90000152587891</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>155.7100067138672</v>
+        <v>61.52000045776367</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>149.3999938964844</v>
+        <v>58.88000106811523</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>155.7100067138672</v>
+        <v>61.52000045776367</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>31196247</v>
+        <v>3353931</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.22</v>
+        <v>4.48</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Fertiliser Stocks Jump Up To 10% — FACT, Paradeep Phosphates, NFL Gain. Here's Why - NDTV Profit</t>
+          <t>DELTACORP Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>FACT, Rashtriya Chemicals and Fertilisers, Paradeep Phosphates: Fertiliser shares surge up to 15%; here is why - Upstox</t>
+          <t>DELTACORP Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>FACT, Rashtriya Chemicals and Fertilisers, Paradeep Phosphates: Fertiliser shares surge up to 15%; here is why - Upstox</t>
+          <t>Delta Corp Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-24 — cnbctv:1dafb002e094b:0 - TradingView</t>
-        </is>
-      </c>
+          <t>Delta Corp Publishes AGM, Book Closure and E-Voting Notice - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1617,68 +1617,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER.NS</t>
+          <t>ACUTAAS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Empower India Limited</t>
+          <t>Acutaas Chemicals Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.380000114440918</v>
+        <v>3189.89990234375</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2.470000028610229</v>
+        <v>3325</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2.369999885559082</v>
+        <v>3138</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.470000028610229</v>
+        <v>3313.39990234375</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2.369999885559082</v>
+        <v>3173</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.470000028610229</v>
+        <v>3313.39990234375</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5668630</v>
+        <v>409507</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.22</v>
+        <v>4.42</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Empower India - 11 penny stocks surged up to 198% in 6 months. Do you own any? - The Economic Times</t>
+          <t>We Ran A Stock Scan For Earnings Growth And Acutaas Chemicals (NSE:ACUTAAS) Passed With Ease - simplywall.st</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+          <t>We Ran A Stock Scan For Earnings Growth And Acutaas Chemicals (NSE:ACUTAAS) Passed With Ease - simplywall.st</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Empower India shareholders approve Rajesh Chavan as managing director - scanx.trade</t>
+          <t>Acutaas Chem Standalone June 2026 Net Sales at Rs 322.41 crore, up 56.53% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Empower Q2 Results: Base earnings rise 34% to $332 million - scanx.trade</t>
+          <t>Acutaas Chem Consolidated June 2026 Net Sales at Rs 329.67 crore, up 59.08% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+          <t>Acutaas Chemicals - 10 microcap stocks surged up to 170% in 6 months; 5 turned multibaggers - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1686,68 +1686,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PITTIENG.NS</t>
+          <t>DHARMAJ.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Pitti Engineering Limited</t>
+          <t>Dharmaj Crop Guard Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1120</v>
+        <v>260.6499938964844</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1149.5</v>
+        <v>278</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1100.5</v>
+        <v>256.8999938964844</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1143.650024414062</v>
+        <v>271.25</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1098.25</v>
+        <v>260.6499938964844</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1143.650024414062</v>
+        <v>271.25</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>361017</v>
+        <v>59403</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Pitti Engineering Ltd. Share Price at Fresh 52-Week High - Univest</t>
+          <t>Insecticides India vs Dharmaj Crop Guard: Which Agro Stock - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Pitti Engineering Publishes AGM and E-Voting Details for Shareholders - TipRanks</t>
+          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Pitti Engineering Publishes AGM and E-Voting Details for Shareholders - TipRanks</t>
+          <t>Dharmaj Crop Consolidated June 2026 Net Sales at Rs 382.38 crore, up 4.08% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Pitti Engineering షేర్: Q1లో అద్భుత వృద్ధి! రెవెన్యూ **16%** పెరిగి **₹529 కోట్లకు**, వాల్యూమ్ **19%** జంప్! - Whalesbook</t>
+          <t>Dharmaj Crop Standalone June 2026 Net Sales at Rs 384.10 crore, up 4.55% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Pitti Engineering Share Price: FY27ના પ્રથમ ક્વાર્ટરમાં રેવન્યુમાં **16%** નો વધારો, શેર હોલ્ડર્સની વધી દિશા - Whalesbook</t>
+          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1755,68 +1755,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DHARMAJ.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Guard Limited</t>
+          <t>Pine Labs Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>260.6499938964844</v>
+        <v>157.8500061035156</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>271.5</v>
+        <v>165.9499969482422</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>256.8999938964844</v>
+        <v>156.5099945068359</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>271.2000122070312</v>
+        <v>163.6900024414062</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>260.6499938964844</v>
+        <v>157.5399932861328</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>271.2000122070312</v>
+        <v>163.6900024414062</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>30691</v>
+        <v>32229753</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Insecticides India vs Dharmaj Crop Guard: Which Agro Stock - Univest</t>
+          <t>Pine Labs Limited: Top Mutual Funds Holders | PINELABS | INE15B701018 - marketscreener.com</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+          <t>Pine Labs Limited: Top Mutual Funds Holders | PINELABS | INE15B701018 - marketscreener.com</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Consolidated June 2026 Net Sales at Rs 382.38 crore, up 4.08% Y-o-Y - Moneycontrol.com</t>
+          <t>PINELABS Stock Price and Chart — NSE:PINELABS - TradingView</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Standalone June 2026 Net Sales at Rs 384.10 crore, up 4.55% Y-o-Y - Moneycontrol.com</t>
+          <t>Pine Labs Q1 profit soars four-fold YoY to ₹20 crore, revenue jumps 20%; shares surge 5% - Upstox</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+          <t>Pine Labs reports Rs 737 Cr revenue in Q1 FY27; profit jumps over 4X - Entrackr</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1824,55 +1824,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SREEL.NS</t>
+          <t>DCMFINSERV.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Limited</t>
+          <t>DCM Financial Services Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>248.0500030517578</v>
+        <v>5.130000114440918</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>261.7799987792969</v>
+        <v>5.489999771118164</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>248.0500030517578</v>
+        <v>5.010000228881836</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>259.510009765625</v>
+        <v>5.329999923706055</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>249.7100067138672</v>
+        <v>5.130000114440918</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>259.510009765625</v>
+        <v>5.329999923706055</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>28223</v>
+        <v>9336</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
+          <t>DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
+          <t>Shinhan (SHG) Latest Quarter: EPS Clears the Reported Estimate in the Latest Reading; Closing Reaction: Shares Move 4.07% Higher for the Current Session - Earnings Decline Risk - vinanet.vn</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers shareholders approve Bhaskar Chatterjee as independent director - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Shinhan (SHG) Latest Quarter: EPS Clears the Reported Estimate in the Latest Reading; Closing Reaction: Shares Move 4.07% Higher for the Current Session - Earnings Decline Risk - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Dcm Financial Services Limited Announces Resignation of Richa Kathuria as Independent Director, Member of the Audit Committee, Nomination and Remuneration Committee and Stakeholders Relationship Committee, Effective August 11, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1898,7 +1906,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -1997,7 +2005,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2023,50 +2031,50 @@
         <v>703.7000122070312</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>743.1500244140625</v>
+        <v>779.4500122070312</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>867</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>743.1500244140625</v>
+        <v>779.4500122070312</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1534524</v>
+        <v>4680449</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-14.28</v>
+        <v>-10.1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>Rashi Peripherals director quits citing governance lapses - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals director quits citing governance lapses - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Rashi Peripherals Limited (NSE:RPTECH) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Rashi Peripherals Ltd. Share Price Today - Rashi Peripherals Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Pros and Cons of Investing in Rashi Peripherals Share: IT Distributor Analysis 2026 - Univest</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits New 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2101,7 +2109,7 @@
         <v>35.25</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>778688</v>
+        <v>805383</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>-9.98</v>
@@ -2123,19 +2131,19 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
+          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
           <t>Kothari Sugars and Chemicals gets NSE no objection for merger with Kothari Petrochemicals - ChiniMandi</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2158,53 +2166,53 @@
         <v>205.3600006103516</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>185.1000061035156</v>
+        <v>184.8300018310547</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>188</v>
+        <v>186.1399993896484</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>205.3600006103516</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>188</v>
+        <v>186.1399993896484</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>791879</v>
+        <v>1026560</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-8.449999999999999</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>Kronox Lab Sciences Ltd. Share Price News and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Ltd. Share Price News and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Kronox Lab Sciences schedules 17th AGM for September 16, 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Indo Borax to acquire 64.26% stake in Kronox Lab Sciences in Rs 246-crore deal - Indian Chemical News</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Indo Borax to Acquire Stakes in Kronox Lab Sciences - Entrepreneur India</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2212,68 +2220,56 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HINDCOPPER.NS</t>
+          <t>RAJMET.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hindustan Copper Limited</t>
+          <t>Rajnandini Metal Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>542</v>
+        <v>3.509999990463257</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>551.8499755859375</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>529.3499755859375</v>
+        <v>3.130000114440918</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>531.9500122070312</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>574.1500244140625</v>
+        <v>3.5</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>531.9500122070312</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>27269605</v>
+        <v>2145804</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.35</v>
+        <v>-8.57</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Hindustan Copper: Govt to sell up to 6% stake via OFS; check floor price details - Upstox</t>
+          <t>Rajnandini Metal Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Govt''s 6% HindCopper Share Sale Begins - Rediff MoneyWiz</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Top stocks in news: TCS, Suzlon, ICICI Bank, HindCopper, Sunshine, Kotak Bank, Afcons, Shankesh - Business Today</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Hindustan Copper Share Price Up 3.13% Today - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>HINDCOPPER Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
-        </is>
-      </c>
+          <t>Rajnandini Metal Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2281,68 +2277,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>TDPOWERSYS.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited</t>
+          <t>TD Power Systems Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>24.10000038146973</v>
+        <v>780.2000122070312</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>24.35000038146973</v>
+        <v>782.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>22.42000007629395</v>
+        <v>719</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>22.55999946594238</v>
+        <v>729.4000244140625</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.22999954223633</v>
+        <v>780.0999755859375</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22.55999946594238</v>
+        <v>729.4000244140625</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>72632672</v>
+        <v>1924050</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.89</v>
+        <v>-6.5</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
+          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+          <t>TD Power Systems: Promoter Group Adjusts Ownership - InvestyWise</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>TDPOWERSYS: Revenue and profit surged year-over-year, with robust EPS and improved margins - TradingView</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+          <t>Interested In TD Power Systems' (NSE:TDPOWERSYS) Upcoming ₹1.10 Dividend? You Have One Day Left - simplywall.st</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
+          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2350,68 +2346,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SAKHTISUG.NS</t>
+          <t>RAIN.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Limited</t>
+          <t>Rain Industries Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>22</v>
+        <v>213.8899993896484</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>22.56999969482422</v>
+        <v>213.8899993896484</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>21</v>
+        <v>198.3699951171875</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>21.14999961853027</v>
+        <v>200.4900054931641</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.39999961853027</v>
+        <v>213.6900024414062</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.14999961853027</v>
+        <v>200.4900054931641</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>353444</v>
+        <v>4541018</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5.58</v>
+        <v>-6.18</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Share Price news with sector and peer view - Univest</t>
+          <t>"2 Hours 15 Minutes In Traffic": Man Shares How Rain Affected His Commute To Bengaluru Airport - NDTV</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Share Price news with sector and peer view - Univest</t>
+          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Limited Appoints R. Jeysree to Head the Internal Audit Department(In-House), Effective August 13, 2026 - marketscreener.com</t>
+          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Ltd. Share Price Up 10.82%: Stock Analysis - Univest</t>
+          <t>RAIN Should I Buy - Intellectia AI</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
+          <t>Just Three Days Till Rain Industries Limited (NSE:RAIN) Will Be Trading Ex-Dividend - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2419,68 +2415,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems Limited</t>
+          <t>Bajaj Hindusthan Sugar Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>780.2000122070312</v>
+        <v>24.10000038146973</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>782.5</v>
+        <v>24.35000038146973</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>733.4000244140625</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>739</v>
+        <v>22.80999946594238</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>780.0999755859375</v>
+        <v>24.22999954223633</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>739</v>
+        <v>22.80999946594238</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1130167</v>
+        <v>113228799</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.27</v>
+        <v>-5.86</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
+          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Why Did TD Power Systems Shares Crash 50% Today? Check the Reason - Trade Brains</t>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS: Revenue and profit surged year-over-year, with robust EPS and improved margins - TradingView</t>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Interested In TD Power Systems' (NSE:TDPOWERSYS) Upcoming ₹1.10 Dividend? You Have One Day Left - simplywall.st</t>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
+          <t>Most Active Equities on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2488,68 +2484,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ELITECON.NS</t>
+          <t>ATLANTAELE.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Limited</t>
+          <t>Atlanta Electricals Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.19999980926514</v>
+        <v>1801</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>15.47999954223633</v>
+        <v>1812</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>14.39999961853027</v>
+        <v>1712.599975585938</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>14.39999961853027</v>
+        <v>1719.599975585938</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15.1899995803833</v>
+        <v>1819.5</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14.39999961853027</v>
+        <v>1719.599975585938</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1197314</v>
+        <v>120591</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.2</v>
+        <v>-5.49</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Elitecon appoints Vipin Sharma and Pradeep Kumar as Executive Directors - scanx.trade</t>
+          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Elitecon appoints Vipin Sharma and Pradeep Kumar as Executive Directors - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Small-cap stock under ₹50 Elitecon International hits 10% upper circuit for second day in a row - Livemint</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Elitecon International: Kumar Anubhav Upadhyay ceases as Additional Director - scanx.trade</t>
-        </is>
-      </c>
+          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2557,68 +2541,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TAKE.NS</t>
+          <t>GSLSU.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>TAKE Limited</t>
+          <t>Global Surfaces Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.04999923706055</v>
+        <v>30</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>19.29000091552734</v>
+        <v>31.47999954223633</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>29.82999992370605</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>29.82999992370605</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.79000091552734</v>
+        <v>31.39999961853027</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>29.82999992370605</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>123313</v>
+        <v>67344</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4.95</v>
+        <v>-5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+          <t>Global Surfaces Limited Announces CFO Changes - marketscreener.com</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Take-Two's Twin Headwinds: A Leak Offensive and a Stock That Analysts Refuse to Abandon - Ad-hoc-news.de</t>
+          <t>Global Surfaces posts ₹25.4m standalone PAT in Q1FY27; re-submits results - scanx.trade</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
+          <t>Global Surfaces Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Woman shares emotional moment as parents take first-ever flight: ‘Life has come full circle’ | Trending - Hindustan Times</t>
+          <t>Global Surfaces posts ₹25.4m standalone PAT in Q1FY27; re-submits results - scanx.trade</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Delhi: Swine Flu Cases On The Rise, High-level Meeting To Take Stock - ETV Bharat</t>
+          <t>Global Surfaces Ltd to host Q1-FY27 earnings call on Aug 11 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2626,56 +2610,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE.NS</t>
+          <t>TAKE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Electricals Limited</t>
+          <t>TAKE Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1801</v>
+        <v>19.04999923706055</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1812</v>
+        <v>19.29000091552734</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1725.099975585938</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1733.699951171875</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1819.5</v>
+        <v>19.79000091552734</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1733.699951171875</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>68111</v>
+        <v>136633</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.72</v>
+        <v>-4.95</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
+          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Commerce Bank Buys Shares of 14,555 Take-Two Interactive Software, Inc. $TTWO - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Enter Energy Somalia: Rapid Stock-take Assessment Report, March 2026 - ReliefWeb</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>It Won’t Take Much to Burst the Stock Market Bubble - Advisor Perspectives</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2710,7 +2706,7 @@
         <v>2.839999914169312</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1949939</v>
+        <v>1970998</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>-4.7</v>
@@ -2744,7 +2740,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2752,64 +2748,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE.NS</t>
+          <t>IIFL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging Limited</t>
+          <t>IIFL Finance Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.860000014305115</v>
+        <v>667</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2</v>
+        <v>681.0999755859375</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1.860000014305115</v>
+        <v>643.5499877929688</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.860000014305115</v>
+        <v>666.25</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.950000047683716</v>
+        <v>696.4000244140625</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.860000014305115</v>
+        <v>666.25</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>18057141</v>
+        <v>8284153</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.62</v>
+        <v>-4.33</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
+          <t>IIFL Finance shares decline over 7% after home finance arm receives ₹963 crore income tax demand notice; here's why - Upstox</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
+          <t>IIFL Finance Shares Plunge Nearly 8% on ₹963 Crore Tax Demand - Business Outreach Magazine</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging opens Rights Issue at ₹1.63 per share - scanx.trade</t>
+          <t>IFL Finance shares drop 8% as IIFL Home Finance gets Rs 963 crore tax demand - The Economic Times</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>IIFL Finance shares crack 8% after ₹963-crore tax demand for subsidiary - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares fall 4% after subsidiary faces Rs 963 crore tax demand - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2817,68 +2817,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DATAPATTNS.NS</t>
+          <t>RANASUG.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Data Patterns (India) Limited</t>
+          <t>Rana Sugars Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4730</v>
+        <v>15.77999973297119</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4768.7001953125</v>
+        <v>16.19000053405762</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4500.10009765625</v>
+        <v>15.01000022888184</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4522</v>
+        <v>15.26000022888184</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4736.2001953125</v>
+        <v>15.92000007629395</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4522</v>
+        <v>15.26000022888184</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>845786</v>
+        <v>889584</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.52</v>
+        <v>-4.15</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
+          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Defence stock with Rs 2,654-crore order book hits record high; here's why - Business Today</t>
+          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Data Patterns shares collapse 7% as Q1FY27 earnings show subdued performance - Upstox</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Data Patterns Share Price Today: Stock Rises 3.11% - Univest</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Data Patterns (India) Ltd. Share Price News and Analysis - Univest</t>
-        </is>
-      </c>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2886,60 +2878,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RANASUG.NS</t>
+          <t>DATAPATTNS.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Limited</t>
+          <t>Data Patterns (India) Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15.77999973297119</v>
+        <v>4730</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>16.19000053405762</v>
+        <v>4768.7001953125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15.01000022888184</v>
+        <v>4500.10009765625</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>15.19999980926514</v>
+        <v>4542.2998046875</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15.92000007629395</v>
+        <v>4736.2001953125</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15.19999980926514</v>
+        <v>4542.2998046875</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>670550</v>
+        <v>1198221</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.52</v>
+        <v>-4.09</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
+          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
-        </is>
-      </c>
+          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2947,68 +2935,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KMSUGAR.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>K.M.Sugar Mills Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34.04000091552734</v>
+        <v>57.79999923706055</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>35</v>
+        <v>59.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>31.1200008392334</v>
+        <v>54.13999938964844</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>32.54999923706055</v>
+        <v>55.65999984741211</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.04999923706055</v>
+        <v>58.0099983215332</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>32.54999923706055</v>
+        <v>55.65999984741211</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>370950</v>
+        <v>1072021</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.41</v>
+        <v>-4.05</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Share Price rises 8.17%: valuation, peers - Univest</t>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Share Price rises 8.17%: valuation, peers - Univest</t>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Ltd. Share Price Today With Fundamentals - Univest</t>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Ltd. Share Price Rise With Valuation View - Univest</t>
+          <t>The Ugar Sugar Works Ltd. Share Price Today: Key Analysis - Univest</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Keysight Technologies (KEYS) Slips 1.5% as Shares Hold Above Key Support - Earnings Breakout Stocks - vinanet.vn</t>
+          <t>The Ugar Sugar Works Ltd. Share Price Near 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3016,68 +3004,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>NETWEB.NS</t>
+          <t>WHEELS.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Netweb Technologies India Limited</t>
+          <t>Wheels India Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5400</v>
+        <v>1565</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5413.2001953125</v>
+        <v>1579.599975585938</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5208</v>
+        <v>1489.099975585938</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>5220</v>
+        <v>1499.300048828125</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5454.5</v>
+        <v>1561.400024414062</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5220</v>
+        <v>1499.300048828125</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1241468</v>
+        <v>137084</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.3</v>
+        <v>-3.98</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Netweb Technologies shares fall over 3% after Rs 1,200 crore QIP - Moneycontrol.com</t>
+          <t>Wheels India Approves Issuing 1,269,391 Equity Shares At ₹1,418 To Raise ₹180 Crores - Sahi</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Netweb Technologies shares fall 4% after raising Rs 1,200 crore through QIP - The Economic Times</t>
+          <t>Wheels Up Experience Stock Price Forecast. Should You Buy UP? - StockInvest.us</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Netweb Technologies shares fall 4% after raising Rs 1,200 crore through QIP - The Economic Times</t>
+          <t>TSF Investments Approves Subscription To Preferential Issue Of Wheels India Equity Shares - TradingView</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Netweb Tech raises Rs 1,200 crore via QIP; stock falls for 2nd day, down 4% - Business Today</t>
+          <t>Wheels India board approves ₹180 crore preferential issue at ₹1,418 per share - scanx.trade</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Netweb Tech Raises ₹1,200 Crore By Issuing 25,05,219 Equity Shares At ₹4,790 Each - Sahi</t>
+          <t>Stock Alert: Bharat Electronics, Godfrey Phillips India, Wheels India, Tata Chemicals - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3085,68 +3073,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>IIFL.NS</t>
+          <t>ALICON.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance Limited</t>
+          <t>Alicon Castalloy Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>667</v>
+        <v>727</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>681.0999755859375</v>
+        <v>727.25</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>643.5499877929688</v>
+        <v>690</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>670.2999877929688</v>
+        <v>697.7999877929688</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>696.4000244140625</v>
+        <v>726.5</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>670.2999877929688</v>
+        <v>697.7999877929688</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>6270881</v>
+        <v>57256</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.75</v>
+        <v>-3.95</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance shares decline over 7% after home finance arm receives ₹963 crore income tax demand notice; here's why - Upstox</t>
+          <t>Alicon Castalloy declares ₹3 per share final dividend for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>IFL Finance shares drop 8% as IIFL Home Finance gets Rs 963 crore tax demand - The Economic Times</t>
+          <t>₹8,094 Cr Order Book: Smallcap Stock With BMW, Volkswagen and Bosch as Clients to Add to Your Watchlist - Trade Brains</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance shares fall 4% after subsidiary faces Rs 963 crore tax demand - Moneycontrol.com</t>
+          <t>Alicon Castalloy Ltd. Share Price: Major 8.55% Increase - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance shares crack 8% after ₹963-crore tax demand for subsidiary - Business Standard</t>
+          <t>Alicon Castalloy Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance shares fall nearly 8% after receiving tax demand of ₹963 crore for home finance arm - CNBC TV18</t>
+          <t>Alicon Castalloy approves ₹1,255 mn plant for castings - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3154,56 +3142,56 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>GOCOLORS.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>Go Fashion (India) Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>285</v>
+        <v>354.7999877929688</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>285.3999938964844</v>
+        <v>354.7999877929688</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>274.0499877929688</v>
+        <v>337.1000061035156</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>275.5</v>
+        <v>340.25</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>286.2000122070312</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>275.5</v>
+        <v>340.25</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>498776</v>
+        <v>197680</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.74</v>
+        <v>-3.69</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
+          <t>GOCOLORS Share Price Today - Go Fashion (India) Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
+          <t>GOCOLORS Share Price Today - Go Fashion (India) Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+          <t>Go Fashion (India) Limited Just Missed EPS By 18%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
+          <t>Go Fashion (India) Ltd sees SSSG turn positive in Q1 FY27 as revenue holds steady - scanx.trade</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -3211,7 +3199,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3219,68 +3207,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP.NS</t>
+          <t>REDINGTON.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Voltamp Transformers Limited</t>
+          <t>Redington Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11382.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>11400</v>
+        <v>366.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>10670</v>
+        <v>350.1499938964844</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10875</v>
+        <v>352.6499938964844</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>11292</v>
+        <v>365.1000061035156</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10875</v>
+        <v>352.6499938964844</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>41420</v>
+        <v>4485539</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.69</v>
+        <v>-3.41</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Voltamp Transformers Share Price today: price, valuation - Univest</t>
+          <t>Redington Share Price hits fresh 52-week high at Rs 364 - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Voltamp Transformers Share Price today: price, valuation - Univest</t>
+          <t>Redington Share Price hits fresh 52-week high at Rs 364 - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Voltamp Transformers posts ₹912M profit in Q1FY27, updates capex plan - scanx.trade</t>
+          <t>Redington shares jump 11% to fresh record high, rally 29% in five sessions; key triggers explained - Upstox</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Voltamp Trans Standalone June 2026 Net Sales at Rs 543.78 crore, up 28.38% Y-o-Y - Moneycontrol.com</t>
+          <t>Redington shares rise up to 15% as Q1 net profit nearly doubles to Rs 453 crore - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Voltamp Transformers declares ₹100 final dividend per share for FY26 - scanx.trade</t>
+          <t>Redington shares rally 15% after Q1 profit surges 77%; revenue rises 35% YoY - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:50:15 IST</t>
+          <t>2026-08-25 16:30:30 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3288,63 +3276,59 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RAIN.NS</t>
+          <t>SOMICONVEY.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Rain Industries Limited</t>
+          <t>Somi Conveyor Beltings Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>213.8899993896484</v>
+        <v>98.62000274658203</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>213.8899993896484</v>
+        <v>99.19999694824219</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>204.0099945068359</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>205.8999938964844</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>213.6900024414062</v>
+        <v>97.36000061035156</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>205.8999938964844</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2272466</v>
+        <v>27366</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.65</v>
+        <v>-3.39</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>"2 Hours 15 Minutes In Traffic": Man Shares How Rain Affected His Commute To Bengaluru Airport - NDTV</t>
+          <t>Somi Conveyor Beltings Ltd. Share Price Up 15.77% Today - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+          <t>Somi Conveyor Beltings Ltd. Share Price Up 15.77% Today - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>RAIN Should I Buy - Intellectia AI</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Just Three Days Till Rain Industries Limited (NSE:RAIN) Will Be Trading Ex-Dividend - simplywall.st</t>
-        </is>
-      </c>
+          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GENESYS.NS</t>
+          <t>DTIL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corporation Limited</t>
+          <t>Dhunseri Tea &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>181.3000030517578</v>
+        <v>172</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>214.25</v>
+        <v>183.2200012207031</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>181.3000030517578</v>
+        <v>165.1199951171875</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>214.25</v>
+        <v>183.2200012207031</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>178.5500030517578</v>
+        <v>152.6900024414062</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>214.25</v>
+        <v>183.2200012207031</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4189199</v>
+        <v>437530</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>19.99</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
+          <t>A gene-editing treatment for Duchenne muscular dystrophy doses its first patient - Stock Titan</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corporation Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Precision BioSciences (DTIL) draws 1.1M-share Weinstein stake - Stock Titan</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corp fixes rights issue price at ₹50 for 2.5Cr shares - scanx.trade</t>
+          <t>Precision (DTIL) Momentum: Rises 1.61% to $8.86 in the Current Update; Chart View: the $8.42 to $9.30 Range Remains in Focus for the Current Session - Retracement Entry - vinanet.vn</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corporation Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Precision BioSciences (DTIL) Stock Faces Dilution Risk As Revenue Fades - simplywall.st</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Taxes of Genesys International Corporation Limited Rights 2026-21.08.26 For Shares – BSE:GENESYS_RE - TradingView</t>
+          <t>Precision BioSciences: Promising HBV Editing Evidence (NASDAQ:DTIL) - Seeking Alpha</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,64 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DUCON.NS</t>
+          <t>TVSSRICHAK.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Limited</t>
+          <t>TVS Srichakra Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.259999990463257</v>
+        <v>4792.89990234375</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2.539999961853027</v>
+        <v>5322.60009765625</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2.210000038146973</v>
+        <v>4792.89990234375</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.400000095367432</v>
+        <v>5313.2001953125</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.175652027130127</v>
+        <v>4812</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.400000095367432</v>
+        <v>5313.2001953125</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3670210</v>
+        <v>84858</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>10.31</v>
+        <v>10.42</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Ltd. Share Price Today: 11.98% Gain - Univest</t>
+          <t>TVS Srichakra Ltd. Share Price Today: Market Cap Context - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Ltd. Share Price Today: 11.98% Gain - Univest</t>
+          <t>TVS Srichakra Ltd. Share Price Today: Market Cap Context - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade</t>
+          <t>TVS Srichakra Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Wins Contract With India's Largest Aluminium Smelter - Sahi</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Ducon Infratechnologies approves rights issue of up to ₹25 Crore - scanx.trade</t>
-        </is>
-      </c>
+          <t>TVS Srichakra share price jumps16% on robust Q1 earnings performance; profit jumps 165% - Upstox</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +687,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>TARMAT.NS</t>
+          <t>ARIES.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Limited</t>
+          <t>Aries Agro Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>50.02999877929688</v>
+        <v>446.6499938964844</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>55.45000076293945</v>
+        <v>512.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>49.59999847412109</v>
+        <v>445.1000061035156</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>54.22999954223633</v>
+        <v>491</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>50.13999938964844</v>
+        <v>446.75</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>54.22999954223633</v>
+        <v>491</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>96996</v>
+        <v>508690</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>8.16</v>
+        <v>9.9</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
+          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
+          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest</t>
+          <t>Aries Agro Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Ltd Downgraded to Sell by MarketsMOJO Amid Mixed Financial and Technical Signals - marketsmojo.com</t>
+          <t>Salesforce (CRM) Stock Analysis Today - Gotrade</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Ltd. Share Price Drop: Price Action and Sector View - Univest</t>
+          <t>Daily Nadi Horoscope for Aries (7th August 2026): Moon–Mars Energy May Bring Profit, but Family Peace Nee - The Times of India</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +756,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CYIENT.NS</t>
+          <t>MEIL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Cyient Limited</t>
+          <t>Mangal Electrical Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>909</v>
+        <v>280.0499877929688</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>989</v>
+        <v>304.9500122070312</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>898.6500244140625</v>
+        <v>280.0499877929688</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>979.0499877929688</v>
+        <v>298.2999877929688</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>909.0499877929688</v>
+        <v>276.2000122070312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>979.0499877929688</v>
+        <v>298.2999877929688</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4712452</v>
+        <v>538891</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Ltd. (CYIENTDLM) Share Price Hits Fresh 52-Week High at Rs 768.95 - Univest</t>
+          <t>Why Investors Shouldn't Be Surprised By Mangal Electrical Industries Limited's (NSE:MEIL) 30% Share Price Plunge - simplywall.st</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Top Gainers &amp; Losers on 25 Aug: FACT, Vodafone Idea, Cyient, Paytm, Angel One, Pine Labs among top gainers - Livemint</t>
+          <t>Mangal Electrical Industries Limited (MEIL.NS) Mar 2026 Earnings: Moderate Revenue Growth with Higher EPS - vinanet.vn</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Top Gainers &amp; Losers on 25 Aug: FACT, Vodafone Idea, Cyient, Paytm, Angel One, Pine Labs among top gainers - Livemint</t>
+          <t>MEIL Stock Price and Chart — NSE:MEIL - TradingView</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Stocks to Watch Today, August 25, 2026: Cyient, Great Eastern Shipping Company, Tata Consultancy Services, Pace Digitek and Chemplast Sanmar - scanx.trade</t>
+          <t>MEIL Holdings Limited Releases Share Encumbrance on Olectra Greentech Following Loan Closure - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>HAL shares gain up to 1% after NCLT dissolves joint venture with Cyient - Moneycontrol.com</t>
+          <t>Mangal Electrical Industries (MEIL.NS) Holds Near Support After Minor Dip - Price Surge Stocks - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,68 +825,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>INVENTURE.NS</t>
+          <t>WABAG.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Inventure Growth &amp; Securities Limited</t>
+          <t>VA Tech Wabag Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8500000238418579</v>
+        <v>2025.699951171875</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9300000071525574</v>
+        <v>2144</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.8500000238418579</v>
+        <v>2016.099975585938</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.9100000262260437</v>
+        <v>2142</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.8500000238418579</v>
+        <v>2021.5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9100000262260437</v>
+        <v>2142</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2156001</v>
+        <v>854170</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>7.06</v>
+        <v>5.96</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Inventure Grow Standalone June 2026 Net Sales at Rs 10.67 crore, down 26.91% Y-o-Y - Moneycontrol.com</t>
+          <t>Va Tech Wabag Denies Rs 600 Crore Saudi Arabia Contract, Awaits Kuwait Award Letter - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Inventure Growth &amp; Securities posts ₹4.61 crore profit in Q1FY26 - scanx.trade</t>
+          <t>Va Tech Wabag Denies Rs 600 Crore Saudi Arabia Contract, Awaits Kuwait Award Letter - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Inventure Growth &amp; Securities withdraws scheme after RBI denial - scanx.trade</t>
+          <t>VA Tech Wabag (NSEI:WABAG) Stock Gets Fair Value Boost On Higher P E View - Yahoo Finance</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Inventure Grow Consolidated June 2026 Net Sales at Rs 13.16 crore, down 23.98% Y-o-Y - Moneycontrol.com</t>
+          <t>Rekha Jhunjhunwala stock: DIIs triple stake in two years; Systematix lists out triggers - Business Today</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Andriy Verevskyi Begins Kernel Share Buyout Ahead of Warsaw Stock Exchange Delisting - Inventure.com.ua.</t>
+          <t>Rekha Jhunjhunwala portfolio stock VA Tech Wabag jumps 5%; Axis Securities raises target price after Q1 results - Livemint</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -898,56 +894,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GIPCL.NS</t>
+          <t>RATNAVEER.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Industries Power Company Limited</t>
+          <t>Ratnaveer Precision Engineering Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>177.3999938964844</v>
+        <v>265.0299987792969</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>191.25</v>
+        <v>279.7999877929688</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>177.3999938964844</v>
+        <v>264</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>190.7200012207031</v>
+        <v>278.989990234375</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>178.3899993896484</v>
+        <v>263.4299926757812</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>190.7200012207031</v>
+        <v>278.989990234375</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3502664</v>
+        <v>3064038</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6.91</v>
+        <v>5.91</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
+          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Ratnaveer Approves ₹330 Crore Rights Issue at ₹264; Shares Touch All-Time High of ₹282.50 - ACCESS Newswire</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Ratnaveer Approves Rs 330 Crore Rights Issue at Rs 264; Shares Touch All-Time High of Rs 282.50 - Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>80% rally in YTD! Ratnaveer Precision Engineering declares rights issue worth ₹330 crore - Livemint</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Ratnaveer targets ₹2,500 crore revenue with CCL project - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,68 +963,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP.NS</t>
+          <t>QUESS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Paradeep Phosphates Limited</t>
+          <t>Quess Corp Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>150.8000030517578</v>
+        <v>349.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>160.6000061035156</v>
+        <v>376.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>150.8000030517578</v>
+        <v>348</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>159.6300048828125</v>
+        <v>365.5499877929688</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>149.3999938964844</v>
+        <v>347</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>159.6300048828125</v>
+        <v>365.5499877929688</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>51528268</v>
+        <v>4331313</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.85</v>
+        <v>5.35</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Fertiliser Stocks Jump Up To 10% — FACT, Paradeep Phosphates, NFL Gain. Here's Why - NDTV Profit</t>
+          <t>Only Three Days Left To Cash In On Quess' (NSE:QUESS) Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - BusinessToday - India IPO</t>
+          <t>Stocks to buy for short term: Grasim, Quess Corp among 6 stocks experts recommend buying today for next 1-2 weeks - Livemint</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - Business Today</t>
+          <t>Quess Corp Ltd. Share Price With Price and Market Cap View - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - BusinessToday - India IPO</t>
+          <t>Quess Corp Q1 net profit jumps 61% on professional staffing, overseas growth - CNBC TV18</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+          <t>Stocks to buy for short term: Grasim, Quess Corp among 6 stocks experts recommend buying today for next 1-2 weeks - Livemint</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1024,64 +1032,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SHREEPUSHK.NS</t>
+          <t>ISFT.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Shree Pushkar Chemicals &amp; Fertilisers Limited</t>
+          <t>Intrasoft Technologies Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>427.5</v>
+        <v>91.5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>459.5</v>
+        <v>97.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>424.0499877929688</v>
+        <v>91.44000244140625</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>454.1000061035156</v>
+        <v>96</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>426.8999938964844</v>
+        <v>91.44000244140625</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>454.1000061035156</v>
+        <v>96</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>258193</v>
+        <v>82738</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6.37</v>
+        <v>4.99</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Shree Pushkar Chemicals &amp; Fertilisers Limited Announces Board Changes, Effective August 13, 2026 - marketscreener.com</t>
+          <t>ICEsoft Technologies Canada Corp (CN: ISFT) Share Price, ISFT Stock News, ISFT Share Price &amp; Updates - Kalkine</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Shree Pushkar Chemicals &amp; Fertilisers Adds 10 MW Solar Capacity in Maharashtra - marketscreener.com</t>
+          <t>ICEsoft Releases Q2 2026 Financial Results - TradingView</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Shree Pushkar Chemicals Q1 Results: Earnings call set for Aug 13 - scanx.trade</t>
+          <t>Intrasoft Technologies Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Shree Pushkar Chemicals &amp; Fertilisers Adds 10 MW Solar Capacity in Maharashtra - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>IntraSoft Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>ICEsoft Releases Q2 2026 Financial Results - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1089,64 +1101,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TFCILTD.NS</t>
+          <t>HINDZINC.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Tourism Finance Corporation of India Limited</t>
+          <t>Hindustan Zinc Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>130</v>
+        <v>605</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>137.9400024414062</v>
+        <v>623.75</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>129.2200012207031</v>
+        <v>600.1500244140625</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>137.0200042724609</v>
+        <v>621.4500122070312</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>129.5599975585938</v>
+        <v>592.5999755859375</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>137.0200042724609</v>
+        <v>621.4500122070312</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>20325175</v>
+        <v>11140806</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5.76</v>
+        <v>4.87</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>LIC confirms no fresh encumbrance on TFCI shares in FY26 - scanx.trade</t>
+          <t>Hindustan Zinc Share Price - Live NSE: HINDZINC Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>LIC confirms no fresh encumbrance on TFCI shares in FY26 - scanx.trade</t>
+          <t>Hindustan Zinc Share Price Today: ₹588, the Market's Biggest Faller - The Eastern Herald</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Tourism Finance Corporation Of India Ltd. (TFCILTD) Share Price Hits Fresh 52-Week High - Univest</t>
+          <t>Hindustan Zinc Adds Independent Director Appointed by Ministry of Mines - The Globe and Mail</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Tourism Finance Corporation Of India Ltd. Share Price Near - Univest</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Hindustan Zinc Share Price Today, August 24, 2026: Closes at ₹604 - The Eastern Herald</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Share Price Today: ₹588, the Market's Biggest Faller - The Eastern Herald</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1154,64 +1170,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NECLIFE.NS</t>
+          <t>OLAELEC.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences Limited</t>
+          <t>Ola Electric Mobility Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10.72000026702881</v>
+        <v>36.68999862670898</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>11.4399995803833</v>
+        <v>38.68000030517578</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>10.72000026702881</v>
+        <v>36.63000106811523</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>11.32999992370605</v>
+        <v>37.90000152587891</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10.72000026702881</v>
+        <v>36.20000076293945</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11.32999992370605</v>
+        <v>37.90000152587891</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>317808</v>
+        <v>65587786</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5.69</v>
+        <v>4.7</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences Limited Changes Its Corporate Office in Chandigarh - marketscreener.com</t>
+          <t>Ola Electric Publishes Q1 FY2026 Unaudited Results in Newspapers - The Globe and Mail</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
+          <t>Ola Electric Mobility Limited (NSE:OLAELEC) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
-        </is>
-      </c>
+          <t>Ola Electric Mobility Limited (NSE:OLAELEC) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1219,56 +1231,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES.NS</t>
+          <t>SURYODAY.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Balaji Amines Limited</t>
+          <t>Suryoday Small Finance Bank Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2241.60009765625</v>
+        <v>151.4900054931641</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2390</v>
+        <v>160.8800048828125</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2205.300048828125</v>
+        <v>151.4900054931641</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2343.60009765625</v>
+        <v>157.8000030517578</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2224.5</v>
+        <v>151.0200042724609</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2343.60009765625</v>
+        <v>157.8000030517578</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>600301</v>
+        <v>449439</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.35</v>
+        <v>4.49</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Balaji Amines Share Price news: Rs 2,210.70 and sector view - Univest</t>
+          <t>Despite Suryoday Small Finance Bank's Pullback, Insiders Still Gained ₹1.9m - simplywall.st</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Balaji Amines Share Price news: Rs 2,210.70 and sector view - Univest</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Suryoday Small Finance Bank Q4 FY26: Gross Advances At ₹13,201 Crore, Up 29% YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Suryoday Small Finance Bank Q4 FY26: Gross Advances At ₹13,201 Crore, Up 29% YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Suryoday Small Finance Bank Share Price Falls 9.5% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Suryoday Small Finance Bank vs Utkarsh Small Finance Bank: Which Stock Should You Track - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1276,68 +1300,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>JARO.NS</t>
+          <t>PARAS.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Jaro Institute of Technology Management and Research Limited</t>
+          <t>Paras Defence and Space Technologies Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>450</v>
+        <v>1450.099975585938</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>476.3999938964844</v>
+        <v>1510</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>445.8999938964844</v>
+        <v>1435</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>468.5499877929688</v>
+        <v>1508.599975585938</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>445.2000122070312</v>
+        <v>1445.199951171875</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>468.5499877929688</v>
+        <v>1508.599975585938</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>344015</v>
+        <v>698453</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.24</v>
+        <v>4.39</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Jaro Institute of Technology Management and Research Limited Actuals &amp; Estimates (NSE:JARO) - TradingView</t>
+          <t>Bonus, dividends &amp; stock splits: Paras Defence, NBCC, MCX among 67 stocks turning ex-record date this week - The Economic Times</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Jaro Inst promoter Balkrishna Salunkhe buys 7,390 shares in open market - scanx.trade</t>
+          <t>Stock Market Live | Coal India, Tejas Network, Tata Steel, Paras Defence Share में क्या करें? Anas Sarwar (iWHytEj8x1) - Mshale</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Jaro Inst promoter acquires 300 equity shares in open market - scanx.trade</t>
+          <t>MCX, Honasa Consumer, Paras Defence, other upcoming dividend stocks, bonus issues in focus this week; check list - Upstox</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Jaro Education shares make muted market debut; later tanks nearly 18 pc - News18</t>
+          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock under ₹500 jumps 5% despite muted trend on Dalal Street - Livemint</t>
+          <t>Corporate Actions This Week: P&amp;G Health, Gillette India, PFC, TD Power, Senco Gold, Paras Defence &amp; More - NDTV Profit</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1345,68 +1369,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CEWATER.NS</t>
+          <t>DCBBANK.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Concord Enviro Systems Limited</t>
+          <t>DCB Bank Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>253.5</v>
+        <v>210</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>271.3999938964844</v>
+        <v>216.6699981689453</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>251.9499969482422</v>
+        <v>209.2400054931641</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>265.4500122070312</v>
+        <v>216.3000030517578</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>253.1499938964844</v>
+        <v>207.3699951171875</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>265.4500122070312</v>
+        <v>216.3000030517578</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>219118</v>
+        <v>4060703</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4.86</v>
+        <v>4.31</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Investors Aren't Entirely Convinced By Concord Enviro Systems Limited's (NSE:CEWATER) Earnings - simplywall.st</t>
+          <t>DCB Bank Ltd. Share Price: Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Concord Enviro Systems (CEWATER.NS) Gains 3.43% – Bulls Defend Key Support at ₹366.8 - Double Bottom - vinanet.vn</t>
+          <t>DCB Bank Ltd. Share Price: Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>CONCORD ENVIRO SYSTEMS L Share Price - Upstox</t>
+          <t>Here's Why We Think DCB Bank (NSE:DCBBANK) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Concord Enviro Systems Limited Announces Equity Shareholders Meeting for Scheme of Arrangement Approval - scanx.trade</t>
+          <t>DCB Bank Share Price at 52-week high: price, fundamentals - Univest</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>CEWATER Mar 2026 Earnings: Strong EPS of ₹2.06 on Revenue of ₹17.64 Crore; Stock Gains 3.35% - Mid-Term Outlook - vinanet.vn</t>
+          <t>Bank Stock to Buy Now for an Upside of 54%; Recommended by Anand Rathi - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1414,68 +1438,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RCF.NS</t>
+          <t>IDBI.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Rashtriya Chemicals and Fertilizers Limited</t>
+          <t>IDBI Bank Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>121</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>128.5500030517578</v>
+        <v>92.69999694824219</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>120.25</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>124.4700012207031</v>
+        <v>92.08999633789062</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>119.0299987792969</v>
+        <v>88.30999755859375</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>124.4700012207031</v>
+        <v>92.08999633789062</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>18084974</v>
+        <v>20477384</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4.57</v>
+        <v>4.28</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Why did FACT, RCF, NFL and other fertiliser stocks rally up to 14% today? Explained - Livemint</t>
+          <t>IDBI Bank Share Price Jumps 10% In Trade: What's Driving The Rally? - NDTV Profit</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Why did FACT, RCF, NFL and other fertiliser stocks rally up to 14% today? Explained - Livemint</t>
+          <t>IDBI Bank Shares Surge Over 10%! Fairfax Deal May Be Near, Government, LIC Stake Sale &amp; RBI Challenges - Thekanal</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+          <t>LIC stake sale in IDBI Bank: Officers’ body seeks IRDAI intervention - BusinessLine</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>RCF Q1 PAT jumps 35% YoY to Rs 74 crore - Business Standard</t>
+          <t>Centre may clear Fairfax bid for controlling stake in IDBI Bank within a week: Report - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Stocks to Watch today: Bajaj Finance, Vedanta, Tata Steel, Dabur, PNB, RCF - Business Standard</t>
+          <t>IDBI Bank shares rise 2% as lender clarifies on surge in trading volumes; details here - Business Today</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1483,68 +1507,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>IREDA.NS</t>
+          <t>OLECTRA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Indian Renewable Energy Development Agency Limited</t>
+          <t>Olectra Greentech Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>115</v>
+        <v>1294.900024414062</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>121.1399993896484</v>
+        <v>1359.199951171875</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>114.4000015258789</v>
+        <v>1294.900024414062</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>120.6100006103516</v>
+        <v>1346.800048828125</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>115.4000015258789</v>
+        <v>1291.800048828125</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>120.6100006103516</v>
+        <v>1346.800048828125</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>11092821</v>
+        <v>562972</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.51</v>
+        <v>4.26</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Stocks to watch: Reliance Industries, Power Grid, IREDA among shares to be in focus today. Details here - Livemint</t>
+          <t>Olectra Greentech Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Stocks to watch: Reliance Industries, Power Grid, IREDA among shares to be in focus today. Details here - Livemint</t>
+          <t>Olectra Greentech Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>IREDA Q1 Results 2027: Revenue Rises 16% YoY to ₹2,249 Cr, PAT Jumps 37% to ₹339 Cr - Sahi</t>
+          <t>Olectra rally 7% on order win from BEST - Upstox</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Dividend Delight! THIS Navratna PSU To Pay 6% Dividend; Stock Up 4%: How To Get Eligible Before Record Date? - Goodreturns</t>
+          <t>Olectra Greentech Q1FY27 revenue up 66% YoY to ₹575.5 crore - scanx.trade</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Buy, Sell Or Hold: Suzlon, HDFC Bank, Colgate, Torrent Pharma And IREDA — Ask Profit - NDTV Profit</t>
+          <t>Olectra Greentech Shares Decline Nearly 4% After Q1 Results - NDTV Profit</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1552,64 +1576,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP.NS</t>
+          <t>CYIENT.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited</t>
+          <t>Cyient Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>59.16999816894531</v>
+        <v>994</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>62.2400016784668</v>
+        <v>1054.849975585938</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>58.90000152587891</v>
+        <v>984.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.52000045776367</v>
+        <v>1020.25</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>58.88000106811523</v>
+        <v>979.0499877929688</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>61.52000045776367</v>
+        <v>1020.25</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3353931</v>
+        <v>7154604</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.48</v>
+        <v>4.21</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
+          <t>Cyient shares jump 4% after investor day; JPMorgan sees ₹1,050 target on double-digit growth outlook - CNBC TV18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
+          <t>Cyient shares rocket 8% after investor day, but brokerages see up to 24% downside. Here’s why - The Economic Times</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Cyient shares soar 8% as CCI approves acquisition of California-based Tao Digital Solutions - Upstox</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Publishes AGM, Book Closure and E-Voting Notice - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Cyient Stock: JPMorgan Sees Transformation, Morgan Stanley Waits for Execution - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Cyient shares surge 8%: Targets by MOFSL, Antique, Choice, Nuvama post Investor Day - Business Today</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1617,68 +1645,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS.NS</t>
+          <t>AEROFLEX.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals Limited</t>
+          <t>Aeroflex Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3189.89990234375</v>
+        <v>496</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3325</v>
+        <v>517.5999755859375</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3138</v>
+        <v>492</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3313.39990234375</v>
+        <v>516.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3173</v>
+        <v>495.75</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3313.39990234375</v>
+        <v>516.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>409507</v>
+        <v>965740</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.42</v>
+        <v>4.19</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And Acutaas Chemicals (NSE:ACUTAAS) Passed With Ease - simplywall.st</t>
+          <t>Aeroflex Industries Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And Acutaas Chemicals (NSE:ACUTAAS) Passed With Ease - simplywall.st</t>
+          <t>Aeroflex Neu Allots ₹3 Cr Stake in Stilonn Valves - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Acutaas Chem Standalone June 2026 Net Sales at Rs 322.41 crore, up 56.53% Y-o-Y - Moneycontrol.com</t>
+          <t>Aeroflex Neu Allots ₹3 Cr Stake in Stilonn Valves - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Acutaas Chem Consolidated June 2026 Net Sales at Rs 329.67 crore, up 59.08% Y-o-Y - Moneycontrol.com</t>
+          <t>Market Trading Guide: Aeroflex Industries among 2 stock recommendations for Wednesday - The Economic Times</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals - 10 microcap stocks surged up to 170% in 6 months; 5 turned multibaggers - The Economic Times</t>
+          <t>Aeroflex Ind. Consolidated June 2026 Net Sales at Rs 145.38 crore, up 72.38% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1686,68 +1714,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DHARMAJ.NS</t>
+          <t>ALEMBICLTD.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Guard Limited</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>260.6499938964844</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>278</v>
+        <v>98.62999725341797</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>256.8999938964844</v>
+        <v>95.02999877929688</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>271.25</v>
+        <v>98.62999725341797</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>260.6499938964844</v>
+        <v>94.66000366210938</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>271.25</v>
+        <v>98.62999725341797</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>59403</v>
+        <v>593212</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.07</v>
+        <v>4.19</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Insecticides India vs Dharmaj Crop Guard: Which Agro Stock - Univest</t>
+          <t>Alembic fixes Aug 4 record date for FY26 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+          <t>Beta (BBNX) Earnings Update: EPS Clears the Reported Estimate in Latest Trading; After Earnings: Shares Finish 2.21% Lower on the Day - Profitability Analysis - vinanet.vn</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Consolidated June 2026 Net Sales at Rs 382.38 crore, up 4.08% Y-o-Y - Moneycontrol.com</t>
+          <t>Alembic Limited reports 11.8% net profit decline in Q1FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Standalone June 2026 Net Sales at Rs 384.10 crore, up 4.55% Y-o-Y - Moneycontrol.com</t>
+          <t>Alembic Limited shareholders approve FY26 results, dividend with near-unanimous support - scanx.trade</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+          <t>Beta (BBNX) Earnings Update: EPS Clears the Reported Estimate in Latest Trading; After Earnings: Shares Finish 2.21% Lower on the Day - Profitability Analysis - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1755,68 +1783,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>TEMBO.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs Limited</t>
+          <t>Tembo Global Industries Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>157.8500061035156</v>
+        <v>56.34999847412109</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>165.9499969482422</v>
+        <v>59.25</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>156.5099945068359</v>
+        <v>56</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>163.6900024414062</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>157.5399932861328</v>
+        <v>56.29999923706055</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>163.6900024414062</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>32229753</v>
+        <v>929246</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3.9</v>
+        <v>4.17</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs Limited: Top Mutual Funds Holders | PINELABS | INE15B701018 - marketscreener.com</t>
+          <t>2 Companies Declaring Stock Splits in August 2026 - Equitymaster</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs Limited: Top Mutual Funds Holders | PINELABS | INE15B701018 - marketscreener.com</t>
+          <t>Tembo Global Industries forms strategic JV for indigenous UAV manufacturing - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>PINELABS Stock Price and Chart — NSE:PINELABS - TradingView</t>
+          <t>Tembo Global Industries forms strategic JV for indigenous UAV manufacturing - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs Q1 profit soars four-fold YoY to ₹20 crore, revenue jumps 20%; shares surge 5% - Upstox</t>
+          <t>Tembo Global Industries Share Price Outlook: Where It Could Be in 3 Years - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs reports Rs 737 Cr revenue in Q1 FY27; profit jumps over 4X - Entrackr</t>
+          <t>Lake Victoria’s Tembo holds 600K oz. gold near Barrick - The Northern Miner</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1824,61 +1852,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DCMFINSERV.NS</t>
+          <t>MAPMYINDIA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>DCM Financial Services Limited</t>
+          <t>C.E. Info Systems Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>5.130000114440918</v>
+        <v>970</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>5.489999771118164</v>
+        <v>1025</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>5.010000228881836</v>
+        <v>964.2999877929688</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>5.329999923706055</v>
+        <v>1004</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5.130000114440918</v>
+        <v>964.2999877929688</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5.329999923706055</v>
+        <v>1004</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>9336</v>
+        <v>513721</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>3.9</v>
+        <v>4.12</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>MapMyIndia shares drop 8% despite strong Q1 earnings; PAT jumps 8% YoY - The Economic Times</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Shinhan (SHG) Latest Quarter: EPS Clears the Reported Estimate in the Latest Reading; Closing Reaction: Shares Move 4.07% Higher for the Current Session - Earnings Decline Risk - vinanet.vn</t>
+          <t>C.E. Info Systems Ltd (MAPMYINDIA) Share Price - Business Today</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Shinhan (SHG) Latest Quarter: EPS Clears the Reported Estimate in the Latest Reading; Closing Reaction: Shares Move 4.07% Higher for the Current Session - Earnings Decline Risk - vinanet.vn</t>
+          <t>MapmyIndia Q1 Results 2027: PAT Rises 6%, Shares Open 6% Lower - Sahi</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Dcm Financial Services Limited Announces Resignation of Richa Kathuria as Independent Director, Member of the Audit Committee, Nomination and Remuneration Committee and Stakeholders Relationship Committee, Effective August 11, 2026 - marketscreener.com</t>
+          <t>C.E. Info Systems Ltd (MAPMYINDIA) Share Price - Business Today</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
+          <t>Results: C. E. Info Systems Limited Beat Earnings Expectations And Analysts Now Have New Forecasts - simplywall.st</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1927,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2005,7 +2033,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2013,68 +2041,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RPTECH.NS</t>
+          <t>SHAH.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Rashi Peripherals Limited</t>
+          <t>Shah Metacorp Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>868.3499755859375</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>878.4500122070312</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>703.7000122070312</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>779.4500122070312</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>867</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>779.4500122070312</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4680449</v>
+        <v>28315180</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-10.1</v>
+        <v>-20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Rashi Peripherals director quits citing governance lapses - scanx.trade</t>
+          <t>'Not Too High, Not Too Low': Nilesh Shah's Rule For Stock Picking; Check His Sectoral Picks - NDTV Profit</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Rashi Peripherals director quits citing governance lapses - scanx.trade</t>
+          <t>Welspun Corp shares fall as CEO Vipul Shah among likely sellers in Rs 1,433 cr block deals - Business Today</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Rashi Peripherals Limited (NSE:RPTECH) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+          <t>Precigen COO Rutul Shah sells $375,000 in shares - Investing.com India</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits Fresh 52-Week High - Univest</t>
+          <t>Welspun Corp shares fall as CEO Vipul Shah among likely sellers in Rs 1,433 cr block deals - Business Today</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Rashi Peripherals Ltd. Share Price Today - Rashi Peripherals Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>What Is Changing At Shah Rukh Khan's Rs 300-Crore Mannat? Anand Pandit Shares Renovation Details - NDTV</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2082,68 +2110,64 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KOTARISUG.NS</t>
+          <t>KOHINOOR.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Limited</t>
+          <t>Kohinoor Foods Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>38.59999847412109</v>
+        <v>35.5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38.59999847412109</v>
+        <v>36.29999923706055</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>35.25</v>
+        <v>32.75</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>35.25</v>
+        <v>33.59000015258789</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>39.15999984741211</v>
+        <v>35.77999877929688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35.25</v>
+        <v>33.59000015258789</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>805383</v>
+        <v>228119</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.98</v>
+        <v>-6.12</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Share Price Today at Rs 36.35 - Univest</t>
+          <t>Enterprise value to revenue forward of Kohinoor Chemical Company (Bangladesh) PLC – DSEBD:KOHINOOR - TradingView</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
+          <t>Enterprise value to revenue forward of Kohinoor Chemical Company (Bangladesh) PLC – DSEBD:KOHINOOR - TradingView</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Ltd. (KOTARISUG) Share Price Rises 13.52% Today - Univest</t>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Sugars and Chemicals gets NSE no objection for merger with Kothari Petrochemicals - ChiniMandi</t>
-        </is>
-      </c>
+          <t>Kohinoor Textile to install 48MW battery storage amid 9MW solar expansion - Business Recorder</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2151,68 +2175,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KRONOX.NS</t>
+          <t>TAKE.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Limited</t>
+          <t>TAKE Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>205.3600006103516</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>205.3600006103516</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>184.8300018310547</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>186.1399993896484</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>205.3600006103516</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>186.1399993896484</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1026560</v>
+        <v>63703</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.359999999999999</v>
+        <v>-5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Ltd. Share Price News and Valuation - Univest</t>
+          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Ltd. Share Price News and Valuation - Univest</t>
+          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax to acquire 64.26% stake in Kronox Lab Sciences in Rs 246-crore deal - Indian Chemical News</t>
+          <t>Microsoft Just Ripped 28% in a Month. What Would It Take to Get MSFT Stock Up to $600? - 24/7 Wall St.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2220,56 +2244,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>RAJMET.NS</t>
+          <t>KANPRPLA.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Rajnandini Metal Limited</t>
+          <t>Kanpur Plastipack Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.509999990463257</v>
+        <v>282.9500122070312</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.650000095367432</v>
+        <v>283.010009765625</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.130000114440918</v>
+        <v>264</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3.200000047683716</v>
+        <v>264.3599853515625</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3.5</v>
+        <v>277.1900024414062</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.200000047683716</v>
+        <v>264.3599853515625</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2145804</v>
+        <v>26950</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-8.57</v>
+        <v>-4.63</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Rajnandini Metal Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Kanpur Plastipack Share Price Today With Valuation View - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Rajnandini Metal Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack to allot equity shares on warrant conversion - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack shareholders approve all 7 AGM resolutions - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2277,68 +2313,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS.NS</t>
+          <t>GROWW.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems Limited</t>
+          <t>Billionbrains Garage Ventures Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>780.2000122070312</v>
+        <v>199.9799957275391</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>782.5</v>
+        <v>199.9799957275391</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>719</v>
+        <v>195.1000061035156</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>729.4000244140625</v>
+        <v>196</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>780.0999755859375</v>
+        <v>203.0099945068359</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>729.4000244140625</v>
+        <v>196</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1924050</v>
+        <v>169757187</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.5</v>
+        <v>-3.45</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
+          <t>Groww stock falls 3% as 2.1% equity changes hands in Rs 2,500-crore block deal; Ribbit Capital likely... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems: Promoter Group Adjusts Ownership - InvestyWise</t>
+          <t>Five block deals worth over ₹6,000 crore change hands today — Check details here - CNBC TV18</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS: Revenue and profit surged year-over-year, with robust EPS and improved margins - TradingView</t>
+          <t>₹2,500 crore Groww block deal knocks shares down 3% - Dealroom</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Interested In TD Power Systems' (NSE:TDPOWERSYS) Upcoming ₹1.10 Dividend? You Have One Day Left - simplywall.st</t>
+          <t>Daily and Weekly Digest - Latest News and Updates on Digest at Groww - Groww</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
+          <t>Groww Block Deal: Stock down 3% after ₹2,500 crore worth equity changes hands - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2346,68 +2382,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>RAIN.NS</t>
+          <t>PREMIERENE.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Rain Industries Limited</t>
+          <t>Premier Energies Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>213.8899993896484</v>
+        <v>1036.5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>213.8899993896484</v>
+        <v>1040</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>198.3699951171875</v>
+        <v>999.4000244140625</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>200.4900054931641</v>
+        <v>1005.900024414062</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>213.6900024414062</v>
+        <v>1036</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>200.4900054931641</v>
+        <v>1005.900024414062</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4541018</v>
+        <v>1004598</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.18</v>
+        <v>-2.91</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>"2 Hours 15 Minutes In Traffic": Man Shares How Rain Affected His Commute To Bengaluru Airport - NDTV</t>
+          <t>Premier Energies Ltd. Share Price Today: Price Action Review - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+          <t>Premier Energies Ltd. Share Price Today: Price Action Review - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+          <t>Premier Energies Limited (NSE:PREMIERENE) Just Released Its First-Quarter Results And Analysts Are Updating Their Estimates - simplywall.st</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>RAIN Should I Buy - Intellectia AI</t>
+          <t>Premier Energies’ Long-Term Credit Rating Upgraded to A+/Positive by CRISIL - TipRanks</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Just Three Days Till Rain Industries Limited (NSE:RAIN) Will Be Trading Ex-Dividend - simplywall.st</t>
+          <t>CRISIL Upgrades Premier Energies Group to A+ Positive on Bank Facilities - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2415,68 +2451,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>UTTAMSUGAR.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited</t>
+          <t>Uttam Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>24.10000038146973</v>
+        <v>321</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>24.35000038146973</v>
+        <v>329.8999938964844</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>22.20000076293945</v>
+        <v>305.5899963378906</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>22.80999946594238</v>
+        <v>314.8800048828125</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24.22999954223633</v>
+        <v>323.1300048828125</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22.80999946594238</v>
+        <v>314.8800048828125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>113228799</v>
+        <v>323738</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.86</v>
+        <v>-2.55</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
+          <t>Uttam Sugar Mills Q1 Net Profit Plummets 94.69% YoY to ₹85 lakh - Sahi</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2484,56 +2520,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE.NS</t>
+          <t>BI.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Electricals Limited</t>
+          <t>Bilcare Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1801</v>
+        <v>94</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1812</v>
+        <v>96</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1712.599975585938</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1719.599975585938</v>
+        <v>92</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1819.5</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1719.599975585938</v>
+        <v>92</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>120591</v>
+        <v>9407</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.49</v>
+        <v>-2.53</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
+          <t>'Lee Gyu-hyeok♥' Son Dam-bi shares happy parenting moments with her daughter, who inherited her mother's talent - starnewskorea.com</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>'Lee Gyu-hyeok♥' Son Dam-bi shares happy parenting moments with her daughter, who inherited her mother's talent - starnewskorea.com</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Fund Update: New $13.2M $SNDK stock position opened by BI Asset Management Fondsmaeglerselskab A|S - Quiver Quantitative</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Fund Update: New $8.3M $LYG stock position opened by BI Asset Management Fondsmaeglerselskab A|S - Quiver Quantitative</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2541,68 +2589,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GSLSU.NS</t>
+          <t>APOLLOPIPE.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Global Surfaces Limited</t>
+          <t>Apollo Pipes Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30</v>
+        <v>658</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>31.47999954223633</v>
+        <v>664</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>29.82999992370605</v>
+        <v>646.0499877929688</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>29.82999992370605</v>
+        <v>647.2000122070312</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.39999961853027</v>
+        <v>663.75</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29.82999992370605</v>
+        <v>647.2000122070312</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>67344</v>
+        <v>281130</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5</v>
+        <v>-2.49</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Global Surfaces Limited Announces CFO Changes - marketscreener.com</t>
+          <t>Apollo Pipes board to consider raising funds via equity or convertible securities - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Global Surfaces posts ₹25.4m standalone PAT in Q1FY27; re-submits results - scanx.trade</t>
+          <t>Apollo Pipes board to consider raising funds via equity or convertible securities - scanx.trade</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Global Surfaces Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Apollo Pipes appoints Sanjay Gupta as Chairman after AGM approval - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Global Surfaces posts ₹25.4m standalone PAT in Q1FY27; re-submits results - scanx.trade</t>
+          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Global Surfaces Ltd to host Q1-FY27 earnings call on Aug 11 - scanx.trade</t>
+          <t>Apollo Pipes Ltd. (APOLLOPIPE) Share Price Within 2% of 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2610,68 +2658,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TAKE.NS</t>
+          <t>VBL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>TAKE Limited</t>
+          <t>Varun Beverages Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>19.04999923706055</v>
+        <v>447.8999938964844</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>19.29000091552734</v>
+        <v>447.8999938964844</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>425.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>427.3500061035156</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>19.79000091552734</v>
+        <v>438</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>427.3500061035156</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>136633</v>
+        <v>18897319</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.95</v>
+        <v>-2.43</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
+          <t>Varun Beverages Begins First Step To Enter Alcoholic Beverages. But Why Is The Stock Falling? - NDTV Profit</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Commerce Bank Buys Shares of 14,555 Take-Two Interactive Software, Inc. $TTWO - MarketBeat</t>
+          <t>Varun Beverages Begins First Step To Enter Alcoholic Beverages. But Why Is The Stock Falling? - NDTV Profit</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+          <t>Varun Beverages shares: VBL stock plunges 8% after Q2 results; here's why - Business Today</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Enter Energy Somalia: Rapid Stock-take Assessment Report, March 2026 - ReliefWeb</t>
+          <t>VBL shares bounce back after mixed earnings, but can India volume growth hold up? - Livemint</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>It Won’t Take Much to Burst the Stock Market Bubble - Advisor Perspectives</t>
+          <t>VBL Q1 Results 2027: PAT Rises 15% YoY; Revenue Grows 21% - Sahi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2679,68 +2727,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>GRADIENTE.NS</t>
+          <t>TIIL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Gradiente Infotainment Limited</t>
+          <t>Technocraft Industries (India) Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3.029999971389771</v>
+        <v>3460</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3.029999971389771</v>
+        <v>3485.60009765625</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2.839999914169312</v>
+        <v>3355.5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.839999914169312</v>
+        <v>3371.300048828125</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2.980000019073486</v>
+        <v>3454.89990234375</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.839999914169312</v>
+        <v>3371.300048828125</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1970998</v>
+        <v>16621</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.7</v>
+        <v>-2.42</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Gradiente Infotainment Considers Capital Raising Initiatives in Board Meeting - Sahi</t>
+          <t>Technocraft Industries (India) Ltd. (TIIL) Share Price Hits Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Gradiente Asian Fashion Tour India - Mumbai Curtain Raiser Marks the 25th Season with Fashion, Glamour and New Talent - Big News Network.com</t>
+          <t>Technocraft Industries (India) Ltd. (TIIL) Share Price Hits Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Gradiente Infotainment approves ₹65 Cr capex for micro dramas and music videos - scanx.trade</t>
+          <t>Technocraft Industries Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Price Band Hitters, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Major Push for the Orange Economy: Gradiente Infotainment Unveils ₹5,000 Crore Mega Investment Roadmap - The Tribune</t>
-        </is>
-      </c>
+          <t>Tube Investments of India acquires Shanthi Gears shares for Rs 77.49 crore - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2748,68 +2792,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>IIFL.NS</t>
+          <t>BTML.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance Limited</t>
+          <t>Bodhi Tree Multimedia Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>667</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>681.0999755859375</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>643.5499877929688</v>
+        <v>8.649999618530273</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>666.25</v>
+        <v>8.75</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>696.4000244140625</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>666.25</v>
+        <v>8.75</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>8284153</v>
+        <v>294142</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.33</v>
+        <v>-2.34</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance shares decline over 7% after home finance arm receives ₹963 crore income tax demand notice; here's why - Upstox</t>
+          <t>Bodhi Tree Multimedia Share Price Fall and Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance Shares Plunge Nearly 8% on ₹963 Crore Tax Demand - Business Outreach Magazine</t>
+          <t>Bodhi Tree Multimedia Share Price Fall and Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>IFL Finance shares drop 8% as IIFL Home Finance gets Rs 963 crore tax demand - The Economic Times</t>
+          <t>Bodhi Tree Multimedia Ltd. Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance shares crack 8% after ₹963-crore tax demand for subsidiary - Business Standard</t>
+          <t>Bodhi Tree Multimedia Ltd. Share Price Today Gains 10.81% - Univest</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>IIFL Finance shares fall 4% after subsidiary faces Rs 963 crore tax demand - Moneycontrol.com</t>
+          <t>Bodhi Tree Multimedia Ltd. Stock News: Price Rise Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2817,60 +2861,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>RANASUG.NS</t>
+          <t>AARNAV.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Limited</t>
+          <t>Aarnav Fashions Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.77999973297119</v>
+        <v>33.2599983215332</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>16.19000053405762</v>
+        <v>33.2599983215332</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15.01000022888184</v>
+        <v>32.02000045776367</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>15.26000022888184</v>
+        <v>32.5</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15.92000007629395</v>
+        <v>33.2599983215332</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15.26000022888184</v>
+        <v>32.5</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>889584</v>
+        <v>1705</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.15</v>
+        <v>-2.29</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Aarnav Fashions Q1 Results: Net profit drops 11% YoY to ₹168 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Ltd. Share Price Declines Significantly - Univest</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>RSD Finance Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2878,56 +2930,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DATAPATTNS.NS</t>
+          <t>LEMERITE.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Data Patterns (India) Limited</t>
+          <t>Le Merite Exports Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4730</v>
+        <v>23</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>4768.7001953125</v>
+        <v>23.5</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4500.10009765625</v>
+        <v>22.05999946594238</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>4542.2998046875</v>
+        <v>22.3799991607666</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4736.2001953125</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4542.2998046875</v>
+        <v>22.3799991607666</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1198221</v>
+        <v>146721</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.09</v>
+        <v>-2.27</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
+          <t>Do Le Merite Exports' (NSE:LEMERITE) Earnings Warrant Your Attention? - simplywall.st</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Le Merite Exports Limited (LEMERITE.NS) Q4 FY26 Earnings: Modest Revenue Amidst Thin Margins - Quarterly Profit Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>InvestingPro’s Fair Value spotted 45% decline in Le Merite Exports By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Le Merite Exports splits shares 1:5, credits new ISIN - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Le Merite Exports (LEMERITE) Declines Nearly 5%: Testing Key Support Levels - Trend Following Picks - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2935,68 +2999,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>CLEANMAX.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>Clean Max Enviro Energy Solutions Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>57.79999923706055</v>
+        <v>1237.5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>59.5</v>
+        <v>1243</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>54.13999938964844</v>
+        <v>1171</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.65999984741211</v>
+        <v>1206</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>58.0099983215332</v>
+        <v>1233.699951171875</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>55.65999984741211</v>
+        <v>1206</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1072021</v>
+        <v>237790</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.05</v>
+        <v>-2.25</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
+          <t>After muted listing, this stock turns multibagger in just 3 months; should you still buy? - Business Today</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Ltd. Share Price Today: Key Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>The Ugar Sugar Works Ltd. Share Price Near 52-Week High - Univest</t>
-        </is>
-      </c>
+          <t>Clean Max Enviro Energy Solutions Allots 35,800 Equity Shares Under ESOS - SolarQuarter</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3004,68 +3064,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>WHEELS.NS</t>
+          <t>TRIVENI.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Wheels India Limited</t>
+          <t>Triveni Engineering &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1565</v>
+        <v>290.3500061035156</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1579.599975585938</v>
+        <v>294.1199951171875</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1489.099975585938</v>
+        <v>282.1000061035156</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1499.300048828125</v>
+        <v>286.6099853515625</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1561.400024414062</v>
+        <v>292.8800048828125</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1499.300048828125</v>
+        <v>286.6099853515625</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>137084</v>
+        <v>470396</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-3.98</v>
+        <v>-2.14</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Wheels India Approves Issuing 1,269,391 Equity Shares At ₹1,418 To Raise ₹180 Crores - Sahi</t>
+          <t>Triveni Engineering fixes June 3 record date for SSEL merger - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Wheels Up Experience Stock Price Forecast. Should You Buy UP? - StockInvest.us</t>
+          <t>Triveni Turbines releases Q1 FY27 concall transcript with margin guidance - scanx.trade</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>TSF Investments Approves Subscription To Preferential Issue Of Wheels India Equity Shares - TradingView</t>
+          <t>Triveni Turbine Consolidated June 2026 Net Sales at Rs 442.70 crore, up 19.23% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Wheels India board approves ₹180 crore preferential issue at ₹1,418 per share - scanx.trade</t>
+          <t>Triveni Engineering &amp; Industries Share Price Rises 8.27% - Univest</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Stock Alert: Bharat Electronics, Godfrey Phillips India, Wheels India, Tata Chemicals - Business Standard</t>
+          <t>Triveni Turbine shares tumble 8% after Q1 profit drops 20%, margins shrink - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3073,68 +3133,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ALICON.NS</t>
+          <t>ACI.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Alicon Castalloy Limited</t>
+          <t>Archean Chemical Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>727</v>
+        <v>500.75</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>727.25</v>
+        <v>500.75</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>690</v>
+        <v>488.1000061035156</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>697.7999877929688</v>
+        <v>488.75</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>726.5</v>
+        <v>499.25</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>697.7999877929688</v>
+        <v>488.75</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>57256</v>
+        <v>120558</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.95</v>
+        <v>-2.1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Alicon Castalloy declares ₹3 per share final dividend for FY26 - scanx.trade</t>
+          <t>ACI Worldwide (NASDAQ:ACIW) Fits Peter Lynch's Growth-at-a-Reasonable-Price Screen - ChartMill</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>₹8,094 Cr Order Book: Smallcap Stock With BMW, Volkswagen and Bosch as Clients to Add to Your Watchlist - Trade Brains</t>
+          <t>Airport sensing without new cabling: Agereh will discuss its tools in Philadelphia - Stock Titan</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Alicon Castalloy Ltd. Share Price: Major 8.55% Increase - Univest</t>
+          <t>Airport sensing without new cabling: Agereh will discuss its tools in Philadelphia - Stock Titan</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Alicon Castalloy Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
+          <t>ACI Infocom open offer timeline set; Mandavias file draft letter - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Alicon Castalloy approves ₹1,255 mn plant for castings - scanx.trade</t>
+          <t>AC Immune shares rise after encouraging early Phase 1 data for ACI-19764 - Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3142,64 +3202,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>GOCOLORS.NS</t>
+          <t>ADVENTHTL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Go Fashion (India) Limited</t>
+          <t>Advent Hotels International Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>354.7999877929688</v>
+        <v>141.9499969482422</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>354.7999877929688</v>
+        <v>144.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>337.1000061035156</v>
+        <v>138</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>340.25</v>
+        <v>139</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>353.2999877929688</v>
+        <v>141.8300018310547</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>340.25</v>
+        <v>139</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>197680</v>
+        <v>105997</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.69</v>
+        <v>-2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>GOCOLORS Share Price Today - Go Fashion (India) Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>ADVENTHTL Stock Price and Chart — NSE:ADVENTHTL - TradingView</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>GOCOLORS Share Price Today - Go Fashion (India) Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>Advent Hotels International (ADVENTHTL.NS) Faces Pressure Near Resistance; Support at ₹139.29 in Focus - Overnight Profile - vinanet.vn</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Go Fashion (India) Limited Just Missed EPS By 18%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+          <t>Advent Hotels Listing Tomorrow After Valor Estate Demerger - HDFC Sky</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Go Fashion (India) Ltd sees SSSG turn positive in Q1 FY27 as revenue holds steady - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Advent Hotels International (ADVENTHTL.NS) Faces Pressure Near Resistance; Support at ₹139.29 in Focus - Overnight Profile - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Advent Hotels International (ADVENTHTL.NS) Gains 1.79%: Nears Key Resistance at ₹136.96 - NAAIM Exposure - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3207,68 +3271,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>REDINGTON.NS</t>
+          <t>WELCORP.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Redington Limited</t>
+          <t>Welspun Corp Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>365.8999938964844</v>
+        <v>2300</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>366.5</v>
+        <v>2350</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>350.1499938964844</v>
+        <v>2203.699951171875</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>352.6499938964844</v>
+        <v>2300</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>365.1000061035156</v>
+        <v>2345.5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>352.6499938964844</v>
+        <v>2300</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4485539</v>
+        <v>4217184</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.41</v>
+        <v>-1.94</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Redington Share Price hits fresh 52-week high at Rs 364 - Univest</t>
+          <t>Welspun Corp shares rise post Q1 results: Target prices by five analysts - Business Today</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Redington Share Price hits fresh 52-week high at Rs 364 - Univest</t>
+          <t>Welspun Investments approves sale of Welspun Corp stake at ₹2,250 - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Redington shares jump 11% to fresh record high, rally 29% in five sessions; key triggers explained - Upstox</t>
+          <t>Welspun Corp publishes Q1 FY27 earnings call transcript online - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Redington shares rise up to 15% as Q1 net profit nearly doubles to Rs 453 crore - Moneycontrol.com</t>
+          <t>Welspun Corp Ltd. (WELCORP) Share Price Trades Within 2% of 52-Week High - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Redington shares rally 15% after Q1 profit surges 77%; revenue rises 35% YoY - The Economic Times</t>
+          <t>Welspun Corp Ltd. (WELCORP) Share Price Hits Fresh 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 16:30:30 IST</t>
+          <t>2026-08-26 11:29:17 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3276,59 +3340,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SOMICONVEY.NS</t>
+          <t>KUSUMGAR.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Limited</t>
+          <t>Kusumgar Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>98.62000274658203</v>
+        <v>600</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>99.19999694824219</v>
+        <v>600.0499877929688</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>93.19999694824219</v>
+        <v>581.1500244140625</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>94.05999755859375</v>
+        <v>588.2999877929688</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>97.36000061035156</v>
+        <v>599.2000122070312</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>94.05999755859375</v>
+        <v>588.2999877929688</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>27366</v>
+        <v>104765</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.39</v>
+        <v>-1.82</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Up 15.77% Today - Univest</t>
+          <t>Kusumgar Share Price news: valuation and peers in focus - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Up 15.77% Today - Univest</t>
+          <t>Kusumgar Share Price news: valuation and peers in focus - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+          <t>Kusumgar Ltd. Share Price and 52-Week High Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Kusumgar Ltd. Share Price and 52-Week High Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Kusumgar Ltd. Share Price Hits New 52-Week High - Univest</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DTIL.NS</t>
+          <t>RAMBHAJO.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Dhunseri Tea &amp; Industries Limited</t>
+          <t>Advit Jewels Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>172</v>
+        <v>215.0099945068359</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>183.2200012207031</v>
+        <v>255.8399963378906</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>165.1199951171875</v>
+        <v>210.6199951171875</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>183.2200012207031</v>
+        <v>255.6900024414062</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>152.6900024414062</v>
+        <v>213.1999969482422</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>183.2200012207031</v>
+        <v>255.6900024414062</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>437530</v>
+        <v>12226520</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.99</v>
+        <v>19.93</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>A gene-editing treatment for Duchenne muscular dystrophy doses its first patient - Stock Titan</t>
+          <t>ADVIT JEWELS LIMITED Share Price - Live NSE: RAMBHAJO Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Precision BioSciences (DTIL) draws 1.1M-share Weinstein stake - Stock Titan</t>
+          <t>Advit Jewels Delivers Strong FY26 Growth with 33.68% YoY Rise in Income and 35.56% YoY Increase in Net Profit - indiagazette.com</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Precision (DTIL) Momentum: Rises 1.61% to $8.86 in the Current Update; Chart View: the $8.42 to $9.30 Range Remains in Focus for the Current Session - Retracement Entry - vinanet.vn</t>
+          <t>Advit Jewels IPO Listing: Rambhajo Shares Glitter On Debut, List At 37% Premium - Outlook Money</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Precision BioSciences (DTIL) Stock Faces Dilution Risk As Revenue Fades - simplywall.st</t>
+          <t>Advit Jewels IPO: Check Allotment Status &amp; Listing Date Here - Sahi</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Precision BioSciences: Promising HBV Editing Evidence (NASDAQ:DTIL) - Seeking Alpha</t>
+          <t>Jewellery brand Rambhajo parent files RHP, IPO to hit Dalal Street next week - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,64 +622,56 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>TVSSRICHAK.NS</t>
+          <t>DHUNINV.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>TVS Srichakra Limited</t>
+          <t>Dhunseri Investments Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4792.89990234375</v>
+        <v>980</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5322.60009765625</v>
+        <v>1151.75</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4792.89990234375</v>
+        <v>980</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>5313.2001953125</v>
+        <v>1115.900024414062</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4812</v>
+        <v>959.7999877929688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5313.2001953125</v>
+        <v>1115.900024414062</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>84858</v>
+        <v>63610</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>10.42</v>
+        <v>16.26</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>TVS Srichakra Ltd. Share Price Today: Market Cap Context - Univest</t>
+          <t>Dhunseri Investments sees Raj Vardhan Kejriwal complete final director term - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>TVS Srichakra Ltd. Share Price Today: Market Cap Context - Univest</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>TVS Srichakra Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>TVS Srichakra share price jumps16% on robust Q1 earnings performance; profit jumps 165% - Upstox</t>
-        </is>
-      </c>
+          <t>Dhunseri Investments sees Raj Vardhan Kejriwal complete final director term - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -687,68 +679,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ARIES.NS</t>
+          <t>VOEPL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Aries Agro Limited</t>
+          <t>Virtuoso Optoelectronics Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>446.6499938964844</v>
+        <v>508</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>512.5</v>
+        <v>593.4500122070312</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>445.1000061035156</v>
+        <v>497.3999938964844</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>491</v>
+        <v>579.5499877929688</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>446.75</v>
+        <v>498.75</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>491</v>
+        <v>579.5499877929688</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>508690</v>
+        <v>2738595</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>9.9</v>
+        <v>16.2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
+          <t>Virtuoso Optoelectronics Share Price rises 12.29% to Rs 560 - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
+          <t>Virtuoso Optoelectronics Share Price rises 12.29% to Rs 560 - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Aries Agro Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+          <t>Transcript : Virtuoso Optoelectronics Limited, Q1 2027 Earnings Call, Aug 17, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Salesforce (CRM) Stock Analysis Today - Gotrade</t>
+          <t>Virtuoso Optoelectronics Limited announced that it has received INR 662.499446 million in funding from Malabar Investments, Fair Value Capital Management - marketscreener.com</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Daily Nadi Horoscope for Aries (7th August 2026): Moon–Mars Energy May Bring Profit, but Family Peace Nee - The Times of India</t>
+          <t>Virtuoso Optoelectronics Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -756,68 +748,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MEIL.NS</t>
+          <t>RGL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Mangal Electrical Industries Limited</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>280.0499877929688</v>
+        <v>133.3000030517578</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>304.9500122070312</v>
+        <v>159</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>280.0499877929688</v>
+        <v>131.7599945068359</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>298.2999877929688</v>
+        <v>152.5800018310547</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>276.2000122070312</v>
+        <v>132.8699951171875</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>298.2999877929688</v>
+        <v>152.5800018310547</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>538891</v>
+        <v>39921956</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>8</v>
+        <v>14.83</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Why Investors Shouldn't Be Surprised By Mangal Electrical Industries Limited's (NSE:MEIL) 30% Share Price Plunge - simplywall.st</t>
+          <t>Riversgold (ASX:RGL) Shares Jump 20% as Kalgoorlie Gold Development Moves Forward - Kalkine</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Mangal Electrical Industries Limited (MEIL.NS) Mar 2026 Earnings: Moderate Revenue Growth with Higher EPS - vinanet.vn</t>
+          <t>Riversgold (ASX:RGL) Shares Jump 20% as Kalgoorlie Gold Development Moves Forward - Kalkine</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>MEIL Stock Price and Chart — NSE:MEIL - TradingView</t>
+          <t>Should You Be Adding Renaissance Global (NSE:RGL) To Your Watchlist Today? - simplywall.st</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>MEIL Holdings Limited Releases Share Encumbrance on Olectra Greentech Following Loan Closure - scanx.trade</t>
+          <t>Renaissance Global Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Mangal Electrical Industries (MEIL.NS) Holds Near Support After Minor Dip - Price Surge Stocks - vinanet.vn</t>
+          <t>Titan Minerals (ASX:TTM) Shares Jump as New Gold Discovery Returns 33.5m at 6.6 g/t - Kalkine</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -825,68 +817,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>WABAG.NS</t>
+          <t>INDSWFTLAB.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>VA Tech Wabag Limited</t>
+          <t>Ind-Swift Laboratories Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2025.699951171875</v>
+        <v>326</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2144</v>
+        <v>373.7200012207031</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2016.099975585938</v>
+        <v>325.9800109863281</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2142</v>
+        <v>367.4800109863281</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2021.5</v>
+        <v>324.3800048828125</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2142</v>
+        <v>367.4800109863281</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>854170</v>
+        <v>7364038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5.96</v>
+        <v>13.29</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Va Tech Wabag Denies Rs 600 Crore Saudi Arabia Contract, Awaits Kuwait Award Letter - scanx.trade</t>
+          <t>Ind-Swift Laboratories Share Price rises 12.36%: analysis - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Va Tech Wabag Denies Rs 600 Crore Saudi Arabia Contract, Awaits Kuwait Award Letter - scanx.trade</t>
+          <t>Ind-Swift Laboratories Share Price rises 12.36%: analysis - Univest</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>VA Tech Wabag (NSEI:WABAG) Stock Gets Fair Value Boost On Higher P E View - Yahoo Finance</t>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Rekha Jhunjhunwala stock: DIIs triple stake in two years; Systematix lists out triggers - Business Today</t>
+          <t>Ind-Swift Laboratories Limited Is Upgrading the Manufacturing Facility Located At Jammu - marketscreener.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Rekha Jhunjhunwala portfolio stock VA Tech Wabag jumps 5%; Axis Securities raises target price after Q1 results - Livemint</t>
+          <t>Ind-Swift Laboratories secures 99.99% shareholder approval for ₹137.20 crore warrant issue - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -894,68 +886,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER.NS</t>
+          <t>ARIES.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Limited</t>
+          <t>Aries Agro Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>265.0299987792969</v>
+        <v>446.6499938964844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>279.7999877929688</v>
+        <v>517.9000244140625</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>264</v>
+        <v>445.1000061035156</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>278.989990234375</v>
+        <v>503.7000122070312</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>263.4299926757812</v>
+        <v>446.75</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>278.989990234375</v>
+        <v>503.7000122070312</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3064038</v>
+        <v>1074702</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5.91</v>
+        <v>12.75</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
+          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Approves ₹330 Crore Rights Issue at ₹264; Shares Touch All-Time High of ₹282.50 - ACCESS Newswire</t>
+          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Approves Rs 330 Crore Rights Issue at Rs 264; Shares Touch All-Time High of Rs 282.50 - Deccan Chronicle</t>
+          <t>Aries Agro Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80% rally in YTD! Ratnaveer Precision Engineering declares rights issue worth ₹330 crore - Livemint</t>
+          <t>Salesforce (CRM) Stock Analysis Today - Gotrade</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer targets ₹2,500 crore revenue with CCL project - scanx.trade</t>
+          <t>Daily Nadi Horoscope for Aries (7th August 2026): Moon–Mars Energy May Bring Profit, but Family Peace Nee - The Times of India</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -963,68 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>QUESS.NS</t>
+          <t>GENCON.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Quess Corp Limited</t>
+          <t>Generic Engineering Construction and Projects Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>349.5</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>376.5</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>348</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>365.5499877929688</v>
+        <v>46.77000045776367</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>347</v>
+        <v>41.5</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>365.5499877929688</v>
+        <v>46.77000045776367</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4331313</v>
+        <v>1098363</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>5.35</v>
+        <v>12.7</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Only Three Days Left To Cash In On Quess' (NSE:QUESS) Dividend - simplywall.st</t>
+          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 8.63% Today - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Stocks to buy for short term: Grasim, Quess Corp among 6 stocks experts recommend buying today for next 1-2 weeks - Livemint</t>
+          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 8.63% Today - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Quess Corp Ltd. Share Price With Price and Market Cap View - Univest</t>
+          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 12.15% Today - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Quess Corp Q1 net profit jumps 61% on professional staffing, overseas growth - CNBC TV18</t>
+          <t>Geeks of Wrath – Gencon 2026 Wrap Up! - Non-Productive.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Stocks to buy for short term: Grasim, Quess Corp among 6 stocks experts recommend buying today for next 1-2 weeks - Livemint</t>
+          <t>America’s Biggest Gaming Convention Just Wrapped. These Are the Five Board Games We’re Most Excited to Test. - The New York Times</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1032,68 +1024,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ISFT.NS</t>
+          <t>SPLIL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Intrasoft Technologies Limited</t>
+          <t>SPL Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>91.5</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>97.5</v>
+        <v>34.84999847412109</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>91.44000244140625</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>96</v>
+        <v>34.13999938964844</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>91.44000244140625</v>
+        <v>30.5</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>96</v>
+        <v>34.13999938964844</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>82738</v>
+        <v>47626</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>4.99</v>
+        <v>11.93</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>ICEsoft Technologies Canada Corp (CN: ISFT) Share Price, ISFT Stock News, ISFT Share Price &amp; Updates - Kalkine</t>
+          <t>SPL Industries Limited's (NSE:SPLIL) Share Price Not Quite Adding Up - simplywall.st</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>ICEsoft Releases Q2 2026 Financial Results - TradingView</t>
+          <t>SPLIL Q2 2026 Earnings: Revenue Plunges 50% YoY, EPS at ₹2.43 - Earnings Season Review - vinanet.vn</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Intrasoft Technologies Ltd. Share Price News and Analysis - Univest</t>
+          <t>SPL Industries Managing Director Mukesh Kumar Aggarwal Completes Term, Continues as Board Director - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>IntraSoft Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>SPL Industries Ltd: Marginal Gains Amid Consolidation – SPLIL.NS Holds Near Key Support - ETF NAV Deviation - vinanet.vn</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>ICEsoft Releases Q2 2026 Financial Results - TradingView</t>
+          <t>We Think Shareholders May Want To Consider A Review Of SPL Industries Limited's (NSE:SPLIL) CEO Compensation Package - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1101,68 +1093,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>HINDZINC.NS</t>
+          <t>MADHAVIPL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Limited</t>
+          <t>Madhav Infra Projects Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>605</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>623.75</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>600.1500244140625</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>621.4500122070312</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>592.5999755859375</v>
+        <v>7.230000019073486</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>621.4500122070312</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>11140806</v>
+        <v>1016360</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4.87</v>
+        <v>11.07</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Share Price - Live NSE: HINDZINC Stock Price &amp; Chart - Upstox</t>
+          <t>Madhav Infra Projects (NSE:MADHAVIPL) Cyclically Adjusted P - GuruFocus</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Share Price Today: ₹588, the Market's Biggest Faller - The Eastern Herald</t>
+          <t>Madhav Infra Projects (NSE:MADHAVIPL) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Adds Independent Director Appointed by Ministry of Mines - The Globe and Mail</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Hindustan Zinc Share Price Today, August 24, 2026: Closes at ₹604 - The Eastern Herald</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Hindustan Zinc Share Price Today: ₹588, the Market's Biggest Faller - The Eastern Herald</t>
-        </is>
-      </c>
+          <t>Madhav Infra Projects (NSE:MADHAVIPL) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1170,60 +1154,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>OLAELEC.NS</t>
+          <t>ANDREWYU.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited</t>
+          <t>Andrew Yule &amp; Company Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>36.68999862670898</v>
+        <v>26.98999977111816</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>38.68000030517578</v>
+        <v>30.48999977111816</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>36.63000106811523</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>37.90000152587891</v>
+        <v>29.44000053405762</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>36.20000076293945</v>
+        <v>26.76000022888184</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37.90000152587891</v>
+        <v>29.44000053405762</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>65587786</v>
+        <v>916578</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4.7</v>
+        <v>10.01</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Publishes Q1 FY2026 Unaudited Results in Newspapers - The Globe and Mail</t>
+          <t>Andrew Yule &amp; Company Ltd. Share Price Today: 10.87% gain - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited (NSE:OLAELEC) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
+          <t>Andrew Yule &amp; Company Ltd. Share Price Today: 10.87% gain - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited (NSE:OLAELEC) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Andrew Yule &amp; Company Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Andrew Yule &amp; Company Receives BSE Fine of Rs.5,42,800 for Board Composition Non-Compliance - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Andrew Yule &amp; Co. Ltd. Announces Appointment of Singhai Sanjay Jain as Non-official Independent Director, Effective August 17, 2026 - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1231,68 +1223,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SURYODAY.NS</t>
+          <t>MILKYMIST.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Suryoday Small Finance Bank Limited</t>
+          <t>Milky Mist Dairy Food Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>151.4900054931641</v>
+        <v>201.8999938964844</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>160.8800048828125</v>
+        <v>222.1100006103516</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>151.4900054931641</v>
+        <v>198.0599975585938</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>157.8000030517578</v>
+        <v>222.1100006103516</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>151.0200042724609</v>
+        <v>201.9199981689453</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>157.8000030517578</v>
+        <v>222.1100006103516</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>449439</v>
+        <v>20875349</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4.49</v>
+        <v>10</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Despite Suryoday Small Finance Bank's Pullback, Insiders Still Gained ₹1.9m - simplywall.st</t>
+          <t>Diluted shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Suryoday Small Finance Bank Q4 FY26: Gross Advances At ₹13,201 Crore, Up 29% YoY - scanx.trade</t>
+          <t>Diluted shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Suryoday Small Finance Bank Q4 FY26: Gross Advances At ₹13,201 Crore, Up 29% YoY - scanx.trade</t>
+          <t>Milky Mist Dairy Food Limited Share Price - Upstox</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Suryoday Small Finance Bank Share Price Falls 9.5% Today - Univest</t>
+          <t>Milky Mist Dairy Food Limited Stock (MILKYMIST) - Quote NSE India S.E. - marketscreener.com</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Suryoday Small Finance Bank vs Utkarsh Small Finance Bank: Which Stock Should You Track - Univest</t>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1300,68 +1292,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PARAS.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence and Space Technologies Limited</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1450.099975585938</v>
+        <v>54</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1510</v>
+        <v>56.47999954223633</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1435</v>
+        <v>53.5</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1508.599975585938</v>
+        <v>56.47999954223633</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1445.199951171875</v>
+        <v>51.34999847412109</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1508.599975585938</v>
+        <v>56.47999954223633</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>698453</v>
+        <v>5796445</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>4.39</v>
+        <v>9.99</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Bonus, dividends &amp; stock splits: Paras Defence, NBCC, MCX among 67 stocks turning ex-record date this week - The Economic Times</t>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Stock Market Live | Coal India, Tejas Network, Tata Steel, Paras Defence Share में क्या करें? Anas Sarwar (iWHytEj8x1) - Mshale</t>
+          <t>PVP Ventures Ltd Forms Golden Cross Amid Strong Technical Momentum and Micro-Cap Caveats - MarketsMojo</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>MCX, Honasa Consumer, Paras Defence, other upcoming dividend stocks, bonus issues in focus this week; check list - Upstox</t>
+          <t>PVP Ventures Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+          <t>PVP Ventures Ltd Locks at Upper Circuit With 3.44% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Corporate Actions This Week: P&amp;G Health, Gillette India, PFC, TD Power, Senco Gold, Paras Defence &amp; More - NDTV Profit</t>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1369,68 +1361,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK.NS</t>
+          <t>NECLIFE.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DCB Bank Limited</t>
+          <t>Nectar Lifesciences Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>210</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>216.6699981689453</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>209.2400054931641</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>216.3000030517578</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>207.3699951171875</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>216.3000030517578</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4060703</v>
+        <v>1472512</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4.31</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>DCB Bank Ltd. Share Price: Price, Valuation, Sector View - Univest</t>
+          <t>Nectar Lifesciences Limited Changes Its Corporate Office in Chandigarh - marketscreener.com</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>DCB Bank Ltd. Share Price: Price, Valuation, Sector View - Univest</t>
+          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think DCB Bank (NSE:DCBBANK) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>DCB Bank Share Price at 52-week high: price, fundamentals - Univest</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Bank Stock to Buy Now for an Upside of 54%; Recommended by Anand Rathi - Trade Brains</t>
-        </is>
-      </c>
+          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1438,68 +1426,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>IDBI.NS</t>
+          <t>SAKUMA.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>IDBI Bank Limited</t>
+          <t>Sakuma Exports Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>87.34999847412109</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>92.69999694824219</v>
+        <v>1.789999961853027</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>87.34999847412109</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>92.08999633789062</v>
+        <v>1.789999961853027</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>88.30999755859375</v>
+        <v>1.629999995231628</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>92.08999633789062</v>
+        <v>1.789999961853027</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>20477384</v>
+        <v>2329582</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4.28</v>
+        <v>9.82</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>IDBI Bank Share Price Jumps 10% In Trade: What's Driving The Rally? - NDTV Profit</t>
+          <t>Sakuma Exports consolidated net profit rises 70.91% in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>IDBI Bank Shares Surge Over 10%! Fairfax Deal May Be Near, Government, LIC Stake Sale &amp; RBI Challenges - Thekanal</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>LIC stake sale in IDBI Bank: Officers’ body seeks IRDAI intervention - BusinessLine</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Centre may clear Fairfax bid for controlling stake in IDBI Bank within a week: Report - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>IDBI Bank shares rise 2% as lender clarifies on surge in trading volumes; details here - Business Today</t>
-        </is>
-      </c>
+          <t>Sakuma Exports consolidated net profit rises 70.91% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1507,68 +1483,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>OLECTRA.NS</t>
+          <t>LADDERUP.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Olectra Greentech Limited</t>
+          <t>Ladderup Finance Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1294.900024414062</v>
+        <v>50</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1359.199951171875</v>
+        <v>53.95000076293945</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1294.900024414062</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1346.800048828125</v>
+        <v>53.47000122070312</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1291.800048828125</v>
+        <v>49</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1346.800048828125</v>
+        <v>53.47000122070312</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>562972</v>
+        <v>139</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.26</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Olectra Greentech Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>Blue Cloud Softech Solutions Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Olectra Greentech Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>Blue Cloud Softech Solutions Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Olectra rally 7% on order win from BEST - Upstox</t>
+          <t>Ladderup Finance sets Sep 17 record date for 33rd AGM - scanx.trade</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Olectra Greentech Q1FY27 revenue up 66% YoY to ₹575.5 crore - scanx.trade</t>
+          <t>Ladderup Fin Consolidated June 2026 Net Sales at Rs 9.32 crore, up 61.22% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Olectra Greentech Shares Decline Nearly 4% After Q1 Results - NDTV Profit</t>
+          <t>Ladderup Finance Q1 FY27 Results: Revenue Rs 9 Cr, PAT Rs 3 Cr and Key Highlights - Univest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1576,68 +1552,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CYIENT.NS</t>
+          <t>RRECL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Cyient Limited</t>
+          <t>RDB Real Estate Constructions Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>994</v>
+        <v>151.9900054931641</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1054.849975585938</v>
+        <v>151.9900054931641</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>984.5</v>
+        <v>151</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1020.25</v>
+        <v>151.6600036621094</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>979.0499877929688</v>
+        <v>139</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1020.25</v>
+        <v>151.6600036621094</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>7154604</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.21</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Cyient shares jump 4% after investor day; JPMorgan sees ₹1,050 target on double-digit growth outlook - CNBC TV18</t>
+          <t>RDB Real Estate Constructions (RRECL) Share Price Falls 9.14% to Rs 126.3, Among Top Losers Today - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Cyient shares rocket 8% after investor day, but brokerages see up to 24% downside. Here’s why - The Economic Times</t>
+          <t>RDB Real Estate Constructions (NSE:RRECL) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Cyient shares soar 8% as CCI approves acquisition of California-based Tao Digital Solutions - Upstox</t>
+          <t>RDB Real Estate Constructions (NSE:RRECL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Cyient Stock: JPMorgan Sees Transformation, Morgan Stanley Waits for Execution - NDTV Profit</t>
+          <t>RDB Real Estate Constructions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Cyient shares surge 8%: Targets by MOFSL, Antique, Choice, Nuvama post Investor Day - Business Today</t>
+          <t>RDB Real Estate Constructions Share Price Today Up 9.8% - Univest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1645,68 +1621,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>AEROFLEX.NS</t>
+          <t>PACIFICI.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Limited</t>
+          <t>Pacific Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>496</v>
+        <v>133.1000061035156</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>517.5999755859375</v>
+        <v>152</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>492</v>
+        <v>133.1000061035156</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>516.5</v>
+        <v>146.6699981689453</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>495.75</v>
+        <v>134.4499969482422</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>516.5</v>
+        <v>146.6699981689453</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>965740</v>
+        <v>1330</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.19</v>
+        <v>9.09</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+          <t>Pacific Industries (NSE:PACIFICI) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Neu Allots ₹3 Cr Stake in Stilonn Valves - scanx.trade</t>
+          <t>Pacific Industries (NSE:PACIFICI) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Neu Allots ₹3 Cr Stake in Stilonn Valves - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Market Trading Guide: Aeroflex Industries among 2 stock recommendations for Wednesday - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Aeroflex Ind. Consolidated June 2026 Net Sales at Rs 145.38 crore, up 72.38% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1714,68 +1682,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ALEMBICLTD.NS</t>
+          <t>TECILCHEM.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>TECIL Chemicals and Hydro Power Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>95.86000061035156</v>
+        <v>9.289999961853027</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>98.62999725341797</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>95.02999877929688</v>
+        <v>8</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>98.62999725341797</v>
+        <v>9.489999771118164</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>94.66000366210938</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>98.62999725341797</v>
+        <v>9.489999771118164</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>593212</v>
+        <v>70146</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.19</v>
+        <v>9.08</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Alembic fixes Aug 4 record date for FY26 dividend - scanx.trade</t>
+          <t>TECIL Chemicals (TECILCHEM) Declines to ₹11.6, Approaches Key Support Zone - McClellan Summation - vinanet.vn</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Beta (BBNX) Earnings Update: EPS Clears the Reported Estimate in Latest Trading; After Earnings: Shares Finish 2.21% Lower on the Day - Profitability Analysis - vinanet.vn</t>
+          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - vinanet.vn</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Alembic Limited reports 11.8% net profit decline in Q1FY26 - scanx.trade</t>
+          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - vinanet.vn</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Alembic Limited shareholders approve FY26 results, dividend with near-unanimous support - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Beta (BBNX) Earnings Update: EPS Clears the Reported Estimate in Latest Trading; After Earnings: Shares Finish 2.21% Lower on the Day - Profitability Analysis - vinanet.vn</t>
-        </is>
-      </c>
+          <t>Tecil Chemicals board to meet on May 27 for Q4FY26 results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1783,68 +1747,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>TEMBO.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Tembo Global Industries Limited</t>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>56.34999847412109</v>
+        <v>283</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>59.25</v>
+        <v>309.2000122070312</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>56</v>
+        <v>277.0499877929688</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>58.65000152587891</v>
+        <v>305.7999877929688</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>56.29999923706055</v>
+        <v>280.3500061035156</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>58.65000152587891</v>
+        <v>305.7999877929688</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>929246</v>
+        <v>3966721</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.17</v>
+        <v>9.08</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2 Companies Declaring Stock Splits in August 2026 - Equitymaster</t>
+          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Tembo Global Industries forms strategic JV for indigenous UAV manufacturing - scanx.trade</t>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Tembo Global Industries forms strategic JV for indigenous UAV manufacturing - scanx.trade</t>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Tembo Global Industries Share Price Outlook: Where It Could Be in 3 Years - Univest</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Lake Victoria’s Tembo holds 600K oz. gold near Barrick - The Northern Miner</t>
-        </is>
-      </c>
+          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1852,61 +1812,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MAPMYINDIA.NS</t>
+          <t>SBFC.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>C.E. Info Systems Limited</t>
+          <t>SBFC Finance Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>970</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1025</v>
+        <v>102.2099990844727</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>964.2999877929688</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1004</v>
+        <v>101.1399993896484</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>964.2999877929688</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1004</v>
+        <v>101.1399993896484</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>513721</v>
+        <v>17100733</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4.12</v>
+        <v>9.02</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>MapMyIndia shares drop 8% despite strong Q1 earnings; PAT jumps 8% YoY - The Economic Times</t>
+          <t>Volumes jump at SBFC Finance Ltd counter - Business Standard</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>C.E. Info Systems Ltd (MAPMYINDIA) Share Price - Business Today</t>
+          <t>Volumes jump at SBFC Finance Ltd counter - Business Standard</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>MapmyIndia Q1 Results 2027: PAT Rises 6%, Shares Open 6% Lower - Sahi</t>
+          <t>Top Gainers &amp; Losers on 26 Aug: SBFC Finance, Capri Global, Hindustan Copper, SAIL, OLA, Vedanta among top gainers - Livemint</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>C.E. Info Systems Ltd (MAPMYINDIA) Share Price - Business Today</t>
+          <t>SBFC Finance Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Results: C. E. Info Systems Limited Beat Earnings Expectations And Analysts Now Have New Forecasts - simplywall.st</t>
+          <t>SBFC Finance vs MAS Financial Services: Which MSME NBFC Stock - Univest</t>
         </is>
       </c>
     </row>
@@ -1926,8 +1886,8 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2033,7 +1993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2041,68 +2001,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SHAH.NS</t>
+          <t>ELITECON.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Shah Metacorp Limited</t>
+          <t>Elitecon International Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.299999952316284</v>
+        <v>13.88000011444092</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.299999952316284</v>
+        <v>14.27000045776367</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.559999942779541</v>
+        <v>12.39000034332275</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2.559999942779541</v>
+        <v>12.39000034332275</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3.200000047683716</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.559999942779541</v>
+        <v>12.39000034332275</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>28315180</v>
+        <v>8072629</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-20</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>'Not Too High, Not Too Low': Nilesh Shah's Rule For Stock Picking; Check His Sectoral Picks - NDTV Profit</t>
+          <t>Elitecon International Ltd Hits Intraday Low Amid Price Pressure - MarketsMojo</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp shares fall as CEO Vipul Shah among likely sellers in Rs 1,433 cr block deals - Business Today</t>
+          <t>Elitecon International Ltd Hits Intraday Low Amid Price Pressure - MarketsMojo</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Precigen COO Rutul Shah sells $375,000 in shares - Investing.com India</t>
+          <t>Elitecon International: Kumar Anubhav Upadhyay ceases as Additional Director - scanx.trade</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp shares fall as CEO Vipul Shah among likely sellers in Rs 1,433 cr block deals - Business Today</t>
+          <t>Small-cap stock under ₹50 Elitecon International hits 10% upper circuit for second day in a row - Livemint</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>What Is Changing At Shah Rukh Khan's Rs 300-Crore Mannat? Anand Pandit Shares Renovation Details - NDTV</t>
+          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2110,56 +2070,56 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KOHINOOR.NS</t>
+          <t>NEXTMEDIA.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Limited</t>
+          <t>Next Mediaworks Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>35.5</v>
+        <v>3.910000085830688</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>36.29999923706055</v>
+        <v>3.950000047683716</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>32.75</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>33.59000015258789</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>35.77999877929688</v>
+        <v>3.910000085830688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>33.59000015258789</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>228119</v>
+        <v>80986</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-6.12</v>
+        <v>-8.44</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value to revenue forward of Kohinoor Chemical Company (Bangladesh) PLC – DSEBD:KOHINOOR - TradingView</t>
+          <t>Next Mediaworks schedules 45th AGM for Sep 22 via video conference - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value to revenue forward of Kohinoor Chemical Company (Bangladesh) PLC – DSEBD:KOHINOOR - TradingView</t>
+          <t>Next Mediaworks schedules 45th AGM for Sep 22 via video conference - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+          <t>Next Mediaworks Q1FY26 loss narrows to ₹88 lakh as going concern risk persists - scanx.trade</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Kohinoor Textile to install 48MW battery storage amid 9MW solar expansion - Business Recorder</t>
+          <t>MannKind Corporation (MNKD) Declines 4.38% to $3.93 as Shares Approach Key Support - Put Spread Alert - vinanet.vn</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -2167,7 +2127,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2175,68 +2135,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>TAKE.NS</t>
+          <t>FILATEX.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>TAKE Limited</t>
+          <t>Filatex India Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>82.11000061035156</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>70.73999786376953</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>75.19000244140625</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>82.11000061035156</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>75.19000244140625</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>63703</v>
+        <v>10801532</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-5</v>
+        <v>-8.43</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
+          <t>Filatex India shares can rally to Rs 118? Why Equirus Prive initiated coverage on the stock - The Economic Times</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
+          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+          <t>Filatex Fashions fined ₹24,780 each by NSE, BSE for non-compliance - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
+          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Microsoft Just Ripped 28% in a Month. What Would It Take to Get MSFT Stock Up to $600? - 24/7 Wall St.</t>
+          <t>Filatex India vs Indo Rama Synthetics India: Which Fibre Stock to Track - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2244,68 +2204,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>SAMBANDAM.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Limited</t>
+          <t>Sambandam Spinning Mills Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>282.9500122070312</v>
+        <v>135.1999969482422</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>283.010009765625</v>
+        <v>135.1999969482422</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>264</v>
+        <v>124</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>264.3599853515625</v>
+        <v>125.4700012207031</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>277.1900024414062</v>
+        <v>134.1399993896484</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>264.3599853515625</v>
+        <v>125.4700012207031</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>26950</v>
+        <v>6243</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-4.63</v>
+        <v>-6.46</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Share Price Today With Valuation View - Univest</t>
+          <t>Sambandam Spinning Mills FY26 Results: Net loss narrows to ₹5.74 crore - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+          <t>Sambandam Spinning Mills FY26 Results: Net loss narrows to ₹5.74 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack to allot equity shares on warrant conversion - scanx.trade</t>
+          <t>SAMBANDAM Stock Price and Chart — NSE:SAMBANDAM - TradingView</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+          <t>Sambandam Spinning Mills Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack shareholders approve all 7 AGM resolutions - scanx.trade</t>
+          <t>dj mediaprint and logistics ltd leads losers in b group - Capital Market</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2313,68 +2273,48 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>GROWW.NS</t>
+          <t>WHBRADY.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Billionbrains Garage Ventures Limited</t>
+          <t>WH Brady &amp; Company Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>199.9799957275391</v>
+        <v>500</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>199.9799957275391</v>
+        <v>500.0499877929688</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>195.1000061035156</v>
+        <v>497.5499877929688</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>196</v>
+        <v>497.7999877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>203.0099945068359</v>
+        <v>529.9500122070312</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>196</v>
+        <v>497.7999877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>169757187</v>
+        <v>176</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Groww stock falls 3% as 2.1% equity changes hands in Rs 2,500-crore block deal; Ribbit Capital likely... - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Five block deals worth over ₹6,000 crore change hands today — Check details here - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>₹2,500 crore Groww block deal knocks shares down 3% - Dealroom</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Daily and Weekly Digest - Latest News and Updates on Digest at Groww - Groww</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Groww Block Deal: Stock down 3% after ₹2,500 crore worth equity changes hands - CNBC TV18</t>
-        </is>
-      </c>
+        <v>-6.07</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2382,68 +2322,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PREMIERENE.NS</t>
+          <t>TANLA.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Premier Energies Limited</t>
+          <t>Tanla Platforms Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1036.5</v>
+        <v>558</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1040</v>
+        <v>563.9000244140625</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>999.4000244140625</v>
+        <v>522.0999755859375</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1005.900024414062</v>
+        <v>526.0499877929688</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1036</v>
+        <v>556.0499877929688</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1005.900024414062</v>
+        <v>526.0499877929688</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1004598</v>
+        <v>1298318</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-2.91</v>
+        <v>-5.4</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Premier Energies Ltd. Share Price Today: Price Action Review - Univest</t>
+          <t>Route Mobile vs Tanla Platforms: Which CPaaS Stock to Track - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Premier Energies Ltd. Share Price Today: Price Action Review - Univest</t>
+          <t>Tanla Platforms Share Pros and Cons 2026 | TANLA CPaaS Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Premier Energies Limited (NSE:PREMIERENE) Just Released Its First-Quarter Results And Analysts Are Updating Their Estimates - simplywall.st</t>
+          <t>Tanla Platforms Share Pros and Cons 2026 | TANLA CPaaS Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Premier Energies’ Long-Term Credit Rating Upgraded to A+/Positive by CRISIL - TipRanks</t>
+          <t>Tanla Platforms Consolidated June 2026 Net Sales at Rs 1,226.39 crore, up 17.85% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>CRISIL Upgrades Premier Energies Group to A+ Positive on Bank Facilities - TipRanks</t>
+          <t>Tanla Platforms Standalone June 2026 Net Sales at Rs 214.34 crore, up 28.41% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2451,68 +2391,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR.NS</t>
+          <t>VIYASH.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Limited</t>
+          <t>Viyash Scientific Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>321</v>
+        <v>268.8500061035156</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>329.8999938964844</v>
+        <v>271.1499938964844</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>305.5899963378906</v>
+        <v>259.1000061035156</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>314.8800048828125</v>
+        <v>263.3999938964844</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>323.1300048828125</v>
+        <v>278.3500061035156</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>314.8800048828125</v>
+        <v>263.3999938964844</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>323738</v>
+        <v>115373365</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-2.55</v>
+        <v>-5.37</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Q1 Net Profit Plummets 94.69% YoY to ₹85 lakh - Sahi</t>
+          <t>Six block deals worth over ₹6,000 crore change hands today — Check details here - CNBC TV18</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
+          <t>Viyash Scientific Ltd leads losers in 'A' group - Business Standard</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
+          <t>Viyash Scientific Share Price Gains 7.19%, Most in Three Months - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
+          <t>Viyash Scientif Consolidated June 2026 Net Sales at Rs 946.36 crore, up 114.39% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+          <t>Viyash Scientif Standalone June 2026 Net Sales at Rs 353.69 crore, up 761.19% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2520,68 +2460,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BI.NS</t>
+          <t>DCMSRIND.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bilcare Limited</t>
+          <t>DCM Shriram Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>94</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>96</v>
+        <v>51.38000106811523</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>92</v>
+        <v>47.27999877929688</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>92</v>
+        <v>47.84000015258789</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>94.38999938964844</v>
+        <v>50.5</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>92</v>
+        <v>47.84000015258789</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>9407</v>
+        <v>268616</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-2.53</v>
+        <v>-5.27</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>'Lee Gyu-hyeok♥' Son Dam-bi shares happy parenting moments with her daughter, who inherited her mother's talent - starnewskorea.com</t>
+          <t>DCM Shriram Industries Limited (NSE:DCMSRIND) Stock Goes Ex-Dividend In Just Three Days - simplywall.st</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>'Lee Gyu-hyeok♥' Son Dam-bi shares happy parenting moments with her daughter, who inherited her mother's talent - starnewskorea.com</t>
+          <t>DCM Shriram Industries (DCMSRIND.NS) Slips 2.89% to ₹40.0: Support at ₹38.0 Under Focus - Wave Truncation - vinanet.vn</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Fund Update: New $13.2M $SNDK stock position opened by BI Asset Management Fondsmaeglerselskab A|S - Quiver Quantitative</t>
+          <t>DCM Shriram Industries (DCMSRIND.NS) Slips 2.89% to ₹40.0: Support at ₹38.0 Under Focus - Wave Truncation - vinanet.vn</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+          <t>DCM Shriram Industries Limited's (NSE:DCMSRIND) 68% Dip In Price Shows Sentiment Is Matching Earnings - simplywall.st</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Fund Update: New $8.3M $LYG stock position opened by BI Asset Management Fondsmaeglerselskab A|S - Quiver Quantitative</t>
+          <t>DCM Shriram Industries (DCMSRIND.NS) Mild Decline in Range-Bound Trading – Key Levels in Focus - Option Breadth - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2589,68 +2529,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>APOLLOPIPE.NS</t>
+          <t>SHYAMTEL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes Limited</t>
+          <t>Shyam Telecom Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>658</v>
+        <v>13.82999992370605</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>664</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>646.0499877929688</v>
+        <v>13.02000045776367</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>647.2000122070312</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>663.75</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>647.2000122070312</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>281130</v>
+        <v>7708</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-2.49</v>
+        <v>-5.12</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes board to consider raising funds via equity or convertible securities - scanx.trade</t>
+          <t>Shyam Telecom (SHYAMTEL.NS) Slides 2% Amid Weak Volume – Key Support at ₹19.16 in Focus - Dynamic Hedging - vinanet.vn</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes board to consider raising funds via equity or convertible securities - scanx.trade</t>
+          <t>SHYAMTEL Q4 FY26 Earnings: Net Loss Persists as Business Activities Remain Minimal - Margin Compression Risk - vinanet.vn</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes appoints Sanjay Gupta as Chairman after AGM approval - scanx.trade</t>
+          <t>SHYAMTEL Mar 2026 Earnings: Continued Revenue Absence and Nominal Loss - Dividend Increase Stocks - vinanet.vn</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
+          <t>SHYAMTEL Mar 2026 Earnings: Revenue Stays at Zero, EPS Remains Negative Amidst Operational Lull - Debt Analysis Report - vinanet.vn</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Apollo Pipes Ltd. (APOLLOPIPE) Share Price Within 2% of 52-Week High - Univest</t>
+          <t>Shyam Telecom Limited Q4 FY26 Earnings: Zero Revenue and Negative EPS Highlight Persistent Operational Challenges - Financial Summary - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2658,68 +2598,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VBL.NS</t>
+          <t>KANPRPLA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Varun Beverages Limited</t>
+          <t>Kanpur Plastipack Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>447.8999938964844</v>
+        <v>282.9500122070312</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>447.8999938964844</v>
+        <v>283.010009765625</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>425.25</v>
+        <v>260.3200073242188</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>427.3500061035156</v>
+        <v>263.2699890136719</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>438</v>
+        <v>277.1900024414062</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>427.3500061035156</v>
+        <v>263.2699890136719</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>18897319</v>
+        <v>47054</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-2.43</v>
+        <v>-5.02</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Varun Beverages Begins First Step To Enter Alcoholic Beverages. But Why Is The Stock Falling? - NDTV Profit</t>
+          <t>Kanpur Plastipack Share Price Today With Valuation View - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Varun Beverages Begins First Step To Enter Alcoholic Beverages. But Why Is The Stock Falling? - NDTV Profit</t>
+          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Varun Beverages shares: VBL stock plunges 8% after Q2 results; here's why - Business Today</t>
+          <t>Kanpur Plastipack to allot equity shares on warrant conversion - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>VBL shares bounce back after mixed earnings, but can India volume growth hold up? - Livemint</t>
+          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>VBL Q1 Results 2027: PAT Rises 15% YoY; Revenue Grows 21% - Sahi</t>
+          <t>Kanpur Plastipack shareholders approve all 7 AGM resolutions - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2727,56 +2667,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>TIIL.NS</t>
+          <t>SIMPLXREA.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Technocraft Industries (India) Limited</t>
+          <t>Simplex Realty Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3460</v>
+        <v>132</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3485.60009765625</v>
+        <v>132</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>3355.5</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3371.300048828125</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3454.89990234375</v>
+        <v>132</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3371.300048828125</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>16621</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-2.42</v>
+        <v>-5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Technocraft Industries (India) Ltd. (TIIL) Share Price Hits Fresh 52-Week High - Univest</t>
+          <t>Total common shares outstanding of Simplex Realty Limited – NSE:SIMPLXREA - TradingView</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Technocraft Industries (India) Ltd. (TIIL) Share Price Hits Fresh 52-Week High - Univest</t>
+          <t>Simplex Realty (NSE:SIMPLXREA) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Technocraft Industries Share Price at Fresh 52-Week High - Univest</t>
+          <t>Simplex Realty Limited Announces Board and Committee Changes, Effective August 5, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Tube Investments of India acquires Shanthi Gears shares for Rs 77.49 crore - Business Upturn</t>
+          <t>Simplex Realty (NSE:SIMPLXREA) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -2784,7 +2724,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2792,68 +2732,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BTML.NS</t>
+          <t>NATIONSTD.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Bodhi Tree Multimedia Limited</t>
+          <t>National Standard (India) Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9.090000152587891</v>
+        <v>110.0199966430664</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>9.090000152587891</v>
+        <v>114.9000015258789</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8.649999618530273</v>
+        <v>108.879997253418</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>8.75</v>
+        <v>108.879997253418</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8.960000038146973</v>
+        <v>114.6100006103516</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8.75</v>
+        <v>108.879997253418</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>294142</v>
+        <v>171484</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-2.34</v>
+        <v>-5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Bodhi Tree Multimedia Share Price Fall and Stock Analysis - Univest</t>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bodhi Tree Multimedia Share Price Fall and Stock Analysis - Univest</t>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bodhi Tree Multimedia Ltd. Share Price: Price Rise Analysis - Univest</t>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Bodhi Tree Multimedia Ltd. Share Price Today Gains 10.81% - Univest</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Bodhi Tree Multimedia Ltd. Stock News: Price Rise Analysis - Univest</t>
-        </is>
-      </c>
+          <t>National Standard (India) sets Aug 28 date for 63rd AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2861,68 +2797,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>AARNAV.NS</t>
+          <t>TAKE.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Limited</t>
+          <t>TAKE Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>33.2599983215332</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>33.2599983215332</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>32.02000045776367</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>32.5</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>33.2599983215332</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>32.5</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1705</v>
+        <v>82918</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-2.29</v>
+        <v>-5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+          <t>Silver Mines Shares Retreat as Precious-Metal Traders Take Profits - Kalkine</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Q1 Results: Net profit drops 11% YoY to ₹168 lakh - scanx.trade</t>
+          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Ltd. Share Price Declines Significantly - Univest</t>
+          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>RSD Finance Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Silver Mines Shares Retreat as Precious-Metal Traders Take Profits - Kalkine</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2930,68 +2866,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>LEMERITE.NS</t>
+          <t>SIEL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Le Merite Exports Limited</t>
+          <t>Superior Industrial Enterprises Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>23</v>
+        <v>34.45000076293945</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>23.5</v>
+        <v>34.45000076293945</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>22.05999946594238</v>
+        <v>32.84999847412109</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>22.3799991607666</v>
+        <v>32.84999847412109</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.89999961853027</v>
+        <v>34.56999969482422</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22.3799991607666</v>
+        <v>32.84999847412109</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>146721</v>
+        <v>3833</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-2.27</v>
+        <v>-4.98</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Do Le Merite Exports' (NSE:LEMERITE) Earnings Warrant Your Attention? - simplywall.st</t>
+          <t>SIEL Stock Price and Chart — NSE:SIEL - TradingView</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Le Merite Exports Limited (LEMERITE.NS) Q4 FY26 Earnings: Modest Revenue Amidst Thin Margins - Quarterly Profit Report - vinanet.vn</t>
+          <t>5 Under the Radar Trading Stocks in India - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>InvestingPro’s Fair Value spotted 45% decline in Le Merite Exports By Investing.com - Investing.com India</t>
+          <t>5 Under the Radar Trading Stocks in India - Univest</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Le Merite Exports splits shares 1:5, credits new ISIN - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Le Merite Exports (LEMERITE) Declines Nearly 5%: Testing Key Support Levels - Trend Following Picks - vinanet.vn</t>
-        </is>
-      </c>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2999,64 +2931,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CLEANMAX.NS</t>
+          <t>AQYLON.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Clean Max Enviro Energy Solutions Limited</t>
+          <t>Aqylon Nexus Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1237.5</v>
+        <v>24.34000015258789</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1243</v>
+        <v>24.79000091552734</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1171</v>
+        <v>23.94000053405762</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1206</v>
+        <v>23.95000076293945</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1233.699951171875</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1206</v>
+        <v>23.95000076293945</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>237790</v>
+        <v>1652410</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-2.25</v>
+        <v>-4.96</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+          <t>Leading Leasing Finance Increases Stake in Aqylon Nexus to 14.17% - scanx.trade</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+          <t>Leading Leasing Finance Increases Stake in Aqylon Nexus to 14.17% - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>After muted listing, this stock turns multibagger in just 3 months; should you still buy? - Business Today</t>
+          <t>Leading Leasing sells 1.47 cr Aqylon Nexus shares - scanx.trade</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Clean Max Enviro Energy Solutions Allots 35,800 Equity Shares Under ESOS - SolarQuarter</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Leading Leasing raises Aqylon Nexus stake to 10.30% via open market buy - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Aqylon Nexus appoints Rupareliya as director, Sanghani as CFO - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3064,68 +3000,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI.NS</t>
+          <t>ABINFRA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Triveni Engineering &amp; Industries Limited</t>
+          <t>A B Infrabuild Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>290.3500061035156</v>
+        <v>12.01000022888184</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>294.1199951171875</v>
+        <v>12.77000045776367</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>282.1000061035156</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>286.6099853515625</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>292.8800048828125</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>286.6099853515625</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>470396</v>
+        <v>451661</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-2.14</v>
+        <v>-4.93</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Triveni Engineering fixes June 3 record date for SSEL merger - scanx.trade</t>
+          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Triveni Turbines releases Q1 FY27 concall transcript with margin guidance - scanx.trade</t>
+          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Triveni Turbine Consolidated June 2026 Net Sales at Rs 442.70 crore, up 19.23% Y-o-Y - Moneycontrol.com</t>
+          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Triveni Engineering &amp; Industries Share Price Rises 8.27% - Univest</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Triveni Turbine shares tumble 8% after Q1 profit drops 20%, margins shrink - Business Standard</t>
-        </is>
-      </c>
+          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3133,68 +3065,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ACI.NS</t>
+          <t>GRADIENTE.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Archean Chemical Industries Limited</t>
+          <t>Gradiente Infotainment Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>500.75</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>500.75</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>488.1000061035156</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>488.75</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>499.25</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>488.75</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>120558</v>
+        <v>480408</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-2.1</v>
+        <v>-4.93</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>ACI Worldwide (NASDAQ:ACIW) Fits Peter Lynch's Growth-at-a-Reasonable-Price Screen - ChartMill</t>
+          <t>Gradiente Infotainment Considers Capital Raising Initiatives in Board Meeting - Sahi</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Airport sensing without new cabling: Agereh will discuss its tools in Philadelphia - Stock Titan</t>
+          <t>Momentum Stocks: PNB Housing Finance, Divis Labs, Ipca Labs, Paytm hit 52-week high - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Airport sensing without new cabling: Agereh will discuss its tools in Philadelphia - Stock Titan</t>
+          <t>Momentum Stocks: PNB Housing Finance, Divis Labs, Ipca Labs, Paytm hit 52-week high - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>ACI Infocom open offer timeline set; Mandavias file draft letter - scanx.trade</t>
+          <t>Price Band Hitters, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>AC Immune shares rise after encouraging early Phase 1 data for ACI-19764 - Yahoo Finance</t>
+          <t>Major Push for the Orange Economy: Gradiente Infotainment Unveils ₹5,000 Crore Mega Investment Roadmap - The Tribune</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3202,68 +3134,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ADVENTHTL.NS</t>
+          <t>PNC.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Advent Hotels International Limited</t>
+          <t>Pritish Nandy Communications Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>141.9499969482422</v>
+        <v>18.14999961853027</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>144.5</v>
+        <v>18.14999961853027</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>138</v>
+        <v>16.70999908447266</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>139</v>
+        <v>16.98999977111816</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>141.8300018310547</v>
+        <v>17.8700008392334</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>139</v>
+        <v>16.98999977111816</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>105997</v>
+        <v>39491</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-2</v>
+        <v>-4.92</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>ADVENTHTL Stock Price and Chart — NSE:ADVENTHTL - TradingView</t>
+          <t>280,552 Shares in The PNC Financial Services Group, Inc $PNC Acquired by The Manufacturers Life Insurance Company - MarketBeat</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Advent Hotels International (ADVENTHTL.NS) Faces Pressure Near Resistance; Support at ₹139.29 in Focus - Overnight Profile - vinanet.vn</t>
+          <t>PDT Partners LLC Makes New $3.96 Million Investment in The PNC Financial Services Group, Inc $PNC - MarketBeat</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Advent Hotels Listing Tomorrow After Valor Estate Demerger - HDFC Sky</t>
+          <t>AXIA Energia (OTC: AXIAY) exec in 485-share mandatory redemption - Stock Titan</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Advent Hotels International (ADVENTHTL.NS) Faces Pressure Near Resistance; Support at ₹139.29 in Focus - Overnight Profile - vinanet.vn</t>
+          <t>PNC Financial Services Group (PNC) Stock Stays Reasonable After A 129% Run - Yahoo Finance</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Advent Hotels International (ADVENTHTL.NS) Gains 1.79%: Nears Key Resistance at ₹136.96 - NAAIM Exposure - vinanet.vn</t>
+          <t>Are Wall Street Analysts Predicting PNC Financial Services Stock Will Climb or Sink? - Barchart.com</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3271,68 +3203,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WELCORP.NS</t>
+          <t>EMPOWER.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp Limited</t>
+          <t>Empower India Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2300</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2350</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2203.699951171875</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2300</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2345.5</v>
+        <v>2.460000038146973</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2300</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4217184</v>
+        <v>2078514</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-1.94</v>
+        <v>-4.88</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp shares rise post Q1 results: Target prices by five analysts - Business Today</t>
+          <t>Empower India - 11 penny stocks surged up to 198% in 6 months. Do you own any? - The Economic Times</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Investments approves sale of Welspun Corp stake at ₹2,250 - scanx.trade</t>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp publishes Q1 FY27 earnings call transcript online - scanx.trade</t>
+          <t>Empower Q2 Results: Base earnings rise 34% to $332 million - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp Ltd. (WELCORP) Share Price Trades Within 2% of 52-Week High - Univest</t>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp Ltd. (WELCORP) Share Price Hits Fresh 52-Week High - Univest</t>
+          <t>Domestic Abuse Survivor Shares Story to Empower Others - People Newspapers</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:29:17 IST</t>
+          <t>2026-08-26 16:32:49 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3340,61 +3272,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>KUSUMGAR.NS</t>
+          <t>MPDL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Kusumgar Limited</t>
+          <t>MPDL Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>600</v>
+        <v>34.90000152587891</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>600.0499877929688</v>
+        <v>41.18000030517578</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>581.1500244140625</v>
+        <v>34.90000152587891</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>588.2999877929688</v>
+        <v>35.61999893188477</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>599.2000122070312</v>
+        <v>37.43999862670898</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>588.2999877929688</v>
+        <v>35.61999893188477</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>104765</v>
+        <v>4590</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-1.82</v>
+        <v>-4.86</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Kusumgar Share Price news: valuation and peers in focus - Univest</t>
+          <t>MPDL Stock Price and Chart — NSE:MPDL - TradingView</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Kusumgar Share Price news: valuation and peers in focus - Univest</t>
+          <t>Shah Metacorp Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Kusumgar Ltd. Share Price and 52-Week High Stock Analysis - Univest</t>
+          <t>MPDL shareholders approve Santosh Kumar Jha's remuneration - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Kusumgar Ltd. Share Price and 52-Week High Price Action - Univest</t>
+          <t>Shah Metacorp Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Kusumgar Ltd. Share Price Hits New 52-Week High - Univest</t>
+          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RAMBHAJO.NS</t>
+          <t>IMAGICAA.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Limited</t>
+          <t>Imagicaaworld Entertainment Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>215.0099945068359</v>
+        <v>50.09999847412109</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>255.8399963378906</v>
+        <v>60.20999908447266</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>210.6199951171875</v>
+        <v>50.04999923706055</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>255.6900024414062</v>
+        <v>60.20999908447266</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>213.1999969482422</v>
+        <v>50.18000030517578</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>255.6900024414062</v>
+        <v>60.20999908447266</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>12226520</v>
+        <v>34242785</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.93</v>
+        <v>19.99</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>ADVIT JEWELS LIMITED Share Price - Live NSE: RAMBHAJO Stock Price &amp; Chart - Upstox</t>
+          <t>Imagicaaworld completes ₹50 crore MNPPL stake buyout - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Delivers Strong FY26 Growth with 33.68% YoY Rise in Income and 35.56% YoY Increase in Net Profit - indiagazette.com</t>
+          <t>Imagicaaworld shares hit 20% upper circuit as PL Capital gives 'buy' rating -- check target price - TradingView</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels IPO Listing: Rambhajo Shares Glitter On Debut, List At 37% Premium - Outlook Money</t>
+          <t>Imagicaaworld shares hit 20% upper circuit as PL Capital gives 'buy' rating -- check target price - TradingView</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels IPO: Check Allotment Status &amp; Listing Date Here - Sahi</t>
+          <t>Imagicaaworld Entertainment Share Price: 15.96% rise - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Jewellery brand Rambhajo parent files RHP, IPO to hit Dalal Street next week - Moneycontrol.com</t>
+          <t>Imagicaaworld Entertainment hosts Q1FY27 earnings call on Aug 10 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,56 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DHUNINV.NS</t>
+          <t>SHAH.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Dhunseri Investments Limited</t>
+          <t>Shah Metacorp Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>980</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1151.75</v>
+        <v>3.789999961853027</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>980</v>
+        <v>3.140000104904175</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1115.900024414062</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>959.7999877929688</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1115.900024414062</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>63610</v>
+        <v>43874206</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>16.26</v>
+        <v>19.62</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Dhunseri Investments sees Raj Vardhan Kejriwal complete final director term - scanx.trade</t>
+          <t>Shah Metacorp Share Price Rise: Price Action and Metrics - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Dhunseri Investments sees Raj Vardhan Kejriwal complete final director term - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Fine Organic Industries promoter Jayen Shah transfers 1% stake via HUF partition - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Yash Chemex promoter Paxal Shah buys 1600 shares on BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Precigen COO Rutul Shah sells $375,000 in shares - Investing.com India</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>'Not Too High, Not Too Low': Nilesh Shah's Rule For Stock Picking - NDTV Profit</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -679,68 +691,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>VOEPL.NS</t>
+          <t>ANSALBU.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Virtuoso Optoelectronics Limited</t>
+          <t>Ansal Buildwell Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>508</v>
+        <v>73.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>593.4500122070312</v>
+        <v>85.69000244140625</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>497.3999938964844</v>
+        <v>72.01000213623047</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>579.5499877929688</v>
+        <v>85.69000244140625</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>498.75</v>
+        <v>72.01000213623047</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>579.5499877929688</v>
+        <v>85.69000244140625</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2738595</v>
+        <v>263</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>16.2</v>
+        <v>19</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Virtuoso Optoelectronics Share Price rises 12.29% to Rs 560 - Univest</t>
+          <t>Ansal Buildwell (NSE:ANSALBU) Cyclically Adjusted PS Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Virtuoso Optoelectronics Share Price rises 12.29% to Rs 560 - Univest</t>
+          <t>Ansal Buildwell (NSE:ANSALBU) Cyclically Adjusted PS Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Transcript : Virtuoso Optoelectronics Limited, Q1 2027 Earnings Call, Aug 17, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Virtuoso Optoelectronics Limited announced that it has received INR 662.499446 million in funding from Malabar Investments, Fair Value Capital Management - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Virtuoso Optoelectronics Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
+          <t>Ansal Buildwell Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -748,68 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>RGL.NS</t>
+          <t>NATCAPSUQ.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>Natural Capsules Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>133.3000030517578</v>
+        <v>181</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>159</v>
+        <v>216.3300018310547</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>131.7599945068359</v>
+        <v>179.1699981689453</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>152.5800018310547</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>132.8699951171875</v>
+        <v>180.2799987792969</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>152.5800018310547</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>39921956</v>
+        <v>268433</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14.83</v>
+        <v>18.79</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Riversgold (ASX:RGL) Shares Jump 20% as Kalgoorlie Gold Development Moves Forward - Kalkine</t>
+          <t>Natural Capsules Ltd. (NATCAPSUQ) Share Price rises 9.11% as stock gains today - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Riversgold (ASX:RGL) Shares Jump 20% as Kalgoorlie Gold Development Moves Forward - Kalkine</t>
+          <t>Natural Capsules Ltd. (NATCAPSUQ) Share Price rises 9.11% as stock gains today - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Should You Be Adding Renaissance Global (NSE:RGL) To Your Watchlist Today? - simplywall.st</t>
+          <t>Natural Capsules Ltd. Share Price Today: 11.68% Price Rise - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Global Share Price Today: Price Rise Analysis - Univest</t>
+          <t>Natural Capsules adds preferential equity raise to Aug 12 board agenda - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Titan Minerals (ASX:TTM) Shares Jump as New Gold Discovery Returns 33.5m at 6.6 g/t - Kalkine</t>
+          <t>Natural Capsules Ltd. Share Price: Today's Rally Explained - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -817,68 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>INDSWFTLAB.NS</t>
+          <t>MVELECTRO.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Limited</t>
+          <t>MV Electrosystems Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>326</v>
+        <v>565.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>373.7200012207031</v>
+        <v>672.1500244140625</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>325.9800109863281</v>
+        <v>559.9500122070312</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>367.4800109863281</v>
+        <v>646.7999877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>324.3800048828125</v>
+        <v>560.1500244140625</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>367.4800109863281</v>
+        <v>646.7999877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>7364038</v>
+        <v>14676894</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>13.29</v>
+        <v>15.47</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Share Price rises 12.36%: analysis - Univest</t>
+          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Share Price rises 12.36%: analysis - Univest</t>
+          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+          <t>MV ELECTROSYSTEMS LIMITED Share Price - Live NSE: MVELECTRO Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Limited Is Upgrading the Manufacturing Facility Located At Jammu - marketscreener.com</t>
+          <t>Mv Electrosystems Limited Financial Statements – NSE:MVELECTRO - TradingView</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories secures 99.99% shareholder approval for ₹137.20 crore warrant issue - scanx.trade</t>
+          <t>MV Electrosystems IPO Review: India's Railway Propulsion Bet With ₹990 Crore Order Book and Execution Challenges - India Infoline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,68 +890,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ARIES.NS</t>
+          <t>BBTC.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Aries Agro Limited</t>
+          <t>The Bombay Burmah Trading Corporation Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>446.6499938964844</v>
+        <v>1450</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>517.9000244140625</v>
+        <v>1639</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>445.1000061035156</v>
+        <v>1449</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>503.7000122070312</v>
+        <v>1613.599975585938</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>446.75</v>
+        <v>1426.199951171875</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>503.7000122070312</v>
+        <v>1613.599975585938</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1074702</v>
+        <v>14319799</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>12.75</v>
+        <v>13.14</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
+          <t>Why did BBTC shares jump nearly 15% in early trade? - Business Today</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
+          <t>HDFC Bank shares hit 52-week low, down 28% YTD; experts see further downside - Business Today</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Aries Agro Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+          <t>Bombay Burmah Trading Corporation Share Price rises 12.13% - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Salesforce (CRM) Stock Analysis Today - Gotrade</t>
+          <t>Bombay Burmah Trading Corporation shares post best day in over a year; here is why - Upstox</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Daily Nadi Horoscope for Aries (7th August 2026): Moon–Mars Energy May Bring Profit, but Family Peace Nee - The Times of India</t>
+          <t>BSE shares down 6% in a month but up 26% YTD; NSE IPO, CAS weigh on stock? - Business Today</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,68 +959,60 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>GENCON.NS</t>
+          <t>INOXINDIA.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Generic Engineering Construction and Projects Limited</t>
+          <t>INOX India Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.40999984741211</v>
+        <v>1935.900024414062</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>47</v>
+        <v>2224</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>41.40999984741211</v>
+        <v>1916.900024414062</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46.77000045776367</v>
+        <v>2177.89990234375</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>41.5</v>
+        <v>1926.699951171875</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46.77000045776367</v>
+        <v>2177.89990234375</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1098363</v>
+        <v>4484155</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>12.7</v>
+        <v>13.04</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 8.63% Today - Univest</t>
+          <t>Inox India Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 8.63% Today - Univest</t>
+          <t>Inox India Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 12.15% Today - Univest</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Geeks of Wrath – Gencon 2026 Wrap Up! - Non-Productive.com</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>America’s Biggest Gaming Convention Just Wrapped. These Are the Five Board Games We’re Most Excited to Test. - The New York Times</t>
-        </is>
-      </c>
+          <t>INOX India Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1024,68 +1020,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SPLIL.NS</t>
+          <t>SHAHALLOYS.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SPL Industries Limited</t>
+          <t>Shah Alloys Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>30.39999961853027</v>
+        <v>78.91999816894531</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>34.84999847412109</v>
+        <v>86.75</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>29.60000038146973</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>34.13999938964844</v>
+        <v>85.95999908447266</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30.5</v>
+        <v>76.05999755859375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>34.13999938964844</v>
+        <v>85.95999908447266</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>47626</v>
+        <v>213084</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>11.93</v>
+        <v>13.02</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>SPL Industries Limited's (NSE:SPLIL) Share Price Not Quite Adding Up - simplywall.st</t>
+          <t>Shah Alloys Ltd. Share Price Up 8.77%: Price, Valuation - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>SPLIL Q2 2026 Earnings: Revenue Plunges 50% YoY, EPS at ₹2.43 - Earnings Season Review - vinanet.vn</t>
+          <t>Shah Alloys Ltd. Share Price Up 8.77%: Price, Valuation - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>SPL Industries Managing Director Mukesh Kumar Aggarwal Completes Term, Continues as Board Director - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>SPL Industries Ltd: Marginal Gains Amid Consolidation – SPLIL.NS Holds Near Key Support - ETF NAV Deviation - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>We Think Shareholders May Want To Consider A Review Of SPL Industries Limited's (NSE:SPLIL) CEO Compensation Package - simplywall.st</t>
-        </is>
-      </c>
+          <t>Shah Alloys Q1 Results: Net loss narrows to ₹2.07 crore as revenue falls 99% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1093,60 +1081,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MADHAVIPL.NS</t>
+          <t>AASTHA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Madhav Infra Projects Limited</t>
+          <t>Aastha Spintex Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7.300000190734863</v>
+        <v>88.37000274658203</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8.300000190734863</v>
+        <v>88.37000274658203</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7.300000190734863</v>
+        <v>88.36000061035156</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8.029999732971191</v>
+        <v>88.36000061035156</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7.230000019073486</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8.029999732971191</v>
+        <v>88.36000061035156</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1016360</v>
+        <v>2787073</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>11.07</v>
+        <v>9.98</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Madhav Infra Projects (NSE:MADHAVIPL) Cyclically Adjusted P - GuruFocus</t>
+          <t>Aastha Spintex shares extend rise to 3rd day, hit upper circuit; check details - TradingView</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Madhav Infra Projects (NSE:MADHAVIPL) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
+          <t>Aastha Spintex shares extend rise to 3rd day, hit upper circuit; check details - TradingView</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Madhav Infra Projects (NSE:MADHAVIPL) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Aastha Spintex: Announced 1:1 Bonus Shares; What’s Next? - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Share Price News: Rs 88.42 and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Textile stock under ₹100 hits 10% upper circuit after declaration of final dividend move | Details here - Livemint</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1154,68 +1150,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ANDREWYU.NS</t>
+          <t>WHIRLPOOL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Company Limited</t>
+          <t>Whirlpool of India Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>26.98999977111816</v>
+        <v>777.8499755859375</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>30.48999977111816</v>
+        <v>858.7000122070312</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>26.54000091552734</v>
+        <v>772</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>29.44000053405762</v>
+        <v>841.1500244140625</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.76000022888184</v>
+        <v>771.7000122070312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>29.44000053405762</v>
+        <v>841.1500244140625</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>916578</v>
+        <v>5451720</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10.01</v>
+        <v>9</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Company Ltd. Share Price Today: 10.87% gain - Univest</t>
+          <t>Whirlpool stock trades close to 12-month low as guidance stays cautious - Ad-hoc-news.de</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Company Ltd. Share Price Today: 10.87% gain - Univest</t>
+          <t>Whirlpool stock trades close to 12-month low as guidance stays cautious - Ad-hoc-news.de</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Company Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+          <t>Don't Race Out To Buy Whirlpool of India Limited (NSE:WHIRLPOOL) Just Because It's Going Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Company Receives BSE Fine of Rs.5,42,800 for Board Composition Non-Compliance - scanx.trade</t>
+          <t>Whirlpool Abandoned Its Global Ambitions. Now It’s in a World of Hurt. - WSJ</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Co. Ltd. Announces Appointment of Singhai Sanjay Jain as Non-official Independent Director, Effective August 17, 2026 - marketscreener.com</t>
+          <t>Wells Fargo initiates Whirlpool stock coverage at Equal Weight - Investing.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1223,68 +1219,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST.NS</t>
+          <t>POLYSPIN.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Limited</t>
+          <t>Polyspin Exports Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>201.8999938964844</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>222.1100006103516</v>
+        <v>31.93000030517578</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>198.0599975585938</v>
+        <v>28</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>222.1100006103516</v>
+        <v>31.93000030517578</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>201.9199981689453</v>
+        <v>29.5</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>222.1100006103516</v>
+        <v>31.93000030517578</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>20875349</v>
+        <v>114</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10</v>
+        <v>8.24</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Limited Share Price - Upstox</t>
+          <t>Polyspin Exports reports ₹390.04 Lakhs net profit in FY26, sets Aug 21 AGM date - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Limited Stock (MILKYMIST) - Quote NSE India S.E. - marketscreener.com</t>
+          <t>Polyspin Exports consolidated net profit rises 7.14% in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
+          <t>Shubham Polyspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1292,68 +1288,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>CLEANMAX.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Limited</t>
+          <t>Clean Max Enviro Energy Solutions Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>54</v>
+        <v>1182.300048828125</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>56.47999954223633</v>
+        <v>1283.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>53.5</v>
+        <v>1182.300048828125</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.47999954223633</v>
+        <v>1274.599975585938</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>51.34999847412109</v>
+        <v>1182.300048828125</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>56.47999954223633</v>
+        <v>1274.599975585938</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5796445</v>
+        <v>285446</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>9.99</v>
+        <v>7.81</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd Forms Golden Cross Amid Strong Technical Momentum and Micro-Cap Caveats - MarketsMojo</t>
+          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>Renewable stock to buy: Recent debutant in bear grip after multibagger rise; Ventura sees 55% rally - Business Today</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd Locks at Upper Circuit With 3.44% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+          <t>After muted listing, this stock turns multibagger in just 3 months; should you still buy? - Business Today</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+          <t>Clean Max Enviro Energy Solutions Allots 35,800 Equity Shares Under ESOS - SolarQuarter</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1361,64 +1357,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>NECLIFE.NS</t>
+          <t>NEXTMEDIA.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences Limited</t>
+          <t>Next Mediaworks Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11.39999961853027</v>
+        <v>3.75</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>12.46000003814697</v>
+        <v>3.940000057220459</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>11.32999992370605</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>12.46000003814697</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11.32999992370605</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12.46000003814697</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1472512</v>
+        <v>21424</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences Limited Changes Its Corporate Office in Chandigarh - marketscreener.com</t>
+          <t>Next Mediaworks schedules 45th AGM for Sep 22 via video conference - scanx.trade</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
+          <t>Next Mediaworks Schedules Virtual AGM to Approve FY26 Results and Director Reappointment - TipRanks</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
-        </is>
-      </c>
+          <t>Next Mediaworks Schedules Virtual AGM to Approve FY26 Results and Director Reappointment - TipRanks</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,56 +1418,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SAKUMA.NS</t>
+          <t>AZADIND.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sakuma Exports Limited</t>
+          <t>Azad India Mobility Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.710000038146973</v>
+        <v>92</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.789999961853027</v>
+        <v>98.90000152587891</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1.710000038146973</v>
+        <v>89.94999694824219</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.789999961853027</v>
+        <v>96.80000305175781</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.629999995231628</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.789999961853027</v>
+        <v>96.80000305175781</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2329582</v>
+        <v>11894</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>9.82</v>
+        <v>7.52</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Sakuma Exports consolidated net profit rises 70.91% in the June 2026 quarter - Business Standard</t>
+          <t>Azad India Mobility Limited Provides Earnings Guidance for the Year 2027 - marketscreener.com</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Sakuma Exports consolidated net profit rises 70.91% in the June 2026 quarter - Business Standard</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Azad India Mobility (NSE:AZADIND) Cyclically Adjusted PS Ra - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Azad India Mobility (NSE:AZADIND) Cyclically Adjusted PS Ra - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Azad India Mobility (NSE:AZADIND) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Azad India Mobility (NSE:AZADIND) Cyclically Adjusted Price-to-FCF : (As of Aug. 25, 2026) - GuruFocus</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1483,68 +1487,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>LADDERUP.NS</t>
+          <t>BIRLAPREC.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Limited</t>
+          <t>Birla Precision Technologies Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50</v>
+        <v>43.5099983215332</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>53.95000076293945</v>
+        <v>47.79999923706055</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>50</v>
+        <v>43.5099983215332</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53.47000122070312</v>
+        <v>47.36999893188477</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>49</v>
+        <v>44.11999893188477</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>53.47000122070312</v>
+        <v>47.36999893188477</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>139</v>
+        <v>436976</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Blue Cloud Softech Solutions Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - vinanet.vn</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Blue Cloud Softech Solutions Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance sets Sep 17 record date for 33rd AGM - scanx.trade</t>
+          <t>Birla Precision Technologies Gains 2.37%: Testing Key Resistance Levels (BIRLAPREC.NS) - Double Top - vinanet.vn</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Fin Consolidated June 2026 Net Sales at Rs 9.32 crore, up 61.22% Y-o-Y - Moneycontrol.com</t>
+          <t>BIRLAPREC.NS Mar 2026 Earnings: Marginal EPS of ₹0.39 on Modest Revenue of ₹63.91 crore; Stock Slides 0.71% - ROA Comparison - vinanet.vn</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Q1 FY27 Results: Revenue Rs 9 Cr, PAT Rs 3 Cr and Key Highlights - Univest</t>
+          <t>Birla Precision Technologies Trades Flat with Marginal Decline; Support at ₹35.62 Holds Key - Risk Reversal - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1552,68 +1556,56 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>RRECL.NS</t>
+          <t>MOHITIND.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions Limited</t>
+          <t>Mohit Industries Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>151.9900054931641</v>
+        <v>23.05999946594238</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>151.9900054931641</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>151</v>
+        <v>23.05999946594238</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>151.6600036621094</v>
+        <v>25.06999969482422</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>139</v>
+        <v>23.47999954223633</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>151.6600036621094</v>
+        <v>25.06999969482422</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3</v>
+        <v>36059</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.109999999999999</v>
+        <v>6.77</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions (RRECL) Share Price Falls 9.14% to Rs 126.3, Among Top Losers Today - Univest</t>
+          <t>Mohit Industries updates contact details of key managerial personnel - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions (NSE:RRECL) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>RDB Real Estate Constructions (NSE:RRECL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>RDB Real Estate Constructions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>RDB Real Estate Constructions Share Price Today Up 9.8% - Univest</t>
-        </is>
-      </c>
+          <t>Mohit Industries updates contact details of key managerial personnel - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1621,60 +1613,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PACIFICI.NS</t>
+          <t>MENNPIS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Limited</t>
+          <t>Menon Pistons Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>133.1000061035156</v>
+        <v>69.91000366210938</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>152</v>
+        <v>75.59999847412109</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>133.1000061035156</v>
+        <v>69.91000366210938</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>146.6699981689453</v>
+        <v>74.58999633789062</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>134.4499969482422</v>
+        <v>69.88999938964844</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>146.6699981689453</v>
+        <v>74.58999633789062</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1330</v>
+        <v>125327</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9.09</v>
+        <v>6.72</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries (NSE:PACIFICI) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>MENNPIS Stock Price and Chart — NSE:MENNPIS - TradingView</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries (NSE:PACIFICI) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>MENNPIS Mar 2026 Earnings: Revenue at ₹60.2 Crore, EPS of ₹0.77; Stock Declines 2.1% - Revenue Surprise History - vinanet.vn</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Menon Pistons (MENNPIS.NS) Gains 3% as Price Approaches Key Resistance - Sector Leader Stocks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Menon Pistons Limited (MENNPIS.NS): Navigating a Mild Pullback Near Support - Iceberg Order - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>MENNPIS Mar 2026 Earnings: Revenue at ₹60.2 Crore, EPS of ₹0.77; Stock Declines 2.1% - Revenue Surprise History - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1682,64 +1682,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM.NS</t>
+          <t>MOSCHIP.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>TECIL Chemicals and Hydro Power Limited</t>
+          <t>Moschip Technologies Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9.289999961853027</v>
+        <v>206</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>10.18000030517578</v>
+        <v>224</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>8</v>
+        <v>206</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.489999771118164</v>
+        <v>219.3600006103516</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8.699999809265137</v>
+        <v>205.5399932861328</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9.489999771118164</v>
+        <v>219.3600006103516</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>70146</v>
+        <v>17472466</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9.08</v>
+        <v>6.72</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>TECIL Chemicals (TECILCHEM) Declines to ₹11.6, Approaches Key Support Zone - McClellan Summation - vinanet.vn</t>
+          <t>Moschip Tech Consolidated June 2026 Net Sales at Rs 116.21 crore, down 14.29% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - vinanet.vn</t>
+          <t>Moschip Tech Consolidated June 2026 Net Sales at Rs 116.21 crore, down 14.29% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Tecil Chemicals board to meet on May 27 for Q4FY26 results - scanx.trade</t>
-        </is>
-      </c>
+          <t>Moschip Tech Standalone June 2026 Net Sales at Rs 101.15 crore, down 14.13% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1747,64 +1743,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>VINCOFE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>Vintage Coffee And Beverages Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>283</v>
+        <v>164.1100006103516</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>309.2000122070312</v>
+        <v>179</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>277.0499877929688</v>
+        <v>164.1100006103516</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>305.7999877929688</v>
+        <v>174.6499938964844</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>280.3500061035156</v>
+        <v>164.0899963378906</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>305.7999877929688</v>
+        <v>174.6499938964844</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3966721</v>
+        <v>9709137</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9.08</v>
+        <v>6.44</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
+          <t>VINCOFE Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+          <t>NCLT sanctions Vintage Coffee merger with subsidiaries - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+          <t>Vintage Coffee and Beverages' (NSE:VINCOFE) Earnings Might Be Weaker Than You Think - simplywall.st</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>With EPS Growth And More, Vintage Coffee and Beverages (NSE:VINCOFE) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Vintage Coffee FY26 PAT Rises 80% to ₹72.19 Cr - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1812,63 +1812,51 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SBFC.NS</t>
+          <t>HEADSUP.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SBFC Finance Limited</t>
+          <t>Heads UP Ventures Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>92.59999847412109</v>
+        <v>6.5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>102.2099990844727</v>
+        <v>6.980000019073486</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>92.59999847412109</v>
+        <v>6.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>101.1399993896484</v>
+        <v>6.869999885559082</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>92.76999664306641</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>101.1399993896484</v>
+        <v>6.869999885559082</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>17100733</v>
+        <v>8022</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9.02</v>
+        <v>6.35</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Volumes jump at SBFC Finance Ltd counter - Business Standard</t>
+          <t>#HeadsUp: Water service shut off scheduled for Aug. 8 in Ethete for repairs - County 10</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Volumes jump at SBFC Finance Ltd counter - Business Standard</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Top Gainers &amp; Losers on 26 Aug: SBFC Finance, Capri Global, Hindustan Copper, SAIL, OLA, Vedanta among top gainers - Livemint</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>SBFC Finance Ltd is Rated Sell - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>SBFC Finance vs MAS Financial Services: Which MSME NBFC Stock - Univest</t>
-        </is>
-      </c>
+          <t>#HeadsUp: Water service shut off scheduled for Aug. 8 in Ethete for repairs - County 10</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1886,8 +1874,8 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1993,7 +1981,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2001,68 +1989,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ELITECON.NS</t>
+          <t>WEL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Limited</t>
+          <t>Wonder Electricals Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13.88000011444092</v>
+        <v>157.5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.27000045776367</v>
+        <v>179.1999969482422</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>12.39000034332275</v>
+        <v>124.7399978637695</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>12.39000034332275</v>
+        <v>124.7399978637695</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>13.76000022888184</v>
+        <v>155.9199981689453</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12.39000034332275</v>
+        <v>124.7399978637695</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>8072629</v>
+        <v>129564647</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-9.960000000000001</v>
+        <v>-20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Ltd Hits Intraday Low Amid Price Pressure - MarketsMojo</t>
+          <t>Wonder Electricals Share Price: stock news and analysis - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Ltd Hits Intraday Low Amid Price Pressure - MarketsMojo</t>
+          <t>Wonder Electricals Share Price: stock news and analysis - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International: Kumar Anubhav Upadhyay ceases as Additional Director - scanx.trade</t>
+          <t>Wonder Electricals Share Price Today: Market Cap and P/E - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock under ₹50 Elitecon International hits 10% upper circuit for second day in a row - Livemint</t>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
+          <t>Wonder Electricals Share Price Today With Valuation View - Univest</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2070,64 +2058,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NEXTMEDIA.NS</t>
+          <t>DAVANGERE.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Next Mediaworks Limited</t>
+          <t>Davangere Sugar Company Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.910000085830688</v>
+        <v>2.630000114440918</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.950000047683716</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3.160000085830688</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3.579999923706055</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3.910000085830688</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.579999923706055</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>80986</v>
+        <v>39331776</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.44</v>
+        <v>-20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Next Mediaworks schedules 45th AGM for Sep 22 via video conference - scanx.trade</t>
+          <t>Davangere Sugar Company Share Price Update and Analysis - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Next Mediaworks schedules 45th AGM for Sep 22 via video conference - scanx.trade</t>
+          <t>Davangere Sugar Company Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Next Mediaworks Q1FY26 loss narrows to ₹88 lakh as going concern risk persists - scanx.trade</t>
+          <t>Davangere Sugar Company Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>MannKind Corporation (MNKD) Declines 4.38% to $3.93 as Shares Approach Key Support - Put Spread Alert - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Davangere Sugar to convert Rs 40.12 crore promoter loan into equity warrants, doubles authorised capital - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Davangere Sugar Company allots 26.59 cr equity shares on conversion of FCCBs - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2135,68 +2127,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>FILATEX.NS</t>
+          <t>ARCHIDPLY.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Limited</t>
+          <t>Archidply Industries Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>82.11000061035156</v>
+        <v>114.9499969482422</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>83.27999877929688</v>
+        <v>114.9899978637695</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70.73999786376953</v>
+        <v>102.2600021362305</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>75.19000244140625</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>82.11000061035156</v>
+        <v>112.9400024414062</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>75.19000244140625</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>10801532</v>
+        <v>113516</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-8.43</v>
+        <v>-8.77</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Filatex India shares can rally to Rs 118? Why Equirus Prive initiated coverage on the stock - The Economic Times</t>
+          <t>Archidply Ind Consolidated June 2026 Net Sales at Rs 189.01 crore, up 27.83% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+          <t>5 Plywood Stocks India 2026: Strong Future Roadmaps - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions fined ₹24,780 each by NSE, BSE for non-compliance - scanx.trade</t>
+          <t>Archidply Industries Ltd. Share Price Today: 10.14% Gain - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+          <t>Archidply Decor Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Filatex India vs Indo Rama Synthetics India: Which Fibre Stock to Track - Univest</t>
+          <t>Archidply Ind Standalone June 2026 Net Sales at Rs 140.12 crore, up 17.42% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2204,68 +2196,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SAMBANDAM.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sambandam Spinning Mills Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>135.1999969482422</v>
+        <v>54.7599983215332</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>135.1999969482422</v>
+        <v>55.90000152587891</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>124</v>
+        <v>50.15000152587891</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>125.4700012207031</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>134.1399993896484</v>
+        <v>54.97000122070312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>125.4700012207031</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>6243</v>
+        <v>757395</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-6.46</v>
+        <v>-7.77</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Sambandam Spinning Mills FY26 Results: Net loss narrows to ₹5.74 crore - scanx.trade</t>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Sambandam Spinning Mills FY26 Results: Net loss narrows to ₹5.74 crore - scanx.trade</t>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>SAMBANDAM Stock Price and Chart — NSE:SAMBANDAM - TradingView</t>
+          <t>UGARSUGAR Share Price Today - The Ugar Sugar Works Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Sambandam Spinning Mills Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>The Ugar Sugar Works Ltd. Share Price Today: Key Analysis - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>dj mediaprint and logistics ltd leads losers in b group - Capital Market</t>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2273,48 +2265,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>WHBRADY.NS</t>
+          <t>MOLBIO.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>WH Brady &amp; Company Limited</t>
+          <t>Molbio Diagnostics Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>500</v>
+        <v>1234</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>500.0499877929688</v>
+        <v>1243.699951171875</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>497.5499877929688</v>
+        <v>1130.099975585938</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>497.7999877929688</v>
+        <v>1144.150024414062</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>529.9500122070312</v>
+        <v>1238.849975585938</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>497.7999877929688</v>
+        <v>1144.150024414062</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>176</v>
+        <v>1151150</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.07</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+        <v>-7.64</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Solid debut! Molbio Diagnostics shares list at 21% premium over IPO price - Business Standard</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>MOLBIO Share Price Today - MOLBIO DIAGNOSTICS LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics' shares jump over 21 pc in market debut trade - ET HealthWorld</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics IPO listing: Shares debut at 21% premium at ₹980 - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics IPO: Price, Dates, P/E Ratio &amp; How to Apply - INDmoney</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2322,68 +2334,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TANLA.NS</t>
+          <t>ALOKINDS.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tanla Platforms Limited</t>
+          <t>Alok Industries Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>558</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>563.9000244140625</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>522.0999755859375</v>
+        <v>9.550000190734863</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>526.0499877929688</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>556.0499877929688</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>526.0499877929688</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1298318</v>
+        <v>59972039</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5.4</v>
+        <v>-7.54</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Route Mobile vs Tanla Platforms: Which CPaaS Stock to Track - Univest</t>
+          <t>Alok Industries (NSE:ALOKINDS) shareholder returns have been , earning 28% in 3 years - simplywall.st</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Tanla Platforms Share Pros and Cons 2026 | TANLA CPaaS Stock Analysis - Univest</t>
+          <t>Alok Industries Stock In Focus After Reporting 6% YoY Revenue Growth In Q1 - Trade Brains</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Tanla Platforms Share Pros and Cons 2026 | TANLA CPaaS Stock Analysis - Univest</t>
+          <t>Alok Industries (ALOKINDS.NS) Maintains Upward Bias as Price Holds Above Key Support - Fibonacci Extension - vinanet.vn</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Tanla Platforms Consolidated June 2026 Net Sales at Rs 1,226.39 crore, up 17.85% Y-o-Y - Moneycontrol.com</t>
+          <t>Alok Industries Limited Schedules Board Meeting for April 16, 2026 to Review Q4FY26 and FY26 Audited Financial Results - scanx.trade</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Tanla Platforms Standalone June 2026 Net Sales at Rs 214.34 crore, up 28.41% Y-o-Y - Moneycontrol.com</t>
+          <t>Alok Industries Limited: Price Gains Momentum Toward Resistance at ₹13.26 - Monthly Profile - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2391,68 +2403,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>VIYASH.NS</t>
+          <t>SHANTIGOLD.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Viyash Scientific Limited</t>
+          <t>Shanti Gold International Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>268.8500061035156</v>
+        <v>258.8999938964844</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>271.1499938964844</v>
+        <v>259.989990234375</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>259.1000061035156</v>
+        <v>242.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>263.3999938964844</v>
+        <v>246.0500030517578</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>278.3500061035156</v>
+        <v>266.0700073242188</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>263.3999938964844</v>
+        <v>246.0500030517578</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>115373365</v>
+        <v>8498549</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.37</v>
+        <v>-7.52</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Six block deals worth over ₹6,000 crore change hands today — Check details here - CNBC TV18</t>
+          <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Viyash Scientific Ltd leads losers in 'A' group - Business Standard</t>
+          <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares - TradingView</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Viyash Scientific Share Price Gains 7.19%, Most in Three Months - Univest</t>
+          <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares Revenue Breakdown – NSE:SHANTI_RE - TradingView</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Viyash Scientif Consolidated June 2026 Net Sales at Rs 946.36 crore, up 114.39% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Viyash Scientif Standalone June 2026 Net Sales at Rs 353.69 crore, up 761.19% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares Earnings and Revenue – NSE:SHANTI_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2460,68 +2468,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DCMSRIND.NS</t>
+          <t>BOHRAIND.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Industries Limited</t>
+          <t>Bohra Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>50.29999923706055</v>
+        <v>13.98999977111816</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>51.38000106811523</v>
+        <v>14.73999977111816</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>47.27999877929688</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>47.84000015258789</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>50.5</v>
+        <v>13.85999965667725</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>47.84000015258789</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>268616</v>
+        <v>90454</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.27</v>
+        <v>-7.29</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Industries Limited (NSE:DCMSRIND) Stock Goes Ex-Dividend In Just Three Days - simplywall.st</t>
+          <t>Bohra Industries (BOHRAIND.NS) Edges Higher, Holds Near Key Support Level - Buyback Factor - vinanet.vn</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Industries (DCMSRIND.NS) Slips 2.89% to ₹40.0: Support at ₹38.0 Under Focus - Wave Truncation - vinanet.vn</t>
+          <t>Bohra Industries accepts resignation of director effective July 11 - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Industries (DCMSRIND.NS) Slips 2.89% to ₹40.0: Support at ₹38.0 Under Focus - Wave Truncation - vinanet.vn</t>
+          <t>Bohra Industries accepts resignation of director effective July 11 - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Industries Limited's (NSE:DCMSRIND) 68% Dip In Price Shows Sentiment Is Matching Earnings - simplywall.st</t>
+          <t>BOHRA INDUSTRIES LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram Industries (DCMSRIND.NS) Mild Decline in Range-Bound Trading – Key Levels in Focus - Option Breadth - vinanet.vn</t>
+          <t>Bohra Industries (BOHRAIND.NS) Slides 1.82% as Price Approaches Key Support at ₹15.39 - Upthrust Pattern - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2529,68 +2537,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL.NS</t>
+          <t>DHAMPURSUG.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Shyam Telecom Limited</t>
+          <t>Dhampur Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.82999992370605</v>
+        <v>186</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>13.85999965667725</v>
+        <v>186.1999969482422</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13.02000045776367</v>
+        <v>170.1000061035156</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>13.14999961853027</v>
+        <v>170.9199981689453</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13.85999965667725</v>
+        <v>183.6699981689453</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13.14999961853027</v>
+        <v>170.9199981689453</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>7708</v>
+        <v>1242517</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.12</v>
+        <v>-6.94</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Shyam Telecom (SHYAMTEL.NS) Slides 2% Amid Weak Volume – Key Support at ₹19.16 in Focus - Dynamic Hedging - vinanet.vn</t>
+          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL Q4 FY26 Earnings: Net Loss Persists as Business Activities Remain Minimal - Margin Compression Risk - vinanet.vn</t>
+          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL Mar 2026 Earnings: Continued Revenue Absence and Nominal Loss - Dividend Increase Stocks - vinanet.vn</t>
+          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL Mar 2026 Earnings: Revenue Stays at Zero, EPS Remains Negative Amidst Operational Lull - Debt Analysis Report - vinanet.vn</t>
+          <t>Dhampur Sugar Mills sets book closure dates for 91st AGM - scanx.trade</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Shyam Telecom Limited Q4 FY26 Earnings: Zero Revenue and Negative EPS Highlight Persistent Operational Challenges - Financial Summary - vinanet.vn</t>
+          <t>Dhampur Sugar Mills Ltd. Share Price: 52-Week High Focus - Univest</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2598,68 +2606,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>KIRIINDUS.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Limited</t>
+          <t>Kiri Industries Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>282.9500122070312</v>
+        <v>514</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>283.010009765625</v>
+        <v>518.8499755859375</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>260.3200073242188</v>
+        <v>473.1499938964844</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>263.2699890136719</v>
+        <v>481.1000061035156</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>277.1900024414062</v>
+        <v>516.2000122070312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>263.2699890136719</v>
+        <v>481.1000061035156</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>47054</v>
+        <v>1021899</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.02</v>
+        <v>-6.8</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Share Price Today With Valuation View - Univest</t>
+          <t>Kiri Industries Ltd. Share Price Today Up 8.18%: Stock News - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+          <t>Kiri Industries Share Price rises 9.56%: valuation view - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack to allot equity shares on warrant conversion - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Kanpur Plastipack shareholders approve all 7 AGM resolutions - scanx.trade</t>
-        </is>
-      </c>
+          <t>Kiri Industries Share Price rises 9.56%: valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2667,64 +2667,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SIMPLXREA.NS</t>
+          <t>SILLYMONKS.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Simplex Realty Limited</t>
+          <t>Silly Monks Entertainment Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>132</v>
+        <v>16.63999938964844</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>132</v>
+        <v>16.63999938964844</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>125.4000015258789</v>
+        <v>15.35000038146973</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>125.4000015258789</v>
+        <v>15.5</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>132</v>
+        <v>16.57999992370605</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>125.4000015258789</v>
+        <v>15.5</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3</v>
+        <v>45633</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5</v>
+        <v>-6.51</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of Simplex Realty Limited – NSE:SIMPLXREA - TradingView</t>
+          <t>Synthetic (GJH): Settles Near the Prior Close at $9.45 on the Day; Levels: the Price Remains Bounded by the Supplied Support and Resistance in Latest Trading - RVOL Spike - vinanet.vn</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Simplex Realty (NSE:SIMPLXREA) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Simplex Realty Limited Announces Board and Committee Changes, Effective August 5, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Simplex Realty (NSE:SIMPLXREA) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
-        </is>
-      </c>
+          <t>Synthetic (GJH): Settles Near the Prior Close at $9.45 on the Day; Levels: the Price Remains Bounded by the Supplied Support and Resistance in Latest Trading - RVOL Spike - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2732,64 +2724,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NATIONSTD.NS</t>
+          <t>KJMCFIN.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) Limited</t>
+          <t>KJMC Financial Services Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>110.0199966430664</v>
+        <v>72.94999694824219</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>114.9000015258789</v>
+        <v>72.94999694824219</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>108.879997253418</v>
+        <v>66.41000366210938</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>108.879997253418</v>
+        <v>69.11000061035156</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>114.6100006103516</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>108.879997253418</v>
+        <v>69.11000061035156</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>171484</v>
+        <v>7457</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5</v>
+        <v>-6.33</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>National Standard (India) sets Aug 28 date for 63rd AGM - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2797,68 +2793,56 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TAKE.NS</t>
+          <t>CLSEL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TAKE Limited</t>
+          <t>Chaman Lal Setia Exports Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>313.2000122070312</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>313.3500061035156</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>294.0499877929688</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>295.2000122070312</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>313.2000122070312</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>295.2000122070312</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>82918</v>
+        <v>258000</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5</v>
+        <v>-5.75</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Silver Mines Shares Retreat as Precious-Metal Traders Take Profits - Kalkine</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Silver Mines Shares Retreat as Precious-Metal Traders Take Profits - Kalkine</t>
-        </is>
-      </c>
+          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2866,64 +2850,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SIEL.NS</t>
+          <t>LCL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises Limited</t>
+          <t>Lohia Corp Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>34.45000076293945</v>
+        <v>594.9000244140625</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>34.45000076293945</v>
+        <v>594.9000244140625</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>32.84999847412109</v>
+        <v>562.3499755859375</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>32.84999847412109</v>
+        <v>566</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>34.56999969482422</v>
+        <v>598.2000122070312</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>32.84999847412109</v>
+        <v>566</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3833</v>
+        <v>377423</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.98</v>
+        <v>-5.38</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>SIEL Stock Price and Chart — NSE:SIEL - TradingView</t>
+          <t>LOHIA CORP LIMITED Share Price Hits One-Year High Today - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5 Under the Radar Trading Stocks in India - Univest</t>
+          <t>Lohia Corp Files Q1 FY27 Earnings Call Transcript With Exchanges - TipRanks</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5 Under the Radar Trading Stocks in India - Univest</t>
+          <t>Lohia Corp Ltd Share Price Today,, LCL Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Lohia Corp IPO - Check Allotment Status, Listing Date, Listing Price - Groww</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Lohia Corp Shares List At Over 8% Premium On NSE - fintechbiznews.com</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2931,68 +2919,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AQYLON.NS</t>
+          <t>OPTIFIN.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus Limited</t>
+          <t>Optimus Finance Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24.34000015258789</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>24.79000091552734</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23.94000053405762</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>23.95000076293945</v>
+        <v>13.09000015258789</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25.20000076293945</v>
+        <v>13.81999969482422</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>23.95000076293945</v>
+        <v>13.09000015258789</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1652410</v>
+        <v>50770</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.96</v>
+        <v>-5.28</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Leading Leasing Finance Increases Stake in Aqylon Nexus to 14.17% - scanx.trade</t>
+          <t>OPTIFIN Stock Price and Chart — NSE:OPTIFIN - TradingView</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Leading Leasing Finance Increases Stake in Aqylon Nexus to 14.17% - scanx.trade</t>
+          <t>Optimus Finance appoints Kheradia as director, new auditor - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Leading Leasing sells 1.47 cr Aqylon Nexus shares - scanx.trade</t>
+          <t>Optimus Finance Limited: Shareholders Board Members Managers and Company Profile | INE031G01022 - marketscreener.com</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Leading Leasing raises Aqylon Nexus stake to 10.30% via open market buy - scanx.trade</t>
+          <t>Optimus Finance shares permitted to trade on NSE from August 17 - scanx.trade</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus appoints Rupareliya as director, Sanghani as CFO - scanx.trade</t>
+          <t>Optimus Finance (NSE:OPTIFIN) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3000,64 +2988,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA.NS</t>
+          <t>RAMCOCEM.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild Limited</t>
+          <t>The Ramco Cements Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12.01000022888184</v>
+        <v>943</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>12.77000045776367</v>
+        <v>943</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>11.94999980926514</v>
+        <v>890.3499755859375</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>11.94999980926514</v>
+        <v>892.5499877929688</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12.56999969482422</v>
+        <v>940.6500244140625</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>11.94999980926514</v>
+        <v>892.5499877929688</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>451661</v>
+        <v>706080</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.93</v>
+        <v>-5.11</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
+          <t>The Ramco Cements Limited (NSE:RAMCOCEM) Pays A ₹2.50 Dividend In Just Three Days - simplywall.st</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
+          <t>The Ramco Cements Share Price rise: valuation and peers - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
+          <t>The Ramco Cements Ltd. Share Price Declines: August 5, 2026 - Univest</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>The Ramco Cements Share Price rise: valuation and peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Ramco Cements Details Virtual 68th Annual General Meeting Proceedings - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3065,68 +3057,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GRADIENTE.NS</t>
+          <t>MODIS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Gradiente Infotainment Limited</t>
+          <t>Modis Navnirman Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.849999904632568</v>
+        <v>402.1000061035156</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2.849999904632568</v>
+        <v>404</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2.700000047683716</v>
+        <v>377.3999938964844</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.700000047683716</v>
+        <v>379.7000122070312</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2.839999914169312</v>
+        <v>399.8999938964844</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.700000047683716</v>
+        <v>379.7000122070312</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>480408</v>
+        <v>216453</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.93</v>
+        <v>-5.05</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Gradiente Infotainment Considers Capital Raising Initiatives in Board Meeting - Sahi</t>
+          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Momentum Stocks: PNB Housing Finance, Divis Labs, Ipca Labs, Paytm hit 52-week high - Moneycontrol.com</t>
+          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Momentum Stocks: PNB Housing Finance, Divis Labs, Ipca Labs, Paytm hit 52-week high - Moneycontrol.com</t>
+          <t>Modis Navnirman Standalone June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Price Band Hitters, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
+          <t>Modis Navnirman Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Major Push for the Orange Economy: Gradiente Infotainment Unveils ₹5,000 Crore Mega Investment Roadmap - The Tribune</t>
+          <t>Modis Navnirman hosts Q1 FY27 earnings call on Aug 10 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3134,68 +3126,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PNC.NS</t>
+          <t>NATIONSTD.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Pritish Nandy Communications Limited</t>
+          <t>National Standard (India) Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>18.14999961853027</v>
+        <v>103.4400024414062</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>18.14999961853027</v>
+        <v>107.4499969482422</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>16.70999908447266</v>
+        <v>103.4400024414062</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>16.98999977111816</v>
+        <v>103.4400024414062</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>17.8700008392334</v>
+        <v>108.879997253418</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16.98999977111816</v>
+        <v>103.4400024414062</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>39491</v>
+        <v>39226</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.92</v>
+        <v>-5</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>280,552 Shares in The PNC Financial Services Group, Inc $PNC Acquired by The Manufacturers Life Insurance Company - MarketBeat</t>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>PDT Partners LLC Makes New $3.96 Million Investment in The PNC Financial Services Group, Inc $PNC - MarketBeat</t>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>AXIA Energia (OTC: AXIAY) exec in 485-share mandatory redemption - Stock Titan</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group (PNC) Stock Stays Reasonable After A 129% Run - Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Are Wall Street Analysts Predicting PNC Financial Services Stock Will Climb or Sink? - Barchart.com</t>
-        </is>
-      </c>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3203,68 +3187,60 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER.NS</t>
+          <t>NEAGI.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Empower India Limited</t>
+          <t>Neelamalai Agro Industries Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.339999914169312</v>
+        <v>3400</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.339999914169312</v>
+        <v>3400</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2.339999914169312</v>
+        <v>3306</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.339999914169312</v>
+        <v>3306</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.460000038146973</v>
+        <v>3480</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.339999914169312</v>
+        <v>3306</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2078514</v>
+        <v>99</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.88</v>
+        <v>-5</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Empower India - 11 penny stocks surged up to 198% in 6 months. Do you own any? - The Economic Times</t>
+          <t>Neelamalai Agro Industries (NSE:NEAGI) Cyclically Adjusted PB Ratio : (As of Aug. 26, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+          <t>Neelamalai Agro Industries (NSE:NEAGI) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Empower Q2 Results: Base earnings rise 34% to $332 million - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Domestic Abuse Survivor Shares Story to Empower Others - People Newspapers</t>
-        </is>
-      </c>
+          <t>Neelamalai Agro Industries (NSE:NEAGI) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:32:49 IST</t>
+          <t>2026-08-27 18:30:33 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3272,61 +3248,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MPDL.NS</t>
+          <t>MYSORPETRO.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MPDL Limited</t>
+          <t>Mysore Petro Chemicals Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>34.90000152587891</v>
+        <v>131.6499938964844</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>41.18000030517578</v>
+        <v>131.6499938964844</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>34.90000152587891</v>
+        <v>131.6499938964844</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>35.61999893188477</v>
+        <v>131.6499938964844</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>37.43999862670898</v>
+        <v>138.5700073242188</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>35.61999893188477</v>
+        <v>131.6499938964844</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4590</v>
+        <v>2605</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.86</v>
+        <v>-4.99</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>MPDL Stock Price and Chart — NSE:MPDL - TradingView</t>
+          <t>MYSORPETRO Stock Price and Chart — NSE:MYSORPETRO - TradingView</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Shah Metacorp Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Mysore Petro Chemicals: Denies Undisclosed Material Events Amidst Share Price Movement - InvestyWise</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>MPDL shareholders approve Santosh Kumar Jha's remuneration - scanx.trade</t>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Cyclically Adjusted PB Ratio : (As of Aug. 20, 2026) - GuruFocus</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Shah Metacorp Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,56 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA.NS</t>
+          <t>NIRAJISPAT.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Imagicaaworld Entertainment Limited</t>
+          <t>Niraj Ispat Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>50.09999847412109</v>
+        <v>286</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>60.20999908447266</v>
+        <v>295.8999938964844</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>50.04999923706055</v>
+        <v>278.989990234375</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>60.20999908447266</v>
+        <v>295.8999938964844</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>50.18000030517578</v>
+        <v>246.5899963378906</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>60.20999908447266</v>
+        <v>295.8999938964844</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>34242785</v>
+        <v>3053</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.99</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Imagicaaworld completes ₹50 crore MNPPL stake buyout - scanx.trade</t>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Imagicaaworld shares hit 20% upper circuit as PL Capital gives 'buy' rating -- check target price - TradingView</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Imagicaaworld shares hit 20% upper circuit as PL Capital gives 'buy' rating -- check target price - TradingView</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Imagicaaworld Entertainment Share Price: 15.96% rise - Univest</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Imagicaaworld Entertainment hosts Q1FY27 earnings call on Aug 10 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +610,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SHAH.NS</t>
+          <t>XTRANET.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Shah Metacorp Limited</t>
+          <t>Xtranet Technologies Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.200000047683716</v>
+        <v>165</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.789999961853027</v>
+        <v>197.1100006103516</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3.140000104904175</v>
+        <v>163</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3.779999971389771</v>
+        <v>197.1100006103516</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3.160000085830688</v>
+        <v>164.2599945068359</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.779999971389771</v>
+        <v>197.1100006103516</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43874206</v>
+        <v>5428284</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.62</v>
+        <v>20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Shah Metacorp Share Price Rise: Price Action and Metrics - Univest</t>
+          <t>1,970,100 Equity Shares of Xtranet Technologies Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Fine Organic Industries promoter Jayen Shah transfers 1% stake via HUF partition - scanx.trade</t>
+          <t>1,970,100 Equity Shares of Xtranet Technologies Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Yash Chemex promoter Paxal Shah buys 1600 shares on BSE - scanx.trade</t>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Precigen COO Rutul Shah sells $375,000 in shares - Investing.com India</t>
+          <t>Xtranet Technologies releases Q1FY27 earnings call audio recording - scanx.trade</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>'Not Too High, Not Too Low': Nilesh Shah's Rule For Stock Picking - NDTV Profit</t>
+          <t>Xtranet Technologies Shares List at 7% Premium on NSE, Trim Early Gains Amid Profit Booking - India Infoline</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,60 +679,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ANSALBU.NS</t>
+          <t>PRECWIRE.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ansal Buildwell Limited</t>
+          <t>Precision Wires India Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>73.5</v>
+        <v>422.7999877929688</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>85.69000244140625</v>
+        <v>507.3500061035156</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>72.01000213623047</v>
+        <v>421.7000122070312</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>85.69000244140625</v>
+        <v>507.3500061035156</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>72.01000213623047</v>
+        <v>422.7999877929688</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>85.69000244140625</v>
+        <v>507.3500061035156</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>263</v>
+        <v>8561372</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Ansal Buildwell (NSE:ANSALBU) Cyclically Adjusted PS Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+          <t>Should You Be Adding Precision Wires India (NSE:PRECWIRE) To Your Watchlist Today? - simplywall.st</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Ansal Buildwell (NSE:ANSALBU) Cyclically Adjusted PS Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ansal Buildwell Ltd - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Precision Wires India Ltd. (PRECWIRE) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Precision Wires India Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Precision Wires India Limited Announces Chief Financial Officer Changes, Effective August 10, 2026 - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +748,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>NATCAPSUQ.NS</t>
+          <t>SHAHALLOYS.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Natural Capsules Limited</t>
+          <t>Shah Alloys Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>181</v>
+        <v>89.01000213623047</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>216.3300018310547</v>
+        <v>103.1500015258789</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>179.1699981689453</v>
+        <v>87</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>214.1600036621094</v>
+        <v>103.1500015258789</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>180.2799987792969</v>
+        <v>85.95999908447266</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>214.1600036621094</v>
+        <v>103.1500015258789</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>268433</v>
+        <v>1390956</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>18.79</v>
+        <v>20</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Natural Capsules Ltd. (NATCAPSUQ) Share Price rises 9.11% as stock gains today - Univest</t>
+          <t>Shah Alloys Share Price Today: Valuation and Sector View - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Natural Capsules Ltd. (NATCAPSUQ) Share Price rises 9.11% as stock gains today - Univest</t>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Natural Capsules Ltd. Share Price Today: 11.68% Price Rise - Univest</t>
+          <t>Shah Alloys Q1 Results: Net loss narrows to ₹2.07 crore as revenue falls 99% - scanx.trade</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Natural Capsules adds preferential equity raise to Aug 12 board agenda - scanx.trade</t>
+          <t>Shah Alloys Ltd. Share Price Up 8.77%: Price, Valuation - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Natural Capsules Ltd. Share Price: Today's Rally Explained - Univest</t>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,68 +817,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO.NS</t>
+          <t>GVPTECH.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Limited</t>
+          <t>GVP Infotech Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>565.5</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>672.1500244140625</v>
+        <v>9.029999732971191</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>559.9500122070312</v>
+        <v>7.869999885559082</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>646.7999877929688</v>
+        <v>9.029999732971191</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>560.1500244140625</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>646.7999877929688</v>
+        <v>9.029999732971191</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>14676894</v>
+        <v>1285327</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>15.47</v>
+        <v>19.92</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
+          <t>GVP Infotech Limited (GVPTECH.NS) Mar 2026 Earnings: Negative EPS Amid Modest Revenue - EPS Surprise History - vinanet.vn</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
+          <t>GVP Infotech Limited (GVPTECH) Gains 1.47%; Near Key Resistance at ₹7.23 - IPO Entry Watch - vinanet.vn</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>MV ELECTROSYSTEMS LIMITED Share Price - Live NSE: MVELECTRO Stock Price &amp; Chart - Upstox</t>
+          <t>GVP Infotech Ltd (GVPTECH.NS) Modestly Declines as Stock Tests Support Near ₹7.0 Zone - Channel Breakout - vinanet.vn</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Mv Electrosystems Limited Financial Statements – NSE:MVELECTRO - TradingView</t>
+          <t>GVP INFOTECH LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems IPO Review: India's Railway Propulsion Bet With ₹990 Crore Order Book and Execution Challenges - India Infoline</t>
+          <t>GVP Infotech Limited (GVPTECH) Gains 1.47%; Near Key Resistance at ₹7.23 - IPO Entry Watch - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -890,68 +886,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BBTC.NS</t>
+          <t>EXXARO.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The Bombay Burmah Trading Corporation Limited</t>
+          <t>Exxaro Tiles Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1450</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1639</v>
+        <v>7.420000076293945</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1449</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1613.599975585938</v>
+        <v>7.409999847412109</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1426.199951171875</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1613.599975585938</v>
+        <v>7.409999847412109</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>14319799</v>
+        <v>12070592</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>13.14</v>
+        <v>19.71</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Why did BBTC shares jump nearly 15% in early trade? - Business Today</t>
+          <t>Momentum Stocks: Next Mediaworks, Exxaro, Tejas Networks gains up to 19% on sheer momentum - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>HDFC Bank shares hit 52-week low, down 28% YTD; experts see further downside - Business Today</t>
+          <t>Next Mediaworks, Exxaro Shares See Sharp Price Swings - Whalesbook</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Bombay Burmah Trading Corporation Share Price rises 12.13% - Univest</t>
+          <t>Exxaro Tiles Standalone June 2026 Net Sales at Rs 73.79 crore, up 16.85% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Bombay Burmah Trading Corporation shares post best day in over a year; here is why - Upstox</t>
+          <t>Eskom supplier Exxaro crashes as robust rand and rising costs tear into profits - news24.com</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>BSE shares down 6% in a month but up 26% YTD; NSE IPO, CAS weigh on stock? - Business Today</t>
+          <t>Exxaro Tiles Consolidated June 2026 Net Sales at Rs 85.22 crore, up 31.26% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -959,60 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA.NS</t>
+          <t>MASTEK.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>INOX India Limited</t>
+          <t>Mastek Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1935.900024414062</v>
+        <v>1615</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2224</v>
+        <v>1933.900024414062</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1916.900024414062</v>
+        <v>1615</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2177.89990234375</v>
+        <v>1901.400024414062</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1926.699951171875</v>
+        <v>1611.599975585938</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2177.89990234375</v>
+        <v>1901.400024414062</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4484155</v>
+        <v>5448423</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>13.04</v>
+        <v>17.98</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Inox India Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+          <t>Volume Gainers Today; SecMark, Exxaro Tiles And Mastek Lead Trading Surge asof 4:00 PM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Inox India Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+          <t>Volume Gainers Today; SecMark, Exxaro Tiles And Mastek Lead Trading Surge asof 4:00 PM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>INOX India Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Mid-cap IT stock jumps 19%; brokerage sees turnaround potential, here's what it said - Business Today</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Glenmark Pharma, Mastek, Triveni Engineering Dividends: Last Day To Buy Shares To Qualify - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Should You Buy Mastek Limited (NSE:MASTEK) For Its Upcoming Dividend? - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1020,60 +1024,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SHAHALLOYS.NS</t>
+          <t>IKIO.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Limited</t>
+          <t>IKIO Technologies Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>78.91999816894531</v>
+        <v>186.1399993896484</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>86.75</v>
+        <v>217.6999969482422</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>78</v>
+        <v>186.1399993896484</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>85.95999908447266</v>
+        <v>213.7200012207031</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>76.05999755859375</v>
+        <v>186.1399993896484</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>85.95999908447266</v>
+        <v>213.7200012207031</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>213084</v>
+        <v>6393269</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>13.02</v>
+        <v>14.82</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Ltd. Share Price Up 8.77%: Price, Valuation - Univest</t>
+          <t>News by CNBC TV18 on TradingView, 2026-08-28 — cnbctv:5fd8494be094b:0 - TradingView</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Ltd. Share Price Up 8.77%: Price, Valuation - Univest</t>
+          <t>News by CNBC TV18 on TradingView, 2026-08-28 — cnbctv:5fd8494be094b:0 - TradingView</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Q1 Results: Net loss narrows to ₹2.07 crore as revenue falls 99% - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>IKIO Share Price rise highlights valuation versus peers - Univest</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>IKIO Technologies holds investor meet on Aug 27, no UPSI shared - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>IKIO Tech Standalone June 2026 Net Sales at Rs 44.84 crore, up 15.9% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1081,68 +1093,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AASTHA.NS</t>
+          <t>OAL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Limited</t>
+          <t>Oriental Aromatics Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>88.37000274658203</v>
+        <v>425</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>88.37000274658203</v>
+        <v>492.7000122070312</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>88.36000061035156</v>
+        <v>424</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>88.36000061035156</v>
+        <v>487.7999877929688</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>80.33999633789062</v>
+        <v>428.9500122070312</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>88.36000061035156</v>
+        <v>487.7999877929688</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2787073</v>
+        <v>765462</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.98</v>
+        <v>13.72</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex shares extend rise to 3rd day, hit upper circuit; check details - TradingView</t>
+          <t>Oriental Aromatics Q1 Results: Earnings Call Recording Available Online - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex shares extend rise to 3rd day, hit upper circuit; check details - TradingView</t>
+          <t>Coal India incorporates Singapore-based wholly owned subsidiary; shares fall - Dailyhunt</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex: Announced 1:1 Bonus Shares; What’s Next? - Investing.com India</t>
+          <t>Oriental Aromatics appoints Nitin Budhavalekar as VP Sales Fragrance - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Share Price News: Rs 88.42 and Valuation - Univest</t>
+          <t>Oriental Aromatics crosses ₹1,000 crore revenue in FY26; declares ₹0.50 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Textile stock under ₹100 hits 10% upper circuit after declaration of final dividend move | Details here - Livemint</t>
+          <t>Oriental Aromatics profit surges 42% as margins recover sequentially - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1150,68 +1162,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>WHIRLPOOL.NS</t>
+          <t>ASIANTNE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool of India Limited</t>
+          <t>Asian Tea &amp; Exports Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>777.8499755859375</v>
+        <v>9.899999618530273</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>858.7000122070312</v>
+        <v>10.98999977111816</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>772</v>
+        <v>9.720000267028809</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>841.1500244140625</v>
+        <v>10.89000034332275</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>771.7000122070312</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>841.1500244140625</v>
+        <v>10.89000034332275</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>5451720</v>
+        <v>58850</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9</v>
+        <v>12.85</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool stock trades close to 12-month low as guidance stays cautious - Ad-hoc-news.de</t>
+          <t>Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool stock trades close to 12-month low as guidance stays cautious - Ad-hoc-news.de</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Don't Race Out To Buy Whirlpool of India Limited (NSE:WHIRLPOOL) Just Because It's Going Ex-Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Whirlpool Abandoned Its Global Ambitions. Now It’s in a World of Hurt. - WSJ</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Wells Fargo initiates Whirlpool stock coverage at Equal Weight - Investing.com</t>
-        </is>
-      </c>
+          <t>Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 18:30:33 IST</t>
+          <t>2026-08-28 20:01:22 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1219,68 +1219,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>POLYSPIN.NS</t>
+          <t>ODYCORP.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
